--- a/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\540 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21FB476-1338-4F82-8588-AE62DC12AC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E60E07-EA81-4EEB-83E2-34F7A982AE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10454,7 +10454,7 @@
         <v>582</v>
       </c>
       <c r="B70" s="1">
-        <v>3780</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="71" spans="1:2">

--- a/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\540 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\550 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E60E07-EA81-4EEB-83E2-34F7A982AE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40CDD40-99ED-4CA9-9F39-AF25C9DC73B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="828">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -2501,6 +2501,18 @@
   </si>
   <si>
     <t>BATERÍA 35 AH</t>
+  </si>
+  <si>
+    <t>CARBURADOR (ORIGINAL)</t>
+  </si>
+  <si>
+    <t>ESPEJO RETROVISOR INTERIOR PANORÁMICO</t>
+  </si>
+  <si>
+    <t>PARABRISAS ATOS (05-11)</t>
+  </si>
+  <si>
+    <t>PROTECTORES DE MANILLAS JUEGO</t>
   </si>
 </sst>
 </file>
@@ -3002,7 +3014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B363"/>
+  <dimension ref="A1:B365"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.85546875" customWidth="1"/>
@@ -3022,7 +3034,7 @@
         <v>166</v>
       </c>
       <c r="B2" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3030,7 +3042,7 @@
         <v>421</v>
       </c>
       <c r="B3" s="1">
-        <v>6480</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3038,7 +3050,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3046,7 +3058,7 @@
         <v>459</v>
       </c>
       <c r="B5" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3054,7 +3066,7 @@
         <v>460</v>
       </c>
       <c r="B6" s="1">
-        <v>3780</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3062,7 +3074,7 @@
         <v>593</v>
       </c>
       <c r="B7" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3070,7 +3082,7 @@
         <v>168</v>
       </c>
       <c r="B8" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3078,7 +3090,7 @@
         <v>461</v>
       </c>
       <c r="B9" s="1">
-        <v>48600</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3086,7 +3098,7 @@
         <v>169</v>
       </c>
       <c r="B10" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3094,7 +3106,7 @@
         <v>170</v>
       </c>
       <c r="B11" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3102,7 +3114,7 @@
         <v>171</v>
       </c>
       <c r="B12" s="1">
-        <v>86400</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3110,7 +3122,7 @@
         <v>174</v>
       </c>
       <c r="B13" s="1">
-        <v>18900</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3118,7 +3130,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="1">
-        <v>81000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3126,7 +3138,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="1">
-        <v>59400</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3134,7 +3146,7 @@
         <v>666</v>
       </c>
       <c r="B16" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3142,7 +3154,7 @@
         <v>175</v>
       </c>
       <c r="B17" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3150,7 +3162,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3158,7 +3170,7 @@
         <v>589</v>
       </c>
       <c r="B19" s="1">
-        <v>3240</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3166,7 +3178,7 @@
         <v>462</v>
       </c>
       <c r="B20" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3174,7 +3186,7 @@
         <v>177</v>
       </c>
       <c r="B21" s="1">
-        <v>1620</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3182,7 +3194,7 @@
         <v>178</v>
       </c>
       <c r="B22" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3190,7 +3202,7 @@
         <v>179</v>
       </c>
       <c r="B23" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3198,7 +3210,7 @@
         <v>550</v>
       </c>
       <c r="B24" s="1">
-        <v>27000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3206,7 +3218,7 @@
         <v>180</v>
       </c>
       <c r="B25" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3214,7 +3226,7 @@
         <v>181</v>
       </c>
       <c r="B26" s="1">
-        <v>48600</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3222,7 +3234,7 @@
         <v>182</v>
       </c>
       <c r="B27" s="1">
-        <v>18900</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3230,7 +3242,7 @@
         <v>183</v>
       </c>
       <c r="B28" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3238,7 +3250,7 @@
         <v>184</v>
       </c>
       <c r="B29" s="1">
-        <v>81000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3246,7 +3258,7 @@
         <v>185</v>
       </c>
       <c r="B30" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3254,7 +3266,7 @@
         <v>186</v>
       </c>
       <c r="B31" s="1">
-        <v>86400</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3262,7 +3274,7 @@
         <v>187</v>
       </c>
       <c r="B32" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3270,7 +3282,7 @@
         <v>188</v>
       </c>
       <c r="B33" s="1">
-        <v>24300</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3278,7 +3290,7 @@
         <v>606</v>
       </c>
       <c r="B34" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3286,7 +3298,7 @@
         <v>569</v>
       </c>
       <c r="B35" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3294,7 +3306,7 @@
         <v>594</v>
       </c>
       <c r="B36" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3302,7 +3314,7 @@
         <v>823</v>
       </c>
       <c r="B37" s="1">
-        <v>45900</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3310,7 +3322,7 @@
         <v>430</v>
       </c>
       <c r="B38" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3318,7 +3330,7 @@
         <v>163</v>
       </c>
       <c r="B39" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3326,7 +3338,7 @@
         <v>647</v>
       </c>
       <c r="B40" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3334,7 +3346,7 @@
         <v>581</v>
       </c>
       <c r="B41" s="1">
-        <v>59400</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3342,7 +3354,7 @@
         <v>648</v>
       </c>
       <c r="B42" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3350,7 +3362,7 @@
         <v>189</v>
       </c>
       <c r="B43" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3358,7 +3370,7 @@
         <v>419</v>
       </c>
       <c r="B44" s="1">
-        <v>27000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3366,7 +3378,7 @@
         <v>408</v>
       </c>
       <c r="B45" s="1">
-        <v>6480</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3374,7 +3386,7 @@
         <v>729</v>
       </c>
       <c r="B46" s="1">
-        <v>24300</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3382,7 +3394,7 @@
         <v>730</v>
       </c>
       <c r="B47" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3390,7 +3402,7 @@
         <v>190</v>
       </c>
       <c r="B48" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3398,7 +3410,7 @@
         <v>191</v>
       </c>
       <c r="B49" s="1">
-        <v>24300</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3406,7 +3418,7 @@
         <v>192</v>
       </c>
       <c r="B50" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3414,7 +3426,7 @@
         <v>193</v>
       </c>
       <c r="B51" s="1">
-        <v>24300</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3422,7 +3434,7 @@
         <v>692</v>
       </c>
       <c r="B52" s="1">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3430,7 +3442,7 @@
         <v>194</v>
       </c>
       <c r="B53" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3438,7 +3450,7 @@
         <v>406</v>
       </c>
       <c r="B54" s="1">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3446,7 +3458,7 @@
         <v>402</v>
       </c>
       <c r="B55" s="1">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3454,7 +3466,7 @@
         <v>429</v>
       </c>
       <c r="B56" s="1">
-        <v>1620</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3462,7 +3474,7 @@
         <v>195</v>
       </c>
       <c r="B57" s="1">
-        <v>48600</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3470,7 +3482,7 @@
         <v>196</v>
       </c>
       <c r="B58" s="1">
-        <v>6480</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3478,7 +3490,7 @@
         <v>197</v>
       </c>
       <c r="B59" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3486,7 +3498,7 @@
         <v>595</v>
       </c>
       <c r="B60" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3494,7 +3506,7 @@
         <v>596</v>
       </c>
       <c r="B61" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3502,7 +3514,7 @@
         <v>198</v>
       </c>
       <c r="B62" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3510,7 +3522,7 @@
         <v>199</v>
       </c>
       <c r="B63" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3518,7 +3530,7 @@
         <v>200</v>
       </c>
       <c r="B64" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3526,7 +3538,7 @@
         <v>201</v>
       </c>
       <c r="B65" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3534,7 +3546,7 @@
         <v>202</v>
       </c>
       <c r="B66" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3542,7 +3554,7 @@
         <v>203</v>
       </c>
       <c r="B67" s="1">
-        <v>6480</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3550,7 +3562,7 @@
         <v>204</v>
       </c>
       <c r="B68" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3558,7 +3570,7 @@
         <v>205</v>
       </c>
       <c r="B69" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3566,7 +3578,7 @@
         <v>206</v>
       </c>
       <c r="B70" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3574,7 +3586,7 @@
         <v>208</v>
       </c>
       <c r="B71" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3582,7 +3594,7 @@
         <v>212</v>
       </c>
       <c r="B72" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3590,7 +3602,7 @@
         <v>209</v>
       </c>
       <c r="B73" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3598,7 +3610,7 @@
         <v>210</v>
       </c>
       <c r="B74" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3606,7 +3618,7 @@
         <v>211</v>
       </c>
       <c r="B75" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3614,7 +3626,7 @@
         <v>476</v>
       </c>
       <c r="B76" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3622,7 +3634,7 @@
         <v>207</v>
       </c>
       <c r="B77" s="1">
-        <v>3780</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3630,7 +3642,7 @@
         <v>213</v>
       </c>
       <c r="B78" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3638,7 +3650,7 @@
         <v>214</v>
       </c>
       <c r="B79" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3646,7 +3658,7 @@
         <v>215</v>
       </c>
       <c r="B80" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3654,7 +3666,7 @@
         <v>216</v>
       </c>
       <c r="B81" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3662,7 +3674,7 @@
         <v>217</v>
       </c>
       <c r="B82" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3670,7 +3682,7 @@
         <v>218</v>
       </c>
       <c r="B83" s="1">
-        <v>24300</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3678,7 +3690,7 @@
         <v>219</v>
       </c>
       <c r="B84" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3686,7 +3698,7 @@
         <v>220</v>
       </c>
       <c r="B85" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3694,7 +3706,7 @@
         <v>607</v>
       </c>
       <c r="B86" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3702,7 +3714,7 @@
         <v>221</v>
       </c>
       <c r="B87" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3710,7 +3722,7 @@
         <v>608</v>
       </c>
       <c r="B88" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3718,7 +3730,7 @@
         <v>417</v>
       </c>
       <c r="B89" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3726,7 +3738,7 @@
         <v>418</v>
       </c>
       <c r="B90" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3734,7 +3746,7 @@
         <v>222</v>
       </c>
       <c r="B91" s="1">
-        <v>24300</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3742,7 +3754,7 @@
         <v>223</v>
       </c>
       <c r="B92" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3750,7 +3762,7 @@
         <v>224</v>
       </c>
       <c r="B93" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3758,7 +3770,7 @@
         <v>225</v>
       </c>
       <c r="B94" s="1">
-        <v>189000</v>
+        <v>192500</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3766,2151 +3778,2167 @@
         <v>226</v>
       </c>
       <c r="B95" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>227</v>
+        <v>824</v>
       </c>
       <c r="B96" s="1">
-        <v>162000</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B97" s="1">
-        <v>27000</v>
+        <v>154000</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>551</v>
+        <v>228</v>
       </c>
       <c r="B98" s="1">
-        <v>8100</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="4" t="s">
-        <v>667</v>
+        <v>551</v>
       </c>
       <c r="B99" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>409</v>
+        <v>667</v>
       </c>
       <c r="B100" s="1">
-        <v>37800</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>229</v>
+        <v>409</v>
       </c>
       <c r="B101" s="1">
-        <v>24300</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B102" s="1">
-        <v>43200</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B103" s="1">
-        <v>10800</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="4" t="s">
-        <v>424</v>
+        <v>231</v>
       </c>
       <c r="B104" s="1">
-        <v>13500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>232</v>
+        <v>424</v>
       </c>
       <c r="B105" s="1">
-        <v>10800</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>570</v>
+        <v>232</v>
       </c>
       <c r="B106" s="1">
-        <v>24300</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>483</v>
+        <v>570</v>
       </c>
       <c r="B107" s="1">
-        <v>135000</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>587</v>
+        <v>483</v>
       </c>
       <c r="B108" s="1">
-        <v>13500</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>233</v>
+        <v>587</v>
       </c>
       <c r="B109" s="1">
-        <v>18900</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B110" s="1">
-        <v>37800</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>731</v>
+        <v>234</v>
       </c>
       <c r="B111" s="1">
-        <v>24300</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>717</v>
+        <v>731</v>
       </c>
       <c r="B112" s="1">
-        <v>27000</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>571</v>
+        <v>717</v>
       </c>
       <c r="B113" s="1">
-        <v>16200</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="B114" s="1">
-        <v>108</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>235</v>
+        <v>590</v>
       </c>
       <c r="B115" s="1">
-        <v>54000</v>
+        <v>110</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>732</v>
+        <v>235</v>
       </c>
       <c r="B116" s="1">
-        <v>10800</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>236</v>
+        <v>732</v>
       </c>
       <c r="B117" s="1">
-        <v>16200</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>733</v>
+        <v>236</v>
       </c>
       <c r="B118" s="1">
-        <v>1080</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>237</v>
+        <v>733</v>
       </c>
       <c r="B119" s="1">
-        <v>32400</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>410</v>
+        <v>237</v>
       </c>
       <c r="B120" s="1">
-        <v>3780</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>238</v>
+        <v>410</v>
       </c>
       <c r="B121" s="1">
-        <v>10800</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B122" s="1">
-        <v>8100</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B123" s="1">
-        <v>10800</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B124" s="1">
-        <v>32400</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B125" s="1">
-        <v>81000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B126" s="1">
-        <v>21600</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>668</v>
+        <v>243</v>
       </c>
       <c r="B127" s="1">
-        <v>54000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B128" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>431</v>
+        <v>669</v>
       </c>
       <c r="B129" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>244</v>
+        <v>431</v>
       </c>
       <c r="B130" s="1">
-        <v>13500</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>597</v>
+        <v>244</v>
       </c>
       <c r="B131" s="1">
-        <v>232200</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>245</v>
+        <v>597</v>
       </c>
       <c r="B132" s="1">
-        <v>97200</v>
+        <v>236500</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>456</v>
+        <v>245</v>
       </c>
       <c r="B133" s="1">
-        <v>3780</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B134" s="1">
-        <v>10800</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B135" s="1">
-        <v>16200</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>246</v>
+        <v>458</v>
       </c>
       <c r="B136" s="1">
-        <v>32400</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B137" s="1">
-        <v>64800</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B138" s="1">
-        <v>10800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B139" s="1">
-        <v>43200</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>420</v>
+        <v>250</v>
       </c>
       <c r="B140" s="1">
-        <v>135000</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>420</v>
       </c>
       <c r="B141" s="1">
-        <v>64800</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>602</v>
+        <v>14</v>
       </c>
       <c r="B142" s="1">
-        <v>108</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>249</v>
+        <v>602</v>
       </c>
       <c r="B143" s="1">
-        <v>8100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>552</v>
+        <v>249</v>
       </c>
       <c r="B144" s="1">
-        <v>4320</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>251</v>
+        <v>552</v>
       </c>
       <c r="B145" s="1">
-        <v>27000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B146" s="1">
-        <v>32400</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>253</v>
+        <v>825</v>
       </c>
       <c r="B147" s="1">
-        <v>54000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>598</v>
+        <v>252</v>
       </c>
       <c r="B148" s="1">
-        <v>6480</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B149" s="1">
-        <v>21600</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>255</v>
+        <v>598</v>
       </c>
       <c r="B150" s="1">
-        <v>37800</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B151" s="1">
-        <v>4320</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B152" s="1">
-        <v>5400</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B153" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B154" s="1">
-        <v>16200</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B155" s="1">
-        <v>48600</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B156" s="1">
-        <v>27000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>404</v>
+        <v>262</v>
       </c>
       <c r="B157" s="1">
-        <v>2700</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B158" s="1">
-        <v>16200</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>463</v>
+        <v>404</v>
       </c>
       <c r="B159" s="1">
-        <v>10800</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B160" s="1">
-        <v>64800</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>264</v>
+        <v>463</v>
       </c>
       <c r="B161" s="1">
-        <v>2700</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>689</v>
+        <v>260</v>
       </c>
       <c r="B162" s="1">
-        <v>18900</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>641</v>
+        <v>264</v>
       </c>
       <c r="B163" s="1">
-        <v>1620</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>642</v>
+        <v>689</v>
       </c>
       <c r="B164" s="1">
-        <v>1620</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>603</v>
+        <v>641</v>
       </c>
       <c r="B165" s="1">
-        <v>108</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>604</v>
+        <v>642</v>
       </c>
       <c r="B166" s="1">
-        <v>108</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>484</v>
+        <v>603</v>
       </c>
       <c r="B167" s="1">
-        <v>3240</v>
+        <v>110</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>265</v>
+        <v>604</v>
       </c>
       <c r="B168" s="1">
-        <v>2700</v>
+        <v>110</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>609</v>
+        <v>484</v>
       </c>
       <c r="B169" s="1">
-        <v>54000</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>734</v>
+        <v>265</v>
       </c>
       <c r="B170" s="1">
-        <v>2160</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>735</v>
+        <v>609</v>
       </c>
       <c r="B171" s="1">
-        <v>4320</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>266</v>
+        <v>734</v>
       </c>
       <c r="B172" s="1">
-        <v>32400</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>267</v>
+        <v>735</v>
       </c>
       <c r="B173" s="1">
-        <v>16200</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B174" s="1">
-        <v>54000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B175" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B176" s="1">
-        <v>3780</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B177" s="1">
-        <v>8100</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B178" s="1">
-        <v>16200</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B179" s="1">
-        <v>4320</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>422</v>
+        <v>272</v>
       </c>
       <c r="B180" s="1">
-        <v>4320</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>423</v>
+        <v>273</v>
       </c>
       <c r="B181" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>610</v>
+        <v>422</v>
       </c>
       <c r="B182" s="1">
-        <v>3780</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>611</v>
+        <v>423</v>
       </c>
       <c r="B183" s="1">
-        <v>2700</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B184" s="1">
-        <v>8100</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B185" s="1">
-        <v>3780</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B186" s="1">
-        <v>3780</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B187" s="1">
-        <v>2700</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>274</v>
+        <v>614</v>
       </c>
       <c r="B188" s="1">
-        <v>10800</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>276</v>
+        <v>615</v>
       </c>
       <c r="B189" s="1">
-        <v>1080</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B190" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>616</v>
+        <v>276</v>
       </c>
       <c r="B191" s="1">
-        <v>27000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B192" s="1">
-        <v>21600</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>464</v>
+        <v>616</v>
       </c>
       <c r="B193" s="1">
-        <v>81000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B194" s="1">
-        <v>48600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>736</v>
+        <v>464</v>
       </c>
       <c r="B195" s="1">
-        <v>1620</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>391</v>
+        <v>278</v>
       </c>
       <c r="B196" s="1">
-        <v>4320</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>396</v>
+        <v>736</v>
       </c>
       <c r="B197" s="1">
-        <v>3780</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>466</v>
+        <v>391</v>
       </c>
       <c r="B198" s="1">
-        <v>172800</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>279</v>
+        <v>396</v>
       </c>
       <c r="B199" s="1">
-        <v>280800</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>649</v>
+        <v>466</v>
       </c>
       <c r="B200" s="1">
-        <v>286200</v>
+        <v>176000</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B201" s="1">
-        <v>3240</v>
+        <v>286000</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>696</v>
+        <v>649</v>
       </c>
       <c r="B202" s="1">
-        <v>6480</v>
+        <v>291500</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>737</v>
+        <v>280</v>
       </c>
       <c r="B203" s="1">
-        <v>4320</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>411</v>
+        <v>696</v>
       </c>
       <c r="B204" s="1">
-        <v>10800</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>281</v>
+        <v>737</v>
       </c>
       <c r="B205" s="1">
-        <v>8100</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B206" s="1">
-        <v>2700</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B207" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>283</v>
+        <v>412</v>
       </c>
       <c r="B208" s="1">
-        <v>37800</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B209" s="1">
-        <v>4320</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B210" s="1">
-        <v>5400</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B211" s="1">
-        <v>10800</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B212" s="1">
-        <v>4320</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B213" s="1">
-        <v>4320</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B214" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>553</v>
+        <v>288</v>
       </c>
       <c r="B215" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B216" s="1">
-        <v>27000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>738</v>
+        <v>553</v>
       </c>
       <c r="B217" s="1">
-        <v>2700</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>739</v>
+        <v>290</v>
       </c>
       <c r="B218" s="1">
-        <v>2700</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>291</v>
+        <v>738</v>
       </c>
       <c r="B219" s="1">
-        <v>16200</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>292</v>
+        <v>739</v>
       </c>
       <c r="B220" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B221" s="1">
-        <v>151200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B222" s="1">
-        <v>81000</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>572</v>
+        <v>293</v>
       </c>
       <c r="B223" s="1">
-        <v>35100</v>
+        <v>154000</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>670</v>
+        <v>294</v>
       </c>
       <c r="B224" s="1">
-        <v>43200</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>295</v>
+        <v>572</v>
       </c>
       <c r="B225" s="1">
-        <v>16200</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B226" s="1">
-        <v>81000</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B227" s="1">
-        <v>81000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>718</v>
+        <v>671</v>
       </c>
       <c r="B228" s="1">
-        <v>29700</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>719</v>
+        <v>296</v>
       </c>
       <c r="B229" s="1">
-        <v>32400</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B230" s="1">
-        <v>35100</v>
+        <v>30250</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B231" s="1">
-        <v>35100</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>617</v>
+        <v>720</v>
       </c>
       <c r="B232" s="1">
-        <v>3780</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>297</v>
+        <v>721</v>
       </c>
       <c r="B233" s="1">
-        <v>5400</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>573</v>
+        <v>617</v>
       </c>
       <c r="B234" s="1">
-        <v>32400</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B235" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>299</v>
+        <v>573</v>
       </c>
       <c r="B236" s="1">
-        <v>10800</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B237" s="1">
-        <v>54000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B238" s="1">
-        <v>64800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B239" s="1">
-        <v>162000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>672</v>
+        <v>301</v>
       </c>
       <c r="B240" s="1">
-        <v>162000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B241" s="1">
-        <v>86400</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>740</v>
+        <v>672</v>
       </c>
       <c r="B242" s="1">
-        <v>118800</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B243" s="1">
-        <v>59400</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>305</v>
+        <v>740</v>
       </c>
       <c r="B244" s="1">
-        <v>86400</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B245" s="1">
-        <v>16200</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>618</v>
+        <v>305</v>
       </c>
       <c r="B246" s="1">
-        <v>16200</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B247" s="1">
-        <v>91800</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>308</v>
+        <v>618</v>
       </c>
       <c r="B248" s="1">
-        <v>37800</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B249" s="1">
-        <v>108000</v>
+        <v>93500</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B250" s="1">
-        <v>48600</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>690</v>
+        <v>309</v>
       </c>
       <c r="B251" s="1">
-        <v>10800</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B252" s="1">
-        <v>37800</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>312</v>
+        <v>690</v>
       </c>
       <c r="B253" s="1">
-        <v>13500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B254" s="1">
-        <v>5400</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>467</v>
+        <v>312</v>
       </c>
       <c r="B255" s="1">
-        <v>10800</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>741</v>
+        <v>313</v>
       </c>
       <c r="B256" s="1">
-        <v>6480</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>742</v>
+        <v>467</v>
       </c>
       <c r="B257" s="1">
-        <v>6480</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>468</v>
+        <v>741</v>
       </c>
       <c r="B258" s="1">
-        <v>10800</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>314</v>
+        <v>742</v>
       </c>
       <c r="B259" s="1">
-        <v>10800</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>315</v>
+        <v>468</v>
       </c>
       <c r="B260" s="1">
-        <v>13500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B261" s="1">
-        <v>32400</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
-        <v>414</v>
+        <v>315</v>
       </c>
       <c r="B262" s="1">
-        <v>21600</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B263" s="1">
-        <v>16200</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
-        <v>318</v>
+        <v>414</v>
       </c>
       <c r="B264" s="1">
-        <v>10800</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>605</v>
+        <v>317</v>
       </c>
       <c r="B265" s="1">
-        <v>108</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B266" s="1">
-        <v>81000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>320</v>
+        <v>605</v>
       </c>
       <c r="B267" s="1">
-        <v>162000</v>
+        <v>110</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B268" s="1">
-        <v>10800</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B269" s="1">
-        <v>10800</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B270" s="1">
-        <v>8100</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B271" s="1">
-        <v>16200</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B272" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B273" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B274" s="1">
-        <v>21600</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B275" s="1">
-        <v>54000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B276" s="1">
-        <v>37800</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B277" s="1">
-        <v>5400</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B278" s="1">
-        <v>70200</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B279" s="1">
-        <v>108000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B280" s="1">
-        <v>13500</v>
+        <v>71500</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B281" s="1">
-        <v>8100</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>574</v>
+        <v>333</v>
       </c>
       <c r="B282" s="1">
-        <v>54000</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>599</v>
+        <v>334</v>
       </c>
       <c r="B283" s="1">
-        <v>32400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>600</v>
+        <v>574</v>
       </c>
       <c r="B284" s="1">
-        <v>51300</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>743</v>
+        <v>599</v>
       </c>
       <c r="B285" s="1">
-        <v>2700</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>619</v>
+        <v>600</v>
       </c>
       <c r="B286" s="1">
-        <v>2700</v>
+        <v>52250</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>335</v>
+        <v>743</v>
       </c>
       <c r="B287" s="1">
-        <v>4320</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B288" s="1">
-        <v>3780</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B289" s="1">
-        <v>10800</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>337</v>
+        <v>620</v>
       </c>
       <c r="B290" s="1">
-        <v>4320</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B291" s="1">
-        <v>5400</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B292" s="1">
-        <v>5400</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B293" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B294" s="1">
-        <v>8100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B295" s="1">
-        <v>8100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B296" s="1">
-        <v>6480</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>415</v>
+        <v>342</v>
       </c>
       <c r="B297" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>416</v>
+        <v>343</v>
       </c>
       <c r="B298" s="1">
-        <v>3240</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>601</v>
+        <v>415</v>
       </c>
       <c r="B299" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
-        <v>344</v>
+        <v>416</v>
       </c>
       <c r="B300" s="1">
-        <v>81000</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>345</v>
+        <v>601</v>
       </c>
       <c r="B301" s="1">
-        <v>97200</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="302" spans="1:2">
       <c r="A302" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B302" s="1">
-        <v>48600</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B303" s="1">
-        <v>16200</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B304" s="1">
-        <v>10800</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B305" s="1">
-        <v>2160</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>744</v>
+        <v>348</v>
       </c>
       <c r="B306" s="1">
-        <v>1080</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" t="s">
-        <v>673</v>
+        <v>349</v>
       </c>
       <c r="B307" s="1">
-        <v>64800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
-        <v>350</v>
+        <v>744</v>
       </c>
       <c r="B308" s="1">
-        <v>40500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>351</v>
+        <v>673</v>
       </c>
       <c r="B309" s="1">
-        <v>13500</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B310" s="1">
-        <v>32400</v>
+        <v>41250</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>575</v>
+        <v>351</v>
       </c>
       <c r="B311" s="1">
-        <v>5400</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B312" s="1">
-        <v>6480</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>354</v>
+        <v>575</v>
       </c>
       <c r="B313" s="1">
-        <v>135000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="314" spans="1:2">
       <c r="A314" t="s">
-        <v>407</v>
+        <v>353</v>
       </c>
       <c r="B314" s="1">
-        <v>297000</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B315" s="1">
-        <v>13500</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>356</v>
+        <v>407</v>
       </c>
       <c r="B316" s="1">
-        <v>5400</v>
+        <v>302500</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>576</v>
+        <v>355</v>
       </c>
       <c r="B317" s="1">
-        <v>10800</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B318" s="1">
-        <v>4320</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>358</v>
+        <v>576</v>
       </c>
       <c r="B319" s="1">
-        <v>4320</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>651</v>
+        <v>357</v>
       </c>
       <c r="B320" s="1">
-        <v>2160</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>577</v>
+        <v>358</v>
       </c>
       <c r="B321" s="1">
-        <v>8100</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>588</v>
+        <v>651</v>
       </c>
       <c r="B322" s="1">
-        <v>4320</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>359</v>
+        <v>577</v>
       </c>
       <c r="B323" s="1">
-        <v>3780</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>360</v>
+        <v>588</v>
       </c>
       <c r="B324" s="1">
-        <v>24300</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B325" s="1">
-        <v>2160</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B326" s="1">
-        <v>2700</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B327" s="1">
-        <v>2700</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B328" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B329" s="1">
-        <v>10800</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>403</v>
+        <v>364</v>
       </c>
       <c r="B330" s="1">
-        <v>4320</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>546</v>
+        <v>365</v>
       </c>
       <c r="B331" s="1">
-        <v>6480</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>822</v>
+        <v>403</v>
       </c>
       <c r="B332" s="1">
-        <v>6480</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>366</v>
+        <v>546</v>
       </c>
       <c r="B333" s="1">
-        <v>8100</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>556</v>
+        <v>822</v>
       </c>
       <c r="B334" s="1">
-        <v>10800</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>557</v>
+        <v>366</v>
       </c>
       <c r="B335" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
-        <v>367</v>
+        <v>556</v>
       </c>
       <c r="B336" s="1">
-        <v>2700</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
-        <v>368</v>
+        <v>557</v>
       </c>
       <c r="B337" s="1">
-        <v>3780</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B338" s="1">
-        <v>3240</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B339" s="1">
-        <v>1080</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B340" s="1">
-        <v>2700</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B341" s="1">
-        <v>1620</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B342" s="1">
-        <v>2160</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="B343" s="1">
-        <v>1620</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>465</v>
+        <v>373</v>
       </c>
       <c r="B344" s="1">
-        <v>3780</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>621</v>
+        <v>413</v>
       </c>
       <c r="B345" s="1">
-        <v>1620</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>374</v>
+        <v>465</v>
       </c>
       <c r="B346" s="1">
-        <v>1080</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>485</v>
+        <v>621</v>
       </c>
       <c r="B347" s="1">
-        <v>97200</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
-        <v>469</v>
+        <v>374</v>
       </c>
       <c r="B348" s="1">
-        <v>5400</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
-        <v>375</v>
+        <v>485</v>
       </c>
       <c r="B349" s="1">
-        <v>10800</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
-        <v>674</v>
+        <v>469</v>
       </c>
       <c r="B350" s="1">
-        <v>16200</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
-        <v>675</v>
+        <v>375</v>
       </c>
       <c r="B351" s="1">
-        <v>16200</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
-        <v>376</v>
+        <v>674</v>
       </c>
       <c r="B352" s="1">
-        <v>10800</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
-        <v>377</v>
+        <v>675</v>
       </c>
       <c r="B353" s="1">
-        <v>24300</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B354" s="1">
-        <v>8100</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
-        <v>622</v>
+        <v>377</v>
       </c>
       <c r="B355" s="1">
-        <v>1620</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B356" s="1">
-        <v>32400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
-        <v>470</v>
+        <v>622</v>
       </c>
       <c r="B357" s="1">
-        <v>8100</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
-        <v>471</v>
+        <v>379</v>
       </c>
       <c r="B358" s="1">
-        <v>8100</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>676</v>
+        <v>470</v>
       </c>
       <c r="B359" s="1">
-        <v>108000</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>380</v>
+        <v>471</v>
       </c>
       <c r="B360" s="1">
-        <v>18900</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>381</v>
+        <v>676</v>
       </c>
       <c r="B361" s="1">
-        <v>5400</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
-        <v>454</v>
+        <v>380</v>
       </c>
       <c r="B362" s="1">
-        <v>2160</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
+        <v>381</v>
+      </c>
+      <c r="B363" s="1">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" t="s">
+        <v>454</v>
+      </c>
+      <c r="B364" s="1">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" t="s">
         <v>382</v>
       </c>
-      <c r="B363" s="1">
-        <v>6480</v>
+      <c r="B365" s="1">
+        <v>6600</v>
       </c>
     </row>
   </sheetData>
@@ -5920,7 +5948,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B165"/>
+  <dimension ref="A1:B167"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="64.5703125" bestFit="1" customWidth="1"/>
@@ -5940,7 +5968,7 @@
         <v>486</v>
       </c>
       <c r="B2" s="1">
-        <v>75600</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5948,7 +5976,7 @@
         <v>123</v>
       </c>
       <c r="B3" s="1">
-        <v>108000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5956,7 +5984,7 @@
         <v>757</v>
       </c>
       <c r="B4" s="1">
-        <v>18900</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5964,7 +5992,7 @@
         <v>578</v>
       </c>
       <c r="B5" s="1">
-        <v>97200</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5972,7 +6000,7 @@
         <v>164</v>
       </c>
       <c r="B6" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -5980,7 +6008,7 @@
         <v>579</v>
       </c>
       <c r="B7" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5988,7 +6016,7 @@
         <v>589</v>
       </c>
       <c r="B8" s="1">
-        <v>3240</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -5996,7 +6024,7 @@
         <v>758</v>
       </c>
       <c r="B9" s="1">
-        <v>70200</v>
+        <v>71500</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6004,7 +6032,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6012,7 +6040,7 @@
         <v>759</v>
       </c>
       <c r="B11" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6020,7 +6048,7 @@
         <v>124</v>
       </c>
       <c r="B12" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6028,7 +6056,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6036,7 +6064,7 @@
         <v>823</v>
       </c>
       <c r="B14" s="1">
-        <v>45900</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6044,7 +6072,7 @@
         <v>430</v>
       </c>
       <c r="B15" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6052,7 +6080,7 @@
         <v>163</v>
       </c>
       <c r="B16" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6060,7 +6088,7 @@
         <v>647</v>
       </c>
       <c r="B17" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6068,7 +6096,7 @@
         <v>581</v>
       </c>
       <c r="B18" s="1">
-        <v>59400</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6076,7 +6104,7 @@
         <v>648</v>
       </c>
       <c r="B19" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6084,7 +6112,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6092,7 +6120,7 @@
         <v>125</v>
       </c>
       <c r="B21" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6100,7 +6128,7 @@
         <v>478</v>
       </c>
       <c r="B22" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6108,7 +6136,7 @@
         <v>36</v>
       </c>
       <c r="B23" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6116,7 +6144,7 @@
         <v>487</v>
       </c>
       <c r="B24" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6124,7 +6152,7 @@
         <v>488</v>
       </c>
       <c r="B25" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6132,7 +6160,7 @@
         <v>692</v>
       </c>
       <c r="B26" s="1">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6140,7 +6168,7 @@
         <v>406</v>
       </c>
       <c r="B27" s="1">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6148,7 +6176,7 @@
         <v>402</v>
       </c>
       <c r="B28" s="1">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6156,7 +6184,7 @@
         <v>439</v>
       </c>
       <c r="B29" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6164,7 +6192,7 @@
         <v>760</v>
       </c>
       <c r="B30" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6172,7 +6200,7 @@
         <v>489</v>
       </c>
       <c r="B31" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6180,7 +6208,7 @@
         <v>490</v>
       </c>
       <c r="B32" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6188,7 +6216,7 @@
         <v>761</v>
       </c>
       <c r="B33" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6196,7 +6224,7 @@
         <v>12</v>
       </c>
       <c r="B34" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6204,7 +6232,7 @@
         <v>762</v>
       </c>
       <c r="B35" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6212,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="1">
-        <v>1350</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6220,7 +6248,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6228,7 +6256,7 @@
         <v>434</v>
       </c>
       <c r="B38" s="1">
-        <v>3780</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6236,7 +6264,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6244,7 +6272,7 @@
         <v>491</v>
       </c>
       <c r="B40" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6252,7 +6280,7 @@
         <v>479</v>
       </c>
       <c r="B41" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6260,7 +6288,7 @@
         <v>763</v>
       </c>
       <c r="B42" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6268,7 +6296,7 @@
         <v>438</v>
       </c>
       <c r="B43" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6276,7 +6304,7 @@
         <v>440</v>
       </c>
       <c r="B44" s="1">
-        <v>27000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6284,7 +6312,7 @@
         <v>492</v>
       </c>
       <c r="B45" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6292,7 +6320,7 @@
         <v>493</v>
       </c>
       <c r="B46" s="1">
-        <v>27000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6300,7 +6328,7 @@
         <v>494</v>
       </c>
       <c r="B47" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6308,7 +6336,7 @@
         <v>764</v>
       </c>
       <c r="B48" s="1">
-        <v>189000</v>
+        <v>192500</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -6316,7 +6344,7 @@
         <v>551</v>
       </c>
       <c r="B49" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -6324,7 +6352,7 @@
         <v>765</v>
       </c>
       <c r="B50" s="1">
-        <v>70200</v>
+        <v>71500</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -6332,7 +6360,7 @@
         <v>751</v>
       </c>
       <c r="B51" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -6340,7 +6368,7 @@
         <v>722</v>
       </c>
       <c r="B52" s="1">
-        <v>27000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -6348,7 +6376,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="1">
-        <v>18900</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -6356,7 +6384,7 @@
         <v>766</v>
       </c>
       <c r="B54" s="1">
-        <v>75600</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -6364,7 +6392,7 @@
         <v>495</v>
       </c>
       <c r="B55" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -6372,7 +6400,7 @@
         <v>436</v>
       </c>
       <c r="B56" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -6380,7 +6408,7 @@
         <v>126</v>
       </c>
       <c r="B57" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -6388,7 +6416,7 @@
         <v>496</v>
       </c>
       <c r="B58" s="1">
-        <v>108000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -6396,7 +6424,7 @@
         <v>767</v>
       </c>
       <c r="B59" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -6404,7 +6432,7 @@
         <v>30</v>
       </c>
       <c r="B60" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -6412,7 +6440,7 @@
         <v>427</v>
       </c>
       <c r="B61" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -6420,7 +6448,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="1">
-        <v>81000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -6428,7 +6456,7 @@
         <v>768</v>
       </c>
       <c r="B63" s="1">
-        <v>135000</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -6436,7 +6464,7 @@
         <v>769</v>
       </c>
       <c r="B64" s="1">
-        <v>118800</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -6444,7 +6472,7 @@
         <v>127</v>
       </c>
       <c r="B65" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -6452,7 +6480,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -6460,7 +6488,7 @@
         <v>116</v>
       </c>
       <c r="B67" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6468,7 +6496,7 @@
         <v>14</v>
       </c>
       <c r="B68" s="1">
-        <v>70200</v>
+        <v>71500</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6476,7 +6504,7 @@
         <v>770</v>
       </c>
       <c r="B69" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -6484,7 +6512,7 @@
         <v>771</v>
       </c>
       <c r="B70" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -6492,7 +6520,7 @@
         <v>426</v>
       </c>
       <c r="B71" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -6500,751 +6528,767 @@
         <v>552</v>
       </c>
       <c r="B72" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="5" t="s">
-        <v>497</v>
+        <v>825</v>
       </c>
       <c r="B73" s="1">
-        <v>32400</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B74" s="1">
-        <v>29700</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="11" t="s">
-        <v>772</v>
+        <v>498</v>
       </c>
       <c r="B75" s="1">
-        <v>37800</v>
+        <v>30250</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="20" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B76" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="10" t="s">
-        <v>586</v>
+        <v>773</v>
       </c>
       <c r="B77" s="1">
-        <v>5400</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="5" t="s">
-        <v>15</v>
+        <v>586</v>
       </c>
       <c r="B78" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B79" s="1">
-        <v>16200</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="13" t="s">
-        <v>580</v>
+        <v>16</v>
       </c>
       <c r="B80" s="1">
-        <v>8100</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="5" t="s">
-        <v>688</v>
+        <v>580</v>
       </c>
       <c r="B81" s="1">
-        <v>18900</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="5" t="s">
-        <v>774</v>
+        <v>688</v>
       </c>
       <c r="B82" s="1">
-        <v>2160</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="5" t="s">
-        <v>484</v>
+        <v>774</v>
       </c>
       <c r="B83" s="1">
-        <v>3240</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
-        <v>775</v>
+        <v>484</v>
       </c>
       <c r="B84" s="1">
-        <v>54000</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>735</v>
+        <v>775</v>
       </c>
       <c r="B85" s="1">
-        <v>4320</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="11" t="s">
-        <v>3</v>
+        <v>735</v>
       </c>
       <c r="B86" s="1">
-        <v>64800</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="17" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B87" s="1">
-        <v>5400</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="17" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="B88" s="1">
-        <v>10800</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="17" t="s">
-        <v>715</v>
+        <v>128</v>
       </c>
       <c r="B89" s="1">
-        <v>5400</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="21" t="s">
-        <v>499</v>
+        <v>715</v>
       </c>
       <c r="B90" s="1">
-        <v>37800</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="5" t="s">
-        <v>9</v>
+        <v>499</v>
       </c>
       <c r="B91" s="1">
-        <v>32400</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="5" t="s">
-        <v>623</v>
+        <v>9</v>
       </c>
       <c r="B92" s="1">
-        <v>280800</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="5" t="s">
-        <v>776</v>
+        <v>623</v>
       </c>
       <c r="B93" s="1">
-        <v>10800</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="5" t="s">
-        <v>18</v>
+        <v>776</v>
       </c>
       <c r="B94" s="1">
-        <v>13500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B95" s="1">
-        <v>8100</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="10" t="s">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="B96" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B97" s="1">
-        <v>8100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="5" t="s">
-        <v>25</v>
+        <v>501</v>
       </c>
       <c r="B98" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="22" t="s">
-        <v>553</v>
+        <v>25</v>
       </c>
       <c r="B99" s="1">
-        <v>4320</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>777</v>
+        <v>553</v>
       </c>
       <c r="B100" s="1">
-        <v>24300</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B101" s="1">
-        <v>18900</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B102" s="1">
-        <v>21600</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="5" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B103" s="1">
-        <v>18900</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="5" t="s">
-        <v>129</v>
+        <v>780</v>
       </c>
       <c r="B104" s="1">
-        <v>108000</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>502</v>
+        <v>129</v>
       </c>
       <c r="B105" s="1">
-        <v>8100</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>781</v>
+        <v>502</v>
       </c>
       <c r="B106" s="1">
-        <v>24300</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>752</v>
+        <v>781</v>
       </c>
       <c r="B107" s="1">
-        <v>35100</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>723</v>
+        <v>752</v>
       </c>
       <c r="B108" s="1">
-        <v>35100</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B109" s="1">
-        <v>35100</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B110" s="1">
-        <v>35100</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="4" t="s">
-        <v>503</v>
+        <v>721</v>
       </c>
       <c r="B111" s="1">
-        <v>6480</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>100</v>
+        <v>503</v>
       </c>
       <c r="B112" s="1">
-        <v>97200</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>654</v>
+        <v>100</v>
       </c>
       <c r="B113" s="1">
-        <v>189000</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>24</v>
+        <v>826</v>
       </c>
       <c r="B114" s="1">
-        <v>97200</v>
+        <v>192500</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>782</v>
+        <v>654</v>
       </c>
       <c r="B115" s="1">
-        <v>27000</v>
+        <v>192500</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>740</v>
+        <v>24</v>
       </c>
       <c r="B116" s="1">
-        <v>118800</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>20</v>
+        <v>782</v>
       </c>
       <c r="B117" s="1">
-        <v>32400</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>433</v>
+        <v>740</v>
       </c>
       <c r="B118" s="1">
-        <v>21600</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>783</v>
+        <v>20</v>
       </c>
       <c r="B119" s="1">
-        <v>64800</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>115</v>
+        <v>433</v>
       </c>
       <c r="B120" s="1">
-        <v>37800</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>504</v>
+        <v>783</v>
       </c>
       <c r="B121" s="1">
-        <v>10800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>505</v>
+        <v>115</v>
       </c>
       <c r="B122" s="1">
-        <v>8100</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>784</v>
+        <v>504</v>
       </c>
       <c r="B123" s="1">
-        <v>8100</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>716</v>
+        <v>505</v>
       </c>
       <c r="B124" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B125" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>506</v>
+        <v>716</v>
       </c>
       <c r="B126" s="1">
-        <v>40500</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>21</v>
+        <v>785</v>
       </c>
       <c r="B127" s="1">
-        <v>27000</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>756</v>
+        <v>506</v>
       </c>
       <c r="B128" s="1">
-        <v>81000</v>
+        <v>41250</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>480</v>
+        <v>21</v>
       </c>
       <c r="B129" s="1">
-        <v>81000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>786</v>
+        <v>756</v>
       </c>
       <c r="B130" s="1">
-        <v>70200</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>787</v>
+        <v>480</v>
       </c>
       <c r="B131" s="1">
-        <v>97200</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B132" s="1">
-        <v>54000</v>
+        <v>71500</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B133" s="1">
-        <v>48600</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>73</v>
+        <v>788</v>
       </c>
       <c r="B134" s="1">
-        <v>2700</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>74</v>
+        <v>789</v>
       </c>
       <c r="B135" s="1">
-        <v>5400</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>162</v>
+        <v>73</v>
       </c>
       <c r="B136" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>790</v>
+        <v>74</v>
       </c>
       <c r="B137" s="1">
-        <v>40500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="B138" s="1">
-        <v>18900</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B139" s="1">
-        <v>1620</v>
+        <v>41250</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>709</v>
+        <v>130</v>
       </c>
       <c r="B140" s="1">
-        <v>8100</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>432</v>
+        <v>791</v>
       </c>
       <c r="B141" s="1">
-        <v>21600</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>507</v>
+        <v>709</v>
       </c>
       <c r="B142" s="1">
-        <v>21600</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>508</v>
+        <v>432</v>
       </c>
       <c r="B143" s="1">
-        <v>37800</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>437</v>
+        <v>507</v>
       </c>
       <c r="B144" s="1">
-        <v>10800</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B145" s="1">
-        <v>21600</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>792</v>
+        <v>437</v>
       </c>
       <c r="B146" s="1">
-        <v>5400</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>4</v>
+        <v>509</v>
       </c>
       <c r="B147" s="1">
-        <v>8100</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B148" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>650</v>
+        <v>4</v>
       </c>
       <c r="B149" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>651</v>
+        <v>793</v>
       </c>
       <c r="B150" s="1">
-        <v>2700</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>588</v>
+        <v>650</v>
       </c>
       <c r="B151" s="1">
-        <v>4320</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>554</v>
+        <v>651</v>
       </c>
       <c r="B152" s="1">
-        <v>4320</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>510</v>
+        <v>588</v>
       </c>
       <c r="B153" s="1">
-        <v>16200</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>403</v>
+        <v>554</v>
       </c>
       <c r="B154" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>546</v>
+        <v>510</v>
       </c>
       <c r="B155" s="1">
-        <v>6480</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>441</v>
+        <v>403</v>
       </c>
       <c r="B156" s="1">
-        <v>8100</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="B157" s="1">
-        <v>10800</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>557</v>
+        <v>441</v>
       </c>
       <c r="B158" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>794</v>
+        <v>556</v>
       </c>
       <c r="B159" s="1">
-        <v>8100</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>435</v>
+        <v>557</v>
       </c>
       <c r="B160" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B161" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>796</v>
+        <v>435</v>
       </c>
       <c r="B162" s="1">
-        <v>6480</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>624</v>
+        <v>795</v>
       </c>
       <c r="B163" s="1">
-        <v>54000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>10</v>
+        <v>796</v>
       </c>
       <c r="B164" s="1">
-        <v>18900</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
+        <v>624</v>
+      </c>
+      <c r="B165" s="1">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>10</v>
+      </c>
+      <c r="B166" s="1">
+        <v>19250</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" t="s">
         <v>797</v>
       </c>
-      <c r="B165" s="1">
-        <v>5400</v>
+      <c r="B167" s="1">
+        <v>5500</v>
       </c>
     </row>
   </sheetData>
@@ -7254,7 +7298,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B261"/>
+  <dimension ref="A1:B262"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.85546875" bestFit="1" customWidth="1"/>
@@ -7274,7 +7318,7 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>75600</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7282,7 +7326,7 @@
         <v>745</v>
       </c>
       <c r="B3" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7290,7 +7334,7 @@
         <v>746</v>
       </c>
       <c r="B4" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7298,7 +7342,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1">
-        <v>75600</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7306,7 +7350,7 @@
         <v>747</v>
       </c>
       <c r="B6" s="1">
-        <v>108000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7314,7 +7358,7 @@
         <v>122</v>
       </c>
       <c r="B7" s="1">
-        <v>108000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7322,7 +7366,7 @@
         <v>131</v>
       </c>
       <c r="B8" s="1">
-        <v>135000</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7330,7 +7374,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>86400</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7338,7 +7382,7 @@
         <v>567</v>
       </c>
       <c r="B10" s="1">
-        <v>97200</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7346,7 +7390,7 @@
         <v>82</v>
       </c>
       <c r="B11" s="1">
-        <v>97200</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7354,7 +7398,7 @@
         <v>165</v>
       </c>
       <c r="B12" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7362,7 +7406,7 @@
         <v>589</v>
       </c>
       <c r="B13" s="1">
-        <v>3240</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7370,7 +7414,7 @@
         <v>798</v>
       </c>
       <c r="B14" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7378,7 +7422,7 @@
         <v>132</v>
       </c>
       <c r="B15" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -7386,7 +7430,7 @@
         <v>133</v>
       </c>
       <c r="B16" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -7394,7 +7438,7 @@
         <v>753</v>
       </c>
       <c r="B17" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -7402,7 +7446,7 @@
         <v>625</v>
       </c>
       <c r="B18" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -7410,7 +7454,7 @@
         <v>823</v>
       </c>
       <c r="B19" s="1">
-        <v>45900</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7418,7 +7462,7 @@
         <v>430</v>
       </c>
       <c r="B20" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7426,7 +7470,7 @@
         <v>163</v>
       </c>
       <c r="B21" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7434,7 +7478,7 @@
         <v>647</v>
       </c>
       <c r="B22" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7442,7 +7486,7 @@
         <v>581</v>
       </c>
       <c r="B23" s="1">
-        <v>59400</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7450,7 +7494,7 @@
         <v>648</v>
       </c>
       <c r="B24" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7458,7 +7502,7 @@
         <v>83</v>
       </c>
       <c r="B25" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7466,7 +7510,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7474,7 +7518,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7482,7 +7526,7 @@
         <v>121</v>
       </c>
       <c r="B28" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7490,7 +7534,7 @@
         <v>134</v>
       </c>
       <c r="B29" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7498,7 +7542,7 @@
         <v>698</v>
       </c>
       <c r="B30" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7506,7 +7550,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7514,7 +7558,7 @@
         <v>477</v>
       </c>
       <c r="B32" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7522,7 +7566,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7530,7 +7574,7 @@
         <v>158</v>
       </c>
       <c r="B34" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7538,7 +7582,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>24300</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7546,7 +7590,7 @@
         <v>692</v>
       </c>
       <c r="B36" s="1">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7554,7 +7598,7 @@
         <v>406</v>
       </c>
       <c r="B37" s="1">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7562,7 +7606,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="1">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7570,7 +7614,7 @@
         <v>626</v>
       </c>
       <c r="B39" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7578,7 +7622,7 @@
         <v>627</v>
       </c>
       <c r="B40" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7586,7 +7630,7 @@
         <v>628</v>
       </c>
       <c r="B41" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7594,7 +7638,7 @@
         <v>629</v>
       </c>
       <c r="B42" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -7602,7 +7646,7 @@
         <v>511</v>
       </c>
       <c r="B43" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7610,7 +7654,7 @@
         <v>85</v>
       </c>
       <c r="B44" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -7618,7 +7662,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -7626,7 +7670,7 @@
         <v>86</v>
       </c>
       <c r="B46" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7634,7 +7678,7 @@
         <v>135</v>
       </c>
       <c r="B47" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7642,7 +7686,7 @@
         <v>136</v>
       </c>
       <c r="B48" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -7650,7 +7694,7 @@
         <v>87</v>
       </c>
       <c r="B49" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -7658,7 +7702,7 @@
         <v>444</v>
       </c>
       <c r="B50" s="1">
-        <v>3780</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -7666,7 +7710,7 @@
         <v>512</v>
       </c>
       <c r="B51" s="1">
-        <v>3780</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -7674,7 +7718,7 @@
         <v>137</v>
       </c>
       <c r="B52" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -7682,7 +7726,7 @@
         <v>513</v>
       </c>
       <c r="B53" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -7690,7 +7734,7 @@
         <v>451</v>
       </c>
       <c r="B54" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -7698,7 +7742,7 @@
         <v>452</v>
       </c>
       <c r="B55" s="1">
-        <v>48600</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -7706,7 +7750,7 @@
         <v>138</v>
       </c>
       <c r="B56" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -7714,7 +7758,7 @@
         <v>699</v>
       </c>
       <c r="B57" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -7722,7 +7766,7 @@
         <v>583</v>
       </c>
       <c r="B58" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -7730,7 +7774,7 @@
         <v>584</v>
       </c>
       <c r="B59" s="1">
-        <v>40500</v>
+        <v>41250</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -7738,7 +7782,7 @@
         <v>139</v>
       </c>
       <c r="B60" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -7746,7 +7790,7 @@
         <v>551</v>
       </c>
       <c r="B61" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -7754,7 +7798,7 @@
         <v>140</v>
       </c>
       <c r="B62" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -7762,7 +7806,7 @@
         <v>89</v>
       </c>
       <c r="B63" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -7770,7 +7814,7 @@
         <v>88</v>
       </c>
       <c r="B64" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -7778,7 +7822,7 @@
         <v>559</v>
       </c>
       <c r="B65" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -7786,7 +7830,7 @@
         <v>722</v>
       </c>
       <c r="B66" s="1">
-        <v>27000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -7794,7 +7838,7 @@
         <v>118</v>
       </c>
       <c r="B67" s="1">
-        <v>18900</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -7802,7 +7846,7 @@
         <v>799</v>
       </c>
       <c r="B68" s="1">
-        <v>86400</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -7810,7 +7854,7 @@
         <v>39</v>
       </c>
       <c r="B69" s="1">
-        <v>86400</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -7818,7 +7862,7 @@
         <v>40</v>
       </c>
       <c r="B70" s="1">
-        <v>86400</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -7826,7 +7870,7 @@
         <v>800</v>
       </c>
       <c r="B71" s="1">
-        <v>86400</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -7834,7 +7878,7 @@
         <v>120</v>
       </c>
       <c r="B72" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7842,7 +7886,7 @@
         <v>41</v>
       </c>
       <c r="B73" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7850,7 +7894,7 @@
         <v>42</v>
       </c>
       <c r="B74" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7858,7 +7902,7 @@
         <v>43</v>
       </c>
       <c r="B75" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7866,7 +7910,7 @@
         <v>44</v>
       </c>
       <c r="B76" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7874,7 +7918,7 @@
         <v>45</v>
       </c>
       <c r="B77" s="1">
-        <v>81000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7882,7 +7926,7 @@
         <v>46</v>
       </c>
       <c r="B78" s="1">
-        <v>108000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7890,7 +7934,7 @@
         <v>687</v>
       </c>
       <c r="B79" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7898,7 +7942,7 @@
         <v>90</v>
       </c>
       <c r="B80" s="1">
-        <v>27000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7906,7 +7950,7 @@
         <v>32</v>
       </c>
       <c r="B81" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7914,7 +7958,7 @@
         <v>27</v>
       </c>
       <c r="B82" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7922,7 +7966,7 @@
         <v>33</v>
       </c>
       <c r="B83" s="1">
-        <v>86400</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7930,7 +7974,7 @@
         <v>141</v>
       </c>
       <c r="B84" s="1">
-        <v>86400</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7938,7 +7982,7 @@
         <v>49</v>
       </c>
       <c r="B85" s="1">
-        <v>135000</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7946,7 +7990,7 @@
         <v>48</v>
       </c>
       <c r="B86" s="1">
-        <v>135000</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7954,7 +7998,7 @@
         <v>47</v>
       </c>
       <c r="B87" s="1">
-        <v>124200</v>
+        <v>126500</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -7962,7 +8006,7 @@
         <v>50</v>
       </c>
       <c r="B88" s="1">
-        <v>135000</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -7970,7 +8014,7 @@
         <v>51</v>
       </c>
       <c r="B89" s="1">
-        <v>135000</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -7978,7 +8022,7 @@
         <v>474</v>
       </c>
       <c r="B90" s="1">
-        <v>135000</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -7986,7 +8030,7 @@
         <v>55</v>
       </c>
       <c r="B91" s="1">
-        <v>81000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -7994,7 +8038,7 @@
         <v>52</v>
       </c>
       <c r="B92" s="1">
-        <v>108000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -8002,7 +8046,7 @@
         <v>53</v>
       </c>
       <c r="B93" s="1">
-        <v>118800</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -8010,7 +8054,7 @@
         <v>54</v>
       </c>
       <c r="B94" s="1">
-        <v>118800</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -8018,7 +8062,7 @@
         <v>56</v>
       </c>
       <c r="B95" s="1">
-        <v>118800</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -8026,7 +8070,7 @@
         <v>475</v>
       </c>
       <c r="B96" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -8034,7 +8078,7 @@
         <v>514</v>
       </c>
       <c r="B97" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -8042,7 +8086,7 @@
         <v>700</v>
       </c>
       <c r="B98" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -8050,7 +8094,7 @@
         <v>701</v>
       </c>
       <c r="B99" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -8058,7 +8102,7 @@
         <v>142</v>
       </c>
       <c r="B100" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -8066,7 +8110,7 @@
         <v>801</v>
       </c>
       <c r="B101" s="1">
-        <v>75600</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -8074,7 +8118,7 @@
         <v>544</v>
       </c>
       <c r="B102" s="1">
-        <v>75600</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -8082,7 +8126,7 @@
         <v>802</v>
       </c>
       <c r="B103" s="1">
-        <v>97200</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -8090,7 +8134,7 @@
         <v>643</v>
       </c>
       <c r="B104" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -8098,7 +8142,7 @@
         <v>515</v>
       </c>
       <c r="B105" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -8106,7 +8150,7 @@
         <v>428</v>
       </c>
       <c r="B106" s="1">
-        <v>27000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -8114,7 +8158,7 @@
         <v>693</v>
       </c>
       <c r="B107" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -8122,1231 +8166,1239 @@
         <v>552</v>
       </c>
       <c r="B108" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="17" t="s">
-        <v>702</v>
+        <v>825</v>
       </c>
       <c r="B109" s="1">
-        <v>32400</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="17" t="s">
-        <v>93</v>
+        <v>702</v>
       </c>
       <c r="B110" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B111" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B112" s="1">
-        <v>64800</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B113" s="1">
-        <v>81000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>585</v>
+        <v>94</v>
       </c>
       <c r="B114" s="1">
-        <v>5400</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="17" t="s">
-        <v>646</v>
+        <v>585</v>
       </c>
       <c r="B115" s="1">
-        <v>8100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="17" t="s">
-        <v>560</v>
+        <v>646</v>
       </c>
       <c r="B116" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="17" t="s">
-        <v>57</v>
+        <v>560</v>
       </c>
       <c r="B117" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B118" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B119" s="1">
-        <v>8100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="17" t="s">
-        <v>561</v>
+        <v>59</v>
       </c>
       <c r="B120" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B121" s="1">
-        <v>10800</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="17" t="s">
-        <v>677</v>
+        <v>562</v>
       </c>
       <c r="B122" s="1">
-        <v>6480</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="17" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="B123" s="1">
-        <v>18900</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="17" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B124" s="1">
-        <v>18900</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="17" t="s">
-        <v>484</v>
+        <v>686</v>
       </c>
       <c r="B125" s="1">
-        <v>3240</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="17" t="s">
-        <v>735</v>
+        <v>484</v>
       </c>
       <c r="B126" s="1">
-        <v>4320</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="32" t="s">
-        <v>60</v>
+        <v>735</v>
       </c>
       <c r="B127" s="1">
-        <v>13500</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B128" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="17" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="B129" s="1">
-        <v>10800</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="17" t="s">
-        <v>62</v>
+        <v>157</v>
       </c>
       <c r="B130" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="17" t="s">
-        <v>754</v>
+        <v>62</v>
       </c>
       <c r="B131" s="1">
-        <v>5400</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="17" t="s">
-        <v>694</v>
+        <v>754</v>
       </c>
       <c r="B132" s="1">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="28" t="s">
-        <v>563</v>
+        <v>694</v>
       </c>
       <c r="B133" s="1">
-        <v>75600</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="17" t="s">
-        <v>697</v>
+        <v>563</v>
       </c>
       <c r="B134" s="1">
-        <v>32400</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="33" t="s">
-        <v>455</v>
+        <v>697</v>
       </c>
       <c r="B135" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="17" t="s">
-        <v>623</v>
+        <v>455</v>
       </c>
       <c r="B136" s="1">
-        <v>280800</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="17" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="B137" s="1">
-        <v>297000</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="17" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B138" s="1">
-        <v>307800</v>
+        <v>302500</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="17" t="s">
-        <v>449</v>
+        <v>631</v>
       </c>
       <c r="B139" s="1">
-        <v>10800</v>
+        <v>313500</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B140" s="1">
-        <v>8100</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="17" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B141" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="17" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B142" s="1">
-        <v>13500</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="17" t="s">
-        <v>143</v>
+        <v>447</v>
       </c>
       <c r="B143" s="1">
-        <v>5400</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="17" t="s">
-        <v>446</v>
+        <v>143</v>
       </c>
       <c r="B144" s="1">
-        <v>8100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="17" t="s">
-        <v>144</v>
+        <v>446</v>
       </c>
       <c r="B145" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="17" t="s">
-        <v>591</v>
+        <v>144</v>
       </c>
       <c r="B146" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="17" t="s">
-        <v>96</v>
+        <v>591</v>
       </c>
       <c r="B147" s="1">
-        <v>8100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B148" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B149" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="17" t="s">
-        <v>553</v>
+        <v>97</v>
       </c>
       <c r="B150" s="1">
-        <v>4320</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>803</v>
+        <v>553</v>
       </c>
       <c r="B151" s="1">
-        <v>24300</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="17" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B152" s="1">
-        <v>18900</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>145</v>
+        <v>804</v>
       </c>
       <c r="B153" s="1">
-        <v>135000</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="17" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="B154" s="1">
-        <v>108000</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="17" t="s">
-        <v>703</v>
+        <v>119</v>
       </c>
       <c r="B155" s="1">
-        <v>40500</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B156" s="1">
-        <v>40500</v>
+        <v>41250</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="17" t="s">
-        <v>98</v>
+        <v>704</v>
       </c>
       <c r="B157" s="1">
-        <v>81000</v>
+        <v>41250</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="17" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="B158" s="1">
-        <v>81000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="17" t="s">
-        <v>472</v>
+        <v>63</v>
       </c>
       <c r="B159" s="1">
-        <v>75600</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="17" t="s">
-        <v>99</v>
+        <v>472</v>
       </c>
       <c r="B160" s="1">
-        <v>64800</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="17" t="s">
-        <v>720</v>
+        <v>99</v>
       </c>
       <c r="B161" s="1">
-        <v>35100</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="17" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B162" s="1">
-        <v>40500</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="17" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B163" s="1">
-        <v>35100</v>
+        <v>41250</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="17" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B164" s="1">
-        <v>43200</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="30" t="s">
-        <v>695</v>
+        <v>725</v>
       </c>
       <c r="B165" s="1">
-        <v>810</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>101</v>
+        <v>695</v>
       </c>
       <c r="B166" s="1">
-        <v>108000</v>
+        <v>825</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B167" s="1">
-        <v>124200</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B168" s="1">
-        <v>189000</v>
+        <v>126500</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="17" t="s">
-        <v>632</v>
+        <v>103</v>
       </c>
       <c r="B169" s="1">
-        <v>189000</v>
+        <v>192500</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="17" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B170" s="1">
-        <v>194400</v>
+        <v>192500</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="17" t="s">
-        <v>678</v>
+        <v>633</v>
       </c>
       <c r="B171" s="1">
-        <v>199800</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="17" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B172" s="1">
-        <v>189000</v>
+        <v>203500</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="17" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B173" s="1">
-        <v>189000</v>
+        <v>192500</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B174" s="1">
-        <v>189000</v>
+        <v>192500</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="17" t="s">
-        <v>740</v>
+        <v>681</v>
       </c>
       <c r="B175" s="1">
-        <v>118800</v>
+        <v>192500</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="17" t="s">
-        <v>23</v>
+        <v>740</v>
       </c>
       <c r="B176" s="1">
-        <v>97200</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="17" t="s">
-        <v>442</v>
+        <v>23</v>
       </c>
       <c r="B177" s="1">
-        <v>97200</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="17" t="s">
-        <v>564</v>
+        <v>442</v>
       </c>
       <c r="B178" s="1">
-        <v>108000</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="17" t="s">
-        <v>146</v>
+        <v>564</v>
       </c>
       <c r="B179" s="1">
-        <v>21600</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B180" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>755</v>
+        <v>147</v>
       </c>
       <c r="B181" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>705</v>
+        <v>755</v>
       </c>
       <c r="B182" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="17" t="s">
-        <v>652</v>
+        <v>705</v>
       </c>
       <c r="B183" s="1">
-        <v>37800</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="17" t="s">
-        <v>805</v>
+        <v>652</v>
       </c>
       <c r="B184" s="1">
-        <v>64800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="17" t="s">
-        <v>748</v>
+        <v>805</v>
       </c>
       <c r="B185" s="1">
-        <v>32400</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="17" t="s">
-        <v>148</v>
+        <v>748</v>
       </c>
       <c r="B186" s="1">
-        <v>37800</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="17" t="s">
-        <v>706</v>
+        <v>148</v>
       </c>
       <c r="B187" s="1">
-        <v>48600</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>516</v>
+        <v>706</v>
       </c>
       <c r="B188" s="1">
-        <v>10800</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>749</v>
+        <v>516</v>
       </c>
       <c r="B189" s="1">
-        <v>16200</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>149</v>
+        <v>749</v>
       </c>
       <c r="B190" s="1">
-        <v>32400</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>565</v>
+        <v>149</v>
       </c>
       <c r="B191" s="1">
-        <v>18900</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>707</v>
+        <v>565</v>
       </c>
       <c r="B192" s="1">
-        <v>8100</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>150</v>
+        <v>707</v>
       </c>
       <c r="B193" s="1">
-        <v>24300</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="B194" s="1">
-        <v>13500</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>517</v>
+        <v>104</v>
       </c>
       <c r="B195" s="1">
-        <v>40500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>151</v>
+        <v>517</v>
       </c>
       <c r="B196" s="1">
-        <v>24300</v>
+        <v>41250</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>481</v>
+        <v>151</v>
       </c>
       <c r="B197" s="1">
-        <v>81000</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>708</v>
+        <v>481</v>
       </c>
       <c r="B198" s="1">
-        <v>91800</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>64</v>
+        <v>708</v>
       </c>
       <c r="B199" s="1">
-        <v>86400</v>
+        <v>93500</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="B200" s="1">
-        <v>81000</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="4" t="s">
-        <v>65</v>
+        <v>152</v>
       </c>
       <c r="B201" s="1">
-        <v>108000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>545</v>
+        <v>65</v>
       </c>
       <c r="B202" s="1">
-        <v>75600</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B203" s="1">
-        <v>97200</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>66</v>
+        <v>547</v>
       </c>
       <c r="B204" s="1">
-        <v>70200</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B205" s="1">
-        <v>43200</v>
+        <v>71500</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B206" s="1">
-        <v>54000</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B207" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B208" s="1">
-        <v>64800</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B209" s="1">
-        <v>54000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B210" s="1">
-        <v>64800</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>473</v>
+        <v>72</v>
       </c>
       <c r="B211" s="1">
-        <v>97200</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>160</v>
+        <v>473</v>
       </c>
       <c r="B212" s="1">
-        <v>2700</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B213" s="1">
-        <v>5400</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="B214" s="1">
-        <v>4320</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>159</v>
+        <v>75</v>
       </c>
       <c r="B215" s="1">
-        <v>2700</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="B216" s="1">
-        <v>135000</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B217" s="1">
-        <v>108000</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B218" s="1">
-        <v>108000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B219" s="1">
-        <v>81000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B220" s="1">
-        <v>81000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B221" s="1">
-        <v>97200</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B222" s="1">
-        <v>97200</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="B223" s="1">
-        <v>18900</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B224" s="1">
-        <v>18900</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="B225" s="1">
-        <v>16200</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B226" s="1">
-        <v>21600</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>714</v>
+        <v>77</v>
       </c>
       <c r="B227" s="1">
-        <v>16200</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>78</v>
+        <v>714</v>
       </c>
       <c r="B228" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>443</v>
+        <v>78</v>
       </c>
       <c r="B229" s="1">
-        <v>21600</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>79</v>
+        <v>443</v>
       </c>
       <c r="B230" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>518</v>
+        <v>79</v>
       </c>
       <c r="B231" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>80</v>
+        <v>518</v>
       </c>
       <c r="B232" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B233" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>519</v>
+        <v>81</v>
       </c>
       <c r="B234" s="1">
-        <v>18900</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>113</v>
+        <v>519</v>
       </c>
       <c r="B235" s="1">
-        <v>10800</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B236" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>453</v>
+        <v>114</v>
       </c>
       <c r="B237" s="1">
-        <v>37800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>710</v>
+        <v>453</v>
       </c>
       <c r="B238" s="1">
-        <v>37800</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>750</v>
+        <v>710</v>
       </c>
       <c r="B239" s="1">
-        <v>8100</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="B240" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>588</v>
+        <v>650</v>
       </c>
       <c r="B241" s="1">
-        <v>4320</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>555</v>
+        <v>588</v>
       </c>
       <c r="B242" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>117</v>
+        <v>555</v>
       </c>
       <c r="B243" s="1">
-        <v>16200</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>403</v>
+        <v>117</v>
       </c>
       <c r="B244" s="1">
-        <v>4320</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>546</v>
+        <v>403</v>
       </c>
       <c r="B245" s="1">
-        <v>6480</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="B246" s="1">
-        <v>10800</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B247" s="1">
-        <v>16200</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="B248" s="1">
-        <v>10800</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B249" s="1">
-        <v>5400</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>634</v>
+        <v>557</v>
       </c>
       <c r="B250" s="1">
-        <v>8100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>711</v>
+        <v>634</v>
       </c>
       <c r="B251" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B252" s="1">
-        <v>10800</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>558</v>
+        <v>712</v>
       </c>
       <c r="B253" s="1">
-        <v>1620</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>635</v>
+        <v>558</v>
       </c>
       <c r="B254" s="1">
-        <v>124200</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>713</v>
+        <v>635</v>
       </c>
       <c r="B255" s="1">
-        <v>10800</v>
+        <v>126500</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>794</v>
+        <v>713</v>
       </c>
       <c r="B256" s="1">
-        <v>8100</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>445</v>
+        <v>794</v>
       </c>
       <c r="B257" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>682</v>
+        <v>445</v>
       </c>
       <c r="B258" s="1">
-        <v>54000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>112</v>
+        <v>682</v>
       </c>
       <c r="B259" s="1">
-        <v>32400</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="B260" s="1">
-        <v>18900</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
+        <v>155</v>
+      </c>
+      <c r="B261" s="1">
+        <v>19250</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" t="s">
         <v>156</v>
       </c>
-      <c r="B261" s="1">
-        <v>21600</v>
+      <c r="B262" s="1">
+        <v>22000</v>
       </c>
     </row>
   </sheetData>
@@ -9356,7 +9408,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.140625" customWidth="1"/>
@@ -9376,7 +9428,7 @@
         <v>592</v>
       </c>
       <c r="B2" s="1">
-        <v>97200</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9384,7 +9436,7 @@
         <v>806</v>
       </c>
       <c r="B3" s="1">
-        <v>72900</v>
+        <v>74250</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9392,7 +9444,7 @@
         <v>807</v>
       </c>
       <c r="B4" s="1">
-        <v>48600</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9400,7 +9452,7 @@
         <v>589</v>
       </c>
       <c r="B5" s="1">
-        <v>3240</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9408,7 +9460,7 @@
         <v>808</v>
       </c>
       <c r="B6" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9416,7 +9468,7 @@
         <v>581</v>
       </c>
       <c r="B7" s="1">
-        <v>59400</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9424,7 +9476,7 @@
         <v>648</v>
       </c>
       <c r="B8" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9432,7 +9484,7 @@
         <v>520</v>
       </c>
       <c r="B9" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -9440,7 +9492,7 @@
         <v>521</v>
       </c>
       <c r="B10" s="1">
-        <v>18900</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9448,7 +9500,7 @@
         <v>522</v>
       </c>
       <c r="B11" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9456,7 +9508,7 @@
         <v>523</v>
       </c>
       <c r="B12" s="1">
-        <v>48600</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -9464,7 +9516,7 @@
         <v>809</v>
       </c>
       <c r="B13" s="1">
-        <v>6480</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -9472,7 +9524,7 @@
         <v>551</v>
       </c>
       <c r="B14" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -9480,7 +9532,7 @@
         <v>722</v>
       </c>
       <c r="B15" s="1">
-        <v>27000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -9488,7 +9540,7 @@
         <v>524</v>
       </c>
       <c r="B16" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -9496,7 +9548,7 @@
         <v>525</v>
       </c>
       <c r="B17" s="1">
-        <v>18900</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -9504,7 +9556,7 @@
         <v>691</v>
       </c>
       <c r="B18" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -9512,7 +9564,7 @@
         <v>526</v>
       </c>
       <c r="B19" s="1">
-        <v>27000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -9520,7 +9572,7 @@
         <v>810</v>
       </c>
       <c r="B20" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -9528,7 +9580,7 @@
         <v>527</v>
       </c>
       <c r="B21" s="1">
-        <v>13500</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -9536,351 +9588,359 @@
         <v>552</v>
       </c>
       <c r="B22" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="36" t="s">
-        <v>528</v>
+        <v>825</v>
       </c>
       <c r="B23" s="1">
-        <v>5400</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="36" t="s">
-        <v>821</v>
+        <v>528</v>
       </c>
       <c r="B24" s="1">
-        <v>8100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="36" t="s">
-        <v>529</v>
+        <v>821</v>
       </c>
       <c r="B25" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="36" t="s">
-        <v>684</v>
+        <v>529</v>
       </c>
       <c r="B26" s="1">
-        <v>18900</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="36" t="s">
-        <v>484</v>
+        <v>684</v>
       </c>
       <c r="B27" s="1">
-        <v>3240</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>735</v>
+        <v>484</v>
       </c>
       <c r="B28">
-        <v>4320</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>530</v>
+        <v>735</v>
       </c>
       <c r="B29">
-        <v>8100</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B30">
-        <v>13500</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B31">
-        <v>10800</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B32">
-        <v>5400</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B33">
-        <v>64800</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B34">
-        <v>59400</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>631</v>
+        <v>535</v>
       </c>
       <c r="B35">
-        <v>297000</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>553</v>
+        <v>631</v>
       </c>
       <c r="B36">
-        <v>4320</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>726</v>
+        <v>553</v>
       </c>
       <c r="B37">
-        <v>45900</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B38">
-        <v>48600</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>536</v>
+        <v>727</v>
       </c>
       <c r="B39">
-        <v>16200</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>683</v>
+        <v>536</v>
       </c>
       <c r="B40">
-        <v>194400</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>636</v>
+        <v>683</v>
       </c>
       <c r="B41">
-        <v>199800</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>740</v>
+        <v>636</v>
       </c>
       <c r="B42">
-        <v>118800</v>
+        <v>203500</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>537</v>
+        <v>740</v>
       </c>
       <c r="B43">
-        <v>48600</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B44">
-        <v>27000</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>811</v>
+        <v>538</v>
       </c>
       <c r="B45">
-        <v>2700</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B46">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B47">
-        <v>8100</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>539</v>
+        <v>813</v>
       </c>
       <c r="B48">
-        <v>24300</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>814</v>
+        <v>539</v>
       </c>
       <c r="B49">
-        <v>21600</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B50">
-        <v>10800</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B51">
-        <v>13500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>588</v>
+        <v>816</v>
       </c>
       <c r="B52">
-        <v>4320</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>817</v>
+        <v>588</v>
       </c>
       <c r="B53">
-        <v>2700</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B54">
-        <v>5400</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B55">
-        <v>2700</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>548</v>
+        <v>819</v>
       </c>
       <c r="B56">
-        <v>37800</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B57">
-        <v>16200</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>403</v>
+        <v>549</v>
       </c>
       <c r="B58">
-        <v>4320</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>546</v>
+        <v>403</v>
       </c>
       <c r="B59">
-        <v>6480</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="B60">
-        <v>10800</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B61">
-        <v>5400</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="B62">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B63">
-        <v>5400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>637</v>
+        <v>541</v>
       </c>
       <c r="B64">
-        <v>54000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
+        <v>637</v>
+      </c>
+      <c r="B65">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
         <v>542</v>
       </c>
-      <c r="B65">
-        <v>16200</v>
+      <c r="B66">
+        <v>16500</v>
       </c>
     </row>
   </sheetData>
@@ -9890,7 +9950,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58.140625" customWidth="1"/>
@@ -9910,7 +9970,7 @@
         <v>383</v>
       </c>
       <c r="B2" s="1">
-        <v>3780</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9918,7 +9978,7 @@
         <v>384</v>
       </c>
       <c r="B3" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9926,7 +9986,7 @@
         <v>385</v>
       </c>
       <c r="B4" s="1">
-        <v>3780</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9934,7 +9994,7 @@
         <v>386</v>
       </c>
       <c r="B5" s="1">
-        <v>16200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9942,7 +10002,7 @@
         <v>640</v>
       </c>
       <c r="B6" s="1">
-        <v>18900</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9950,7 +10010,7 @@
         <v>387</v>
       </c>
       <c r="B7" s="1">
-        <v>18900</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9958,7 +10018,7 @@
         <v>660</v>
       </c>
       <c r="B8" s="1">
-        <v>21600</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9966,7 +10026,7 @@
         <v>662</v>
       </c>
       <c r="B9" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -9974,7 +10034,7 @@
         <v>661</v>
       </c>
       <c r="B10" s="1">
-        <v>17280</v>
+        <v>17600</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9982,7 +10042,7 @@
         <v>388</v>
       </c>
       <c r="B11" s="1">
-        <v>3240</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9990,7 +10050,7 @@
         <v>405</v>
       </c>
       <c r="B12" s="1">
-        <v>3780</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -9998,7 +10058,7 @@
         <v>659</v>
       </c>
       <c r="B13" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -10006,7 +10066,7 @@
         <v>665</v>
       </c>
       <c r="B14" s="1">
-        <v>3240</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -10014,7 +10074,7 @@
         <v>745</v>
       </c>
       <c r="B15" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -10022,7 +10082,7 @@
         <v>389</v>
       </c>
       <c r="B16" s="1">
-        <v>4860</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -10030,7 +10090,7 @@
         <v>589</v>
       </c>
       <c r="B17" s="1">
-        <v>3240</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -10038,7 +10098,7 @@
         <v>823</v>
       </c>
       <c r="B18" s="1">
-        <v>45900</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -10046,7 +10106,7 @@
         <v>663</v>
       </c>
       <c r="B19" s="1">
-        <v>94500</v>
+        <v>96250</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -10054,7 +10114,7 @@
         <v>655</v>
       </c>
       <c r="B20" s="1">
-        <v>105300</v>
+        <v>107250</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -10062,7 +10122,7 @@
         <v>656</v>
       </c>
       <c r="B21" s="1">
-        <v>118800</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -10070,7 +10130,7 @@
         <v>430</v>
       </c>
       <c r="B22" s="1">
-        <v>43200</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -10078,7 +10138,7 @@
         <v>163</v>
       </c>
       <c r="B23" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -10086,7 +10146,7 @@
         <v>647</v>
       </c>
       <c r="B24" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -10094,7 +10154,7 @@
         <v>581</v>
       </c>
       <c r="B25" s="1">
-        <v>59400</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -10102,7 +10162,7 @@
         <v>648</v>
       </c>
       <c r="B26" s="1">
-        <v>64800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -10110,7 +10170,7 @@
         <v>657</v>
       </c>
       <c r="B27" s="1">
-        <v>72900</v>
+        <v>74250</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -10118,7 +10178,7 @@
         <v>658</v>
       </c>
       <c r="B28" s="1">
-        <v>86400</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -10126,7 +10186,7 @@
         <v>664</v>
       </c>
       <c r="B29" s="1">
-        <v>91800</v>
+        <v>93500</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -10134,7 +10194,7 @@
         <v>692</v>
       </c>
       <c r="B30" s="1">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -10142,7 +10202,7 @@
         <v>406</v>
       </c>
       <c r="B31" s="1">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -10150,7 +10210,7 @@
         <v>402</v>
       </c>
       <c r="B32" s="1">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -10158,7 +10218,7 @@
         <v>429</v>
       </c>
       <c r="B33" s="1">
-        <v>1620</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -10166,7 +10226,7 @@
         <v>551</v>
       </c>
       <c r="B34" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -10174,7 +10234,7 @@
         <v>390</v>
       </c>
       <c r="B35" s="1">
-        <v>3240</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -10182,367 +10242,383 @@
         <v>552</v>
       </c>
       <c r="B36" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="B37" s="1">
-        <v>2700</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>404</v>
+        <v>820</v>
       </c>
       <c r="B38" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>259</v>
+        <v>404</v>
       </c>
       <c r="B39" s="1">
-        <v>16200</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>425</v>
+        <v>259</v>
       </c>
       <c r="B40" s="1">
-        <v>2160</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>484</v>
+        <v>425</v>
       </c>
       <c r="B41" s="1">
-        <v>3240</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>735</v>
+        <v>484</v>
       </c>
       <c r="B42" s="1">
-        <v>4320</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>391</v>
+        <v>735</v>
       </c>
       <c r="B43" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B44" s="1">
-        <v>3780</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B45" s="1">
-        <v>8100</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>638</v>
+        <v>393</v>
       </c>
       <c r="B46" s="1">
-        <v>3240</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>394</v>
+        <v>638</v>
       </c>
       <c r="B47" s="1">
-        <v>5400</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B48" s="1">
-        <v>4320</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B49" s="1">
-        <v>3780</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>728</v>
+        <v>396</v>
       </c>
       <c r="B50" s="1">
-        <v>2700</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>553</v>
+        <v>728</v>
       </c>
       <c r="B51" s="1">
-        <v>4320</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>718</v>
+        <v>553</v>
       </c>
       <c r="B52" s="1">
-        <v>29700</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B53" s="1">
-        <v>32400</v>
+        <v>30250</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>752</v>
+        <v>719</v>
       </c>
       <c r="B54" s="1">
-        <v>35100</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>723</v>
+        <v>752</v>
       </c>
       <c r="B55" s="1">
-        <v>35100</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B56" s="1">
-        <v>35100</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B57" s="1">
-        <v>40500</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B58" s="1">
-        <v>35100</v>
+        <v>41250</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B59" s="1">
-        <v>43200</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B60" s="1">
-        <v>45900</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B61" s="1">
-        <v>48600</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="B62" s="1">
-        <v>118800</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>639</v>
+        <v>740</v>
       </c>
       <c r="B63" s="1">
-        <v>5400</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>543</v>
+        <v>827</v>
       </c>
       <c r="B64" s="1">
-        <v>8100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>397</v>
+        <v>639</v>
       </c>
       <c r="B65" s="1">
-        <v>9720</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>653</v>
+        <v>543</v>
       </c>
       <c r="B66" s="1">
-        <v>5400</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B67" s="1">
-        <v>5400</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>399</v>
+        <v>653</v>
       </c>
       <c r="B68" s="1">
-        <v>2700</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B69" s="1">
-        <v>3780</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>582</v>
+        <v>399</v>
       </c>
       <c r="B70" s="1">
-        <v>5400</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B71" s="1">
-        <v>5400</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="B72" s="1">
-        <v>4320</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>554</v>
+        <v>401</v>
       </c>
       <c r="B73" s="1">
-        <v>4320</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>555</v>
+        <v>588</v>
       </c>
       <c r="B74" s="1">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>644</v>
+        <v>554</v>
       </c>
       <c r="B75" s="1">
-        <v>3780</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>645</v>
+        <v>555</v>
       </c>
       <c r="B76" s="1">
-        <v>2700</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>403</v>
+        <v>644</v>
       </c>
       <c r="B77" s="1">
-        <v>4320</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>546</v>
+        <v>645</v>
       </c>
       <c r="B78" s="1">
-        <v>6480</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>556</v>
+        <v>403</v>
       </c>
       <c r="B79" s="1">
-        <v>10800</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="B80" s="1">
-        <v>5400</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
+        <v>556</v>
+      </c>
+      <c r="B81" s="1">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>557</v>
+      </c>
+      <c r="B82" s="1">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
         <v>558</v>
       </c>
-      <c r="B81" s="1">
-        <v>1620</v>
+      <c r="B83" s="1">
+        <v>1650</v>
       </c>
     </row>
   </sheetData>

--- a/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\550 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\560 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40CDD40-99ED-4CA9-9F39-AF25C9DC73B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16E5369-0296-4E1A-9A06-423ED8C364D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3034,7 +3034,7 @@
         <v>166</v>
       </c>
       <c r="B2" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3042,7 +3042,7 @@
         <v>421</v>
       </c>
       <c r="B3" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3050,7 +3050,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3058,7 +3058,7 @@
         <v>459</v>
       </c>
       <c r="B5" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3066,7 +3066,7 @@
         <v>460</v>
       </c>
       <c r="B6" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3074,7 +3074,7 @@
         <v>593</v>
       </c>
       <c r="B7" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3082,7 +3082,7 @@
         <v>168</v>
       </c>
       <c r="B8" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3090,7 +3090,7 @@
         <v>461</v>
       </c>
       <c r="B9" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3098,7 +3098,7 @@
         <v>169</v>
       </c>
       <c r="B10" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3106,7 +3106,7 @@
         <v>170</v>
       </c>
       <c r="B11" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3114,7 +3114,7 @@
         <v>171</v>
       </c>
       <c r="B12" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3122,7 +3122,7 @@
         <v>174</v>
       </c>
       <c r="B13" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3130,7 +3130,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3138,7 +3138,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="1">
-        <v>60500</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3146,7 +3146,7 @@
         <v>666</v>
       </c>
       <c r="B16" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3154,7 +3154,7 @@
         <v>175</v>
       </c>
       <c r="B17" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3162,7 +3162,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3170,7 +3170,7 @@
         <v>589</v>
       </c>
       <c r="B19" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3178,7 +3178,7 @@
         <v>462</v>
       </c>
       <c r="B20" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3186,7 +3186,7 @@
         <v>177</v>
       </c>
       <c r="B21" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3194,7 +3194,7 @@
         <v>178</v>
       </c>
       <c r="B22" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3202,7 +3202,7 @@
         <v>179</v>
       </c>
       <c r="B23" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3210,7 +3210,7 @@
         <v>550</v>
       </c>
       <c r="B24" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3218,7 +3218,7 @@
         <v>180</v>
       </c>
       <c r="B25" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3226,7 +3226,7 @@
         <v>181</v>
       </c>
       <c r="B26" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3234,7 +3234,7 @@
         <v>182</v>
       </c>
       <c r="B27" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3242,7 +3242,7 @@
         <v>183</v>
       </c>
       <c r="B28" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3250,7 +3250,7 @@
         <v>184</v>
       </c>
       <c r="B29" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3258,7 +3258,7 @@
         <v>185</v>
       </c>
       <c r="B30" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3266,7 +3266,7 @@
         <v>186</v>
       </c>
       <c r="B31" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3274,7 +3274,7 @@
         <v>187</v>
       </c>
       <c r="B32" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3282,7 +3282,7 @@
         <v>188</v>
       </c>
       <c r="B33" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3290,7 +3290,7 @@
         <v>606</v>
       </c>
       <c r="B34" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3298,7 +3298,7 @@
         <v>569</v>
       </c>
       <c r="B35" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3306,7 +3306,7 @@
         <v>594</v>
       </c>
       <c r="B36" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3314,7 +3314,7 @@
         <v>823</v>
       </c>
       <c r="B37" s="1">
-        <v>46750</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3322,7 +3322,7 @@
         <v>430</v>
       </c>
       <c r="B38" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3330,7 +3330,7 @@
         <v>163</v>
       </c>
       <c r="B39" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3338,7 +3338,7 @@
         <v>647</v>
       </c>
       <c r="B40" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3346,7 +3346,7 @@
         <v>581</v>
       </c>
       <c r="B41" s="1">
-        <v>60500</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3354,7 +3354,7 @@
         <v>648</v>
       </c>
       <c r="B42" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3362,7 +3362,7 @@
         <v>189</v>
       </c>
       <c r="B43" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3370,7 +3370,7 @@
         <v>419</v>
       </c>
       <c r="B44" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3378,7 +3378,7 @@
         <v>408</v>
       </c>
       <c r="B45" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3386,7 +3386,7 @@
         <v>729</v>
       </c>
       <c r="B46" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3394,7 +3394,7 @@
         <v>730</v>
       </c>
       <c r="B47" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3402,7 +3402,7 @@
         <v>190</v>
       </c>
       <c r="B48" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3410,7 +3410,7 @@
         <v>191</v>
       </c>
       <c r="B49" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3418,7 +3418,7 @@
         <v>192</v>
       </c>
       <c r="B50" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3426,7 +3426,7 @@
         <v>193</v>
       </c>
       <c r="B51" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3434,7 +3434,7 @@
         <v>692</v>
       </c>
       <c r="B52" s="1">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3442,7 +3442,7 @@
         <v>194</v>
       </c>
       <c r="B53" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3450,7 +3450,7 @@
         <v>406</v>
       </c>
       <c r="B54" s="1">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3458,7 +3458,7 @@
         <v>402</v>
       </c>
       <c r="B55" s="1">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3466,7 +3466,7 @@
         <v>429</v>
       </c>
       <c r="B56" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3474,7 +3474,7 @@
         <v>195</v>
       </c>
       <c r="B57" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3482,7 +3482,7 @@
         <v>196</v>
       </c>
       <c r="B58" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3490,7 +3490,7 @@
         <v>197</v>
       </c>
       <c r="B59" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3498,7 +3498,7 @@
         <v>595</v>
       </c>
       <c r="B60" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3506,7 +3506,7 @@
         <v>596</v>
       </c>
       <c r="B61" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3514,7 +3514,7 @@
         <v>198</v>
       </c>
       <c r="B62" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3522,7 +3522,7 @@
         <v>199</v>
       </c>
       <c r="B63" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3530,7 +3530,7 @@
         <v>200</v>
       </c>
       <c r="B64" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3538,7 +3538,7 @@
         <v>201</v>
       </c>
       <c r="B65" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3546,7 +3546,7 @@
         <v>202</v>
       </c>
       <c r="B66" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3554,7 +3554,7 @@
         <v>203</v>
       </c>
       <c r="B67" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3562,7 +3562,7 @@
         <v>204</v>
       </c>
       <c r="B68" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3570,7 +3570,7 @@
         <v>205</v>
       </c>
       <c r="B69" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3578,7 +3578,7 @@
         <v>206</v>
       </c>
       <c r="B70" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3586,7 +3586,7 @@
         <v>208</v>
       </c>
       <c r="B71" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3594,7 +3594,7 @@
         <v>212</v>
       </c>
       <c r="B72" s="1">
-        <v>1100</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3602,7 +3602,7 @@
         <v>209</v>
       </c>
       <c r="B73" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3610,7 +3610,7 @@
         <v>210</v>
       </c>
       <c r="B74" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3618,7 +3618,7 @@
         <v>211</v>
       </c>
       <c r="B75" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3626,7 +3626,7 @@
         <v>476</v>
       </c>
       <c r="B76" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3634,7 +3634,7 @@
         <v>207</v>
       </c>
       <c r="B77" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3642,7 +3642,7 @@
         <v>213</v>
       </c>
       <c r="B78" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3650,7 +3650,7 @@
         <v>214</v>
       </c>
       <c r="B79" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3658,7 +3658,7 @@
         <v>215</v>
       </c>
       <c r="B80" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3666,7 +3666,7 @@
         <v>216</v>
       </c>
       <c r="B81" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3674,7 +3674,7 @@
         <v>217</v>
       </c>
       <c r="B82" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3682,7 +3682,7 @@
         <v>218</v>
       </c>
       <c r="B83" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3690,7 +3690,7 @@
         <v>219</v>
       </c>
       <c r="B84" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3698,7 +3698,7 @@
         <v>220</v>
       </c>
       <c r="B85" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3706,7 +3706,7 @@
         <v>607</v>
       </c>
       <c r="B86" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3714,7 +3714,7 @@
         <v>221</v>
       </c>
       <c r="B87" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3722,7 +3722,7 @@
         <v>608</v>
       </c>
       <c r="B88" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3730,7 +3730,7 @@
         <v>417</v>
       </c>
       <c r="B89" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3738,7 +3738,7 @@
         <v>418</v>
       </c>
       <c r="B90" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3746,7 +3746,7 @@
         <v>222</v>
       </c>
       <c r="B91" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3754,7 +3754,7 @@
         <v>223</v>
       </c>
       <c r="B92" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3762,7 +3762,7 @@
         <v>224</v>
       </c>
       <c r="B93" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3770,7 +3770,7 @@
         <v>225</v>
       </c>
       <c r="B94" s="1">
-        <v>192500</v>
+        <v>196000</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3778,7 +3778,7 @@
         <v>226</v>
       </c>
       <c r="B95" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3786,7 +3786,7 @@
         <v>824</v>
       </c>
       <c r="B96" s="1">
-        <v>165000</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3794,7 +3794,7 @@
         <v>227</v>
       </c>
       <c r="B97" s="1">
-        <v>154000</v>
+        <v>156800</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3802,7 +3802,7 @@
         <v>228</v>
       </c>
       <c r="B98" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3810,7 +3810,7 @@
         <v>551</v>
       </c>
       <c r="B99" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3818,7 +3818,7 @@
         <v>667</v>
       </c>
       <c r="B100" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3826,7 +3826,7 @@
         <v>409</v>
       </c>
       <c r="B101" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3834,7 +3834,7 @@
         <v>229</v>
       </c>
       <c r="B102" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3842,7 +3842,7 @@
         <v>230</v>
       </c>
       <c r="B103" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3850,7 +3850,7 @@
         <v>231</v>
       </c>
       <c r="B104" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3858,7 +3858,7 @@
         <v>424</v>
       </c>
       <c r="B105" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3866,7 +3866,7 @@
         <v>232</v>
       </c>
       <c r="B106" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3874,7 +3874,7 @@
         <v>570</v>
       </c>
       <c r="B107" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3882,7 +3882,7 @@
         <v>483</v>
       </c>
       <c r="B108" s="1">
-        <v>137500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3890,7 +3890,7 @@
         <v>587</v>
       </c>
       <c r="B109" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3898,7 +3898,7 @@
         <v>233</v>
       </c>
       <c r="B110" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3906,7 +3906,7 @@
         <v>234</v>
       </c>
       <c r="B111" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3914,7 +3914,7 @@
         <v>731</v>
       </c>
       <c r="B112" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3922,7 +3922,7 @@
         <v>717</v>
       </c>
       <c r="B113" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3930,7 +3930,7 @@
         <v>571</v>
       </c>
       <c r="B114" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3938,7 +3938,7 @@
         <v>590</v>
       </c>
       <c r="B115" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3946,7 +3946,7 @@
         <v>235</v>
       </c>
       <c r="B116" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3954,7 +3954,7 @@
         <v>732</v>
       </c>
       <c r="B117" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3962,7 +3962,7 @@
         <v>236</v>
       </c>
       <c r="B118" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3970,7 +3970,7 @@
         <v>733</v>
       </c>
       <c r="B119" s="1">
-        <v>1100</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3978,7 +3978,7 @@
         <v>237</v>
       </c>
       <c r="B120" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3986,7 +3986,7 @@
         <v>410</v>
       </c>
       <c r="B121" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3994,7 +3994,7 @@
         <v>238</v>
       </c>
       <c r="B122" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4002,7 +4002,7 @@
         <v>239</v>
       </c>
       <c r="B123" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4010,7 +4010,7 @@
         <v>240</v>
       </c>
       <c r="B124" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4018,7 +4018,7 @@
         <v>241</v>
       </c>
       <c r="B125" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4026,7 +4026,7 @@
         <v>242</v>
       </c>
       <c r="B126" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4034,7 +4034,7 @@
         <v>243</v>
       </c>
       <c r="B127" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4042,7 +4042,7 @@
         <v>668</v>
       </c>
       <c r="B128" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4050,7 +4050,7 @@
         <v>669</v>
       </c>
       <c r="B129" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4058,7 +4058,7 @@
         <v>431</v>
       </c>
       <c r="B130" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4066,7 +4066,7 @@
         <v>244</v>
       </c>
       <c r="B131" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4074,7 +4074,7 @@
         <v>597</v>
       </c>
       <c r="B132" s="1">
-        <v>236500</v>
+        <v>240800</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4082,7 +4082,7 @@
         <v>245</v>
       </c>
       <c r="B133" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4090,7 +4090,7 @@
         <v>456</v>
       </c>
       <c r="B134" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4098,7 +4098,7 @@
         <v>457</v>
       </c>
       <c r="B135" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4106,7 +4106,7 @@
         <v>458</v>
       </c>
       <c r="B136" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4114,7 +4114,7 @@
         <v>246</v>
       </c>
       <c r="B137" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4122,7 +4122,7 @@
         <v>247</v>
       </c>
       <c r="B138" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4130,7 +4130,7 @@
         <v>248</v>
       </c>
       <c r="B139" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4138,7 +4138,7 @@
         <v>250</v>
       </c>
       <c r="B140" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4146,7 +4146,7 @@
         <v>420</v>
       </c>
       <c r="B141" s="1">
-        <v>137500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4154,7 +4154,7 @@
         <v>14</v>
       </c>
       <c r="B142" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4162,7 +4162,7 @@
         <v>602</v>
       </c>
       <c r="B143" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4170,7 +4170,7 @@
         <v>249</v>
       </c>
       <c r="B144" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4178,7 +4178,7 @@
         <v>552</v>
       </c>
       <c r="B145" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4186,7 +4186,7 @@
         <v>251</v>
       </c>
       <c r="B146" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4194,7 +4194,7 @@
         <v>825</v>
       </c>
       <c r="B147" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4202,7 +4202,7 @@
         <v>252</v>
       </c>
       <c r="B148" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4210,7 +4210,7 @@
         <v>253</v>
       </c>
       <c r="B149" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4218,7 +4218,7 @@
         <v>598</v>
       </c>
       <c r="B150" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4226,7 +4226,7 @@
         <v>254</v>
       </c>
       <c r="B151" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4234,7 +4234,7 @@
         <v>255</v>
       </c>
       <c r="B152" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4242,7 +4242,7 @@
         <v>256</v>
       </c>
       <c r="B153" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4250,7 +4250,7 @@
         <v>257</v>
       </c>
       <c r="B154" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4258,7 +4258,7 @@
         <v>258</v>
       </c>
       <c r="B155" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4266,7 +4266,7 @@
         <v>261</v>
       </c>
       <c r="B156" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4274,7 +4274,7 @@
         <v>262</v>
       </c>
       <c r="B157" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4282,7 +4282,7 @@
         <v>263</v>
       </c>
       <c r="B158" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4290,7 +4290,7 @@
         <v>404</v>
       </c>
       <c r="B159" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4298,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="B160" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4306,7 +4306,7 @@
         <v>463</v>
       </c>
       <c r="B161" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4314,7 +4314,7 @@
         <v>260</v>
       </c>
       <c r="B162" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4322,7 +4322,7 @@
         <v>264</v>
       </c>
       <c r="B163" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4330,7 +4330,7 @@
         <v>689</v>
       </c>
       <c r="B164" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4338,7 +4338,7 @@
         <v>641</v>
       </c>
       <c r="B165" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4346,7 +4346,7 @@
         <v>642</v>
       </c>
       <c r="B166" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4354,7 +4354,7 @@
         <v>603</v>
       </c>
       <c r="B167" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4362,7 +4362,7 @@
         <v>604</v>
       </c>
       <c r="B168" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4370,7 +4370,7 @@
         <v>484</v>
       </c>
       <c r="B169" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4378,7 +4378,7 @@
         <v>265</v>
       </c>
       <c r="B170" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4386,7 +4386,7 @@
         <v>609</v>
       </c>
       <c r="B171" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4394,7 +4394,7 @@
         <v>734</v>
       </c>
       <c r="B172" s="1">
-        <v>2200</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4402,7 +4402,7 @@
         <v>735</v>
       </c>
       <c r="B173" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4410,7 +4410,7 @@
         <v>266</v>
       </c>
       <c r="B174" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4418,7 +4418,7 @@
         <v>267</v>
       </c>
       <c r="B175" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4426,7 +4426,7 @@
         <v>268</v>
       </c>
       <c r="B176" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4434,7 +4434,7 @@
         <v>269</v>
       </c>
       <c r="B177" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4442,7 +4442,7 @@
         <v>270</v>
       </c>
       <c r="B178" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4450,7 +4450,7 @@
         <v>271</v>
       </c>
       <c r="B179" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4458,7 +4458,7 @@
         <v>272</v>
       </c>
       <c r="B180" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4466,7 +4466,7 @@
         <v>273</v>
       </c>
       <c r="B181" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4474,7 +4474,7 @@
         <v>422</v>
       </c>
       <c r="B182" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4482,7 +4482,7 @@
         <v>423</v>
       </c>
       <c r="B183" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4490,7 +4490,7 @@
         <v>610</v>
       </c>
       <c r="B184" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4498,7 +4498,7 @@
         <v>611</v>
       </c>
       <c r="B185" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4506,7 +4506,7 @@
         <v>612</v>
       </c>
       <c r="B186" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4514,7 +4514,7 @@
         <v>613</v>
       </c>
       <c r="B187" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4522,7 +4522,7 @@
         <v>614</v>
       </c>
       <c r="B188" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4530,7 +4530,7 @@
         <v>615</v>
       </c>
       <c r="B189" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4538,7 +4538,7 @@
         <v>274</v>
       </c>
       <c r="B190" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4546,7 +4546,7 @@
         <v>276</v>
       </c>
       <c r="B191" s="1">
-        <v>1100</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4554,7 +4554,7 @@
         <v>275</v>
       </c>
       <c r="B192" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4562,7 +4562,7 @@
         <v>616</v>
       </c>
       <c r="B193" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4570,7 +4570,7 @@
         <v>277</v>
       </c>
       <c r="B194" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4578,7 +4578,7 @@
         <v>464</v>
       </c>
       <c r="B195" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4586,7 +4586,7 @@
         <v>278</v>
       </c>
       <c r="B196" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4594,7 +4594,7 @@
         <v>736</v>
       </c>
       <c r="B197" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4602,7 +4602,7 @@
         <v>391</v>
       </c>
       <c r="B198" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4610,7 +4610,7 @@
         <v>396</v>
       </c>
       <c r="B199" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4618,7 +4618,7 @@
         <v>466</v>
       </c>
       <c r="B200" s="1">
-        <v>176000</v>
+        <v>179200</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4626,7 +4626,7 @@
         <v>279</v>
       </c>
       <c r="B201" s="1">
-        <v>286000</v>
+        <v>291200</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4634,7 +4634,7 @@
         <v>649</v>
       </c>
       <c r="B202" s="1">
-        <v>291500</v>
+        <v>296800</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4642,7 +4642,7 @@
         <v>280</v>
       </c>
       <c r="B203" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4650,7 +4650,7 @@
         <v>696</v>
       </c>
       <c r="B204" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4658,7 +4658,7 @@
         <v>737</v>
       </c>
       <c r="B205" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4666,7 +4666,7 @@
         <v>411</v>
       </c>
       <c r="B206" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4674,7 +4674,7 @@
         <v>281</v>
       </c>
       <c r="B207" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4682,7 +4682,7 @@
         <v>412</v>
       </c>
       <c r="B208" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4690,7 +4690,7 @@
         <v>282</v>
       </c>
       <c r="B209" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4698,7 +4698,7 @@
         <v>283</v>
       </c>
       <c r="B210" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4706,7 +4706,7 @@
         <v>284</v>
       </c>
       <c r="B211" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4714,7 +4714,7 @@
         <v>285</v>
       </c>
       <c r="B212" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4722,7 +4722,7 @@
         <v>286</v>
       </c>
       <c r="B213" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4730,7 +4730,7 @@
         <v>287</v>
       </c>
       <c r="B214" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4738,7 +4738,7 @@
         <v>288</v>
       </c>
       <c r="B215" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4746,7 +4746,7 @@
         <v>289</v>
       </c>
       <c r="B216" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4754,7 +4754,7 @@
         <v>553</v>
       </c>
       <c r="B217" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4762,7 +4762,7 @@
         <v>290</v>
       </c>
       <c r="B218" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4770,7 +4770,7 @@
         <v>738</v>
       </c>
       <c r="B219" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4778,7 +4778,7 @@
         <v>739</v>
       </c>
       <c r="B220" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4786,7 +4786,7 @@
         <v>291</v>
       </c>
       <c r="B221" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4794,7 +4794,7 @@
         <v>292</v>
       </c>
       <c r="B222" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4802,7 +4802,7 @@
         <v>293</v>
       </c>
       <c r="B223" s="1">
-        <v>154000</v>
+        <v>156800</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4810,7 +4810,7 @@
         <v>294</v>
       </c>
       <c r="B224" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4818,7 +4818,7 @@
         <v>572</v>
       </c>
       <c r="B225" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4826,7 +4826,7 @@
         <v>670</v>
       </c>
       <c r="B226" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4834,7 +4834,7 @@
         <v>295</v>
       </c>
       <c r="B227" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4842,7 +4842,7 @@
         <v>671</v>
       </c>
       <c r="B228" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4850,7 +4850,7 @@
         <v>296</v>
       </c>
       <c r="B229" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4858,7 +4858,7 @@
         <v>718</v>
       </c>
       <c r="B230" s="1">
-        <v>30250</v>
+        <v>30800</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4866,7 +4866,7 @@
         <v>719</v>
       </c>
       <c r="B231" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4874,7 +4874,7 @@
         <v>720</v>
       </c>
       <c r="B232" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4882,7 +4882,7 @@
         <v>721</v>
       </c>
       <c r="B233" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4890,7 +4890,7 @@
         <v>617</v>
       </c>
       <c r="B234" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4898,7 +4898,7 @@
         <v>297</v>
       </c>
       <c r="B235" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4906,7 +4906,7 @@
         <v>573</v>
       </c>
       <c r="B236" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4914,7 +4914,7 @@
         <v>298</v>
       </c>
       <c r="B237" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4922,7 +4922,7 @@
         <v>299</v>
       </c>
       <c r="B238" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4930,7 +4930,7 @@
         <v>300</v>
       </c>
       <c r="B239" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4938,7 +4938,7 @@
         <v>301</v>
       </c>
       <c r="B240" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4946,7 +4946,7 @@
         <v>302</v>
       </c>
       <c r="B241" s="1">
-        <v>165000</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4954,7 +4954,7 @@
         <v>672</v>
       </c>
       <c r="B242" s="1">
-        <v>165000</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4962,7 +4962,7 @@
         <v>303</v>
       </c>
       <c r="B243" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4970,7 +4970,7 @@
         <v>740</v>
       </c>
       <c r="B244" s="1">
-        <v>121000</v>
+        <v>123200</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4978,7 +4978,7 @@
         <v>304</v>
       </c>
       <c r="B245" s="1">
-        <v>60500</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4986,7 +4986,7 @@
         <v>305</v>
       </c>
       <c r="B246" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4994,7 +4994,7 @@
         <v>306</v>
       </c>
       <c r="B247" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5002,7 +5002,7 @@
         <v>618</v>
       </c>
       <c r="B248" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5010,7 +5010,7 @@
         <v>307</v>
       </c>
       <c r="B249" s="1">
-        <v>93500</v>
+        <v>95200</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5018,7 +5018,7 @@
         <v>308</v>
       </c>
       <c r="B250" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5026,7 +5026,7 @@
         <v>309</v>
       </c>
       <c r="B251" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5034,7 +5034,7 @@
         <v>310</v>
       </c>
       <c r="B252" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5042,7 +5042,7 @@
         <v>690</v>
       </c>
       <c r="B253" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5050,7 +5050,7 @@
         <v>311</v>
       </c>
       <c r="B254" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5058,7 +5058,7 @@
         <v>312</v>
       </c>
       <c r="B255" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5066,7 +5066,7 @@
         <v>313</v>
       </c>
       <c r="B256" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5074,7 +5074,7 @@
         <v>467</v>
       </c>
       <c r="B257" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5082,7 +5082,7 @@
         <v>741</v>
       </c>
       <c r="B258" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5090,7 +5090,7 @@
         <v>742</v>
       </c>
       <c r="B259" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5098,7 +5098,7 @@
         <v>468</v>
       </c>
       <c r="B260" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5106,7 +5106,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5114,7 +5114,7 @@
         <v>315</v>
       </c>
       <c r="B262" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5122,7 +5122,7 @@
         <v>316</v>
       </c>
       <c r="B263" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5130,7 +5130,7 @@
         <v>414</v>
       </c>
       <c r="B264" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5138,7 +5138,7 @@
         <v>317</v>
       </c>
       <c r="B265" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5146,7 +5146,7 @@
         <v>318</v>
       </c>
       <c r="B266" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5154,7 +5154,7 @@
         <v>605</v>
       </c>
       <c r="B267" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5162,7 +5162,7 @@
         <v>319</v>
       </c>
       <c r="B268" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5170,7 +5170,7 @@
         <v>320</v>
       </c>
       <c r="B269" s="1">
-        <v>165000</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5178,7 +5178,7 @@
         <v>321</v>
       </c>
       <c r="B270" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5186,7 +5186,7 @@
         <v>322</v>
       </c>
       <c r="B271" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5194,7 +5194,7 @@
         <v>323</v>
       </c>
       <c r="B272" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5202,7 +5202,7 @@
         <v>324</v>
       </c>
       <c r="B273" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5210,7 +5210,7 @@
         <v>325</v>
       </c>
       <c r="B274" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5218,7 +5218,7 @@
         <v>326</v>
       </c>
       <c r="B275" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5226,7 +5226,7 @@
         <v>327</v>
       </c>
       <c r="B276" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5234,7 +5234,7 @@
         <v>328</v>
       </c>
       <c r="B277" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5242,7 +5242,7 @@
         <v>329</v>
       </c>
       <c r="B278" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5250,7 +5250,7 @@
         <v>330</v>
       </c>
       <c r="B279" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5258,7 +5258,7 @@
         <v>331</v>
       </c>
       <c r="B280" s="1">
-        <v>71500</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5266,7 +5266,7 @@
         <v>332</v>
       </c>
       <c r="B281" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5274,7 +5274,7 @@
         <v>333</v>
       </c>
       <c r="B282" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5282,7 +5282,7 @@
         <v>334</v>
       </c>
       <c r="B283" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5290,7 +5290,7 @@
         <v>574</v>
       </c>
       <c r="B284" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5298,7 +5298,7 @@
         <v>599</v>
       </c>
       <c r="B285" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5306,7 +5306,7 @@
         <v>600</v>
       </c>
       <c r="B286" s="1">
-        <v>52250</v>
+        <v>53200</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5314,7 +5314,7 @@
         <v>743</v>
       </c>
       <c r="B287" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5322,7 +5322,7 @@
         <v>619</v>
       </c>
       <c r="B288" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5330,7 +5330,7 @@
         <v>335</v>
       </c>
       <c r="B289" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5338,7 +5338,7 @@
         <v>620</v>
       </c>
       <c r="B290" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5346,7 +5346,7 @@
         <v>336</v>
       </c>
       <c r="B291" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5354,7 +5354,7 @@
         <v>337</v>
       </c>
       <c r="B292" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5362,7 +5362,7 @@
         <v>338</v>
       </c>
       <c r="B293" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5370,7 +5370,7 @@
         <v>339</v>
       </c>
       <c r="B294" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5378,7 +5378,7 @@
         <v>340</v>
       </c>
       <c r="B295" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5386,7 +5386,7 @@
         <v>341</v>
       </c>
       <c r="B296" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5394,7 +5394,7 @@
         <v>342</v>
       </c>
       <c r="B297" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5402,7 +5402,7 @@
         <v>343</v>
       </c>
       <c r="B298" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5410,7 +5410,7 @@
         <v>415</v>
       </c>
       <c r="B299" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5418,7 +5418,7 @@
         <v>416</v>
       </c>
       <c r="B300" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5426,7 +5426,7 @@
         <v>601</v>
       </c>
       <c r="B301" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5434,7 +5434,7 @@
         <v>344</v>
       </c>
       <c r="B302" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5442,7 +5442,7 @@
         <v>345</v>
       </c>
       <c r="B303" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5450,7 +5450,7 @@
         <v>346</v>
       </c>
       <c r="B304" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5458,7 +5458,7 @@
         <v>347</v>
       </c>
       <c r="B305" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5466,7 +5466,7 @@
         <v>348</v>
       </c>
       <c r="B306" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5474,7 +5474,7 @@
         <v>349</v>
       </c>
       <c r="B307" s="1">
-        <v>2200</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5482,7 +5482,7 @@
         <v>744</v>
       </c>
       <c r="B308" s="1">
-        <v>1100</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5490,7 +5490,7 @@
         <v>673</v>
       </c>
       <c r="B309" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5498,7 +5498,7 @@
         <v>350</v>
       </c>
       <c r="B310" s="1">
-        <v>41250</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5506,7 +5506,7 @@
         <v>351</v>
       </c>
       <c r="B311" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5514,7 +5514,7 @@
         <v>352</v>
       </c>
       <c r="B312" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5522,7 +5522,7 @@
         <v>575</v>
       </c>
       <c r="B313" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5530,7 +5530,7 @@
         <v>353</v>
       </c>
       <c r="B314" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5538,7 +5538,7 @@
         <v>354</v>
       </c>
       <c r="B315" s="1">
-        <v>137500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5546,7 +5546,7 @@
         <v>407</v>
       </c>
       <c r="B316" s="1">
-        <v>302500</v>
+        <v>308000</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5554,7 +5554,7 @@
         <v>355</v>
       </c>
       <c r="B317" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5562,7 +5562,7 @@
         <v>356</v>
       </c>
       <c r="B318" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5570,7 +5570,7 @@
         <v>576</v>
       </c>
       <c r="B319" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5578,7 +5578,7 @@
         <v>357</v>
       </c>
       <c r="B320" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5586,7 +5586,7 @@
         <v>358</v>
       </c>
       <c r="B321" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5594,7 +5594,7 @@
         <v>651</v>
       </c>
       <c r="B322" s="1">
-        <v>2200</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5602,7 +5602,7 @@
         <v>577</v>
       </c>
       <c r="B323" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5610,7 +5610,7 @@
         <v>588</v>
       </c>
       <c r="B324" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5618,7 +5618,7 @@
         <v>359</v>
       </c>
       <c r="B325" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5626,7 +5626,7 @@
         <v>360</v>
       </c>
       <c r="B326" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5634,7 +5634,7 @@
         <v>361</v>
       </c>
       <c r="B327" s="1">
-        <v>2200</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5642,7 +5642,7 @@
         <v>362</v>
       </c>
       <c r="B328" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5650,7 +5650,7 @@
         <v>363</v>
       </c>
       <c r="B329" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5658,7 +5658,7 @@
         <v>364</v>
       </c>
       <c r="B330" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5666,7 +5666,7 @@
         <v>365</v>
       </c>
       <c r="B331" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5674,7 +5674,7 @@
         <v>403</v>
       </c>
       <c r="B332" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5682,7 +5682,7 @@
         <v>546</v>
       </c>
       <c r="B333" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5690,7 +5690,7 @@
         <v>822</v>
       </c>
       <c r="B334" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5698,7 +5698,7 @@
         <v>366</v>
       </c>
       <c r="B335" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5706,7 +5706,7 @@
         <v>556</v>
       </c>
       <c r="B336" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5714,7 +5714,7 @@
         <v>557</v>
       </c>
       <c r="B337" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5722,7 +5722,7 @@
         <v>367</v>
       </c>
       <c r="B338" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5730,7 +5730,7 @@
         <v>368</v>
       </c>
       <c r="B339" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5738,7 +5738,7 @@
         <v>369</v>
       </c>
       <c r="B340" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5746,7 +5746,7 @@
         <v>370</v>
       </c>
       <c r="B341" s="1">
-        <v>1100</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5754,7 +5754,7 @@
         <v>371</v>
       </c>
       <c r="B342" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5762,7 +5762,7 @@
         <v>372</v>
       </c>
       <c r="B343" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5770,7 +5770,7 @@
         <v>373</v>
       </c>
       <c r="B344" s="1">
-        <v>2200</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5778,7 +5778,7 @@
         <v>413</v>
       </c>
       <c r="B345" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5786,7 +5786,7 @@
         <v>465</v>
       </c>
       <c r="B346" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5794,7 +5794,7 @@
         <v>621</v>
       </c>
       <c r="B347" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5802,7 +5802,7 @@
         <v>374</v>
       </c>
       <c r="B348" s="1">
-        <v>1100</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5810,7 +5810,7 @@
         <v>485</v>
       </c>
       <c r="B349" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5818,7 +5818,7 @@
         <v>469</v>
       </c>
       <c r="B350" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5826,7 +5826,7 @@
         <v>375</v>
       </c>
       <c r="B351" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5834,7 +5834,7 @@
         <v>674</v>
       </c>
       <c r="B352" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5842,7 +5842,7 @@
         <v>675</v>
       </c>
       <c r="B353" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5850,7 +5850,7 @@
         <v>376</v>
       </c>
       <c r="B354" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5858,7 +5858,7 @@
         <v>377</v>
       </c>
       <c r="B355" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5866,7 +5866,7 @@
         <v>378</v>
       </c>
       <c r="B356" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5874,7 +5874,7 @@
         <v>622</v>
       </c>
       <c r="B357" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5882,7 +5882,7 @@
         <v>379</v>
       </c>
       <c r="B358" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5890,7 +5890,7 @@
         <v>470</v>
       </c>
       <c r="B359" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5898,7 +5898,7 @@
         <v>471</v>
       </c>
       <c r="B360" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5906,7 +5906,7 @@
         <v>676</v>
       </c>
       <c r="B361" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5914,7 +5914,7 @@
         <v>380</v>
       </c>
       <c r="B362" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5922,7 +5922,7 @@
         <v>381</v>
       </c>
       <c r="B363" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5930,7 +5930,7 @@
         <v>454</v>
       </c>
       <c r="B364" s="1">
-        <v>2200</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5938,7 +5938,7 @@
         <v>382</v>
       </c>
       <c r="B365" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
   </sheetData>
@@ -5968,7 +5968,7 @@
         <v>486</v>
       </c>
       <c r="B2" s="1">
-        <v>77000</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5976,7 +5976,7 @@
         <v>123</v>
       </c>
       <c r="B3" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5984,7 +5984,7 @@
         <v>757</v>
       </c>
       <c r="B4" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5992,7 +5992,7 @@
         <v>578</v>
       </c>
       <c r="B5" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6000,7 +6000,7 @@
         <v>164</v>
       </c>
       <c r="B6" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6008,7 +6008,7 @@
         <v>579</v>
       </c>
       <c r="B7" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6016,7 +6016,7 @@
         <v>589</v>
       </c>
       <c r="B8" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6024,7 +6024,7 @@
         <v>758</v>
       </c>
       <c r="B9" s="1">
-        <v>71500</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6032,7 +6032,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6040,7 +6040,7 @@
         <v>759</v>
       </c>
       <c r="B11" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6048,7 +6048,7 @@
         <v>124</v>
       </c>
       <c r="B12" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6056,7 +6056,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6064,7 +6064,7 @@
         <v>823</v>
       </c>
       <c r="B14" s="1">
-        <v>46750</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6072,7 +6072,7 @@
         <v>430</v>
       </c>
       <c r="B15" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6080,7 +6080,7 @@
         <v>163</v>
       </c>
       <c r="B16" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6088,7 +6088,7 @@
         <v>647</v>
       </c>
       <c r="B17" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6096,7 +6096,7 @@
         <v>581</v>
       </c>
       <c r="B18" s="1">
-        <v>60500</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6104,7 +6104,7 @@
         <v>648</v>
       </c>
       <c r="B19" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6112,7 +6112,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6120,7 +6120,7 @@
         <v>125</v>
       </c>
       <c r="B21" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6128,7 +6128,7 @@
         <v>478</v>
       </c>
       <c r="B22" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6136,7 +6136,7 @@
         <v>36</v>
       </c>
       <c r="B23" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6144,7 +6144,7 @@
         <v>487</v>
       </c>
       <c r="B24" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6152,7 +6152,7 @@
         <v>488</v>
       </c>
       <c r="B25" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6160,7 +6160,7 @@
         <v>692</v>
       </c>
       <c r="B26" s="1">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6168,7 +6168,7 @@
         <v>406</v>
       </c>
       <c r="B27" s="1">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6176,7 +6176,7 @@
         <v>402</v>
       </c>
       <c r="B28" s="1">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6184,7 +6184,7 @@
         <v>439</v>
       </c>
       <c r="B29" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6192,7 +6192,7 @@
         <v>760</v>
       </c>
       <c r="B30" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6200,7 +6200,7 @@
         <v>489</v>
       </c>
       <c r="B31" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6208,7 +6208,7 @@
         <v>490</v>
       </c>
       <c r="B32" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6216,7 +6216,7 @@
         <v>761</v>
       </c>
       <c r="B33" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6224,7 +6224,7 @@
         <v>12</v>
       </c>
       <c r="B34" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6232,7 +6232,7 @@
         <v>762</v>
       </c>
       <c r="B35" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="1">
-        <v>1375</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6248,7 +6248,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6256,7 +6256,7 @@
         <v>434</v>
       </c>
       <c r="B38" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6264,7 +6264,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6272,7 +6272,7 @@
         <v>491</v>
       </c>
       <c r="B40" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6280,7 +6280,7 @@
         <v>479</v>
       </c>
       <c r="B41" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6288,7 +6288,7 @@
         <v>763</v>
       </c>
       <c r="B42" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6296,7 +6296,7 @@
         <v>438</v>
       </c>
       <c r="B43" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6304,7 +6304,7 @@
         <v>440</v>
       </c>
       <c r="B44" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6312,7 +6312,7 @@
         <v>492</v>
       </c>
       <c r="B45" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6320,7 +6320,7 @@
         <v>493</v>
       </c>
       <c r="B46" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6328,7 +6328,7 @@
         <v>494</v>
       </c>
       <c r="B47" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6336,7 +6336,7 @@
         <v>764</v>
       </c>
       <c r="B48" s="1">
-        <v>192500</v>
+        <v>196000</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -6344,7 +6344,7 @@
         <v>551</v>
       </c>
       <c r="B49" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -6352,7 +6352,7 @@
         <v>765</v>
       </c>
       <c r="B50" s="1">
-        <v>71500</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -6360,7 +6360,7 @@
         <v>751</v>
       </c>
       <c r="B51" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -6368,7 +6368,7 @@
         <v>722</v>
       </c>
       <c r="B52" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -6376,7 +6376,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -6384,7 +6384,7 @@
         <v>766</v>
       </c>
       <c r="B54" s="1">
-        <v>77000</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -6392,7 +6392,7 @@
         <v>495</v>
       </c>
       <c r="B55" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -6400,7 +6400,7 @@
         <v>436</v>
       </c>
       <c r="B56" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -6408,7 +6408,7 @@
         <v>126</v>
       </c>
       <c r="B57" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -6416,7 +6416,7 @@
         <v>496</v>
       </c>
       <c r="B58" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -6424,7 +6424,7 @@
         <v>767</v>
       </c>
       <c r="B59" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -6432,7 +6432,7 @@
         <v>30</v>
       </c>
       <c r="B60" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -6440,7 +6440,7 @@
         <v>427</v>
       </c>
       <c r="B61" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -6448,7 +6448,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -6456,7 +6456,7 @@
         <v>768</v>
       </c>
       <c r="B63" s="1">
-        <v>137500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -6464,7 +6464,7 @@
         <v>769</v>
       </c>
       <c r="B64" s="1">
-        <v>121000</v>
+        <v>123200</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -6472,7 +6472,7 @@
         <v>127</v>
       </c>
       <c r="B65" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -6480,7 +6480,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -6488,7 +6488,7 @@
         <v>116</v>
       </c>
       <c r="B67" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6496,7 +6496,7 @@
         <v>14</v>
       </c>
       <c r="B68" s="1">
-        <v>71500</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6504,7 +6504,7 @@
         <v>770</v>
       </c>
       <c r="B69" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -6512,7 +6512,7 @@
         <v>771</v>
       </c>
       <c r="B70" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -6520,7 +6520,7 @@
         <v>426</v>
       </c>
       <c r="B71" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -6528,7 +6528,7 @@
         <v>552</v>
       </c>
       <c r="B72" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -6536,7 +6536,7 @@
         <v>825</v>
       </c>
       <c r="B73" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -6544,7 +6544,7 @@
         <v>497</v>
       </c>
       <c r="B74" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -6552,7 +6552,7 @@
         <v>498</v>
       </c>
       <c r="B75" s="1">
-        <v>30250</v>
+        <v>30800</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -6560,7 +6560,7 @@
         <v>772</v>
       </c>
       <c r="B76" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -6568,7 +6568,7 @@
         <v>773</v>
       </c>
       <c r="B77" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -6576,7 +6576,7 @@
         <v>586</v>
       </c>
       <c r="B78" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -6584,7 +6584,7 @@
         <v>15</v>
       </c>
       <c r="B79" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -6592,7 +6592,7 @@
         <v>16</v>
       </c>
       <c r="B80" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -6600,7 +6600,7 @@
         <v>580</v>
       </c>
       <c r="B81" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -6608,7 +6608,7 @@
         <v>688</v>
       </c>
       <c r="B82" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -6616,7 +6616,7 @@
         <v>774</v>
       </c>
       <c r="B83" s="1">
-        <v>2200</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -6624,7 +6624,7 @@
         <v>484</v>
       </c>
       <c r="B84" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -6632,7 +6632,7 @@
         <v>775</v>
       </c>
       <c r="B85" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -6640,7 +6640,7 @@
         <v>735</v>
       </c>
       <c r="B86" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -6648,7 +6648,7 @@
         <v>3</v>
       </c>
       <c r="B87" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -6656,7 +6656,7 @@
         <v>17</v>
       </c>
       <c r="B88" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -6664,7 +6664,7 @@
         <v>128</v>
       </c>
       <c r="B89" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -6672,7 +6672,7 @@
         <v>715</v>
       </c>
       <c r="B90" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -6680,7 +6680,7 @@
         <v>499</v>
       </c>
       <c r="B91" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -6688,7 +6688,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -6696,7 +6696,7 @@
         <v>623</v>
       </c>
       <c r="B93" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -6704,7 +6704,7 @@
         <v>776</v>
       </c>
       <c r="B94" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -6712,7 +6712,7 @@
         <v>18</v>
       </c>
       <c r="B95" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -6720,7 +6720,7 @@
         <v>19</v>
       </c>
       <c r="B96" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -6728,7 +6728,7 @@
         <v>500</v>
       </c>
       <c r="B97" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -6736,7 +6736,7 @@
         <v>501</v>
       </c>
       <c r="B98" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -6744,7 +6744,7 @@
         <v>25</v>
       </c>
       <c r="B99" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -6752,7 +6752,7 @@
         <v>553</v>
       </c>
       <c r="B100" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -6760,7 +6760,7 @@
         <v>777</v>
       </c>
       <c r="B101" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -6768,7 +6768,7 @@
         <v>778</v>
       </c>
       <c r="B102" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -6776,7 +6776,7 @@
         <v>779</v>
       </c>
       <c r="B103" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -6784,7 +6784,7 @@
         <v>780</v>
       </c>
       <c r="B104" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -6792,7 +6792,7 @@
         <v>129</v>
       </c>
       <c r="B105" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -6800,7 +6800,7 @@
         <v>502</v>
       </c>
       <c r="B106" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -6808,7 +6808,7 @@
         <v>781</v>
       </c>
       <c r="B107" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -6816,7 +6816,7 @@
         <v>752</v>
       </c>
       <c r="B108" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -6824,7 +6824,7 @@
         <v>723</v>
       </c>
       <c r="B109" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -6832,7 +6832,7 @@
         <v>720</v>
       </c>
       <c r="B110" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -6840,7 +6840,7 @@
         <v>721</v>
       </c>
       <c r="B111" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -6848,7 +6848,7 @@
         <v>503</v>
       </c>
       <c r="B112" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -6856,7 +6856,7 @@
         <v>100</v>
       </c>
       <c r="B113" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -6864,7 +6864,7 @@
         <v>826</v>
       </c>
       <c r="B114" s="1">
-        <v>192500</v>
+        <v>196000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -6872,7 +6872,7 @@
         <v>654</v>
       </c>
       <c r="B115" s="1">
-        <v>192500</v>
+        <v>196000</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -6880,7 +6880,7 @@
         <v>24</v>
       </c>
       <c r="B116" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -6888,7 +6888,7 @@
         <v>782</v>
       </c>
       <c r="B117" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -6896,7 +6896,7 @@
         <v>740</v>
       </c>
       <c r="B118" s="1">
-        <v>121000</v>
+        <v>123200</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -6904,7 +6904,7 @@
         <v>20</v>
       </c>
       <c r="B119" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -6912,7 +6912,7 @@
         <v>433</v>
       </c>
       <c r="B120" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -6920,7 +6920,7 @@
         <v>783</v>
       </c>
       <c r="B121" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -6928,7 +6928,7 @@
         <v>115</v>
       </c>
       <c r="B122" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -6936,7 +6936,7 @@
         <v>504</v>
       </c>
       <c r="B123" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -6944,7 +6944,7 @@
         <v>505</v>
       </c>
       <c r="B124" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -6952,7 +6952,7 @@
         <v>784</v>
       </c>
       <c r="B125" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -6960,7 +6960,7 @@
         <v>716</v>
       </c>
       <c r="B126" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -6968,7 +6968,7 @@
         <v>785</v>
       </c>
       <c r="B127" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -6976,7 +6976,7 @@
         <v>506</v>
       </c>
       <c r="B128" s="1">
-        <v>41250</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -6984,7 +6984,7 @@
         <v>21</v>
       </c>
       <c r="B129" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -6992,7 +6992,7 @@
         <v>756</v>
       </c>
       <c r="B130" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7000,7 +7000,7 @@
         <v>480</v>
       </c>
       <c r="B131" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7008,7 +7008,7 @@
         <v>786</v>
       </c>
       <c r="B132" s="1">
-        <v>71500</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7016,7 +7016,7 @@
         <v>787</v>
       </c>
       <c r="B133" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7024,7 +7024,7 @@
         <v>788</v>
       </c>
       <c r="B134" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7032,7 +7032,7 @@
         <v>789</v>
       </c>
       <c r="B135" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7040,7 +7040,7 @@
         <v>73</v>
       </c>
       <c r="B136" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7048,7 +7048,7 @@
         <v>74</v>
       </c>
       <c r="B137" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7056,7 +7056,7 @@
         <v>162</v>
       </c>
       <c r="B138" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7064,7 +7064,7 @@
         <v>790</v>
       </c>
       <c r="B139" s="1">
-        <v>41250</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7072,7 +7072,7 @@
         <v>130</v>
       </c>
       <c r="B140" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7080,7 +7080,7 @@
         <v>791</v>
       </c>
       <c r="B141" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7088,7 +7088,7 @@
         <v>709</v>
       </c>
       <c r="B142" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7096,7 +7096,7 @@
         <v>432</v>
       </c>
       <c r="B143" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7104,7 +7104,7 @@
         <v>507</v>
       </c>
       <c r="B144" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7112,7 +7112,7 @@
         <v>508</v>
       </c>
       <c r="B145" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7120,7 +7120,7 @@
         <v>437</v>
       </c>
       <c r="B146" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7128,7 +7128,7 @@
         <v>509</v>
       </c>
       <c r="B147" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7136,7 +7136,7 @@
         <v>792</v>
       </c>
       <c r="B148" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7144,7 +7144,7 @@
         <v>4</v>
       </c>
       <c r="B149" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7152,7 +7152,7 @@
         <v>793</v>
       </c>
       <c r="B150" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7160,7 +7160,7 @@
         <v>650</v>
       </c>
       <c r="B151" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7168,7 +7168,7 @@
         <v>651</v>
       </c>
       <c r="B152" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7176,7 +7176,7 @@
         <v>588</v>
       </c>
       <c r="B153" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7184,7 +7184,7 @@
         <v>554</v>
       </c>
       <c r="B154" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7192,7 +7192,7 @@
         <v>510</v>
       </c>
       <c r="B155" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7200,7 +7200,7 @@
         <v>403</v>
       </c>
       <c r="B156" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7208,7 +7208,7 @@
         <v>546</v>
       </c>
       <c r="B157" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7216,7 +7216,7 @@
         <v>441</v>
       </c>
       <c r="B158" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7224,7 +7224,7 @@
         <v>556</v>
       </c>
       <c r="B159" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7232,7 +7232,7 @@
         <v>557</v>
       </c>
       <c r="B160" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7240,7 +7240,7 @@
         <v>794</v>
       </c>
       <c r="B161" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7248,7 +7248,7 @@
         <v>435</v>
       </c>
       <c r="B162" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7256,7 +7256,7 @@
         <v>795</v>
       </c>
       <c r="B163" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7264,7 +7264,7 @@
         <v>796</v>
       </c>
       <c r="B164" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -7272,7 +7272,7 @@
         <v>624</v>
       </c>
       <c r="B165" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -7280,7 +7280,7 @@
         <v>10</v>
       </c>
       <c r="B166" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -7288,7 +7288,7 @@
         <v>797</v>
       </c>
       <c r="B167" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
   </sheetData>
@@ -7318,7 +7318,7 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>77000</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7326,7 +7326,7 @@
         <v>745</v>
       </c>
       <c r="B3" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7334,7 +7334,7 @@
         <v>746</v>
       </c>
       <c r="B4" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7342,7 +7342,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1">
-        <v>77000</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7350,7 +7350,7 @@
         <v>747</v>
       </c>
       <c r="B6" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7358,7 +7358,7 @@
         <v>122</v>
       </c>
       <c r="B7" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7366,7 +7366,7 @@
         <v>131</v>
       </c>
       <c r="B8" s="1">
-        <v>137500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7374,7 +7374,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7382,7 +7382,7 @@
         <v>567</v>
       </c>
       <c r="B10" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7390,7 +7390,7 @@
         <v>82</v>
       </c>
       <c r="B11" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7398,7 +7398,7 @@
         <v>165</v>
       </c>
       <c r="B12" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7406,7 +7406,7 @@
         <v>589</v>
       </c>
       <c r="B13" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7414,7 +7414,7 @@
         <v>798</v>
       </c>
       <c r="B14" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7422,7 +7422,7 @@
         <v>132</v>
       </c>
       <c r="B15" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -7430,7 +7430,7 @@
         <v>133</v>
       </c>
       <c r="B16" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -7438,7 +7438,7 @@
         <v>753</v>
       </c>
       <c r="B17" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -7446,7 +7446,7 @@
         <v>625</v>
       </c>
       <c r="B18" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -7454,7 +7454,7 @@
         <v>823</v>
       </c>
       <c r="B19" s="1">
-        <v>46750</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7462,7 +7462,7 @@
         <v>430</v>
       </c>
       <c r="B20" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7470,7 +7470,7 @@
         <v>163</v>
       </c>
       <c r="B21" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7478,7 +7478,7 @@
         <v>647</v>
       </c>
       <c r="B22" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7486,7 +7486,7 @@
         <v>581</v>
       </c>
       <c r="B23" s="1">
-        <v>60500</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7494,7 +7494,7 @@
         <v>648</v>
       </c>
       <c r="B24" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7502,7 +7502,7 @@
         <v>83</v>
       </c>
       <c r="B25" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7510,7 +7510,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7518,7 +7518,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7526,7 +7526,7 @@
         <v>121</v>
       </c>
       <c r="B28" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7534,7 +7534,7 @@
         <v>134</v>
       </c>
       <c r="B29" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7542,7 +7542,7 @@
         <v>698</v>
       </c>
       <c r="B30" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7550,7 +7550,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7558,7 +7558,7 @@
         <v>477</v>
       </c>
       <c r="B32" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7566,7 +7566,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7574,7 +7574,7 @@
         <v>158</v>
       </c>
       <c r="B34" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7582,7 +7582,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7590,7 +7590,7 @@
         <v>692</v>
       </c>
       <c r="B36" s="1">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7598,7 +7598,7 @@
         <v>406</v>
       </c>
       <c r="B37" s="1">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7606,7 +7606,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="1">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7614,7 +7614,7 @@
         <v>626</v>
       </c>
       <c r="B39" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7622,7 +7622,7 @@
         <v>627</v>
       </c>
       <c r="B40" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7630,7 +7630,7 @@
         <v>628</v>
       </c>
       <c r="B41" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7638,7 +7638,7 @@
         <v>629</v>
       </c>
       <c r="B42" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -7646,7 +7646,7 @@
         <v>511</v>
       </c>
       <c r="B43" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7654,7 +7654,7 @@
         <v>85</v>
       </c>
       <c r="B44" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -7662,7 +7662,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -7670,7 +7670,7 @@
         <v>86</v>
       </c>
       <c r="B46" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7678,7 +7678,7 @@
         <v>135</v>
       </c>
       <c r="B47" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7686,7 +7686,7 @@
         <v>136</v>
       </c>
       <c r="B48" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -7694,7 +7694,7 @@
         <v>87</v>
       </c>
       <c r="B49" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -7702,7 +7702,7 @@
         <v>444</v>
       </c>
       <c r="B50" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -7710,7 +7710,7 @@
         <v>512</v>
       </c>
       <c r="B51" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -7718,7 +7718,7 @@
         <v>137</v>
       </c>
       <c r="B52" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -7726,7 +7726,7 @@
         <v>513</v>
       </c>
       <c r="B53" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -7734,7 +7734,7 @@
         <v>451</v>
       </c>
       <c r="B54" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -7742,7 +7742,7 @@
         <v>452</v>
       </c>
       <c r="B55" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -7750,7 +7750,7 @@
         <v>138</v>
       </c>
       <c r="B56" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -7758,7 +7758,7 @@
         <v>699</v>
       </c>
       <c r="B57" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -7766,7 +7766,7 @@
         <v>583</v>
       </c>
       <c r="B58" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -7774,7 +7774,7 @@
         <v>584</v>
       </c>
       <c r="B59" s="1">
-        <v>41250</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -7782,7 +7782,7 @@
         <v>139</v>
       </c>
       <c r="B60" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -7790,7 +7790,7 @@
         <v>551</v>
       </c>
       <c r="B61" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -7798,7 +7798,7 @@
         <v>140</v>
       </c>
       <c r="B62" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -7806,7 +7806,7 @@
         <v>89</v>
       </c>
       <c r="B63" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -7814,7 +7814,7 @@
         <v>88</v>
       </c>
       <c r="B64" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -7822,7 +7822,7 @@
         <v>559</v>
       </c>
       <c r="B65" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -7830,7 +7830,7 @@
         <v>722</v>
       </c>
       <c r="B66" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -7838,7 +7838,7 @@
         <v>118</v>
       </c>
       <c r="B67" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -7846,7 +7846,7 @@
         <v>799</v>
       </c>
       <c r="B68" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -7854,7 +7854,7 @@
         <v>39</v>
       </c>
       <c r="B69" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -7862,7 +7862,7 @@
         <v>40</v>
       </c>
       <c r="B70" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -7870,7 +7870,7 @@
         <v>800</v>
       </c>
       <c r="B71" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -7878,7 +7878,7 @@
         <v>120</v>
       </c>
       <c r="B72" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7886,7 +7886,7 @@
         <v>41</v>
       </c>
       <c r="B73" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7894,7 +7894,7 @@
         <v>42</v>
       </c>
       <c r="B74" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7902,7 +7902,7 @@
         <v>43</v>
       </c>
       <c r="B75" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7910,7 +7910,7 @@
         <v>44</v>
       </c>
       <c r="B76" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7918,7 +7918,7 @@
         <v>45</v>
       </c>
       <c r="B77" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7926,7 +7926,7 @@
         <v>46</v>
       </c>
       <c r="B78" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7934,7 +7934,7 @@
         <v>687</v>
       </c>
       <c r="B79" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7942,7 +7942,7 @@
         <v>90</v>
       </c>
       <c r="B80" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7950,7 +7950,7 @@
         <v>32</v>
       </c>
       <c r="B81" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7958,7 +7958,7 @@
         <v>27</v>
       </c>
       <c r="B82" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7966,7 +7966,7 @@
         <v>33</v>
       </c>
       <c r="B83" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7974,7 +7974,7 @@
         <v>141</v>
       </c>
       <c r="B84" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7982,7 +7982,7 @@
         <v>49</v>
       </c>
       <c r="B85" s="1">
-        <v>137500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7990,7 +7990,7 @@
         <v>48</v>
       </c>
       <c r="B86" s="1">
-        <v>137500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7998,7 +7998,7 @@
         <v>47</v>
       </c>
       <c r="B87" s="1">
-        <v>126500</v>
+        <v>128800</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -8006,7 +8006,7 @@
         <v>50</v>
       </c>
       <c r="B88" s="1">
-        <v>137500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -8014,7 +8014,7 @@
         <v>51</v>
       </c>
       <c r="B89" s="1">
-        <v>137500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -8022,7 +8022,7 @@
         <v>474</v>
       </c>
       <c r="B90" s="1">
-        <v>137500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -8030,7 +8030,7 @@
         <v>55</v>
       </c>
       <c r="B91" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -8038,7 +8038,7 @@
         <v>52</v>
       </c>
       <c r="B92" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -8046,7 +8046,7 @@
         <v>53</v>
       </c>
       <c r="B93" s="1">
-        <v>121000</v>
+        <v>123200</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -8054,7 +8054,7 @@
         <v>54</v>
       </c>
       <c r="B94" s="1">
-        <v>121000</v>
+        <v>123200</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -8062,7 +8062,7 @@
         <v>56</v>
       </c>
       <c r="B95" s="1">
-        <v>121000</v>
+        <v>123200</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -8070,7 +8070,7 @@
         <v>475</v>
       </c>
       <c r="B96" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -8078,7 +8078,7 @@
         <v>514</v>
       </c>
       <c r="B97" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -8086,7 +8086,7 @@
         <v>700</v>
       </c>
       <c r="B98" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -8094,7 +8094,7 @@
         <v>701</v>
       </c>
       <c r="B99" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -8102,7 +8102,7 @@
         <v>142</v>
       </c>
       <c r="B100" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -8110,7 +8110,7 @@
         <v>801</v>
       </c>
       <c r="B101" s="1">
-        <v>77000</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -8118,7 +8118,7 @@
         <v>544</v>
       </c>
       <c r="B102" s="1">
-        <v>77000</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -8126,7 +8126,7 @@
         <v>802</v>
       </c>
       <c r="B103" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -8134,7 +8134,7 @@
         <v>643</v>
       </c>
       <c r="B104" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -8142,7 +8142,7 @@
         <v>515</v>
       </c>
       <c r="B105" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -8150,7 +8150,7 @@
         <v>428</v>
       </c>
       <c r="B106" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -8158,7 +8158,7 @@
         <v>693</v>
       </c>
       <c r="B107" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -8166,7 +8166,7 @@
         <v>552</v>
       </c>
       <c r="B108" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -8174,7 +8174,7 @@
         <v>825</v>
       </c>
       <c r="B109" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -8182,7 +8182,7 @@
         <v>702</v>
       </c>
       <c r="B110" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -8190,7 +8190,7 @@
         <v>93</v>
       </c>
       <c r="B111" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -8198,7 +8198,7 @@
         <v>92</v>
       </c>
       <c r="B112" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -8206,7 +8206,7 @@
         <v>91</v>
       </c>
       <c r="B113" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -8214,7 +8214,7 @@
         <v>94</v>
       </c>
       <c r="B114" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -8222,7 +8222,7 @@
         <v>585</v>
       </c>
       <c r="B115" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -8230,7 +8230,7 @@
         <v>646</v>
       </c>
       <c r="B116" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -8238,7 +8238,7 @@
         <v>560</v>
       </c>
       <c r="B117" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -8246,7 +8246,7 @@
         <v>57</v>
       </c>
       <c r="B118" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -8254,7 +8254,7 @@
         <v>58</v>
       </c>
       <c r="B119" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -8262,7 +8262,7 @@
         <v>59</v>
       </c>
       <c r="B120" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -8270,7 +8270,7 @@
         <v>561</v>
       </c>
       <c r="B121" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -8278,7 +8278,7 @@
         <v>562</v>
       </c>
       <c r="B122" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -8286,7 +8286,7 @@
         <v>677</v>
       </c>
       <c r="B123" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -8294,7 +8294,7 @@
         <v>685</v>
       </c>
       <c r="B124" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -8302,7 +8302,7 @@
         <v>686</v>
       </c>
       <c r="B125" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -8310,7 +8310,7 @@
         <v>484</v>
       </c>
       <c r="B126" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -8318,7 +8318,7 @@
         <v>735</v>
       </c>
       <c r="B127" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -8326,7 +8326,7 @@
         <v>60</v>
       </c>
       <c r="B128" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -8334,7 +8334,7 @@
         <v>61</v>
       </c>
       <c r="B129" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -8342,7 +8342,7 @@
         <v>157</v>
       </c>
       <c r="B130" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -8350,7 +8350,7 @@
         <v>62</v>
       </c>
       <c r="B131" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -8358,7 +8358,7 @@
         <v>754</v>
       </c>
       <c r="B132" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -8366,7 +8366,7 @@
         <v>694</v>
       </c>
       <c r="B133" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -8374,7 +8374,7 @@
         <v>563</v>
       </c>
       <c r="B134" s="1">
-        <v>77000</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -8382,7 +8382,7 @@
         <v>697</v>
       </c>
       <c r="B135" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -8390,7 +8390,7 @@
         <v>455</v>
       </c>
       <c r="B136" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -8398,7 +8398,7 @@
         <v>623</v>
       </c>
       <c r="B137" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -8406,7 +8406,7 @@
         <v>630</v>
       </c>
       <c r="B138" s="1">
-        <v>302500</v>
+        <v>308000</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -8414,7 +8414,7 @@
         <v>631</v>
       </c>
       <c r="B139" s="1">
-        <v>313500</v>
+        <v>319200</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -8422,7 +8422,7 @@
         <v>449</v>
       </c>
       <c r="B140" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -8430,7 +8430,7 @@
         <v>448</v>
       </c>
       <c r="B141" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -8438,7 +8438,7 @@
         <v>450</v>
       </c>
       <c r="B142" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -8446,7 +8446,7 @@
         <v>447</v>
       </c>
       <c r="B143" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -8454,7 +8454,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -8462,7 +8462,7 @@
         <v>446</v>
       </c>
       <c r="B145" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -8470,7 +8470,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -8478,7 +8478,7 @@
         <v>591</v>
       </c>
       <c r="B147" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -8486,7 +8486,7 @@
         <v>96</v>
       </c>
       <c r="B148" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -8494,7 +8494,7 @@
         <v>95</v>
       </c>
       <c r="B149" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -8502,7 +8502,7 @@
         <v>97</v>
       </c>
       <c r="B150" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -8510,7 +8510,7 @@
         <v>553</v>
       </c>
       <c r="B151" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -8518,7 +8518,7 @@
         <v>803</v>
       </c>
       <c r="B152" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -8526,7 +8526,7 @@
         <v>804</v>
       </c>
       <c r="B153" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -8534,7 +8534,7 @@
         <v>145</v>
       </c>
       <c r="B154" s="1">
-        <v>137500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -8542,7 +8542,7 @@
         <v>119</v>
       </c>
       <c r="B155" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -8550,7 +8550,7 @@
         <v>703</v>
       </c>
       <c r="B156" s="1">
-        <v>41250</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -8558,7 +8558,7 @@
         <v>704</v>
       </c>
       <c r="B157" s="1">
-        <v>41250</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -8566,7 +8566,7 @@
         <v>98</v>
       </c>
       <c r="B158" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -8574,7 +8574,7 @@
         <v>63</v>
       </c>
       <c r="B159" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -8582,7 +8582,7 @@
         <v>472</v>
       </c>
       <c r="B160" s="1">
-        <v>77000</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -8590,7 +8590,7 @@
         <v>99</v>
       </c>
       <c r="B161" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -8598,7 +8598,7 @@
         <v>720</v>
       </c>
       <c r="B162" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -8606,7 +8606,7 @@
         <v>724</v>
       </c>
       <c r="B163" s="1">
-        <v>41250</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -8614,7 +8614,7 @@
         <v>721</v>
       </c>
       <c r="B164" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -8622,7 +8622,7 @@
         <v>725</v>
       </c>
       <c r="B165" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -8630,7 +8630,7 @@
         <v>695</v>
       </c>
       <c r="B166" s="1">
-        <v>825</v>
+        <v>840</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -8638,7 +8638,7 @@
         <v>101</v>
       </c>
       <c r="B167" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -8646,7 +8646,7 @@
         <v>102</v>
       </c>
       <c r="B168" s="1">
-        <v>126500</v>
+        <v>128800</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -8654,7 +8654,7 @@
         <v>103</v>
       </c>
       <c r="B169" s="1">
-        <v>192500</v>
+        <v>196000</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -8662,7 +8662,7 @@
         <v>632</v>
       </c>
       <c r="B170" s="1">
-        <v>192500</v>
+        <v>196000</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -8670,7 +8670,7 @@
         <v>633</v>
       </c>
       <c r="B171" s="1">
-        <v>198000</v>
+        <v>201600</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -8678,7 +8678,7 @@
         <v>678</v>
       </c>
       <c r="B172" s="1">
-        <v>203500</v>
+        <v>207200</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -8686,7 +8686,7 @@
         <v>679</v>
       </c>
       <c r="B173" s="1">
-        <v>192500</v>
+        <v>196000</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -8694,7 +8694,7 @@
         <v>680</v>
       </c>
       <c r="B174" s="1">
-        <v>192500</v>
+        <v>196000</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8702,7 +8702,7 @@
         <v>681</v>
       </c>
       <c r="B175" s="1">
-        <v>192500</v>
+        <v>196000</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -8710,7 +8710,7 @@
         <v>740</v>
       </c>
       <c r="B176" s="1">
-        <v>121000</v>
+        <v>123200</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -8718,7 +8718,7 @@
         <v>23</v>
       </c>
       <c r="B177" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -8726,7 +8726,7 @@
         <v>442</v>
       </c>
       <c r="B178" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -8734,7 +8734,7 @@
         <v>564</v>
       </c>
       <c r="B179" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -8742,7 +8742,7 @@
         <v>146</v>
       </c>
       <c r="B180" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -8750,7 +8750,7 @@
         <v>147</v>
       </c>
       <c r="B181" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -8758,7 +8758,7 @@
         <v>755</v>
       </c>
       <c r="B182" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -8766,7 +8766,7 @@
         <v>705</v>
       </c>
       <c r="B183" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -8774,7 +8774,7 @@
         <v>652</v>
       </c>
       <c r="B184" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -8782,7 +8782,7 @@
         <v>805</v>
       </c>
       <c r="B185" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -8790,7 +8790,7 @@
         <v>748</v>
       </c>
       <c r="B186" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -8798,7 +8798,7 @@
         <v>148</v>
       </c>
       <c r="B187" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -8806,7 +8806,7 @@
         <v>706</v>
       </c>
       <c r="B188" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -8814,7 +8814,7 @@
         <v>516</v>
       </c>
       <c r="B189" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -8822,7 +8822,7 @@
         <v>749</v>
       </c>
       <c r="B190" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -8830,7 +8830,7 @@
         <v>149</v>
       </c>
       <c r="B191" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -8838,7 +8838,7 @@
         <v>565</v>
       </c>
       <c r="B192" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -8846,7 +8846,7 @@
         <v>707</v>
       </c>
       <c r="B193" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -8854,7 +8854,7 @@
         <v>150</v>
       </c>
       <c r="B194" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -8862,7 +8862,7 @@
         <v>104</v>
       </c>
       <c r="B195" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -8870,7 +8870,7 @@
         <v>517</v>
       </c>
       <c r="B196" s="1">
-        <v>41250</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -8878,7 +8878,7 @@
         <v>151</v>
       </c>
       <c r="B197" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -8886,7 +8886,7 @@
         <v>481</v>
       </c>
       <c r="B198" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -8894,7 +8894,7 @@
         <v>708</v>
       </c>
       <c r="B199" s="1">
-        <v>93500</v>
+        <v>95200</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -8902,7 +8902,7 @@
         <v>64</v>
       </c>
       <c r="B200" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -8910,7 +8910,7 @@
         <v>152</v>
       </c>
       <c r="B201" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -8918,7 +8918,7 @@
         <v>65</v>
       </c>
       <c r="B202" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -8926,7 +8926,7 @@
         <v>545</v>
       </c>
       <c r="B203" s="1">
-        <v>77000</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -8934,7 +8934,7 @@
         <v>547</v>
       </c>
       <c r="B204" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -8942,7 +8942,7 @@
         <v>66</v>
       </c>
       <c r="B205" s="1">
-        <v>71500</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -8950,7 +8950,7 @@
         <v>67</v>
       </c>
       <c r="B206" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -8958,7 +8958,7 @@
         <v>68</v>
       </c>
       <c r="B207" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -8966,7 +8966,7 @@
         <v>69</v>
       </c>
       <c r="B208" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -8974,7 +8974,7 @@
         <v>70</v>
       </c>
       <c r="B209" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -8982,7 +8982,7 @@
         <v>71</v>
       </c>
       <c r="B210" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -8990,7 +8990,7 @@
         <v>72</v>
       </c>
       <c r="B211" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -8998,7 +8998,7 @@
         <v>473</v>
       </c>
       <c r="B212" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -9006,7 +9006,7 @@
         <v>160</v>
       </c>
       <c r="B213" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -9014,7 +9014,7 @@
         <v>161</v>
       </c>
       <c r="B214" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -9022,7 +9022,7 @@
         <v>75</v>
       </c>
       <c r="B215" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -9030,7 +9030,7 @@
         <v>159</v>
       </c>
       <c r="B216" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -9038,7 +9038,7 @@
         <v>107</v>
       </c>
       <c r="B217" s="1">
-        <v>137500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -9046,7 +9046,7 @@
         <v>108</v>
       </c>
       <c r="B218" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -9054,7 +9054,7 @@
         <v>110</v>
       </c>
       <c r="B219" s="1">
-        <v>110000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -9062,7 +9062,7 @@
         <v>105</v>
       </c>
       <c r="B220" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -9070,7 +9070,7 @@
         <v>106</v>
       </c>
       <c r="B221" s="1">
-        <v>82500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -9078,7 +9078,7 @@
         <v>109</v>
       </c>
       <c r="B222" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -9086,7 +9086,7 @@
         <v>111</v>
       </c>
       <c r="B223" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -9094,7 +9094,7 @@
         <v>153</v>
       </c>
       <c r="B224" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -9102,7 +9102,7 @@
         <v>154</v>
       </c>
       <c r="B225" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -9110,7 +9110,7 @@
         <v>76</v>
       </c>
       <c r="B226" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -9118,7 +9118,7 @@
         <v>77</v>
       </c>
       <c r="B227" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -9126,7 +9126,7 @@
         <v>714</v>
       </c>
       <c r="B228" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -9134,7 +9134,7 @@
         <v>78</v>
       </c>
       <c r="B229" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -9142,7 +9142,7 @@
         <v>443</v>
       </c>
       <c r="B230" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -9150,7 +9150,7 @@
         <v>79</v>
       </c>
       <c r="B231" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -9158,7 +9158,7 @@
         <v>518</v>
       </c>
       <c r="B232" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -9166,7 +9166,7 @@
         <v>80</v>
       </c>
       <c r="B233" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -9174,7 +9174,7 @@
         <v>81</v>
       </c>
       <c r="B234" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -9182,7 +9182,7 @@
         <v>519</v>
       </c>
       <c r="B235" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -9190,7 +9190,7 @@
         <v>113</v>
       </c>
       <c r="B236" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -9198,7 +9198,7 @@
         <v>114</v>
       </c>
       <c r="B237" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -9206,7 +9206,7 @@
         <v>453</v>
       </c>
       <c r="B238" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -9214,7 +9214,7 @@
         <v>710</v>
       </c>
       <c r="B239" s="1">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -9222,7 +9222,7 @@
         <v>750</v>
       </c>
       <c r="B240" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -9230,7 +9230,7 @@
         <v>650</v>
       </c>
       <c r="B241" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -9238,7 +9238,7 @@
         <v>588</v>
       </c>
       <c r="B242" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -9246,7 +9246,7 @@
         <v>555</v>
       </c>
       <c r="B243" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -9254,7 +9254,7 @@
         <v>117</v>
       </c>
       <c r="B244" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -9262,7 +9262,7 @@
         <v>403</v>
       </c>
       <c r="B245" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -9270,7 +9270,7 @@
         <v>546</v>
       </c>
       <c r="B246" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -9278,7 +9278,7 @@
         <v>568</v>
       </c>
       <c r="B247" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -9286,7 +9286,7 @@
         <v>566</v>
       </c>
       <c r="B248" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -9294,7 +9294,7 @@
         <v>556</v>
       </c>
       <c r="B249" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -9302,7 +9302,7 @@
         <v>557</v>
       </c>
       <c r="B250" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -9310,7 +9310,7 @@
         <v>634</v>
       </c>
       <c r="B251" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -9318,7 +9318,7 @@
         <v>711</v>
       </c>
       <c r="B252" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -9326,7 +9326,7 @@
         <v>712</v>
       </c>
       <c r="B253" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -9334,7 +9334,7 @@
         <v>558</v>
       </c>
       <c r="B254" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -9342,7 +9342,7 @@
         <v>635</v>
       </c>
       <c r="B255" s="1">
-        <v>126500</v>
+        <v>128800</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -9350,7 +9350,7 @@
         <v>713</v>
       </c>
       <c r="B256" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -9358,7 +9358,7 @@
         <v>794</v>
       </c>
       <c r="B257" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -9366,7 +9366,7 @@
         <v>445</v>
       </c>
       <c r="B258" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -9374,7 +9374,7 @@
         <v>682</v>
       </c>
       <c r="B259" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -9382,7 +9382,7 @@
         <v>112</v>
       </c>
       <c r="B260" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -9390,7 +9390,7 @@
         <v>155</v>
       </c>
       <c r="B261" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -9398,7 +9398,7 @@
         <v>156</v>
       </c>
       <c r="B262" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
   </sheetData>
@@ -9428,7 +9428,7 @@
         <v>592</v>
       </c>
       <c r="B2" s="1">
-        <v>99000</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9436,7 +9436,7 @@
         <v>806</v>
       </c>
       <c r="B3" s="1">
-        <v>74250</v>
+        <v>75600</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9444,7 +9444,7 @@
         <v>807</v>
       </c>
       <c r="B4" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9452,7 +9452,7 @@
         <v>589</v>
       </c>
       <c r="B5" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9460,7 +9460,7 @@
         <v>808</v>
       </c>
       <c r="B6" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9468,7 +9468,7 @@
         <v>581</v>
       </c>
       <c r="B7" s="1">
-        <v>60500</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9476,7 +9476,7 @@
         <v>648</v>
       </c>
       <c r="B8" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9484,7 +9484,7 @@
         <v>520</v>
       </c>
       <c r="B9" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -9492,7 +9492,7 @@
         <v>521</v>
       </c>
       <c r="B10" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9500,7 +9500,7 @@
         <v>522</v>
       </c>
       <c r="B11" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9508,7 +9508,7 @@
         <v>523</v>
       </c>
       <c r="B12" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -9516,7 +9516,7 @@
         <v>809</v>
       </c>
       <c r="B13" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -9524,7 +9524,7 @@
         <v>551</v>
       </c>
       <c r="B14" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -9532,7 +9532,7 @@
         <v>722</v>
       </c>
       <c r="B15" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -9540,7 +9540,7 @@
         <v>524</v>
       </c>
       <c r="B16" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -9548,7 +9548,7 @@
         <v>525</v>
       </c>
       <c r="B17" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -9556,7 +9556,7 @@
         <v>691</v>
       </c>
       <c r="B18" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -9564,7 +9564,7 @@
         <v>526</v>
       </c>
       <c r="B19" s="1">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -9572,7 +9572,7 @@
         <v>810</v>
       </c>
       <c r="B20" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -9580,7 +9580,7 @@
         <v>527</v>
       </c>
       <c r="B21" s="1">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -9588,7 +9588,7 @@
         <v>552</v>
       </c>
       <c r="B22" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -9596,7 +9596,7 @@
         <v>825</v>
       </c>
       <c r="B23" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -9604,7 +9604,7 @@
         <v>528</v>
       </c>
       <c r="B24" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -9612,7 +9612,7 @@
         <v>821</v>
       </c>
       <c r="B25" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -9620,7 +9620,7 @@
         <v>529</v>
       </c>
       <c r="B26" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -9628,7 +9628,7 @@
         <v>684</v>
       </c>
       <c r="B27" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -9636,7 +9636,7 @@
         <v>484</v>
       </c>
       <c r="B28">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -9644,7 +9644,7 @@
         <v>735</v>
       </c>
       <c r="B29">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -9652,7 +9652,7 @@
         <v>530</v>
       </c>
       <c r="B30">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -9660,7 +9660,7 @@
         <v>531</v>
       </c>
       <c r="B31">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -9668,7 +9668,7 @@
         <v>532</v>
       </c>
       <c r="B32">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -9676,7 +9676,7 @@
         <v>533</v>
       </c>
       <c r="B33">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -9684,7 +9684,7 @@
         <v>534</v>
       </c>
       <c r="B34">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -9692,7 +9692,7 @@
         <v>535</v>
       </c>
       <c r="B35">
-        <v>60500</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -9700,7 +9700,7 @@
         <v>631</v>
       </c>
       <c r="B36">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -9708,7 +9708,7 @@
         <v>553</v>
       </c>
       <c r="B37">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -9716,7 +9716,7 @@
         <v>726</v>
       </c>
       <c r="B38">
-        <v>46750</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -9724,7 +9724,7 @@
         <v>727</v>
       </c>
       <c r="B39">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -9732,7 +9732,7 @@
         <v>536</v>
       </c>
       <c r="B40">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -9740,7 +9740,7 @@
         <v>683</v>
       </c>
       <c r="B41">
-        <v>198000</v>
+        <v>201600</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -9748,7 +9748,7 @@
         <v>636</v>
       </c>
       <c r="B42">
-        <v>203500</v>
+        <v>207200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -9756,7 +9756,7 @@
         <v>740</v>
       </c>
       <c r="B43">
-        <v>121000</v>
+        <v>123200</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -9764,7 +9764,7 @@
         <v>537</v>
       </c>
       <c r="B44">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -9772,7 +9772,7 @@
         <v>538</v>
       </c>
       <c r="B45">
-        <v>27500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -9780,7 +9780,7 @@
         <v>811</v>
       </c>
       <c r="B46">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -9788,7 +9788,7 @@
         <v>812</v>
       </c>
       <c r="B47">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -9796,7 +9796,7 @@
         <v>813</v>
       </c>
       <c r="B48">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -9804,7 +9804,7 @@
         <v>539</v>
       </c>
       <c r="B49">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -9812,7 +9812,7 @@
         <v>814</v>
       </c>
       <c r="B50">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -9820,7 +9820,7 @@
         <v>815</v>
       </c>
       <c r="B51">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -9828,7 +9828,7 @@
         <v>816</v>
       </c>
       <c r="B52">
-        <v>13750</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -9836,7 +9836,7 @@
         <v>588</v>
       </c>
       <c r="B53">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -9844,7 +9844,7 @@
         <v>817</v>
       </c>
       <c r="B54">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -9852,7 +9852,7 @@
         <v>818</v>
       </c>
       <c r="B55">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -9860,7 +9860,7 @@
         <v>819</v>
       </c>
       <c r="B56">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -9868,7 +9868,7 @@
         <v>548</v>
       </c>
       <c r="B57">
-        <v>38500</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -9876,7 +9876,7 @@
         <v>549</v>
       </c>
       <c r="B58">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -9884,7 +9884,7 @@
         <v>403</v>
       </c>
       <c r="B59">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -9892,7 +9892,7 @@
         <v>546</v>
       </c>
       <c r="B60">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -9900,7 +9900,7 @@
         <v>556</v>
       </c>
       <c r="B61">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -9908,7 +9908,7 @@
         <v>557</v>
       </c>
       <c r="B62">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -9916,7 +9916,7 @@
         <v>540</v>
       </c>
       <c r="B63">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -9924,7 +9924,7 @@
         <v>541</v>
       </c>
       <c r="B64">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -9932,7 +9932,7 @@
         <v>637</v>
       </c>
       <c r="B65">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -9940,7 +9940,7 @@
         <v>542</v>
       </c>
       <c r="B66">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
   </sheetData>
@@ -9970,7 +9970,7 @@
         <v>383</v>
       </c>
       <c r="B2" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9978,7 +9978,7 @@
         <v>384</v>
       </c>
       <c r="B3" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9986,7 +9986,7 @@
         <v>385</v>
       </c>
       <c r="B4" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9994,7 +9994,7 @@
         <v>386</v>
       </c>
       <c r="B5" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -10002,7 +10002,7 @@
         <v>640</v>
       </c>
       <c r="B6" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -10010,7 +10010,7 @@
         <v>387</v>
       </c>
       <c r="B7" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -10018,7 +10018,7 @@
         <v>660</v>
       </c>
       <c r="B8" s="1">
-        <v>22000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -10026,7 +10026,7 @@
         <v>662</v>
       </c>
       <c r="B9" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -10034,7 +10034,7 @@
         <v>661</v>
       </c>
       <c r="B10" s="1">
-        <v>17600</v>
+        <v>17920</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -10042,7 +10042,7 @@
         <v>388</v>
       </c>
       <c r="B11" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -10050,7 +10050,7 @@
         <v>405</v>
       </c>
       <c r="B12" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -10058,7 +10058,7 @@
         <v>659</v>
       </c>
       <c r="B13" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -10066,7 +10066,7 @@
         <v>665</v>
       </c>
       <c r="B14" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -10074,7 +10074,7 @@
         <v>745</v>
       </c>
       <c r="B15" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -10082,7 +10082,7 @@
         <v>389</v>
       </c>
       <c r="B16" s="1">
-        <v>4950</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -10090,7 +10090,7 @@
         <v>589</v>
       </c>
       <c r="B17" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -10098,7 +10098,7 @@
         <v>823</v>
       </c>
       <c r="B18" s="1">
-        <v>46750</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -10106,7 +10106,7 @@
         <v>663</v>
       </c>
       <c r="B19" s="1">
-        <v>96250</v>
+        <v>98000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -10114,7 +10114,7 @@
         <v>655</v>
       </c>
       <c r="B20" s="1">
-        <v>107250</v>
+        <v>109200</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -10122,7 +10122,7 @@
         <v>656</v>
       </c>
       <c r="B21" s="1">
-        <v>121000</v>
+        <v>123200</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -10130,7 +10130,7 @@
         <v>430</v>
       </c>
       <c r="B22" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -10138,7 +10138,7 @@
         <v>163</v>
       </c>
       <c r="B23" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -10146,7 +10146,7 @@
         <v>647</v>
       </c>
       <c r="B24" s="1">
-        <v>55000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -10154,7 +10154,7 @@
         <v>581</v>
       </c>
       <c r="B25" s="1">
-        <v>60500</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -10162,7 +10162,7 @@
         <v>648</v>
       </c>
       <c r="B26" s="1">
-        <v>66000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -10170,7 +10170,7 @@
         <v>657</v>
       </c>
       <c r="B27" s="1">
-        <v>74250</v>
+        <v>75600</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -10178,7 +10178,7 @@
         <v>658</v>
       </c>
       <c r="B28" s="1">
-        <v>88000</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -10186,7 +10186,7 @@
         <v>664</v>
       </c>
       <c r="B29" s="1">
-        <v>93500</v>
+        <v>95200</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -10194,7 +10194,7 @@
         <v>692</v>
       </c>
       <c r="B30" s="1">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -10202,7 +10202,7 @@
         <v>406</v>
       </c>
       <c r="B31" s="1">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -10210,7 +10210,7 @@
         <v>402</v>
       </c>
       <c r="B32" s="1">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -10218,7 +10218,7 @@
         <v>429</v>
       </c>
       <c r="B33" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -10226,7 +10226,7 @@
         <v>551</v>
       </c>
       <c r="B34" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -10234,7 +10234,7 @@
         <v>390</v>
       </c>
       <c r="B35" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -10242,7 +10242,7 @@
         <v>552</v>
       </c>
       <c r="B36" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -10250,7 +10250,7 @@
         <v>825</v>
       </c>
       <c r="B37" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -10258,7 +10258,7 @@
         <v>820</v>
       </c>
       <c r="B38" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -10266,7 +10266,7 @@
         <v>404</v>
       </c>
       <c r="B39" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -10274,7 +10274,7 @@
         <v>259</v>
       </c>
       <c r="B40" s="1">
-        <v>16500</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -10282,7 +10282,7 @@
         <v>425</v>
       </c>
       <c r="B41" s="1">
-        <v>2200</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -10290,7 +10290,7 @@
         <v>484</v>
       </c>
       <c r="B42" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -10298,7 +10298,7 @@
         <v>735</v>
       </c>
       <c r="B43" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -10306,7 +10306,7 @@
         <v>391</v>
       </c>
       <c r="B44" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -10314,7 +10314,7 @@
         <v>392</v>
       </c>
       <c r="B45" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -10322,7 +10322,7 @@
         <v>393</v>
       </c>
       <c r="B46" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -10330,7 +10330,7 @@
         <v>638</v>
       </c>
       <c r="B47" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -10338,7 +10338,7 @@
         <v>394</v>
       </c>
       <c r="B48" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -10346,7 +10346,7 @@
         <v>395</v>
       </c>
       <c r="B49" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -10354,7 +10354,7 @@
         <v>396</v>
       </c>
       <c r="B50" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -10362,7 +10362,7 @@
         <v>728</v>
       </c>
       <c r="B51" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -10370,7 +10370,7 @@
         <v>553</v>
       </c>
       <c r="B52" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -10378,7 +10378,7 @@
         <v>718</v>
       </c>
       <c r="B53" s="1">
-        <v>30250</v>
+        <v>30800</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -10386,7 +10386,7 @@
         <v>719</v>
       </c>
       <c r="B54" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -10394,7 +10394,7 @@
         <v>752</v>
       </c>
       <c r="B55" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -10402,7 +10402,7 @@
         <v>723</v>
       </c>
       <c r="B56" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -10410,7 +10410,7 @@
         <v>720</v>
       </c>
       <c r="B57" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -10418,7 +10418,7 @@
         <v>724</v>
       </c>
       <c r="B58" s="1">
-        <v>41250</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -10426,7 +10426,7 @@
         <v>721</v>
       </c>
       <c r="B59" s="1">
-        <v>35750</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -10434,7 +10434,7 @@
         <v>725</v>
       </c>
       <c r="B60" s="1">
-        <v>44000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -10442,7 +10442,7 @@
         <v>726</v>
       </c>
       <c r="B61" s="1">
-        <v>46750</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -10450,7 +10450,7 @@
         <v>727</v>
       </c>
       <c r="B62" s="1">
-        <v>49500</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -10458,7 +10458,7 @@
         <v>740</v>
       </c>
       <c r="B63" s="1">
-        <v>121000</v>
+        <v>123200</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -10466,7 +10466,7 @@
         <v>827</v>
       </c>
       <c r="B64" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -10474,7 +10474,7 @@
         <v>639</v>
       </c>
       <c r="B65" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -10482,7 +10482,7 @@
         <v>543</v>
       </c>
       <c r="B66" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -10490,7 +10490,7 @@
         <v>397</v>
       </c>
       <c r="B67" s="1">
-        <v>9900</v>
+        <v>10080</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -10498,7 +10498,7 @@
         <v>653</v>
       </c>
       <c r="B68" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -10506,7 +10506,7 @@
         <v>398</v>
       </c>
       <c r="B69" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -10514,7 +10514,7 @@
         <v>399</v>
       </c>
       <c r="B70" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -10522,7 +10522,7 @@
         <v>400</v>
       </c>
       <c r="B71" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -10530,7 +10530,7 @@
         <v>582</v>
       </c>
       <c r="B72" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -10538,7 +10538,7 @@
         <v>401</v>
       </c>
       <c r="B73" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -10546,7 +10546,7 @@
         <v>588</v>
       </c>
       <c r="B74" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -10554,7 +10554,7 @@
         <v>554</v>
       </c>
       <c r="B75" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -10562,7 +10562,7 @@
         <v>555</v>
       </c>
       <c r="B76" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -10570,7 +10570,7 @@
         <v>644</v>
       </c>
       <c r="B77" s="1">
-        <v>3850</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -10578,7 +10578,7 @@
         <v>645</v>
       </c>
       <c r="B78" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -10586,7 +10586,7 @@
         <v>403</v>
       </c>
       <c r="B79" s="1">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -10594,7 +10594,7 @@
         <v>546</v>
       </c>
       <c r="B80" s="1">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -10602,7 +10602,7 @@
         <v>556</v>
       </c>
       <c r="B81" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -10610,7 +10610,7 @@
         <v>557</v>
       </c>
       <c r="B82" s="1">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -10618,7 +10618,7 @@
         <v>558</v>
       </c>
       <c r="B83" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
   </sheetData>

--- a/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\560 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\570 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16E5369-0296-4E1A-9A06-423ED8C364D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB9E325-B57F-4FBB-A8FA-5368281D960E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3034,7 +3034,7 @@
         <v>166</v>
       </c>
       <c r="B2" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3042,7 +3042,7 @@
         <v>421</v>
       </c>
       <c r="B3" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3050,7 +3050,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3058,7 +3058,7 @@
         <v>459</v>
       </c>
       <c r="B5" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3066,7 +3066,7 @@
         <v>460</v>
       </c>
       <c r="B6" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3074,7 +3074,7 @@
         <v>593</v>
       </c>
       <c r="B7" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3082,7 +3082,7 @@
         <v>168</v>
       </c>
       <c r="B8" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3090,7 +3090,7 @@
         <v>461</v>
       </c>
       <c r="B9" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3098,7 +3098,7 @@
         <v>169</v>
       </c>
       <c r="B10" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3106,7 +3106,7 @@
         <v>170</v>
       </c>
       <c r="B11" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3114,7 +3114,7 @@
         <v>171</v>
       </c>
       <c r="B12" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3122,7 +3122,7 @@
         <v>174</v>
       </c>
       <c r="B13" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3130,7 +3130,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3138,7 +3138,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="1">
-        <v>61600</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3146,7 +3146,7 @@
         <v>666</v>
       </c>
       <c r="B16" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3154,7 +3154,7 @@
         <v>175</v>
       </c>
       <c r="B17" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3162,7 +3162,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3170,7 +3170,7 @@
         <v>589</v>
       </c>
       <c r="B19" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3178,7 +3178,7 @@
         <v>462</v>
       </c>
       <c r="B20" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3186,7 +3186,7 @@
         <v>177</v>
       </c>
       <c r="B21" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3194,7 +3194,7 @@
         <v>178</v>
       </c>
       <c r="B22" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3202,7 +3202,7 @@
         <v>179</v>
       </c>
       <c r="B23" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3210,7 +3210,7 @@
         <v>550</v>
       </c>
       <c r="B24" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3218,7 +3218,7 @@
         <v>180</v>
       </c>
       <c r="B25" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3226,7 +3226,7 @@
         <v>181</v>
       </c>
       <c r="B26" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3234,7 +3234,7 @@
         <v>182</v>
       </c>
       <c r="B27" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3242,7 +3242,7 @@
         <v>183</v>
       </c>
       <c r="B28" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3250,7 +3250,7 @@
         <v>184</v>
       </c>
       <c r="B29" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3258,7 +3258,7 @@
         <v>185</v>
       </c>
       <c r="B30" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3266,7 +3266,7 @@
         <v>186</v>
       </c>
       <c r="B31" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3274,7 +3274,7 @@
         <v>187</v>
       </c>
       <c r="B32" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3282,7 +3282,7 @@
         <v>188</v>
       </c>
       <c r="B33" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3290,7 +3290,7 @@
         <v>606</v>
       </c>
       <c r="B34" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3298,7 +3298,7 @@
         <v>569</v>
       </c>
       <c r="B35" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3306,7 +3306,7 @@
         <v>594</v>
       </c>
       <c r="B36" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3314,7 +3314,7 @@
         <v>823</v>
       </c>
       <c r="B37" s="1">
-        <v>47600</v>
+        <v>48450</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3322,7 +3322,7 @@
         <v>430</v>
       </c>
       <c r="B38" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3330,7 +3330,7 @@
         <v>163</v>
       </c>
       <c r="B39" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3338,7 +3338,7 @@
         <v>647</v>
       </c>
       <c r="B40" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3346,7 +3346,7 @@
         <v>581</v>
       </c>
       <c r="B41" s="1">
-        <v>61600</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3354,7 +3354,7 @@
         <v>648</v>
       </c>
       <c r="B42" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3362,7 +3362,7 @@
         <v>189</v>
       </c>
       <c r="B43" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3370,7 +3370,7 @@
         <v>419</v>
       </c>
       <c r="B44" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3378,7 +3378,7 @@
         <v>408</v>
       </c>
       <c r="B45" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3386,7 +3386,7 @@
         <v>729</v>
       </c>
       <c r="B46" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3394,7 +3394,7 @@
         <v>730</v>
       </c>
       <c r="B47" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3402,7 +3402,7 @@
         <v>190</v>
       </c>
       <c r="B48" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3410,7 +3410,7 @@
         <v>191</v>
       </c>
       <c r="B49" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3418,7 +3418,7 @@
         <v>192</v>
       </c>
       <c r="B50" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3426,7 +3426,7 @@
         <v>193</v>
       </c>
       <c r="B51" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3434,7 +3434,7 @@
         <v>692</v>
       </c>
       <c r="B52" s="1">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3442,7 +3442,7 @@
         <v>194</v>
       </c>
       <c r="B53" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3450,7 +3450,7 @@
         <v>406</v>
       </c>
       <c r="B54" s="1">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3458,7 +3458,7 @@
         <v>402</v>
       </c>
       <c r="B55" s="1">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3466,7 +3466,7 @@
         <v>429</v>
       </c>
       <c r="B56" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3474,7 +3474,7 @@
         <v>195</v>
       </c>
       <c r="B57" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3482,7 +3482,7 @@
         <v>196</v>
       </c>
       <c r="B58" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3490,7 +3490,7 @@
         <v>197</v>
       </c>
       <c r="B59" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3498,7 +3498,7 @@
         <v>595</v>
       </c>
       <c r="B60" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3506,7 +3506,7 @@
         <v>596</v>
       </c>
       <c r="B61" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3514,7 +3514,7 @@
         <v>198</v>
       </c>
       <c r="B62" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3522,7 +3522,7 @@
         <v>199</v>
       </c>
       <c r="B63" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3530,7 +3530,7 @@
         <v>200</v>
       </c>
       <c r="B64" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3538,7 +3538,7 @@
         <v>201</v>
       </c>
       <c r="B65" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3546,7 +3546,7 @@
         <v>202</v>
       </c>
       <c r="B66" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3554,7 +3554,7 @@
         <v>203</v>
       </c>
       <c r="B67" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3562,7 +3562,7 @@
         <v>204</v>
       </c>
       <c r="B68" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3570,7 +3570,7 @@
         <v>205</v>
       </c>
       <c r="B69" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3578,7 +3578,7 @@
         <v>206</v>
       </c>
       <c r="B70" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3586,7 +3586,7 @@
         <v>208</v>
       </c>
       <c r="B71" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3594,7 +3594,7 @@
         <v>212</v>
       </c>
       <c r="B72" s="1">
-        <v>1120</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3602,7 +3602,7 @@
         <v>209</v>
       </c>
       <c r="B73" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3610,7 +3610,7 @@
         <v>210</v>
       </c>
       <c r="B74" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3618,7 +3618,7 @@
         <v>211</v>
       </c>
       <c r="B75" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3626,7 +3626,7 @@
         <v>476</v>
       </c>
       <c r="B76" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3634,7 +3634,7 @@
         <v>207</v>
       </c>
       <c r="B77" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3642,7 +3642,7 @@
         <v>213</v>
       </c>
       <c r="B78" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3650,7 +3650,7 @@
         <v>214</v>
       </c>
       <c r="B79" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3658,7 +3658,7 @@
         <v>215</v>
       </c>
       <c r="B80" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3666,7 +3666,7 @@
         <v>216</v>
       </c>
       <c r="B81" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3674,7 +3674,7 @@
         <v>217</v>
       </c>
       <c r="B82" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3682,7 +3682,7 @@
         <v>218</v>
       </c>
       <c r="B83" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3690,7 +3690,7 @@
         <v>219</v>
       </c>
       <c r="B84" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3698,7 +3698,7 @@
         <v>220</v>
       </c>
       <c r="B85" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3706,7 +3706,7 @@
         <v>607</v>
       </c>
       <c r="B86" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3714,7 +3714,7 @@
         <v>221</v>
       </c>
       <c r="B87" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3722,7 +3722,7 @@
         <v>608</v>
       </c>
       <c r="B88" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3730,7 +3730,7 @@
         <v>417</v>
       </c>
       <c r="B89" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3738,7 +3738,7 @@
         <v>418</v>
       </c>
       <c r="B90" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3746,7 +3746,7 @@
         <v>222</v>
       </c>
       <c r="B91" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3754,7 +3754,7 @@
         <v>223</v>
       </c>
       <c r="B92" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3762,7 +3762,7 @@
         <v>224</v>
       </c>
       <c r="B93" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3770,7 +3770,7 @@
         <v>225</v>
       </c>
       <c r="B94" s="1">
-        <v>196000</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3778,7 +3778,7 @@
         <v>226</v>
       </c>
       <c r="B95" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3786,7 +3786,7 @@
         <v>824</v>
       </c>
       <c r="B96" s="1">
-        <v>168000</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3794,7 +3794,7 @@
         <v>227</v>
       </c>
       <c r="B97" s="1">
-        <v>156800</v>
+        <v>159600</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3802,7 +3802,7 @@
         <v>228</v>
       </c>
       <c r="B98" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3810,7 +3810,7 @@
         <v>551</v>
       </c>
       <c r="B99" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3818,7 +3818,7 @@
         <v>667</v>
       </c>
       <c r="B100" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3826,7 +3826,7 @@
         <v>409</v>
       </c>
       <c r="B101" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3834,7 +3834,7 @@
         <v>229</v>
       </c>
       <c r="B102" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3842,7 +3842,7 @@
         <v>230</v>
       </c>
       <c r="B103" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3850,7 +3850,7 @@
         <v>231</v>
       </c>
       <c r="B104" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3858,7 +3858,7 @@
         <v>424</v>
       </c>
       <c r="B105" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3866,7 +3866,7 @@
         <v>232</v>
       </c>
       <c r="B106" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3874,7 +3874,7 @@
         <v>570</v>
       </c>
       <c r="B107" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3882,7 +3882,7 @@
         <v>483</v>
       </c>
       <c r="B108" s="1">
-        <v>140000</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3890,7 +3890,7 @@
         <v>587</v>
       </c>
       <c r="B109" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3898,7 +3898,7 @@
         <v>233</v>
       </c>
       <c r="B110" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3906,7 +3906,7 @@
         <v>234</v>
       </c>
       <c r="B111" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3914,7 +3914,7 @@
         <v>731</v>
       </c>
       <c r="B112" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3922,7 +3922,7 @@
         <v>717</v>
       </c>
       <c r="B113" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3930,7 +3930,7 @@
         <v>571</v>
       </c>
       <c r="B114" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3938,7 +3938,7 @@
         <v>590</v>
       </c>
       <c r="B115" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3946,7 +3946,7 @@
         <v>235</v>
       </c>
       <c r="B116" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3954,7 +3954,7 @@
         <v>732</v>
       </c>
       <c r="B117" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3962,7 +3962,7 @@
         <v>236</v>
       </c>
       <c r="B118" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3970,7 +3970,7 @@
         <v>733</v>
       </c>
       <c r="B119" s="1">
-        <v>1120</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3978,7 +3978,7 @@
         <v>237</v>
       </c>
       <c r="B120" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3986,7 +3986,7 @@
         <v>410</v>
       </c>
       <c r="B121" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3994,7 +3994,7 @@
         <v>238</v>
       </c>
       <c r="B122" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4002,7 +4002,7 @@
         <v>239</v>
       </c>
       <c r="B123" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4010,7 +4010,7 @@
         <v>240</v>
       </c>
       <c r="B124" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4018,7 +4018,7 @@
         <v>241</v>
       </c>
       <c r="B125" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4026,7 +4026,7 @@
         <v>242</v>
       </c>
       <c r="B126" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4034,7 +4034,7 @@
         <v>243</v>
       </c>
       <c r="B127" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4042,7 +4042,7 @@
         <v>668</v>
       </c>
       <c r="B128" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4050,7 +4050,7 @@
         <v>669</v>
       </c>
       <c r="B129" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4058,7 +4058,7 @@
         <v>431</v>
       </c>
       <c r="B130" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4066,7 +4066,7 @@
         <v>244</v>
       </c>
       <c r="B131" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4074,7 +4074,7 @@
         <v>597</v>
       </c>
       <c r="B132" s="1">
-        <v>240800</v>
+        <v>245100</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4082,7 +4082,7 @@
         <v>245</v>
       </c>
       <c r="B133" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4090,7 +4090,7 @@
         <v>456</v>
       </c>
       <c r="B134" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4098,7 +4098,7 @@
         <v>457</v>
       </c>
       <c r="B135" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4106,7 +4106,7 @@
         <v>458</v>
       </c>
       <c r="B136" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4114,7 +4114,7 @@
         <v>246</v>
       </c>
       <c r="B137" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4122,7 +4122,7 @@
         <v>247</v>
       </c>
       <c r="B138" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4130,7 +4130,7 @@
         <v>248</v>
       </c>
       <c r="B139" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4138,7 +4138,7 @@
         <v>250</v>
       </c>
       <c r="B140" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4146,7 +4146,7 @@
         <v>420</v>
       </c>
       <c r="B141" s="1">
-        <v>140000</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4154,7 +4154,7 @@
         <v>14</v>
       </c>
       <c r="B142" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4162,7 +4162,7 @@
         <v>602</v>
       </c>
       <c r="B143" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4170,7 +4170,7 @@
         <v>249</v>
       </c>
       <c r="B144" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4178,7 +4178,7 @@
         <v>552</v>
       </c>
       <c r="B145" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4186,7 +4186,7 @@
         <v>251</v>
       </c>
       <c r="B146" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4194,7 +4194,7 @@
         <v>825</v>
       </c>
       <c r="B147" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4202,7 +4202,7 @@
         <v>252</v>
       </c>
       <c r="B148" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4210,7 +4210,7 @@
         <v>253</v>
       </c>
       <c r="B149" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4218,7 +4218,7 @@
         <v>598</v>
       </c>
       <c r="B150" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4226,7 +4226,7 @@
         <v>254</v>
       </c>
       <c r="B151" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4234,7 +4234,7 @@
         <v>255</v>
       </c>
       <c r="B152" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4242,7 +4242,7 @@
         <v>256</v>
       </c>
       <c r="B153" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4250,7 +4250,7 @@
         <v>257</v>
       </c>
       <c r="B154" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4258,7 +4258,7 @@
         <v>258</v>
       </c>
       <c r="B155" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4266,7 +4266,7 @@
         <v>261</v>
       </c>
       <c r="B156" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4274,7 +4274,7 @@
         <v>262</v>
       </c>
       <c r="B157" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4282,7 +4282,7 @@
         <v>263</v>
       </c>
       <c r="B158" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4290,7 +4290,7 @@
         <v>404</v>
       </c>
       <c r="B159" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4298,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="B160" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4306,7 +4306,7 @@
         <v>463</v>
       </c>
       <c r="B161" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4314,7 +4314,7 @@
         <v>260</v>
       </c>
       <c r="B162" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4322,7 +4322,7 @@
         <v>264</v>
       </c>
       <c r="B163" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4330,7 +4330,7 @@
         <v>689</v>
       </c>
       <c r="B164" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4338,7 +4338,7 @@
         <v>641</v>
       </c>
       <c r="B165" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4346,7 +4346,7 @@
         <v>642</v>
       </c>
       <c r="B166" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4354,7 +4354,7 @@
         <v>603</v>
       </c>
       <c r="B167" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4362,7 +4362,7 @@
         <v>604</v>
       </c>
       <c r="B168" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4370,7 +4370,7 @@
         <v>484</v>
       </c>
       <c r="B169" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4378,7 +4378,7 @@
         <v>265</v>
       </c>
       <c r="B170" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4386,7 +4386,7 @@
         <v>609</v>
       </c>
       <c r="B171" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4394,7 +4394,7 @@
         <v>734</v>
       </c>
       <c r="B172" s="1">
-        <v>2240</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4402,7 +4402,7 @@
         <v>735</v>
       </c>
       <c r="B173" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4410,7 +4410,7 @@
         <v>266</v>
       </c>
       <c r="B174" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4418,7 +4418,7 @@
         <v>267</v>
       </c>
       <c r="B175" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4426,7 +4426,7 @@
         <v>268</v>
       </c>
       <c r="B176" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4434,7 +4434,7 @@
         <v>269</v>
       </c>
       <c r="B177" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4442,7 +4442,7 @@
         <v>270</v>
       </c>
       <c r="B178" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4450,7 +4450,7 @@
         <v>271</v>
       </c>
       <c r="B179" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4458,7 +4458,7 @@
         <v>272</v>
       </c>
       <c r="B180" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4466,7 +4466,7 @@
         <v>273</v>
       </c>
       <c r="B181" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4474,7 +4474,7 @@
         <v>422</v>
       </c>
       <c r="B182" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4482,7 +4482,7 @@
         <v>423</v>
       </c>
       <c r="B183" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4490,7 +4490,7 @@
         <v>610</v>
       </c>
       <c r="B184" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4498,7 +4498,7 @@
         <v>611</v>
       </c>
       <c r="B185" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4506,7 +4506,7 @@
         <v>612</v>
       </c>
       <c r="B186" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4514,7 +4514,7 @@
         <v>613</v>
       </c>
       <c r="B187" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4522,7 +4522,7 @@
         <v>614</v>
       </c>
       <c r="B188" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4530,7 +4530,7 @@
         <v>615</v>
       </c>
       <c r="B189" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4538,7 +4538,7 @@
         <v>274</v>
       </c>
       <c r="B190" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4546,7 +4546,7 @@
         <v>276</v>
       </c>
       <c r="B191" s="1">
-        <v>1120</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4554,7 +4554,7 @@
         <v>275</v>
       </c>
       <c r="B192" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4562,7 +4562,7 @@
         <v>616</v>
       </c>
       <c r="B193" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4570,7 +4570,7 @@
         <v>277</v>
       </c>
       <c r="B194" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4578,7 +4578,7 @@
         <v>464</v>
       </c>
       <c r="B195" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4586,7 +4586,7 @@
         <v>278</v>
       </c>
       <c r="B196" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4594,7 +4594,7 @@
         <v>736</v>
       </c>
       <c r="B197" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4602,7 +4602,7 @@
         <v>391</v>
       </c>
       <c r="B198" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4610,7 +4610,7 @@
         <v>396</v>
       </c>
       <c r="B199" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4618,7 +4618,7 @@
         <v>466</v>
       </c>
       <c r="B200" s="1">
-        <v>179200</v>
+        <v>182400</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4626,7 +4626,7 @@
         <v>279</v>
       </c>
       <c r="B201" s="1">
-        <v>291200</v>
+        <v>296400</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4634,7 +4634,7 @@
         <v>649</v>
       </c>
       <c r="B202" s="1">
-        <v>296800</v>
+        <v>302100</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4642,7 +4642,7 @@
         <v>280</v>
       </c>
       <c r="B203" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4650,7 +4650,7 @@
         <v>696</v>
       </c>
       <c r="B204" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4658,7 +4658,7 @@
         <v>737</v>
       </c>
       <c r="B205" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4666,7 +4666,7 @@
         <v>411</v>
       </c>
       <c r="B206" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4674,7 +4674,7 @@
         <v>281</v>
       </c>
       <c r="B207" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4682,7 +4682,7 @@
         <v>412</v>
       </c>
       <c r="B208" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4690,7 +4690,7 @@
         <v>282</v>
       </c>
       <c r="B209" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4698,7 +4698,7 @@
         <v>283</v>
       </c>
       <c r="B210" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4706,7 +4706,7 @@
         <v>284</v>
       </c>
       <c r="B211" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4714,7 +4714,7 @@
         <v>285</v>
       </c>
       <c r="B212" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4722,7 +4722,7 @@
         <v>286</v>
       </c>
       <c r="B213" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4730,7 +4730,7 @@
         <v>287</v>
       </c>
       <c r="B214" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4738,7 +4738,7 @@
         <v>288</v>
       </c>
       <c r="B215" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4746,7 +4746,7 @@
         <v>289</v>
       </c>
       <c r="B216" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4754,7 +4754,7 @@
         <v>553</v>
       </c>
       <c r="B217" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4762,7 +4762,7 @@
         <v>290</v>
       </c>
       <c r="B218" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4770,7 +4770,7 @@
         <v>738</v>
       </c>
       <c r="B219" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4778,7 +4778,7 @@
         <v>739</v>
       </c>
       <c r="B220" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4786,7 +4786,7 @@
         <v>291</v>
       </c>
       <c r="B221" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4794,7 +4794,7 @@
         <v>292</v>
       </c>
       <c r="B222" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4802,7 +4802,7 @@
         <v>293</v>
       </c>
       <c r="B223" s="1">
-        <v>156800</v>
+        <v>159600</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4810,7 +4810,7 @@
         <v>294</v>
       </c>
       <c r="B224" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4818,7 +4818,7 @@
         <v>572</v>
       </c>
       <c r="B225" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4826,7 +4826,7 @@
         <v>670</v>
       </c>
       <c r="B226" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4834,7 +4834,7 @@
         <v>295</v>
       </c>
       <c r="B227" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4842,7 +4842,7 @@
         <v>671</v>
       </c>
       <c r="B228" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4850,7 +4850,7 @@
         <v>296</v>
       </c>
       <c r="B229" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4858,7 +4858,7 @@
         <v>718</v>
       </c>
       <c r="B230" s="1">
-        <v>30800</v>
+        <v>31350</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4866,7 +4866,7 @@
         <v>719</v>
       </c>
       <c r="B231" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4874,7 +4874,7 @@
         <v>720</v>
       </c>
       <c r="B232" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4882,7 +4882,7 @@
         <v>721</v>
       </c>
       <c r="B233" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4890,7 +4890,7 @@
         <v>617</v>
       </c>
       <c r="B234" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4898,7 +4898,7 @@
         <v>297</v>
       </c>
       <c r="B235" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4906,7 +4906,7 @@
         <v>573</v>
       </c>
       <c r="B236" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4914,7 +4914,7 @@
         <v>298</v>
       </c>
       <c r="B237" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4922,7 +4922,7 @@
         <v>299</v>
       </c>
       <c r="B238" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4930,7 +4930,7 @@
         <v>300</v>
       </c>
       <c r="B239" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4938,7 +4938,7 @@
         <v>301</v>
       </c>
       <c r="B240" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4946,7 +4946,7 @@
         <v>302</v>
       </c>
       <c r="B241" s="1">
-        <v>168000</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4954,7 +4954,7 @@
         <v>672</v>
       </c>
       <c r="B242" s="1">
-        <v>168000</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4962,7 +4962,7 @@
         <v>303</v>
       </c>
       <c r="B243" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4970,7 +4970,7 @@
         <v>740</v>
       </c>
       <c r="B244" s="1">
-        <v>123200</v>
+        <v>125400</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4978,7 +4978,7 @@
         <v>304</v>
       </c>
       <c r="B245" s="1">
-        <v>61600</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4986,7 +4986,7 @@
         <v>305</v>
       </c>
       <c r="B246" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4994,7 +4994,7 @@
         <v>306</v>
       </c>
       <c r="B247" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5002,7 +5002,7 @@
         <v>618</v>
       </c>
       <c r="B248" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5010,7 +5010,7 @@
         <v>307</v>
       </c>
       <c r="B249" s="1">
-        <v>95200</v>
+        <v>96900</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5018,7 +5018,7 @@
         <v>308</v>
       </c>
       <c r="B250" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5026,7 +5026,7 @@
         <v>309</v>
       </c>
       <c r="B251" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5034,7 +5034,7 @@
         <v>310</v>
       </c>
       <c r="B252" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5042,7 +5042,7 @@
         <v>690</v>
       </c>
       <c r="B253" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5050,7 +5050,7 @@
         <v>311</v>
       </c>
       <c r="B254" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5058,7 +5058,7 @@
         <v>312</v>
       </c>
       <c r="B255" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5066,7 +5066,7 @@
         <v>313</v>
       </c>
       <c r="B256" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5074,7 +5074,7 @@
         <v>467</v>
       </c>
       <c r="B257" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5082,7 +5082,7 @@
         <v>741</v>
       </c>
       <c r="B258" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5090,7 +5090,7 @@
         <v>742</v>
       </c>
       <c r="B259" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5098,7 +5098,7 @@
         <v>468</v>
       </c>
       <c r="B260" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5106,7 +5106,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5114,7 +5114,7 @@
         <v>315</v>
       </c>
       <c r="B262" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5122,7 +5122,7 @@
         <v>316</v>
       </c>
       <c r="B263" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5130,7 +5130,7 @@
         <v>414</v>
       </c>
       <c r="B264" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5138,7 +5138,7 @@
         <v>317</v>
       </c>
       <c r="B265" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5146,7 +5146,7 @@
         <v>318</v>
       </c>
       <c r="B266" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5154,7 +5154,7 @@
         <v>605</v>
       </c>
       <c r="B267" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5162,7 +5162,7 @@
         <v>319</v>
       </c>
       <c r="B268" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5170,7 +5170,7 @@
         <v>320</v>
       </c>
       <c r="B269" s="1">
-        <v>168000</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5178,7 +5178,7 @@
         <v>321</v>
       </c>
       <c r="B270" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5186,7 +5186,7 @@
         <v>322</v>
       </c>
       <c r="B271" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5194,7 +5194,7 @@
         <v>323</v>
       </c>
       <c r="B272" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5202,7 +5202,7 @@
         <v>324</v>
       </c>
       <c r="B273" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5210,7 +5210,7 @@
         <v>325</v>
       </c>
       <c r="B274" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5218,7 +5218,7 @@
         <v>326</v>
       </c>
       <c r="B275" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5226,7 +5226,7 @@
         <v>327</v>
       </c>
       <c r="B276" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5234,7 +5234,7 @@
         <v>328</v>
       </c>
       <c r="B277" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5242,7 +5242,7 @@
         <v>329</v>
       </c>
       <c r="B278" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5250,7 +5250,7 @@
         <v>330</v>
       </c>
       <c r="B279" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5258,7 +5258,7 @@
         <v>331</v>
       </c>
       <c r="B280" s="1">
-        <v>72800</v>
+        <v>74100</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5266,7 +5266,7 @@
         <v>332</v>
       </c>
       <c r="B281" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5274,7 +5274,7 @@
         <v>333</v>
       </c>
       <c r="B282" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5282,7 +5282,7 @@
         <v>334</v>
       </c>
       <c r="B283" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5290,7 +5290,7 @@
         <v>574</v>
       </c>
       <c r="B284" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5298,7 +5298,7 @@
         <v>599</v>
       </c>
       <c r="B285" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5306,7 +5306,7 @@
         <v>600</v>
       </c>
       <c r="B286" s="1">
-        <v>53200</v>
+        <v>54150</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5314,7 +5314,7 @@
         <v>743</v>
       </c>
       <c r="B287" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5322,7 +5322,7 @@
         <v>619</v>
       </c>
       <c r="B288" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5330,7 +5330,7 @@
         <v>335</v>
       </c>
       <c r="B289" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5338,7 +5338,7 @@
         <v>620</v>
       </c>
       <c r="B290" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5346,7 +5346,7 @@
         <v>336</v>
       </c>
       <c r="B291" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5354,7 +5354,7 @@
         <v>337</v>
       </c>
       <c r="B292" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5362,7 +5362,7 @@
         <v>338</v>
       </c>
       <c r="B293" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5370,7 +5370,7 @@
         <v>339</v>
       </c>
       <c r="B294" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5378,7 +5378,7 @@
         <v>340</v>
       </c>
       <c r="B295" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5386,7 +5386,7 @@
         <v>341</v>
       </c>
       <c r="B296" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5394,7 +5394,7 @@
         <v>342</v>
       </c>
       <c r="B297" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5402,7 +5402,7 @@
         <v>343</v>
       </c>
       <c r="B298" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5410,7 +5410,7 @@
         <v>415</v>
       </c>
       <c r="B299" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5418,7 +5418,7 @@
         <v>416</v>
       </c>
       <c r="B300" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5426,7 +5426,7 @@
         <v>601</v>
       </c>
       <c r="B301" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5434,7 +5434,7 @@
         <v>344</v>
       </c>
       <c r="B302" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5442,7 +5442,7 @@
         <v>345</v>
       </c>
       <c r="B303" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5450,7 +5450,7 @@
         <v>346</v>
       </c>
       <c r="B304" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5458,7 +5458,7 @@
         <v>347</v>
       </c>
       <c r="B305" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5466,7 +5466,7 @@
         <v>348</v>
       </c>
       <c r="B306" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5474,7 +5474,7 @@
         <v>349</v>
       </c>
       <c r="B307" s="1">
-        <v>2240</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5482,7 +5482,7 @@
         <v>744</v>
       </c>
       <c r="B308" s="1">
-        <v>1120</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5490,7 +5490,7 @@
         <v>673</v>
       </c>
       <c r="B309" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5498,7 +5498,7 @@
         <v>350</v>
       </c>
       <c r="B310" s="1">
-        <v>42000</v>
+        <v>42750</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5506,7 +5506,7 @@
         <v>351</v>
       </c>
       <c r="B311" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5514,7 +5514,7 @@
         <v>352</v>
       </c>
       <c r="B312" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5522,7 +5522,7 @@
         <v>575</v>
       </c>
       <c r="B313" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5530,7 +5530,7 @@
         <v>353</v>
       </c>
       <c r="B314" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5538,7 +5538,7 @@
         <v>354</v>
       </c>
       <c r="B315" s="1">
-        <v>140000</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5546,7 +5546,7 @@
         <v>407</v>
       </c>
       <c r="B316" s="1">
-        <v>308000</v>
+        <v>313500</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5554,7 +5554,7 @@
         <v>355</v>
       </c>
       <c r="B317" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5562,7 +5562,7 @@
         <v>356</v>
       </c>
       <c r="B318" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5570,7 +5570,7 @@
         <v>576</v>
       </c>
       <c r="B319" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5578,7 +5578,7 @@
         <v>357</v>
       </c>
       <c r="B320" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5586,7 +5586,7 @@
         <v>358</v>
       </c>
       <c r="B321" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5594,7 +5594,7 @@
         <v>651</v>
       </c>
       <c r="B322" s="1">
-        <v>2240</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5602,7 +5602,7 @@
         <v>577</v>
       </c>
       <c r="B323" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5610,7 +5610,7 @@
         <v>588</v>
       </c>
       <c r="B324" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5618,7 +5618,7 @@
         <v>359</v>
       </c>
       <c r="B325" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5626,7 +5626,7 @@
         <v>360</v>
       </c>
       <c r="B326" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5634,7 +5634,7 @@
         <v>361</v>
       </c>
       <c r="B327" s="1">
-        <v>2240</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5642,7 +5642,7 @@
         <v>362</v>
       </c>
       <c r="B328" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5650,7 +5650,7 @@
         <v>363</v>
       </c>
       <c r="B329" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5658,7 +5658,7 @@
         <v>364</v>
       </c>
       <c r="B330" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5666,7 +5666,7 @@
         <v>365</v>
       </c>
       <c r="B331" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5674,7 +5674,7 @@
         <v>403</v>
       </c>
       <c r="B332" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5682,7 +5682,7 @@
         <v>546</v>
       </c>
       <c r="B333" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5690,7 +5690,7 @@
         <v>822</v>
       </c>
       <c r="B334" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5698,7 +5698,7 @@
         <v>366</v>
       </c>
       <c r="B335" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5706,7 +5706,7 @@
         <v>556</v>
       </c>
       <c r="B336" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5714,7 +5714,7 @@
         <v>557</v>
       </c>
       <c r="B337" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5722,7 +5722,7 @@
         <v>367</v>
       </c>
       <c r="B338" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5730,7 +5730,7 @@
         <v>368</v>
       </c>
       <c r="B339" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5738,7 +5738,7 @@
         <v>369</v>
       </c>
       <c r="B340" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5746,7 +5746,7 @@
         <v>370</v>
       </c>
       <c r="B341" s="1">
-        <v>1120</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5754,7 +5754,7 @@
         <v>371</v>
       </c>
       <c r="B342" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5762,7 +5762,7 @@
         <v>372</v>
       </c>
       <c r="B343" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5770,7 +5770,7 @@
         <v>373</v>
       </c>
       <c r="B344" s="1">
-        <v>2240</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5778,7 +5778,7 @@
         <v>413</v>
       </c>
       <c r="B345" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5786,7 +5786,7 @@
         <v>465</v>
       </c>
       <c r="B346" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5794,7 +5794,7 @@
         <v>621</v>
       </c>
       <c r="B347" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5802,7 +5802,7 @@
         <v>374</v>
       </c>
       <c r="B348" s="1">
-        <v>1120</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5810,7 +5810,7 @@
         <v>485</v>
       </c>
       <c r="B349" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5818,7 +5818,7 @@
         <v>469</v>
       </c>
       <c r="B350" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5826,7 +5826,7 @@
         <v>375</v>
       </c>
       <c r="B351" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5834,7 +5834,7 @@
         <v>674</v>
       </c>
       <c r="B352" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5842,7 +5842,7 @@
         <v>675</v>
       </c>
       <c r="B353" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5850,7 +5850,7 @@
         <v>376</v>
       </c>
       <c r="B354" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5858,7 +5858,7 @@
         <v>377</v>
       </c>
       <c r="B355" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5866,7 +5866,7 @@
         <v>378</v>
       </c>
       <c r="B356" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5874,7 +5874,7 @@
         <v>622</v>
       </c>
       <c r="B357" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5882,7 +5882,7 @@
         <v>379</v>
       </c>
       <c r="B358" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5890,7 +5890,7 @@
         <v>470</v>
       </c>
       <c r="B359" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5898,7 +5898,7 @@
         <v>471</v>
       </c>
       <c r="B360" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5906,7 +5906,7 @@
         <v>676</v>
       </c>
       <c r="B361" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5914,7 +5914,7 @@
         <v>380</v>
       </c>
       <c r="B362" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5922,7 +5922,7 @@
         <v>381</v>
       </c>
       <c r="B363" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5930,7 +5930,7 @@
         <v>454</v>
       </c>
       <c r="B364" s="1">
-        <v>2240</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5938,7 +5938,7 @@
         <v>382</v>
       </c>
       <c r="B365" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
   </sheetData>
@@ -5968,7 +5968,7 @@
         <v>486</v>
       </c>
       <c r="B2" s="1">
-        <v>78400</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5976,7 +5976,7 @@
         <v>123</v>
       </c>
       <c r="B3" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5984,7 +5984,7 @@
         <v>757</v>
       </c>
       <c r="B4" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5992,7 +5992,7 @@
         <v>578</v>
       </c>
       <c r="B5" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6000,7 +6000,7 @@
         <v>164</v>
       </c>
       <c r="B6" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6008,7 +6008,7 @@
         <v>579</v>
       </c>
       <c r="B7" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6016,7 +6016,7 @@
         <v>589</v>
       </c>
       <c r="B8" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6024,7 +6024,7 @@
         <v>758</v>
       </c>
       <c r="B9" s="1">
-        <v>72800</v>
+        <v>74100</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6032,7 +6032,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6040,7 +6040,7 @@
         <v>759</v>
       </c>
       <c r="B11" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6048,7 +6048,7 @@
         <v>124</v>
       </c>
       <c r="B12" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6056,7 +6056,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6064,7 +6064,7 @@
         <v>823</v>
       </c>
       <c r="B14" s="1">
-        <v>47600</v>
+        <v>48450</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6072,7 +6072,7 @@
         <v>430</v>
       </c>
       <c r="B15" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6080,7 +6080,7 @@
         <v>163</v>
       </c>
       <c r="B16" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6088,7 +6088,7 @@
         <v>647</v>
       </c>
       <c r="B17" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6096,7 +6096,7 @@
         <v>581</v>
       </c>
       <c r="B18" s="1">
-        <v>61600</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6104,7 +6104,7 @@
         <v>648</v>
       </c>
       <c r="B19" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6112,7 +6112,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6120,7 +6120,7 @@
         <v>125</v>
       </c>
       <c r="B21" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6128,7 +6128,7 @@
         <v>478</v>
       </c>
       <c r="B22" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6136,7 +6136,7 @@
         <v>36</v>
       </c>
       <c r="B23" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6144,7 +6144,7 @@
         <v>487</v>
       </c>
       <c r="B24" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6152,7 +6152,7 @@
         <v>488</v>
       </c>
       <c r="B25" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6160,7 +6160,7 @@
         <v>692</v>
       </c>
       <c r="B26" s="1">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6168,7 +6168,7 @@
         <v>406</v>
       </c>
       <c r="B27" s="1">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6176,7 +6176,7 @@
         <v>402</v>
       </c>
       <c r="B28" s="1">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6184,7 +6184,7 @@
         <v>439</v>
       </c>
       <c r="B29" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6192,7 +6192,7 @@
         <v>760</v>
       </c>
       <c r="B30" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6200,7 +6200,7 @@
         <v>489</v>
       </c>
       <c r="B31" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6208,7 +6208,7 @@
         <v>490</v>
       </c>
       <c r="B32" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6216,7 +6216,7 @@
         <v>761</v>
       </c>
       <c r="B33" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6224,7 +6224,7 @@
         <v>12</v>
       </c>
       <c r="B34" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6232,7 +6232,7 @@
         <v>762</v>
       </c>
       <c r="B35" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="1">
-        <v>1400</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6248,7 +6248,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6256,7 +6256,7 @@
         <v>434</v>
       </c>
       <c r="B38" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6264,7 +6264,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6272,7 +6272,7 @@
         <v>491</v>
       </c>
       <c r="B40" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6280,7 +6280,7 @@
         <v>479</v>
       </c>
       <c r="B41" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6288,7 +6288,7 @@
         <v>763</v>
       </c>
       <c r="B42" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6296,7 +6296,7 @@
         <v>438</v>
       </c>
       <c r="B43" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6304,7 +6304,7 @@
         <v>440</v>
       </c>
       <c r="B44" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6312,7 +6312,7 @@
         <v>492</v>
       </c>
       <c r="B45" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6320,7 +6320,7 @@
         <v>493</v>
       </c>
       <c r="B46" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6328,7 +6328,7 @@
         <v>494</v>
       </c>
       <c r="B47" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6336,7 +6336,7 @@
         <v>764</v>
       </c>
       <c r="B48" s="1">
-        <v>196000</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -6344,7 +6344,7 @@
         <v>551</v>
       </c>
       <c r="B49" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -6352,7 +6352,7 @@
         <v>765</v>
       </c>
       <c r="B50" s="1">
-        <v>72800</v>
+        <v>74100</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -6360,7 +6360,7 @@
         <v>751</v>
       </c>
       <c r="B51" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -6368,7 +6368,7 @@
         <v>722</v>
       </c>
       <c r="B52" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -6376,7 +6376,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -6384,7 +6384,7 @@
         <v>766</v>
       </c>
       <c r="B54" s="1">
-        <v>78400</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -6392,7 +6392,7 @@
         <v>495</v>
       </c>
       <c r="B55" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -6400,7 +6400,7 @@
         <v>436</v>
       </c>
       <c r="B56" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -6408,7 +6408,7 @@
         <v>126</v>
       </c>
       <c r="B57" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -6416,7 +6416,7 @@
         <v>496</v>
       </c>
       <c r="B58" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -6424,7 +6424,7 @@
         <v>767</v>
       </c>
       <c r="B59" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -6432,7 +6432,7 @@
         <v>30</v>
       </c>
       <c r="B60" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -6440,7 +6440,7 @@
         <v>427</v>
       </c>
       <c r="B61" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -6448,7 +6448,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -6456,7 +6456,7 @@
         <v>768</v>
       </c>
       <c r="B63" s="1">
-        <v>140000</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -6464,7 +6464,7 @@
         <v>769</v>
       </c>
       <c r="B64" s="1">
-        <v>123200</v>
+        <v>125400</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -6472,7 +6472,7 @@
         <v>127</v>
       </c>
       <c r="B65" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -6480,7 +6480,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -6488,7 +6488,7 @@
         <v>116</v>
       </c>
       <c r="B67" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6496,7 +6496,7 @@
         <v>14</v>
       </c>
       <c r="B68" s="1">
-        <v>72800</v>
+        <v>74100</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6504,7 +6504,7 @@
         <v>770</v>
       </c>
       <c r="B69" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -6512,7 +6512,7 @@
         <v>771</v>
       </c>
       <c r="B70" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -6520,7 +6520,7 @@
         <v>426</v>
       </c>
       <c r="B71" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -6528,7 +6528,7 @@
         <v>552</v>
       </c>
       <c r="B72" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -6536,7 +6536,7 @@
         <v>825</v>
       </c>
       <c r="B73" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -6544,7 +6544,7 @@
         <v>497</v>
       </c>
       <c r="B74" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -6552,7 +6552,7 @@
         <v>498</v>
       </c>
       <c r="B75" s="1">
-        <v>30800</v>
+        <v>31350</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -6560,7 +6560,7 @@
         <v>772</v>
       </c>
       <c r="B76" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -6568,7 +6568,7 @@
         <v>773</v>
       </c>
       <c r="B77" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -6576,7 +6576,7 @@
         <v>586</v>
       </c>
       <c r="B78" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -6584,7 +6584,7 @@
         <v>15</v>
       </c>
       <c r="B79" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -6592,7 +6592,7 @@
         <v>16</v>
       </c>
       <c r="B80" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -6600,7 +6600,7 @@
         <v>580</v>
       </c>
       <c r="B81" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -6608,7 +6608,7 @@
         <v>688</v>
       </c>
       <c r="B82" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -6616,7 +6616,7 @@
         <v>774</v>
       </c>
       <c r="B83" s="1">
-        <v>2240</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -6624,7 +6624,7 @@
         <v>484</v>
       </c>
       <c r="B84" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -6632,7 +6632,7 @@
         <v>775</v>
       </c>
       <c r="B85" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -6640,7 +6640,7 @@
         <v>735</v>
       </c>
       <c r="B86" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -6648,7 +6648,7 @@
         <v>3</v>
       </c>
       <c r="B87" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -6656,7 +6656,7 @@
         <v>17</v>
       </c>
       <c r="B88" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -6664,7 +6664,7 @@
         <v>128</v>
       </c>
       <c r="B89" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -6672,7 +6672,7 @@
         <v>715</v>
       </c>
       <c r="B90" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -6680,7 +6680,7 @@
         <v>499</v>
       </c>
       <c r="B91" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -6688,7 +6688,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -6696,7 +6696,7 @@
         <v>623</v>
       </c>
       <c r="B93" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -6704,7 +6704,7 @@
         <v>776</v>
       </c>
       <c r="B94" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -6712,7 +6712,7 @@
         <v>18</v>
       </c>
       <c r="B95" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -6720,7 +6720,7 @@
         <v>19</v>
       </c>
       <c r="B96" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -6728,7 +6728,7 @@
         <v>500</v>
       </c>
       <c r="B97" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -6736,7 +6736,7 @@
         <v>501</v>
       </c>
       <c r="B98" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -6744,7 +6744,7 @@
         <v>25</v>
       </c>
       <c r="B99" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -6752,7 +6752,7 @@
         <v>553</v>
       </c>
       <c r="B100" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -6760,7 +6760,7 @@
         <v>777</v>
       </c>
       <c r="B101" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -6768,7 +6768,7 @@
         <v>778</v>
       </c>
       <c r="B102" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -6776,7 +6776,7 @@
         <v>779</v>
       </c>
       <c r="B103" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -6784,7 +6784,7 @@
         <v>780</v>
       </c>
       <c r="B104" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -6792,7 +6792,7 @@
         <v>129</v>
       </c>
       <c r="B105" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -6800,7 +6800,7 @@
         <v>502</v>
       </c>
       <c r="B106" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -6808,7 +6808,7 @@
         <v>781</v>
       </c>
       <c r="B107" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -6816,7 +6816,7 @@
         <v>752</v>
       </c>
       <c r="B108" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -6824,7 +6824,7 @@
         <v>723</v>
       </c>
       <c r="B109" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -6832,7 +6832,7 @@
         <v>720</v>
       </c>
       <c r="B110" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -6840,7 +6840,7 @@
         <v>721</v>
       </c>
       <c r="B111" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -6848,7 +6848,7 @@
         <v>503</v>
       </c>
       <c r="B112" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -6856,7 +6856,7 @@
         <v>100</v>
       </c>
       <c r="B113" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -6864,7 +6864,7 @@
         <v>826</v>
       </c>
       <c r="B114" s="1">
-        <v>196000</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -6872,7 +6872,7 @@
         <v>654</v>
       </c>
       <c r="B115" s="1">
-        <v>196000</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -6880,7 +6880,7 @@
         <v>24</v>
       </c>
       <c r="B116" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -6888,7 +6888,7 @@
         <v>782</v>
       </c>
       <c r="B117" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -6896,7 +6896,7 @@
         <v>740</v>
       </c>
       <c r="B118" s="1">
-        <v>123200</v>
+        <v>125400</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -6904,7 +6904,7 @@
         <v>20</v>
       </c>
       <c r="B119" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -6912,7 +6912,7 @@
         <v>433</v>
       </c>
       <c r="B120" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -6920,7 +6920,7 @@
         <v>783</v>
       </c>
       <c r="B121" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -6928,7 +6928,7 @@
         <v>115</v>
       </c>
       <c r="B122" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -6936,7 +6936,7 @@
         <v>504</v>
       </c>
       <c r="B123" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -6944,7 +6944,7 @@
         <v>505</v>
       </c>
       <c r="B124" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -6952,7 +6952,7 @@
         <v>784</v>
       </c>
       <c r="B125" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -6960,7 +6960,7 @@
         <v>716</v>
       </c>
       <c r="B126" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -6968,7 +6968,7 @@
         <v>785</v>
       </c>
       <c r="B127" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -6976,7 +6976,7 @@
         <v>506</v>
       </c>
       <c r="B128" s="1">
-        <v>42000</v>
+        <v>42750</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -6984,7 +6984,7 @@
         <v>21</v>
       </c>
       <c r="B129" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -6992,7 +6992,7 @@
         <v>756</v>
       </c>
       <c r="B130" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7000,7 +7000,7 @@
         <v>480</v>
       </c>
       <c r="B131" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7008,7 +7008,7 @@
         <v>786</v>
       </c>
       <c r="B132" s="1">
-        <v>72800</v>
+        <v>74100</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7016,7 +7016,7 @@
         <v>787</v>
       </c>
       <c r="B133" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7024,7 +7024,7 @@
         <v>788</v>
       </c>
       <c r="B134" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7032,7 +7032,7 @@
         <v>789</v>
       </c>
       <c r="B135" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7040,7 +7040,7 @@
         <v>73</v>
       </c>
       <c r="B136" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7048,7 +7048,7 @@
         <v>74</v>
       </c>
       <c r="B137" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7056,7 +7056,7 @@
         <v>162</v>
       </c>
       <c r="B138" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7064,7 +7064,7 @@
         <v>790</v>
       </c>
       <c r="B139" s="1">
-        <v>42000</v>
+        <v>42750</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7072,7 +7072,7 @@
         <v>130</v>
       </c>
       <c r="B140" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7080,7 +7080,7 @@
         <v>791</v>
       </c>
       <c r="B141" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7088,7 +7088,7 @@
         <v>709</v>
       </c>
       <c r="B142" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7096,7 +7096,7 @@
         <v>432</v>
       </c>
       <c r="B143" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7104,7 +7104,7 @@
         <v>507</v>
       </c>
       <c r="B144" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7112,7 +7112,7 @@
         <v>508</v>
       </c>
       <c r="B145" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7120,7 +7120,7 @@
         <v>437</v>
       </c>
       <c r="B146" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7128,7 +7128,7 @@
         <v>509</v>
       </c>
       <c r="B147" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7136,7 +7136,7 @@
         <v>792</v>
       </c>
       <c r="B148" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7144,7 +7144,7 @@
         <v>4</v>
       </c>
       <c r="B149" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7152,7 +7152,7 @@
         <v>793</v>
       </c>
       <c r="B150" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7160,7 +7160,7 @@
         <v>650</v>
       </c>
       <c r="B151" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7168,7 +7168,7 @@
         <v>651</v>
       </c>
       <c r="B152" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7176,7 +7176,7 @@
         <v>588</v>
       </c>
       <c r="B153" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7184,7 +7184,7 @@
         <v>554</v>
       </c>
       <c r="B154" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7192,7 +7192,7 @@
         <v>510</v>
       </c>
       <c r="B155" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7200,7 +7200,7 @@
         <v>403</v>
       </c>
       <c r="B156" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7208,7 +7208,7 @@
         <v>546</v>
       </c>
       <c r="B157" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7216,7 +7216,7 @@
         <v>441</v>
       </c>
       <c r="B158" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7224,7 +7224,7 @@
         <v>556</v>
       </c>
       <c r="B159" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7232,7 +7232,7 @@
         <v>557</v>
       </c>
       <c r="B160" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7240,7 +7240,7 @@
         <v>794</v>
       </c>
       <c r="B161" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7248,7 +7248,7 @@
         <v>435</v>
       </c>
       <c r="B162" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7256,7 +7256,7 @@
         <v>795</v>
       </c>
       <c r="B163" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7264,7 +7264,7 @@
         <v>796</v>
       </c>
       <c r="B164" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -7272,7 +7272,7 @@
         <v>624</v>
       </c>
       <c r="B165" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -7280,7 +7280,7 @@
         <v>10</v>
       </c>
       <c r="B166" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -7288,7 +7288,7 @@
         <v>797</v>
       </c>
       <c r="B167" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
   </sheetData>
@@ -7318,7 +7318,7 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>78400</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7326,7 +7326,7 @@
         <v>745</v>
       </c>
       <c r="B3" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7334,7 +7334,7 @@
         <v>746</v>
       </c>
       <c r="B4" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7342,7 +7342,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1">
-        <v>78400</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7350,7 +7350,7 @@
         <v>747</v>
       </c>
       <c r="B6" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7358,7 +7358,7 @@
         <v>122</v>
       </c>
       <c r="B7" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7366,7 +7366,7 @@
         <v>131</v>
       </c>
       <c r="B8" s="1">
-        <v>140000</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7374,7 +7374,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7382,7 +7382,7 @@
         <v>567</v>
       </c>
       <c r="B10" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7390,7 +7390,7 @@
         <v>82</v>
       </c>
       <c r="B11" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7398,7 +7398,7 @@
         <v>165</v>
       </c>
       <c r="B12" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7406,7 +7406,7 @@
         <v>589</v>
       </c>
       <c r="B13" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7414,7 +7414,7 @@
         <v>798</v>
       </c>
       <c r="B14" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7422,7 +7422,7 @@
         <v>132</v>
       </c>
       <c r="B15" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -7430,7 +7430,7 @@
         <v>133</v>
       </c>
       <c r="B16" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -7438,7 +7438,7 @@
         <v>753</v>
       </c>
       <c r="B17" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -7446,7 +7446,7 @@
         <v>625</v>
       </c>
       <c r="B18" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -7454,7 +7454,7 @@
         <v>823</v>
       </c>
       <c r="B19" s="1">
-        <v>47600</v>
+        <v>48450</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7462,7 +7462,7 @@
         <v>430</v>
       </c>
       <c r="B20" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7470,7 +7470,7 @@
         <v>163</v>
       </c>
       <c r="B21" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7478,7 +7478,7 @@
         <v>647</v>
       </c>
       <c r="B22" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7486,7 +7486,7 @@
         <v>581</v>
       </c>
       <c r="B23" s="1">
-        <v>61600</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7494,7 +7494,7 @@
         <v>648</v>
       </c>
       <c r="B24" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7502,7 +7502,7 @@
         <v>83</v>
       </c>
       <c r="B25" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7510,7 +7510,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7518,7 +7518,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7526,7 +7526,7 @@
         <v>121</v>
       </c>
       <c r="B28" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7534,7 +7534,7 @@
         <v>134</v>
       </c>
       <c r="B29" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7542,7 +7542,7 @@
         <v>698</v>
       </c>
       <c r="B30" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7550,7 +7550,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7558,7 +7558,7 @@
         <v>477</v>
       </c>
       <c r="B32" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7566,7 +7566,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7574,7 +7574,7 @@
         <v>158</v>
       </c>
       <c r="B34" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7582,7 +7582,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7590,7 +7590,7 @@
         <v>692</v>
       </c>
       <c r="B36" s="1">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7598,7 +7598,7 @@
         <v>406</v>
       </c>
       <c r="B37" s="1">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7606,7 +7606,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="1">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7614,7 +7614,7 @@
         <v>626</v>
       </c>
       <c r="B39" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7622,7 +7622,7 @@
         <v>627</v>
       </c>
       <c r="B40" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7630,7 +7630,7 @@
         <v>628</v>
       </c>
       <c r="B41" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7638,7 +7638,7 @@
         <v>629</v>
       </c>
       <c r="B42" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -7646,7 +7646,7 @@
         <v>511</v>
       </c>
       <c r="B43" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7654,7 +7654,7 @@
         <v>85</v>
       </c>
       <c r="B44" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -7662,7 +7662,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -7670,7 +7670,7 @@
         <v>86</v>
       </c>
       <c r="B46" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7678,7 +7678,7 @@
         <v>135</v>
       </c>
       <c r="B47" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7686,7 +7686,7 @@
         <v>136</v>
       </c>
       <c r="B48" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -7694,7 +7694,7 @@
         <v>87</v>
       </c>
       <c r="B49" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -7702,7 +7702,7 @@
         <v>444</v>
       </c>
       <c r="B50" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -7710,7 +7710,7 @@
         <v>512</v>
       </c>
       <c r="B51" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -7718,7 +7718,7 @@
         <v>137</v>
       </c>
       <c r="B52" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -7726,7 +7726,7 @@
         <v>513</v>
       </c>
       <c r="B53" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -7734,7 +7734,7 @@
         <v>451</v>
       </c>
       <c r="B54" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -7742,7 +7742,7 @@
         <v>452</v>
       </c>
       <c r="B55" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -7750,7 +7750,7 @@
         <v>138</v>
       </c>
       <c r="B56" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -7758,7 +7758,7 @@
         <v>699</v>
       </c>
       <c r="B57" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -7766,7 +7766,7 @@
         <v>583</v>
       </c>
       <c r="B58" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -7774,7 +7774,7 @@
         <v>584</v>
       </c>
       <c r="B59" s="1">
-        <v>42000</v>
+        <v>42750</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -7782,7 +7782,7 @@
         <v>139</v>
       </c>
       <c r="B60" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -7790,7 +7790,7 @@
         <v>551</v>
       </c>
       <c r="B61" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -7798,7 +7798,7 @@
         <v>140</v>
       </c>
       <c r="B62" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -7806,7 +7806,7 @@
         <v>89</v>
       </c>
       <c r="B63" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -7814,7 +7814,7 @@
         <v>88</v>
       </c>
       <c r="B64" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -7822,7 +7822,7 @@
         <v>559</v>
       </c>
       <c r="B65" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -7830,7 +7830,7 @@
         <v>722</v>
       </c>
       <c r="B66" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -7838,7 +7838,7 @@
         <v>118</v>
       </c>
       <c r="B67" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -7846,7 +7846,7 @@
         <v>799</v>
       </c>
       <c r="B68" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -7854,7 +7854,7 @@
         <v>39</v>
       </c>
       <c r="B69" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -7862,7 +7862,7 @@
         <v>40</v>
       </c>
       <c r="B70" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -7870,7 +7870,7 @@
         <v>800</v>
       </c>
       <c r="B71" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -7878,7 +7878,7 @@
         <v>120</v>
       </c>
       <c r="B72" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7886,7 +7886,7 @@
         <v>41</v>
       </c>
       <c r="B73" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7894,7 +7894,7 @@
         <v>42</v>
       </c>
       <c r="B74" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7902,7 +7902,7 @@
         <v>43</v>
       </c>
       <c r="B75" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7910,7 +7910,7 @@
         <v>44</v>
       </c>
       <c r="B76" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7918,7 +7918,7 @@
         <v>45</v>
       </c>
       <c r="B77" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7926,7 +7926,7 @@
         <v>46</v>
       </c>
       <c r="B78" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7934,7 +7934,7 @@
         <v>687</v>
       </c>
       <c r="B79" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7942,7 +7942,7 @@
         <v>90</v>
       </c>
       <c r="B80" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7950,7 +7950,7 @@
         <v>32</v>
       </c>
       <c r="B81" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7958,7 +7958,7 @@
         <v>27</v>
       </c>
       <c r="B82" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7966,7 +7966,7 @@
         <v>33</v>
       </c>
       <c r="B83" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7974,7 +7974,7 @@
         <v>141</v>
       </c>
       <c r="B84" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7982,7 +7982,7 @@
         <v>49</v>
       </c>
       <c r="B85" s="1">
-        <v>140000</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7990,7 +7990,7 @@
         <v>48</v>
       </c>
       <c r="B86" s="1">
-        <v>140000</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7998,7 +7998,7 @@
         <v>47</v>
       </c>
       <c r="B87" s="1">
-        <v>128800</v>
+        <v>131100</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -8006,7 +8006,7 @@
         <v>50</v>
       </c>
       <c r="B88" s="1">
-        <v>140000</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -8014,7 +8014,7 @@
         <v>51</v>
       </c>
       <c r="B89" s="1">
-        <v>140000</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -8022,7 +8022,7 @@
         <v>474</v>
       </c>
       <c r="B90" s="1">
-        <v>140000</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -8030,7 +8030,7 @@
         <v>55</v>
       </c>
       <c r="B91" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -8038,7 +8038,7 @@
         <v>52</v>
       </c>
       <c r="B92" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -8046,7 +8046,7 @@
         <v>53</v>
       </c>
       <c r="B93" s="1">
-        <v>123200</v>
+        <v>125400</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -8054,7 +8054,7 @@
         <v>54</v>
       </c>
       <c r="B94" s="1">
-        <v>123200</v>
+        <v>125400</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -8062,7 +8062,7 @@
         <v>56</v>
       </c>
       <c r="B95" s="1">
-        <v>123200</v>
+        <v>125400</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -8070,7 +8070,7 @@
         <v>475</v>
       </c>
       <c r="B96" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -8078,7 +8078,7 @@
         <v>514</v>
       </c>
       <c r="B97" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -8086,7 +8086,7 @@
         <v>700</v>
       </c>
       <c r="B98" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -8094,7 +8094,7 @@
         <v>701</v>
       </c>
       <c r="B99" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -8102,7 +8102,7 @@
         <v>142</v>
       </c>
       <c r="B100" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -8110,7 +8110,7 @@
         <v>801</v>
       </c>
       <c r="B101" s="1">
-        <v>78400</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -8118,7 +8118,7 @@
         <v>544</v>
       </c>
       <c r="B102" s="1">
-        <v>78400</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -8126,7 +8126,7 @@
         <v>802</v>
       </c>
       <c r="B103" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -8134,7 +8134,7 @@
         <v>643</v>
       </c>
       <c r="B104" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -8142,7 +8142,7 @@
         <v>515</v>
       </c>
       <c r="B105" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -8150,7 +8150,7 @@
         <v>428</v>
       </c>
       <c r="B106" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -8158,7 +8158,7 @@
         <v>693</v>
       </c>
       <c r="B107" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -8166,7 +8166,7 @@
         <v>552</v>
       </c>
       <c r="B108" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -8174,7 +8174,7 @@
         <v>825</v>
       </c>
       <c r="B109" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -8182,7 +8182,7 @@
         <v>702</v>
       </c>
       <c r="B110" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -8190,7 +8190,7 @@
         <v>93</v>
       </c>
       <c r="B111" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -8198,7 +8198,7 @@
         <v>92</v>
       </c>
       <c r="B112" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -8206,7 +8206,7 @@
         <v>91</v>
       </c>
       <c r="B113" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -8214,7 +8214,7 @@
         <v>94</v>
       </c>
       <c r="B114" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -8222,7 +8222,7 @@
         <v>585</v>
       </c>
       <c r="B115" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -8230,7 +8230,7 @@
         <v>646</v>
       </c>
       <c r="B116" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -8238,7 +8238,7 @@
         <v>560</v>
       </c>
       <c r="B117" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -8246,7 +8246,7 @@
         <v>57</v>
       </c>
       <c r="B118" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -8254,7 +8254,7 @@
         <v>58</v>
       </c>
       <c r="B119" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -8262,7 +8262,7 @@
         <v>59</v>
       </c>
       <c r="B120" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -8270,7 +8270,7 @@
         <v>561</v>
       </c>
       <c r="B121" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -8278,7 +8278,7 @@
         <v>562</v>
       </c>
       <c r="B122" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -8286,7 +8286,7 @@
         <v>677</v>
       </c>
       <c r="B123" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -8294,7 +8294,7 @@
         <v>685</v>
       </c>
       <c r="B124" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -8302,7 +8302,7 @@
         <v>686</v>
       </c>
       <c r="B125" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -8310,7 +8310,7 @@
         <v>484</v>
       </c>
       <c r="B126" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -8318,7 +8318,7 @@
         <v>735</v>
       </c>
       <c r="B127" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -8326,7 +8326,7 @@
         <v>60</v>
       </c>
       <c r="B128" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -8334,7 +8334,7 @@
         <v>61</v>
       </c>
       <c r="B129" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -8342,7 +8342,7 @@
         <v>157</v>
       </c>
       <c r="B130" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -8350,7 +8350,7 @@
         <v>62</v>
       </c>
       <c r="B131" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -8358,7 +8358,7 @@
         <v>754</v>
       </c>
       <c r="B132" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -8366,7 +8366,7 @@
         <v>694</v>
       </c>
       <c r="B133" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -8374,7 +8374,7 @@
         <v>563</v>
       </c>
       <c r="B134" s="1">
-        <v>78400</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -8382,7 +8382,7 @@
         <v>697</v>
       </c>
       <c r="B135" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -8390,7 +8390,7 @@
         <v>455</v>
       </c>
       <c r="B136" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -8398,7 +8398,7 @@
         <v>623</v>
       </c>
       <c r="B137" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -8406,7 +8406,7 @@
         <v>630</v>
       </c>
       <c r="B138" s="1">
-        <v>308000</v>
+        <v>313500</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -8414,7 +8414,7 @@
         <v>631</v>
       </c>
       <c r="B139" s="1">
-        <v>319200</v>
+        <v>324900</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -8422,7 +8422,7 @@
         <v>449</v>
       </c>
       <c r="B140" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -8430,7 +8430,7 @@
         <v>448</v>
       </c>
       <c r="B141" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -8438,7 +8438,7 @@
         <v>450</v>
       </c>
       <c r="B142" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -8446,7 +8446,7 @@
         <v>447</v>
       </c>
       <c r="B143" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -8454,7 +8454,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -8462,7 +8462,7 @@
         <v>446</v>
       </c>
       <c r="B145" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -8470,7 +8470,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -8478,7 +8478,7 @@
         <v>591</v>
       </c>
       <c r="B147" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -8486,7 +8486,7 @@
         <v>96</v>
       </c>
       <c r="B148" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -8494,7 +8494,7 @@
         <v>95</v>
       </c>
       <c r="B149" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -8502,7 +8502,7 @@
         <v>97</v>
       </c>
       <c r="B150" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -8510,7 +8510,7 @@
         <v>553</v>
       </c>
       <c r="B151" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -8518,7 +8518,7 @@
         <v>803</v>
       </c>
       <c r="B152" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -8526,7 +8526,7 @@
         <v>804</v>
       </c>
       <c r="B153" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -8534,7 +8534,7 @@
         <v>145</v>
       </c>
       <c r="B154" s="1">
-        <v>140000</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -8542,7 +8542,7 @@
         <v>119</v>
       </c>
       <c r="B155" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -8550,7 +8550,7 @@
         <v>703</v>
       </c>
       <c r="B156" s="1">
-        <v>42000</v>
+        <v>42750</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -8558,7 +8558,7 @@
         <v>704</v>
       </c>
       <c r="B157" s="1">
-        <v>42000</v>
+        <v>42750</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -8566,7 +8566,7 @@
         <v>98</v>
       </c>
       <c r="B158" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -8574,7 +8574,7 @@
         <v>63</v>
       </c>
       <c r="B159" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -8582,7 +8582,7 @@
         <v>472</v>
       </c>
       <c r="B160" s="1">
-        <v>78400</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -8590,7 +8590,7 @@
         <v>99</v>
       </c>
       <c r="B161" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -8598,7 +8598,7 @@
         <v>720</v>
       </c>
       <c r="B162" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -8606,7 +8606,7 @@
         <v>724</v>
       </c>
       <c r="B163" s="1">
-        <v>42000</v>
+        <v>42750</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -8614,7 +8614,7 @@
         <v>721</v>
       </c>
       <c r="B164" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -8622,7 +8622,7 @@
         <v>725</v>
       </c>
       <c r="B165" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -8630,7 +8630,7 @@
         <v>695</v>
       </c>
       <c r="B166" s="1">
-        <v>840</v>
+        <v>855</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -8638,7 +8638,7 @@
         <v>101</v>
       </c>
       <c r="B167" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -8646,7 +8646,7 @@
         <v>102</v>
       </c>
       <c r="B168" s="1">
-        <v>128800</v>
+        <v>131100</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -8654,7 +8654,7 @@
         <v>103</v>
       </c>
       <c r="B169" s="1">
-        <v>196000</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -8662,7 +8662,7 @@
         <v>632</v>
       </c>
       <c r="B170" s="1">
-        <v>196000</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -8670,7 +8670,7 @@
         <v>633</v>
       </c>
       <c r="B171" s="1">
-        <v>201600</v>
+        <v>205200</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -8678,7 +8678,7 @@
         <v>678</v>
       </c>
       <c r="B172" s="1">
-        <v>207200</v>
+        <v>210900</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -8686,7 +8686,7 @@
         <v>679</v>
       </c>
       <c r="B173" s="1">
-        <v>196000</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -8694,7 +8694,7 @@
         <v>680</v>
       </c>
       <c r="B174" s="1">
-        <v>196000</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8702,7 +8702,7 @@
         <v>681</v>
       </c>
       <c r="B175" s="1">
-        <v>196000</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -8710,7 +8710,7 @@
         <v>740</v>
       </c>
       <c r="B176" s="1">
-        <v>123200</v>
+        <v>125400</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -8718,7 +8718,7 @@
         <v>23</v>
       </c>
       <c r="B177" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -8726,7 +8726,7 @@
         <v>442</v>
       </c>
       <c r="B178" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -8734,7 +8734,7 @@
         <v>564</v>
       </c>
       <c r="B179" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -8742,7 +8742,7 @@
         <v>146</v>
       </c>
       <c r="B180" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -8750,7 +8750,7 @@
         <v>147</v>
       </c>
       <c r="B181" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -8758,7 +8758,7 @@
         <v>755</v>
       </c>
       <c r="B182" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -8766,7 +8766,7 @@
         <v>705</v>
       </c>
       <c r="B183" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -8774,7 +8774,7 @@
         <v>652</v>
       </c>
       <c r="B184" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -8782,7 +8782,7 @@
         <v>805</v>
       </c>
       <c r="B185" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -8790,7 +8790,7 @@
         <v>748</v>
       </c>
       <c r="B186" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -8798,7 +8798,7 @@
         <v>148</v>
       </c>
       <c r="B187" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -8806,7 +8806,7 @@
         <v>706</v>
       </c>
       <c r="B188" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -8814,7 +8814,7 @@
         <v>516</v>
       </c>
       <c r="B189" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -8822,7 +8822,7 @@
         <v>749</v>
       </c>
       <c r="B190" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -8830,7 +8830,7 @@
         <v>149</v>
       </c>
       <c r="B191" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -8838,7 +8838,7 @@
         <v>565</v>
       </c>
       <c r="B192" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -8846,7 +8846,7 @@
         <v>707</v>
       </c>
       <c r="B193" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -8854,7 +8854,7 @@
         <v>150</v>
       </c>
       <c r="B194" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -8862,7 +8862,7 @@
         <v>104</v>
       </c>
       <c r="B195" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -8870,7 +8870,7 @@
         <v>517</v>
       </c>
       <c r="B196" s="1">
-        <v>42000</v>
+        <v>42750</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -8878,7 +8878,7 @@
         <v>151</v>
       </c>
       <c r="B197" s="1">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -8886,7 +8886,7 @@
         <v>481</v>
       </c>
       <c r="B198" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -8894,7 +8894,7 @@
         <v>708</v>
       </c>
       <c r="B199" s="1">
-        <v>95200</v>
+        <v>96900</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -8902,7 +8902,7 @@
         <v>64</v>
       </c>
       <c r="B200" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -8910,7 +8910,7 @@
         <v>152</v>
       </c>
       <c r="B201" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -8918,7 +8918,7 @@
         <v>65</v>
       </c>
       <c r="B202" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -8926,7 +8926,7 @@
         <v>545</v>
       </c>
       <c r="B203" s="1">
-        <v>78400</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -8934,7 +8934,7 @@
         <v>547</v>
       </c>
       <c r="B204" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -8942,7 +8942,7 @@
         <v>66</v>
       </c>
       <c r="B205" s="1">
-        <v>72800</v>
+        <v>74100</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -8950,7 +8950,7 @@
         <v>67</v>
       </c>
       <c r="B206" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -8958,7 +8958,7 @@
         <v>68</v>
       </c>
       <c r="B207" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -8966,7 +8966,7 @@
         <v>69</v>
       </c>
       <c r="B208" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -8974,7 +8974,7 @@
         <v>70</v>
       </c>
       <c r="B209" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -8982,7 +8982,7 @@
         <v>71</v>
       </c>
       <c r="B210" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -8990,7 +8990,7 @@
         <v>72</v>
       </c>
       <c r="B211" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -8998,7 +8998,7 @@
         <v>473</v>
       </c>
       <c r="B212" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -9006,7 +9006,7 @@
         <v>160</v>
       </c>
       <c r="B213" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -9014,7 +9014,7 @@
         <v>161</v>
       </c>
       <c r="B214" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -9022,7 +9022,7 @@
         <v>75</v>
       </c>
       <c r="B215" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -9030,7 +9030,7 @@
         <v>159</v>
       </c>
       <c r="B216" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -9038,7 +9038,7 @@
         <v>107</v>
       </c>
       <c r="B217" s="1">
-        <v>140000</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -9046,7 +9046,7 @@
         <v>108</v>
       </c>
       <c r="B218" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -9054,7 +9054,7 @@
         <v>110</v>
       </c>
       <c r="B219" s="1">
-        <v>112000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -9062,7 +9062,7 @@
         <v>105</v>
       </c>
       <c r="B220" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -9070,7 +9070,7 @@
         <v>106</v>
       </c>
       <c r="B221" s="1">
-        <v>84000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -9078,7 +9078,7 @@
         <v>109</v>
       </c>
       <c r="B222" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -9086,7 +9086,7 @@
         <v>111</v>
       </c>
       <c r="B223" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -9094,7 +9094,7 @@
         <v>153</v>
       </c>
       <c r="B224" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -9102,7 +9102,7 @@
         <v>154</v>
       </c>
       <c r="B225" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -9110,7 +9110,7 @@
         <v>76</v>
       </c>
       <c r="B226" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -9118,7 +9118,7 @@
         <v>77</v>
       </c>
       <c r="B227" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -9126,7 +9126,7 @@
         <v>714</v>
       </c>
       <c r="B228" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -9134,7 +9134,7 @@
         <v>78</v>
       </c>
       <c r="B229" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -9142,7 +9142,7 @@
         <v>443</v>
       </c>
       <c r="B230" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -9150,7 +9150,7 @@
         <v>79</v>
       </c>
       <c r="B231" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -9158,7 +9158,7 @@
         <v>518</v>
       </c>
       <c r="B232" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -9166,7 +9166,7 @@
         <v>80</v>
       </c>
       <c r="B233" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -9174,7 +9174,7 @@
         <v>81</v>
       </c>
       <c r="B234" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -9182,7 +9182,7 @@
         <v>519</v>
       </c>
       <c r="B235" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -9190,7 +9190,7 @@
         <v>113</v>
       </c>
       <c r="B236" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -9198,7 +9198,7 @@
         <v>114</v>
       </c>
       <c r="B237" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -9206,7 +9206,7 @@
         <v>453</v>
       </c>
       <c r="B238" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -9214,7 +9214,7 @@
         <v>710</v>
       </c>
       <c r="B239" s="1">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -9222,7 +9222,7 @@
         <v>750</v>
       </c>
       <c r="B240" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -9230,7 +9230,7 @@
         <v>650</v>
       </c>
       <c r="B241" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -9238,7 +9238,7 @@
         <v>588</v>
       </c>
       <c r="B242" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -9246,7 +9246,7 @@
         <v>555</v>
       </c>
       <c r="B243" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -9254,7 +9254,7 @@
         <v>117</v>
       </c>
       <c r="B244" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -9262,7 +9262,7 @@
         <v>403</v>
       </c>
       <c r="B245" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -9270,7 +9270,7 @@
         <v>546</v>
       </c>
       <c r="B246" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -9278,7 +9278,7 @@
         <v>568</v>
       </c>
       <c r="B247" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -9286,7 +9286,7 @@
         <v>566</v>
       </c>
       <c r="B248" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -9294,7 +9294,7 @@
         <v>556</v>
       </c>
       <c r="B249" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -9302,7 +9302,7 @@
         <v>557</v>
       </c>
       <c r="B250" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -9310,7 +9310,7 @@
         <v>634</v>
       </c>
       <c r="B251" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -9318,7 +9318,7 @@
         <v>711</v>
       </c>
       <c r="B252" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -9326,7 +9326,7 @@
         <v>712</v>
       </c>
       <c r="B253" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -9334,7 +9334,7 @@
         <v>558</v>
       </c>
       <c r="B254" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -9342,7 +9342,7 @@
         <v>635</v>
       </c>
       <c r="B255" s="1">
-        <v>128800</v>
+        <v>131100</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -9350,7 +9350,7 @@
         <v>713</v>
       </c>
       <c r="B256" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -9358,7 +9358,7 @@
         <v>794</v>
       </c>
       <c r="B257" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -9366,7 +9366,7 @@
         <v>445</v>
       </c>
       <c r="B258" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -9374,7 +9374,7 @@
         <v>682</v>
       </c>
       <c r="B259" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -9382,7 +9382,7 @@
         <v>112</v>
       </c>
       <c r="B260" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -9390,7 +9390,7 @@
         <v>155</v>
       </c>
       <c r="B261" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -9398,7 +9398,7 @@
         <v>156</v>
       </c>
       <c r="B262" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
   </sheetData>
@@ -9428,7 +9428,7 @@
         <v>592</v>
       </c>
       <c r="B2" s="1">
-        <v>100800</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9436,7 +9436,7 @@
         <v>806</v>
       </c>
       <c r="B3" s="1">
-        <v>75600</v>
+        <v>76950</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9444,7 +9444,7 @@
         <v>807</v>
       </c>
       <c r="B4" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9452,7 +9452,7 @@
         <v>589</v>
       </c>
       <c r="B5" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9460,7 +9460,7 @@
         <v>808</v>
       </c>
       <c r="B6" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9468,7 +9468,7 @@
         <v>581</v>
       </c>
       <c r="B7" s="1">
-        <v>61600</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9476,7 +9476,7 @@
         <v>648</v>
       </c>
       <c r="B8" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9484,7 +9484,7 @@
         <v>520</v>
       </c>
       <c r="B9" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -9492,7 +9492,7 @@
         <v>521</v>
       </c>
       <c r="B10" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9500,7 +9500,7 @@
         <v>522</v>
       </c>
       <c r="B11" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9508,7 +9508,7 @@
         <v>523</v>
       </c>
       <c r="B12" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -9516,7 +9516,7 @@
         <v>809</v>
       </c>
       <c r="B13" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -9524,7 +9524,7 @@
         <v>551</v>
       </c>
       <c r="B14" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -9532,7 +9532,7 @@
         <v>722</v>
       </c>
       <c r="B15" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -9540,7 +9540,7 @@
         <v>524</v>
       </c>
       <c r="B16" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -9548,7 +9548,7 @@
         <v>525</v>
       </c>
       <c r="B17" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -9556,7 +9556,7 @@
         <v>691</v>
       </c>
       <c r="B18" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -9564,7 +9564,7 @@
         <v>526</v>
       </c>
       <c r="B19" s="1">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -9572,7 +9572,7 @@
         <v>810</v>
       </c>
       <c r="B20" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -9580,7 +9580,7 @@
         <v>527</v>
       </c>
       <c r="B21" s="1">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -9588,7 +9588,7 @@
         <v>552</v>
       </c>
       <c r="B22" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -9596,7 +9596,7 @@
         <v>825</v>
       </c>
       <c r="B23" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -9604,7 +9604,7 @@
         <v>528</v>
       </c>
       <c r="B24" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -9612,7 +9612,7 @@
         <v>821</v>
       </c>
       <c r="B25" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -9620,7 +9620,7 @@
         <v>529</v>
       </c>
       <c r="B26" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -9628,7 +9628,7 @@
         <v>684</v>
       </c>
       <c r="B27" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -9636,7 +9636,7 @@
         <v>484</v>
       </c>
       <c r="B28">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -9644,7 +9644,7 @@
         <v>735</v>
       </c>
       <c r="B29">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -9652,7 +9652,7 @@
         <v>530</v>
       </c>
       <c r="B30">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -9660,7 +9660,7 @@
         <v>531</v>
       </c>
       <c r="B31">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -9668,7 +9668,7 @@
         <v>532</v>
       </c>
       <c r="B32">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -9676,7 +9676,7 @@
         <v>533</v>
       </c>
       <c r="B33">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -9684,7 +9684,7 @@
         <v>534</v>
       </c>
       <c r="B34">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -9692,7 +9692,7 @@
         <v>535</v>
       </c>
       <c r="B35">
-        <v>61600</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -9700,7 +9700,7 @@
         <v>631</v>
       </c>
       <c r="B36">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -9708,7 +9708,7 @@
         <v>553</v>
       </c>
       <c r="B37">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -9716,7 +9716,7 @@
         <v>726</v>
       </c>
       <c r="B38">
-        <v>47600</v>
+        <v>48450</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -9724,7 +9724,7 @@
         <v>727</v>
       </c>
       <c r="B39">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -9732,7 +9732,7 @@
         <v>536</v>
       </c>
       <c r="B40">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -9740,7 +9740,7 @@
         <v>683</v>
       </c>
       <c r="B41">
-        <v>201600</v>
+        <v>205200</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -9748,7 +9748,7 @@
         <v>636</v>
       </c>
       <c r="B42">
-        <v>207200</v>
+        <v>210900</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -9756,7 +9756,7 @@
         <v>740</v>
       </c>
       <c r="B43">
-        <v>123200</v>
+        <v>125400</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -9764,7 +9764,7 @@
         <v>537</v>
       </c>
       <c r="B44">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -9772,7 +9772,7 @@
         <v>538</v>
       </c>
       <c r="B45">
-        <v>28000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -9780,7 +9780,7 @@
         <v>811</v>
       </c>
       <c r="B46">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -9788,7 +9788,7 @@
         <v>812</v>
       </c>
       <c r="B47">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -9796,7 +9796,7 @@
         <v>813</v>
       </c>
       <c r="B48">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -9804,7 +9804,7 @@
         <v>539</v>
       </c>
       <c r="B49">
-        <v>25200</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -9812,7 +9812,7 @@
         <v>814</v>
       </c>
       <c r="B50">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -9820,7 +9820,7 @@
         <v>815</v>
       </c>
       <c r="B51">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -9828,7 +9828,7 @@
         <v>816</v>
       </c>
       <c r="B52">
-        <v>14000</v>
+        <v>14250</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -9836,7 +9836,7 @@
         <v>588</v>
       </c>
       <c r="B53">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -9844,7 +9844,7 @@
         <v>817</v>
       </c>
       <c r="B54">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -9852,7 +9852,7 @@
         <v>818</v>
       </c>
       <c r="B55">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -9860,7 +9860,7 @@
         <v>819</v>
       </c>
       <c r="B56">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -9868,7 +9868,7 @@
         <v>548</v>
       </c>
       <c r="B57">
-        <v>39200</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -9876,7 +9876,7 @@
         <v>549</v>
       </c>
       <c r="B58">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -9884,7 +9884,7 @@
         <v>403</v>
       </c>
       <c r="B59">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -9892,7 +9892,7 @@
         <v>546</v>
       </c>
       <c r="B60">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -9900,7 +9900,7 @@
         <v>556</v>
       </c>
       <c r="B61">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -9908,7 +9908,7 @@
         <v>557</v>
       </c>
       <c r="B62">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -9916,7 +9916,7 @@
         <v>540</v>
       </c>
       <c r="B63">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -9924,7 +9924,7 @@
         <v>541</v>
       </c>
       <c r="B64">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -9932,7 +9932,7 @@
         <v>637</v>
       </c>
       <c r="B65">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -9940,7 +9940,7 @@
         <v>542</v>
       </c>
       <c r="B66">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
   </sheetData>
@@ -9970,7 +9970,7 @@
         <v>383</v>
       </c>
       <c r="B2" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9978,7 +9978,7 @@
         <v>384</v>
       </c>
       <c r="B3" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9986,7 +9986,7 @@
         <v>385</v>
       </c>
       <c r="B4" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9994,7 +9994,7 @@
         <v>386</v>
       </c>
       <c r="B5" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -10002,7 +10002,7 @@
         <v>640</v>
       </c>
       <c r="B6" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -10010,7 +10010,7 @@
         <v>387</v>
       </c>
       <c r="B7" s="1">
-        <v>19600</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -10018,7 +10018,7 @@
         <v>660</v>
       </c>
       <c r="B8" s="1">
-        <v>22400</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -10026,7 +10026,7 @@
         <v>662</v>
       </c>
       <c r="B9" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -10034,7 +10034,7 @@
         <v>661</v>
       </c>
       <c r="B10" s="1">
-        <v>17920</v>
+        <v>18240</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -10042,7 +10042,7 @@
         <v>388</v>
       </c>
       <c r="B11" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -10050,7 +10050,7 @@
         <v>405</v>
       </c>
       <c r="B12" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -10058,7 +10058,7 @@
         <v>659</v>
       </c>
       <c r="B13" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -10066,7 +10066,7 @@
         <v>665</v>
       </c>
       <c r="B14" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -10074,7 +10074,7 @@
         <v>745</v>
       </c>
       <c r="B15" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -10082,7 +10082,7 @@
         <v>389</v>
       </c>
       <c r="B16" s="1">
-        <v>5040</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -10090,7 +10090,7 @@
         <v>589</v>
       </c>
       <c r="B17" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -10098,7 +10098,7 @@
         <v>823</v>
       </c>
       <c r="B18" s="1">
-        <v>47600</v>
+        <v>48450</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -10106,7 +10106,7 @@
         <v>663</v>
       </c>
       <c r="B19" s="1">
-        <v>98000</v>
+        <v>99750</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -10114,7 +10114,7 @@
         <v>655</v>
       </c>
       <c r="B20" s="1">
-        <v>109200</v>
+        <v>111150</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -10122,7 +10122,7 @@
         <v>656</v>
       </c>
       <c r="B21" s="1">
-        <v>123200</v>
+        <v>125400</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -10130,7 +10130,7 @@
         <v>430</v>
       </c>
       <c r="B22" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -10138,7 +10138,7 @@
         <v>163</v>
       </c>
       <c r="B23" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -10146,7 +10146,7 @@
         <v>647</v>
       </c>
       <c r="B24" s="1">
-        <v>56000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -10154,7 +10154,7 @@
         <v>581</v>
       </c>
       <c r="B25" s="1">
-        <v>61600</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -10162,7 +10162,7 @@
         <v>648</v>
       </c>
       <c r="B26" s="1">
-        <v>67200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -10170,7 +10170,7 @@
         <v>657</v>
       </c>
       <c r="B27" s="1">
-        <v>75600</v>
+        <v>76950</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -10178,7 +10178,7 @@
         <v>658</v>
       </c>
       <c r="B28" s="1">
-        <v>89600</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -10186,7 +10186,7 @@
         <v>664</v>
       </c>
       <c r="B29" s="1">
-        <v>95200</v>
+        <v>96900</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -10194,7 +10194,7 @@
         <v>692</v>
       </c>
       <c r="B30" s="1">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -10202,7 +10202,7 @@
         <v>406</v>
       </c>
       <c r="B31" s="1">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -10210,7 +10210,7 @@
         <v>402</v>
       </c>
       <c r="B32" s="1">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -10218,7 +10218,7 @@
         <v>429</v>
       </c>
       <c r="B33" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -10226,7 +10226,7 @@
         <v>551</v>
       </c>
       <c r="B34" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -10234,7 +10234,7 @@
         <v>390</v>
       </c>
       <c r="B35" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -10242,7 +10242,7 @@
         <v>552</v>
       </c>
       <c r="B36" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -10250,7 +10250,7 @@
         <v>825</v>
       </c>
       <c r="B37" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -10258,7 +10258,7 @@
         <v>820</v>
       </c>
       <c r="B38" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -10266,7 +10266,7 @@
         <v>404</v>
       </c>
       <c r="B39" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -10274,7 +10274,7 @@
         <v>259</v>
       </c>
       <c r="B40" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -10282,7 +10282,7 @@
         <v>425</v>
       </c>
       <c r="B41" s="1">
-        <v>2240</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -10290,7 +10290,7 @@
         <v>484</v>
       </c>
       <c r="B42" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -10298,7 +10298,7 @@
         <v>735</v>
       </c>
       <c r="B43" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -10306,7 +10306,7 @@
         <v>391</v>
       </c>
       <c r="B44" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -10314,7 +10314,7 @@
         <v>392</v>
       </c>
       <c r="B45" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -10322,7 +10322,7 @@
         <v>393</v>
       </c>
       <c r="B46" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -10330,7 +10330,7 @@
         <v>638</v>
       </c>
       <c r="B47" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -10338,7 +10338,7 @@
         <v>394</v>
       </c>
       <c r="B48" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -10346,7 +10346,7 @@
         <v>395</v>
       </c>
       <c r="B49" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -10354,7 +10354,7 @@
         <v>396</v>
       </c>
       <c r="B50" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -10362,7 +10362,7 @@
         <v>728</v>
       </c>
       <c r="B51" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -10370,7 +10370,7 @@
         <v>553</v>
       </c>
       <c r="B52" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -10378,7 +10378,7 @@
         <v>718</v>
       </c>
       <c r="B53" s="1">
-        <v>30800</v>
+        <v>31350</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -10386,7 +10386,7 @@
         <v>719</v>
       </c>
       <c r="B54" s="1">
-        <v>33600</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -10394,7 +10394,7 @@
         <v>752</v>
       </c>
       <c r="B55" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -10402,7 +10402,7 @@
         <v>723</v>
       </c>
       <c r="B56" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -10410,7 +10410,7 @@
         <v>720</v>
       </c>
       <c r="B57" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -10418,7 +10418,7 @@
         <v>724</v>
       </c>
       <c r="B58" s="1">
-        <v>42000</v>
+        <v>42750</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -10426,7 +10426,7 @@
         <v>721</v>
       </c>
       <c r="B59" s="1">
-        <v>36400</v>
+        <v>37050</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -10434,7 +10434,7 @@
         <v>725</v>
       </c>
       <c r="B60" s="1">
-        <v>44800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -10442,7 +10442,7 @@
         <v>726</v>
       </c>
       <c r="B61" s="1">
-        <v>47600</v>
+        <v>48450</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -10450,7 +10450,7 @@
         <v>727</v>
       </c>
       <c r="B62" s="1">
-        <v>50400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -10458,7 +10458,7 @@
         <v>740</v>
       </c>
       <c r="B63" s="1">
-        <v>123200</v>
+        <v>125400</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -10466,7 +10466,7 @@
         <v>827</v>
       </c>
       <c r="B64" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -10474,7 +10474,7 @@
         <v>639</v>
       </c>
       <c r="B65" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -10482,7 +10482,7 @@
         <v>543</v>
       </c>
       <c r="B66" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -10490,7 +10490,7 @@
         <v>397</v>
       </c>
       <c r="B67" s="1">
-        <v>10080</v>
+        <v>10260</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -10498,7 +10498,7 @@
         <v>653</v>
       </c>
       <c r="B68" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -10506,7 +10506,7 @@
         <v>398</v>
       </c>
       <c r="B69" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -10514,7 +10514,7 @@
         <v>399</v>
       </c>
       <c r="B70" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -10522,7 +10522,7 @@
         <v>400</v>
       </c>
       <c r="B71" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -10530,7 +10530,7 @@
         <v>582</v>
       </c>
       <c r="B72" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -10538,7 +10538,7 @@
         <v>401</v>
       </c>
       <c r="B73" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -10546,7 +10546,7 @@
         <v>588</v>
       </c>
       <c r="B74" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -10554,7 +10554,7 @@
         <v>554</v>
       </c>
       <c r="B75" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -10562,7 +10562,7 @@
         <v>555</v>
       </c>
       <c r="B76" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -10570,7 +10570,7 @@
         <v>644</v>
       </c>
       <c r="B77" s="1">
-        <v>3920</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -10578,7 +10578,7 @@
         <v>645</v>
       </c>
       <c r="B78" s="1">
-        <v>2800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -10586,7 +10586,7 @@
         <v>403</v>
       </c>
       <c r="B79" s="1">
-        <v>4480</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -10594,7 +10594,7 @@
         <v>546</v>
       </c>
       <c r="B80" s="1">
-        <v>6720</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -10602,7 +10602,7 @@
         <v>556</v>
       </c>
       <c r="B81" s="1">
-        <v>11200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -10610,7 +10610,7 @@
         <v>557</v>
       </c>
       <c r="B82" s="1">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -10618,7 +10618,7 @@
         <v>558</v>
       </c>
       <c r="B83" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
   </sheetData>

--- a/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\570 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\580 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB9E325-B57F-4FBB-A8FA-5368281D960E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F12C0C4-F4AF-4A63-9F69-0732BC182CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3034,7 +3034,7 @@
         <v>166</v>
       </c>
       <c r="B2" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3042,7 +3042,7 @@
         <v>421</v>
       </c>
       <c r="B3" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3050,7 +3050,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3058,7 +3058,7 @@
         <v>459</v>
       </c>
       <c r="B5" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3066,7 +3066,7 @@
         <v>460</v>
       </c>
       <c r="B6" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3074,7 +3074,7 @@
         <v>593</v>
       </c>
       <c r="B7" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3082,7 +3082,7 @@
         <v>168</v>
       </c>
       <c r="B8" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3090,7 +3090,7 @@
         <v>461</v>
       </c>
       <c r="B9" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3098,7 +3098,7 @@
         <v>169</v>
       </c>
       <c r="B10" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3106,7 +3106,7 @@
         <v>170</v>
       </c>
       <c r="B11" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3114,7 +3114,7 @@
         <v>171</v>
       </c>
       <c r="B12" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3122,7 +3122,7 @@
         <v>174</v>
       </c>
       <c r="B13" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3130,7 +3130,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3138,7 +3138,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="1">
-        <v>62700</v>
+        <v>63800</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3146,7 +3146,7 @@
         <v>666</v>
       </c>
       <c r="B16" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3154,7 +3154,7 @@
         <v>175</v>
       </c>
       <c r="B17" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3162,7 +3162,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3170,7 +3170,7 @@
         <v>589</v>
       </c>
       <c r="B19" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3178,7 +3178,7 @@
         <v>462</v>
       </c>
       <c r="B20" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3186,7 +3186,7 @@
         <v>177</v>
       </c>
       <c r="B21" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3194,7 +3194,7 @@
         <v>178</v>
       </c>
       <c r="B22" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3202,7 +3202,7 @@
         <v>179</v>
       </c>
       <c r="B23" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3210,7 +3210,7 @@
         <v>550</v>
       </c>
       <c r="B24" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3218,7 +3218,7 @@
         <v>180</v>
       </c>
       <c r="B25" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3226,7 +3226,7 @@
         <v>181</v>
       </c>
       <c r="B26" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3234,7 +3234,7 @@
         <v>182</v>
       </c>
       <c r="B27" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3242,7 +3242,7 @@
         <v>183</v>
       </c>
       <c r="B28" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3250,7 +3250,7 @@
         <v>184</v>
       </c>
       <c r="B29" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3258,7 +3258,7 @@
         <v>185</v>
       </c>
       <c r="B30" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3266,7 +3266,7 @@
         <v>186</v>
       </c>
       <c r="B31" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3274,7 +3274,7 @@
         <v>187</v>
       </c>
       <c r="B32" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3282,7 +3282,7 @@
         <v>188</v>
       </c>
       <c r="B33" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3290,7 +3290,7 @@
         <v>606</v>
       </c>
       <c r="B34" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3298,7 +3298,7 @@
         <v>569</v>
       </c>
       <c r="B35" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3306,7 +3306,7 @@
         <v>594</v>
       </c>
       <c r="B36" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3314,7 +3314,7 @@
         <v>823</v>
       </c>
       <c r="B37" s="1">
-        <v>48450</v>
+        <v>49300</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3322,7 +3322,7 @@
         <v>430</v>
       </c>
       <c r="B38" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3330,7 +3330,7 @@
         <v>163</v>
       </c>
       <c r="B39" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3338,7 +3338,7 @@
         <v>647</v>
       </c>
       <c r="B40" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3346,7 +3346,7 @@
         <v>581</v>
       </c>
       <c r="B41" s="1">
-        <v>62700</v>
+        <v>63800</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3354,7 +3354,7 @@
         <v>648</v>
       </c>
       <c r="B42" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3362,7 +3362,7 @@
         <v>189</v>
       </c>
       <c r="B43" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3370,7 +3370,7 @@
         <v>419</v>
       </c>
       <c r="B44" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3378,7 +3378,7 @@
         <v>408</v>
       </c>
       <c r="B45" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3386,7 +3386,7 @@
         <v>729</v>
       </c>
       <c r="B46" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3394,7 +3394,7 @@
         <v>730</v>
       </c>
       <c r="B47" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3402,7 +3402,7 @@
         <v>190</v>
       </c>
       <c r="B48" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3410,7 +3410,7 @@
         <v>191</v>
       </c>
       <c r="B49" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3418,7 +3418,7 @@
         <v>192</v>
       </c>
       <c r="B50" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3426,7 +3426,7 @@
         <v>193</v>
       </c>
       <c r="B51" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3434,7 +3434,7 @@
         <v>692</v>
       </c>
       <c r="B52" s="1">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3442,7 +3442,7 @@
         <v>194</v>
       </c>
       <c r="B53" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3450,7 +3450,7 @@
         <v>406</v>
       </c>
       <c r="B54" s="1">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3458,7 +3458,7 @@
         <v>402</v>
       </c>
       <c r="B55" s="1">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3466,7 +3466,7 @@
         <v>429</v>
       </c>
       <c r="B56" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3474,7 +3474,7 @@
         <v>195</v>
       </c>
       <c r="B57" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3482,7 +3482,7 @@
         <v>196</v>
       </c>
       <c r="B58" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3490,7 +3490,7 @@
         <v>197</v>
       </c>
       <c r="B59" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3498,7 +3498,7 @@
         <v>595</v>
       </c>
       <c r="B60" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3506,7 +3506,7 @@
         <v>596</v>
       </c>
       <c r="B61" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3514,7 +3514,7 @@
         <v>198</v>
       </c>
       <c r="B62" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3522,7 +3522,7 @@
         <v>199</v>
       </c>
       <c r="B63" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3530,7 +3530,7 @@
         <v>200</v>
       </c>
       <c r="B64" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3538,7 +3538,7 @@
         <v>201</v>
       </c>
       <c r="B65" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3546,7 +3546,7 @@
         <v>202</v>
       </c>
       <c r="B66" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3554,7 +3554,7 @@
         <v>203</v>
       </c>
       <c r="B67" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3562,7 +3562,7 @@
         <v>204</v>
       </c>
       <c r="B68" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3570,7 +3570,7 @@
         <v>205</v>
       </c>
       <c r="B69" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3578,7 +3578,7 @@
         <v>206</v>
       </c>
       <c r="B70" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3586,7 +3586,7 @@
         <v>208</v>
       </c>
       <c r="B71" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3594,7 +3594,7 @@
         <v>212</v>
       </c>
       <c r="B72" s="1">
-        <v>1140</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3602,7 +3602,7 @@
         <v>209</v>
       </c>
       <c r="B73" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3610,7 +3610,7 @@
         <v>210</v>
       </c>
       <c r="B74" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3618,7 +3618,7 @@
         <v>211</v>
       </c>
       <c r="B75" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3626,7 +3626,7 @@
         <v>476</v>
       </c>
       <c r="B76" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3634,7 +3634,7 @@
         <v>207</v>
       </c>
       <c r="B77" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3642,7 +3642,7 @@
         <v>213</v>
       </c>
       <c r="B78" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3650,7 +3650,7 @@
         <v>214</v>
       </c>
       <c r="B79" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3658,7 +3658,7 @@
         <v>215</v>
       </c>
       <c r="B80" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3666,7 +3666,7 @@
         <v>216</v>
       </c>
       <c r="B81" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3674,7 +3674,7 @@
         <v>217</v>
       </c>
       <c r="B82" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3682,7 +3682,7 @@
         <v>218</v>
       </c>
       <c r="B83" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3690,7 +3690,7 @@
         <v>219</v>
       </c>
       <c r="B84" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3698,7 +3698,7 @@
         <v>220</v>
       </c>
       <c r="B85" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3706,7 +3706,7 @@
         <v>607</v>
       </c>
       <c r="B86" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3714,7 +3714,7 @@
         <v>221</v>
       </c>
       <c r="B87" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3722,7 +3722,7 @@
         <v>608</v>
       </c>
       <c r="B88" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3730,7 +3730,7 @@
         <v>417</v>
       </c>
       <c r="B89" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3738,7 +3738,7 @@
         <v>418</v>
       </c>
       <c r="B90" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3746,7 +3746,7 @@
         <v>222</v>
       </c>
       <c r="B91" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3754,7 +3754,7 @@
         <v>223</v>
       </c>
       <c r="B92" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3762,7 +3762,7 @@
         <v>224</v>
       </c>
       <c r="B93" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3770,7 +3770,7 @@
         <v>225</v>
       </c>
       <c r="B94" s="1">
-        <v>199500</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3778,7 +3778,7 @@
         <v>226</v>
       </c>
       <c r="B95" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3786,7 +3786,7 @@
         <v>824</v>
       </c>
       <c r="B96" s="1">
-        <v>171000</v>
+        <v>174000</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3794,7 +3794,7 @@
         <v>227</v>
       </c>
       <c r="B97" s="1">
-        <v>159600</v>
+        <v>162400</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3802,7 +3802,7 @@
         <v>228</v>
       </c>
       <c r="B98" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3810,7 +3810,7 @@
         <v>551</v>
       </c>
       <c r="B99" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3818,7 +3818,7 @@
         <v>667</v>
       </c>
       <c r="B100" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3826,7 +3826,7 @@
         <v>409</v>
       </c>
       <c r="B101" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3834,7 +3834,7 @@
         <v>229</v>
       </c>
       <c r="B102" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3842,7 +3842,7 @@
         <v>230</v>
       </c>
       <c r="B103" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3850,7 +3850,7 @@
         <v>231</v>
       </c>
       <c r="B104" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3858,7 +3858,7 @@
         <v>424</v>
       </c>
       <c r="B105" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3866,7 +3866,7 @@
         <v>232</v>
       </c>
       <c r="B106" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3874,7 +3874,7 @@
         <v>570</v>
       </c>
       <c r="B107" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3882,7 +3882,7 @@
         <v>483</v>
       </c>
       <c r="B108" s="1">
-        <v>142500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3890,7 +3890,7 @@
         <v>587</v>
       </c>
       <c r="B109" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3898,7 +3898,7 @@
         <v>233</v>
       </c>
       <c r="B110" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3906,7 +3906,7 @@
         <v>234</v>
       </c>
       <c r="B111" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3914,7 +3914,7 @@
         <v>731</v>
       </c>
       <c r="B112" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3922,7 +3922,7 @@
         <v>717</v>
       </c>
       <c r="B113" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3930,7 +3930,7 @@
         <v>571</v>
       </c>
       <c r="B114" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3938,7 +3938,7 @@
         <v>590</v>
       </c>
       <c r="B115" s="1">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3946,7 +3946,7 @@
         <v>235</v>
       </c>
       <c r="B116" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3954,7 +3954,7 @@
         <v>732</v>
       </c>
       <c r="B117" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3962,7 +3962,7 @@
         <v>236</v>
       </c>
       <c r="B118" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3970,7 +3970,7 @@
         <v>733</v>
       </c>
       <c r="B119" s="1">
-        <v>1140</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3978,7 +3978,7 @@
         <v>237</v>
       </c>
       <c r="B120" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3986,7 +3986,7 @@
         <v>410</v>
       </c>
       <c r="B121" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3994,7 +3994,7 @@
         <v>238</v>
       </c>
       <c r="B122" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4002,7 +4002,7 @@
         <v>239</v>
       </c>
       <c r="B123" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4010,7 +4010,7 @@
         <v>240</v>
       </c>
       <c r="B124" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4018,7 +4018,7 @@
         <v>241</v>
       </c>
       <c r="B125" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4026,7 +4026,7 @@
         <v>242</v>
       </c>
       <c r="B126" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4034,7 +4034,7 @@
         <v>243</v>
       </c>
       <c r="B127" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4042,7 +4042,7 @@
         <v>668</v>
       </c>
       <c r="B128" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4050,7 +4050,7 @@
         <v>669</v>
       </c>
       <c r="B129" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4058,7 +4058,7 @@
         <v>431</v>
       </c>
       <c r="B130" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4066,7 +4066,7 @@
         <v>244</v>
       </c>
       <c r="B131" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4074,7 +4074,7 @@
         <v>597</v>
       </c>
       <c r="B132" s="1">
-        <v>245100</v>
+        <v>249400</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4082,7 +4082,7 @@
         <v>245</v>
       </c>
       <c r="B133" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4090,7 +4090,7 @@
         <v>456</v>
       </c>
       <c r="B134" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4098,7 +4098,7 @@
         <v>457</v>
       </c>
       <c r="B135" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4106,7 +4106,7 @@
         <v>458</v>
       </c>
       <c r="B136" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4114,7 +4114,7 @@
         <v>246</v>
       </c>
       <c r="B137" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4122,7 +4122,7 @@
         <v>247</v>
       </c>
       <c r="B138" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4130,7 +4130,7 @@
         <v>248</v>
       </c>
       <c r="B139" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4138,7 +4138,7 @@
         <v>250</v>
       </c>
       <c r="B140" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4146,7 +4146,7 @@
         <v>420</v>
       </c>
       <c r="B141" s="1">
-        <v>142500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4154,7 +4154,7 @@
         <v>14</v>
       </c>
       <c r="B142" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4162,7 +4162,7 @@
         <v>602</v>
       </c>
       <c r="B143" s="1">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4170,7 +4170,7 @@
         <v>249</v>
       </c>
       <c r="B144" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4178,7 +4178,7 @@
         <v>552</v>
       </c>
       <c r="B145" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4186,7 +4186,7 @@
         <v>251</v>
       </c>
       <c r="B146" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4194,7 +4194,7 @@
         <v>825</v>
       </c>
       <c r="B147" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4202,7 +4202,7 @@
         <v>252</v>
       </c>
       <c r="B148" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4210,7 +4210,7 @@
         <v>253</v>
       </c>
       <c r="B149" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4218,7 +4218,7 @@
         <v>598</v>
       </c>
       <c r="B150" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4226,7 +4226,7 @@
         <v>254</v>
       </c>
       <c r="B151" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4234,7 +4234,7 @@
         <v>255</v>
       </c>
       <c r="B152" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4242,7 +4242,7 @@
         <v>256</v>
       </c>
       <c r="B153" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4250,7 +4250,7 @@
         <v>257</v>
       </c>
       <c r="B154" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4258,7 +4258,7 @@
         <v>258</v>
       </c>
       <c r="B155" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4266,7 +4266,7 @@
         <v>261</v>
       </c>
       <c r="B156" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4274,7 +4274,7 @@
         <v>262</v>
       </c>
       <c r="B157" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4282,7 +4282,7 @@
         <v>263</v>
       </c>
       <c r="B158" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4290,7 +4290,7 @@
         <v>404</v>
       </c>
       <c r="B159" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4298,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="B160" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4306,7 +4306,7 @@
         <v>463</v>
       </c>
       <c r="B161" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4314,7 +4314,7 @@
         <v>260</v>
       </c>
       <c r="B162" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4322,7 +4322,7 @@
         <v>264</v>
       </c>
       <c r="B163" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4330,7 +4330,7 @@
         <v>689</v>
       </c>
       <c r="B164" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4338,7 +4338,7 @@
         <v>641</v>
       </c>
       <c r="B165" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4346,7 +4346,7 @@
         <v>642</v>
       </c>
       <c r="B166" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4354,7 +4354,7 @@
         <v>603</v>
       </c>
       <c r="B167" s="1">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4362,7 +4362,7 @@
         <v>604</v>
       </c>
       <c r="B168" s="1">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4370,7 +4370,7 @@
         <v>484</v>
       </c>
       <c r="B169" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4378,7 +4378,7 @@
         <v>265</v>
       </c>
       <c r="B170" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4386,7 +4386,7 @@
         <v>609</v>
       </c>
       <c r="B171" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4394,7 +4394,7 @@
         <v>734</v>
       </c>
       <c r="B172" s="1">
-        <v>2280</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4402,7 +4402,7 @@
         <v>735</v>
       </c>
       <c r="B173" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4410,7 +4410,7 @@
         <v>266</v>
       </c>
       <c r="B174" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4418,7 +4418,7 @@
         <v>267</v>
       </c>
       <c r="B175" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4426,7 +4426,7 @@
         <v>268</v>
       </c>
       <c r="B176" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4434,7 +4434,7 @@
         <v>269</v>
       </c>
       <c r="B177" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4442,7 +4442,7 @@
         <v>270</v>
       </c>
       <c r="B178" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4450,7 +4450,7 @@
         <v>271</v>
       </c>
       <c r="B179" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4458,7 +4458,7 @@
         <v>272</v>
       </c>
       <c r="B180" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4466,7 +4466,7 @@
         <v>273</v>
       </c>
       <c r="B181" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4474,7 +4474,7 @@
         <v>422</v>
       </c>
       <c r="B182" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4482,7 +4482,7 @@
         <v>423</v>
       </c>
       <c r="B183" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4490,7 +4490,7 @@
         <v>610</v>
       </c>
       <c r="B184" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4498,7 +4498,7 @@
         <v>611</v>
       </c>
       <c r="B185" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4506,7 +4506,7 @@
         <v>612</v>
       </c>
       <c r="B186" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4514,7 +4514,7 @@
         <v>613</v>
       </c>
       <c r="B187" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4522,7 +4522,7 @@
         <v>614</v>
       </c>
       <c r="B188" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4530,7 +4530,7 @@
         <v>615</v>
       </c>
       <c r="B189" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4538,7 +4538,7 @@
         <v>274</v>
       </c>
       <c r="B190" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4546,7 +4546,7 @@
         <v>276</v>
       </c>
       <c r="B191" s="1">
-        <v>1140</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4554,7 +4554,7 @@
         <v>275</v>
       </c>
       <c r="B192" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4562,7 +4562,7 @@
         <v>616</v>
       </c>
       <c r="B193" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4570,7 +4570,7 @@
         <v>277</v>
       </c>
       <c r="B194" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4578,7 +4578,7 @@
         <v>464</v>
       </c>
       <c r="B195" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4586,7 +4586,7 @@
         <v>278</v>
       </c>
       <c r="B196" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4594,7 +4594,7 @@
         <v>736</v>
       </c>
       <c r="B197" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4602,7 +4602,7 @@
         <v>391</v>
       </c>
       <c r="B198" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4610,7 +4610,7 @@
         <v>396</v>
       </c>
       <c r="B199" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4618,7 +4618,7 @@
         <v>466</v>
       </c>
       <c r="B200" s="1">
-        <v>182400</v>
+        <v>185600</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4626,7 +4626,7 @@
         <v>279</v>
       </c>
       <c r="B201" s="1">
-        <v>296400</v>
+        <v>301600</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4634,7 +4634,7 @@
         <v>649</v>
       </c>
       <c r="B202" s="1">
-        <v>302100</v>
+        <v>307400</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4642,7 +4642,7 @@
         <v>280</v>
       </c>
       <c r="B203" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4650,7 +4650,7 @@
         <v>696</v>
       </c>
       <c r="B204" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4658,7 +4658,7 @@
         <v>737</v>
       </c>
       <c r="B205" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4666,7 +4666,7 @@
         <v>411</v>
       </c>
       <c r="B206" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4674,7 +4674,7 @@
         <v>281</v>
       </c>
       <c r="B207" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4682,7 +4682,7 @@
         <v>412</v>
       </c>
       <c r="B208" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4690,7 +4690,7 @@
         <v>282</v>
       </c>
       <c r="B209" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4698,7 +4698,7 @@
         <v>283</v>
       </c>
       <c r="B210" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4706,7 +4706,7 @@
         <v>284</v>
       </c>
       <c r="B211" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4714,7 +4714,7 @@
         <v>285</v>
       </c>
       <c r="B212" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4722,7 +4722,7 @@
         <v>286</v>
       </c>
       <c r="B213" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4730,7 +4730,7 @@
         <v>287</v>
       </c>
       <c r="B214" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4738,7 +4738,7 @@
         <v>288</v>
       </c>
       <c r="B215" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4746,7 +4746,7 @@
         <v>289</v>
       </c>
       <c r="B216" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4754,7 +4754,7 @@
         <v>553</v>
       </c>
       <c r="B217" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4762,7 +4762,7 @@
         <v>290</v>
       </c>
       <c r="B218" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4770,7 +4770,7 @@
         <v>738</v>
       </c>
       <c r="B219" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4778,7 +4778,7 @@
         <v>739</v>
       </c>
       <c r="B220" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4786,7 +4786,7 @@
         <v>291</v>
       </c>
       <c r="B221" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4794,7 +4794,7 @@
         <v>292</v>
       </c>
       <c r="B222" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4802,7 +4802,7 @@
         <v>293</v>
       </c>
       <c r="B223" s="1">
-        <v>159600</v>
+        <v>162400</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4810,7 +4810,7 @@
         <v>294</v>
       </c>
       <c r="B224" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4818,7 +4818,7 @@
         <v>572</v>
       </c>
       <c r="B225" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4826,7 +4826,7 @@
         <v>670</v>
       </c>
       <c r="B226" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4834,7 +4834,7 @@
         <v>295</v>
       </c>
       <c r="B227" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4842,7 +4842,7 @@
         <v>671</v>
       </c>
       <c r="B228" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4850,7 +4850,7 @@
         <v>296</v>
       </c>
       <c r="B229" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4858,7 +4858,7 @@
         <v>718</v>
       </c>
       <c r="B230" s="1">
-        <v>31350</v>
+        <v>31900</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4866,7 +4866,7 @@
         <v>719</v>
       </c>
       <c r="B231" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4874,7 +4874,7 @@
         <v>720</v>
       </c>
       <c r="B232" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4882,7 +4882,7 @@
         <v>721</v>
       </c>
       <c r="B233" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4890,7 +4890,7 @@
         <v>617</v>
       </c>
       <c r="B234" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4898,7 +4898,7 @@
         <v>297</v>
       </c>
       <c r="B235" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4906,7 +4906,7 @@
         <v>573</v>
       </c>
       <c r="B236" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4914,7 +4914,7 @@
         <v>298</v>
       </c>
       <c r="B237" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4922,7 +4922,7 @@
         <v>299</v>
       </c>
       <c r="B238" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4930,7 +4930,7 @@
         <v>300</v>
       </c>
       <c r="B239" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4938,7 +4938,7 @@
         <v>301</v>
       </c>
       <c r="B240" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4946,7 +4946,7 @@
         <v>302</v>
       </c>
       <c r="B241" s="1">
-        <v>171000</v>
+        <v>174000</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4954,7 +4954,7 @@
         <v>672</v>
       </c>
       <c r="B242" s="1">
-        <v>171000</v>
+        <v>174000</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4962,7 +4962,7 @@
         <v>303</v>
       </c>
       <c r="B243" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4970,7 +4970,7 @@
         <v>740</v>
       </c>
       <c r="B244" s="1">
-        <v>125400</v>
+        <v>127600</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4978,7 +4978,7 @@
         <v>304</v>
       </c>
       <c r="B245" s="1">
-        <v>62700</v>
+        <v>63800</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4986,7 +4986,7 @@
         <v>305</v>
       </c>
       <c r="B246" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4994,7 +4994,7 @@
         <v>306</v>
       </c>
       <c r="B247" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5002,7 +5002,7 @@
         <v>618</v>
       </c>
       <c r="B248" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5010,7 +5010,7 @@
         <v>307</v>
       </c>
       <c r="B249" s="1">
-        <v>96900</v>
+        <v>98600</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5018,7 +5018,7 @@
         <v>308</v>
       </c>
       <c r="B250" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5026,7 +5026,7 @@
         <v>309</v>
       </c>
       <c r="B251" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5034,7 +5034,7 @@
         <v>310</v>
       </c>
       <c r="B252" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5042,7 +5042,7 @@
         <v>690</v>
       </c>
       <c r="B253" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5050,7 +5050,7 @@
         <v>311</v>
       </c>
       <c r="B254" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5058,7 +5058,7 @@
         <v>312</v>
       </c>
       <c r="B255" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5066,7 +5066,7 @@
         <v>313</v>
       </c>
       <c r="B256" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5074,7 +5074,7 @@
         <v>467</v>
       </c>
       <c r="B257" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5082,7 +5082,7 @@
         <v>741</v>
       </c>
       <c r="B258" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5090,7 +5090,7 @@
         <v>742</v>
       </c>
       <c r="B259" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5098,7 +5098,7 @@
         <v>468</v>
       </c>
       <c r="B260" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5106,7 +5106,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5114,7 +5114,7 @@
         <v>315</v>
       </c>
       <c r="B262" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5122,7 +5122,7 @@
         <v>316</v>
       </c>
       <c r="B263" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5130,7 +5130,7 @@
         <v>414</v>
       </c>
       <c r="B264" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5138,7 +5138,7 @@
         <v>317</v>
       </c>
       <c r="B265" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5146,7 +5146,7 @@
         <v>318</v>
       </c>
       <c r="B266" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5154,7 +5154,7 @@
         <v>605</v>
       </c>
       <c r="B267" s="1">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5162,7 +5162,7 @@
         <v>319</v>
       </c>
       <c r="B268" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5170,7 +5170,7 @@
         <v>320</v>
       </c>
       <c r="B269" s="1">
-        <v>171000</v>
+        <v>174000</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5178,7 +5178,7 @@
         <v>321</v>
       </c>
       <c r="B270" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5186,7 +5186,7 @@
         <v>322</v>
       </c>
       <c r="B271" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5194,7 +5194,7 @@
         <v>323</v>
       </c>
       <c r="B272" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5202,7 +5202,7 @@
         <v>324</v>
       </c>
       <c r="B273" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5210,7 +5210,7 @@
         <v>325</v>
       </c>
       <c r="B274" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5218,7 +5218,7 @@
         <v>326</v>
       </c>
       <c r="B275" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5226,7 +5226,7 @@
         <v>327</v>
       </c>
       <c r="B276" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5234,7 +5234,7 @@
         <v>328</v>
       </c>
       <c r="B277" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5242,7 +5242,7 @@
         <v>329</v>
       </c>
       <c r="B278" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5250,7 +5250,7 @@
         <v>330</v>
       </c>
       <c r="B279" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5258,7 +5258,7 @@
         <v>331</v>
       </c>
       <c r="B280" s="1">
-        <v>74100</v>
+        <v>75400</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5266,7 +5266,7 @@
         <v>332</v>
       </c>
       <c r="B281" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5274,7 +5274,7 @@
         <v>333</v>
       </c>
       <c r="B282" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5282,7 +5282,7 @@
         <v>334</v>
       </c>
       <c r="B283" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5290,7 +5290,7 @@
         <v>574</v>
       </c>
       <c r="B284" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5298,7 +5298,7 @@
         <v>599</v>
       </c>
       <c r="B285" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5306,7 +5306,7 @@
         <v>600</v>
       </c>
       <c r="B286" s="1">
-        <v>54150</v>
+        <v>55100</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5314,7 +5314,7 @@
         <v>743</v>
       </c>
       <c r="B287" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5322,7 +5322,7 @@
         <v>619</v>
       </c>
       <c r="B288" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5330,7 +5330,7 @@
         <v>335</v>
       </c>
       <c r="B289" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5338,7 +5338,7 @@
         <v>620</v>
       </c>
       <c r="B290" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5346,7 +5346,7 @@
         <v>336</v>
       </c>
       <c r="B291" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5354,7 +5354,7 @@
         <v>337</v>
       </c>
       <c r="B292" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5362,7 +5362,7 @@
         <v>338</v>
       </c>
       <c r="B293" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5370,7 +5370,7 @@
         <v>339</v>
       </c>
       <c r="B294" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5378,7 +5378,7 @@
         <v>340</v>
       </c>
       <c r="B295" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5386,7 +5386,7 @@
         <v>341</v>
       </c>
       <c r="B296" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5394,7 +5394,7 @@
         <v>342</v>
       </c>
       <c r="B297" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5402,7 +5402,7 @@
         <v>343</v>
       </c>
       <c r="B298" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5410,7 +5410,7 @@
         <v>415</v>
       </c>
       <c r="B299" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5418,7 +5418,7 @@
         <v>416</v>
       </c>
       <c r="B300" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5426,7 +5426,7 @@
         <v>601</v>
       </c>
       <c r="B301" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5434,7 +5434,7 @@
         <v>344</v>
       </c>
       <c r="B302" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5442,7 +5442,7 @@
         <v>345</v>
       </c>
       <c r="B303" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5450,7 +5450,7 @@
         <v>346</v>
       </c>
       <c r="B304" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5458,7 +5458,7 @@
         <v>347</v>
       </c>
       <c r="B305" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5466,7 +5466,7 @@
         <v>348</v>
       </c>
       <c r="B306" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5474,7 +5474,7 @@
         <v>349</v>
       </c>
       <c r="B307" s="1">
-        <v>2280</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5482,7 +5482,7 @@
         <v>744</v>
       </c>
       <c r="B308" s="1">
-        <v>1140</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5490,7 +5490,7 @@
         <v>673</v>
       </c>
       <c r="B309" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5498,7 +5498,7 @@
         <v>350</v>
       </c>
       <c r="B310" s="1">
-        <v>42750</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5506,7 +5506,7 @@
         <v>351</v>
       </c>
       <c r="B311" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5514,7 +5514,7 @@
         <v>352</v>
       </c>
       <c r="B312" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5522,7 +5522,7 @@
         <v>575</v>
       </c>
       <c r="B313" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5530,7 +5530,7 @@
         <v>353</v>
       </c>
       <c r="B314" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5538,7 +5538,7 @@
         <v>354</v>
       </c>
       <c r="B315" s="1">
-        <v>142500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5546,7 +5546,7 @@
         <v>407</v>
       </c>
       <c r="B316" s="1">
-        <v>313500</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5554,7 +5554,7 @@
         <v>355</v>
       </c>
       <c r="B317" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5562,7 +5562,7 @@
         <v>356</v>
       </c>
       <c r="B318" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5570,7 +5570,7 @@
         <v>576</v>
       </c>
       <c r="B319" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5578,7 +5578,7 @@
         <v>357</v>
       </c>
       <c r="B320" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5586,7 +5586,7 @@
         <v>358</v>
       </c>
       <c r="B321" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5594,7 +5594,7 @@
         <v>651</v>
       </c>
       <c r="B322" s="1">
-        <v>2280</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5602,7 +5602,7 @@
         <v>577</v>
       </c>
       <c r="B323" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5610,7 +5610,7 @@
         <v>588</v>
       </c>
       <c r="B324" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5618,7 +5618,7 @@
         <v>359</v>
       </c>
       <c r="B325" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5626,7 +5626,7 @@
         <v>360</v>
       </c>
       <c r="B326" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5634,7 +5634,7 @@
         <v>361</v>
       </c>
       <c r="B327" s="1">
-        <v>2280</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5642,7 +5642,7 @@
         <v>362</v>
       </c>
       <c r="B328" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5650,7 +5650,7 @@
         <v>363</v>
       </c>
       <c r="B329" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5658,7 +5658,7 @@
         <v>364</v>
       </c>
       <c r="B330" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5666,7 +5666,7 @@
         <v>365</v>
       </c>
       <c r="B331" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5674,7 +5674,7 @@
         <v>403</v>
       </c>
       <c r="B332" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5682,7 +5682,7 @@
         <v>546</v>
       </c>
       <c r="B333" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5690,7 +5690,7 @@
         <v>822</v>
       </c>
       <c r="B334" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5698,7 +5698,7 @@
         <v>366</v>
       </c>
       <c r="B335" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5706,7 +5706,7 @@
         <v>556</v>
       </c>
       <c r="B336" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5714,7 +5714,7 @@
         <v>557</v>
       </c>
       <c r="B337" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5722,7 +5722,7 @@
         <v>367</v>
       </c>
       <c r="B338" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5730,7 +5730,7 @@
         <v>368</v>
       </c>
       <c r="B339" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5738,7 +5738,7 @@
         <v>369</v>
       </c>
       <c r="B340" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5746,7 +5746,7 @@
         <v>370</v>
       </c>
       <c r="B341" s="1">
-        <v>1140</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5754,7 +5754,7 @@
         <v>371</v>
       </c>
       <c r="B342" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5762,7 +5762,7 @@
         <v>372</v>
       </c>
       <c r="B343" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5770,7 +5770,7 @@
         <v>373</v>
       </c>
       <c r="B344" s="1">
-        <v>2280</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5778,7 +5778,7 @@
         <v>413</v>
       </c>
       <c r="B345" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5786,7 +5786,7 @@
         <v>465</v>
       </c>
       <c r="B346" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5794,7 +5794,7 @@
         <v>621</v>
       </c>
       <c r="B347" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5802,7 +5802,7 @@
         <v>374</v>
       </c>
       <c r="B348" s="1">
-        <v>1140</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5810,7 +5810,7 @@
         <v>485</v>
       </c>
       <c r="B349" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5818,7 +5818,7 @@
         <v>469</v>
       </c>
       <c r="B350" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5826,7 +5826,7 @@
         <v>375</v>
       </c>
       <c r="B351" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5834,7 +5834,7 @@
         <v>674</v>
       </c>
       <c r="B352" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5842,7 +5842,7 @@
         <v>675</v>
       </c>
       <c r="B353" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5850,7 +5850,7 @@
         <v>376</v>
       </c>
       <c r="B354" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5858,7 +5858,7 @@
         <v>377</v>
       </c>
       <c r="B355" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5866,7 +5866,7 @@
         <v>378</v>
       </c>
       <c r="B356" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5874,7 +5874,7 @@
         <v>622</v>
       </c>
       <c r="B357" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5882,7 +5882,7 @@
         <v>379</v>
       </c>
       <c r="B358" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5890,7 +5890,7 @@
         <v>470</v>
       </c>
       <c r="B359" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5898,7 +5898,7 @@
         <v>471</v>
       </c>
       <c r="B360" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5906,7 +5906,7 @@
         <v>676</v>
       </c>
       <c r="B361" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5914,7 +5914,7 @@
         <v>380</v>
       </c>
       <c r="B362" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5922,7 +5922,7 @@
         <v>381</v>
       </c>
       <c r="B363" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5930,7 +5930,7 @@
         <v>454</v>
       </c>
       <c r="B364" s="1">
-        <v>2280</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5938,7 +5938,7 @@
         <v>382</v>
       </c>
       <c r="B365" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
   </sheetData>
@@ -5968,7 +5968,7 @@
         <v>486</v>
       </c>
       <c r="B2" s="1">
-        <v>79800</v>
+        <v>81200</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5976,7 +5976,7 @@
         <v>123</v>
       </c>
       <c r="B3" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5984,7 +5984,7 @@
         <v>757</v>
       </c>
       <c r="B4" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5992,7 +5992,7 @@
         <v>578</v>
       </c>
       <c r="B5" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6000,7 +6000,7 @@
         <v>164</v>
       </c>
       <c r="B6" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6008,7 +6008,7 @@
         <v>579</v>
       </c>
       <c r="B7" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6016,7 +6016,7 @@
         <v>589</v>
       </c>
       <c r="B8" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6024,7 +6024,7 @@
         <v>758</v>
       </c>
       <c r="B9" s="1">
-        <v>74100</v>
+        <v>75400</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6032,7 +6032,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6040,7 +6040,7 @@
         <v>759</v>
       </c>
       <c r="B11" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6048,7 +6048,7 @@
         <v>124</v>
       </c>
       <c r="B12" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6056,7 +6056,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6064,7 +6064,7 @@
         <v>823</v>
       </c>
       <c r="B14" s="1">
-        <v>48450</v>
+        <v>49300</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6072,7 +6072,7 @@
         <v>430</v>
       </c>
       <c r="B15" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6080,7 +6080,7 @@
         <v>163</v>
       </c>
       <c r="B16" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6088,7 +6088,7 @@
         <v>647</v>
       </c>
       <c r="B17" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6096,7 +6096,7 @@
         <v>581</v>
       </c>
       <c r="B18" s="1">
-        <v>62700</v>
+        <v>63800</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6104,7 +6104,7 @@
         <v>648</v>
       </c>
       <c r="B19" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6112,7 +6112,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6120,7 +6120,7 @@
         <v>125</v>
       </c>
       <c r="B21" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6128,7 +6128,7 @@
         <v>478</v>
       </c>
       <c r="B22" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6136,7 +6136,7 @@
         <v>36</v>
       </c>
       <c r="B23" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6144,7 +6144,7 @@
         <v>487</v>
       </c>
       <c r="B24" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6152,7 +6152,7 @@
         <v>488</v>
       </c>
       <c r="B25" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6160,7 +6160,7 @@
         <v>692</v>
       </c>
       <c r="B26" s="1">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6168,7 +6168,7 @@
         <v>406</v>
       </c>
       <c r="B27" s="1">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6176,7 +6176,7 @@
         <v>402</v>
       </c>
       <c r="B28" s="1">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6184,7 +6184,7 @@
         <v>439</v>
       </c>
       <c r="B29" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6192,7 +6192,7 @@
         <v>760</v>
       </c>
       <c r="B30" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6200,7 +6200,7 @@
         <v>489</v>
       </c>
       <c r="B31" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6208,7 +6208,7 @@
         <v>490</v>
       </c>
       <c r="B32" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6216,7 +6216,7 @@
         <v>761</v>
       </c>
       <c r="B33" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6224,7 +6224,7 @@
         <v>12</v>
       </c>
       <c r="B34" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6232,7 +6232,7 @@
         <v>762</v>
       </c>
       <c r="B35" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="1">
-        <v>1425</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6248,7 +6248,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6256,7 +6256,7 @@
         <v>434</v>
       </c>
       <c r="B38" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6264,7 +6264,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6272,7 +6272,7 @@
         <v>491</v>
       </c>
       <c r="B40" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6280,7 +6280,7 @@
         <v>479</v>
       </c>
       <c r="B41" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6288,7 +6288,7 @@
         <v>763</v>
       </c>
       <c r="B42" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6296,7 +6296,7 @@
         <v>438</v>
       </c>
       <c r="B43" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6304,7 +6304,7 @@
         <v>440</v>
       </c>
       <c r="B44" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6312,7 +6312,7 @@
         <v>492</v>
       </c>
       <c r="B45" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6320,7 +6320,7 @@
         <v>493</v>
       </c>
       <c r="B46" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6328,7 +6328,7 @@
         <v>494</v>
       </c>
       <c r="B47" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6336,7 +6336,7 @@
         <v>764</v>
       </c>
       <c r="B48" s="1">
-        <v>199500</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -6344,7 +6344,7 @@
         <v>551</v>
       </c>
       <c r="B49" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -6352,7 +6352,7 @@
         <v>765</v>
       </c>
       <c r="B50" s="1">
-        <v>74100</v>
+        <v>75400</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -6360,7 +6360,7 @@
         <v>751</v>
       </c>
       <c r="B51" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -6368,7 +6368,7 @@
         <v>722</v>
       </c>
       <c r="B52" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -6376,7 +6376,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -6384,7 +6384,7 @@
         <v>766</v>
       </c>
       <c r="B54" s="1">
-        <v>79800</v>
+        <v>81200</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -6392,7 +6392,7 @@
         <v>495</v>
       </c>
       <c r="B55" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -6400,7 +6400,7 @@
         <v>436</v>
       </c>
       <c r="B56" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -6408,7 +6408,7 @@
         <v>126</v>
       </c>
       <c r="B57" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -6416,7 +6416,7 @@
         <v>496</v>
       </c>
       <c r="B58" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -6424,7 +6424,7 @@
         <v>767</v>
       </c>
       <c r="B59" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -6432,7 +6432,7 @@
         <v>30</v>
       </c>
       <c r="B60" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -6440,7 +6440,7 @@
         <v>427</v>
       </c>
       <c r="B61" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -6448,7 +6448,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -6456,7 +6456,7 @@
         <v>768</v>
       </c>
       <c r="B63" s="1">
-        <v>142500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -6464,7 +6464,7 @@
         <v>769</v>
       </c>
       <c r="B64" s="1">
-        <v>125400</v>
+        <v>127600</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -6472,7 +6472,7 @@
         <v>127</v>
       </c>
       <c r="B65" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -6480,7 +6480,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -6488,7 +6488,7 @@
         <v>116</v>
       </c>
       <c r="B67" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6496,7 +6496,7 @@
         <v>14</v>
       </c>
       <c r="B68" s="1">
-        <v>74100</v>
+        <v>75400</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6504,7 +6504,7 @@
         <v>770</v>
       </c>
       <c r="B69" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -6512,7 +6512,7 @@
         <v>771</v>
       </c>
       <c r="B70" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -6520,7 +6520,7 @@
         <v>426</v>
       </c>
       <c r="B71" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -6528,7 +6528,7 @@
         <v>552</v>
       </c>
       <c r="B72" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -6536,7 +6536,7 @@
         <v>825</v>
       </c>
       <c r="B73" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -6544,7 +6544,7 @@
         <v>497</v>
       </c>
       <c r="B74" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -6552,7 +6552,7 @@
         <v>498</v>
       </c>
       <c r="B75" s="1">
-        <v>31350</v>
+        <v>31900</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -6560,7 +6560,7 @@
         <v>772</v>
       </c>
       <c r="B76" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -6568,7 +6568,7 @@
         <v>773</v>
       </c>
       <c r="B77" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -6576,7 +6576,7 @@
         <v>586</v>
       </c>
       <c r="B78" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -6584,7 +6584,7 @@
         <v>15</v>
       </c>
       <c r="B79" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -6592,7 +6592,7 @@
         <v>16</v>
       </c>
       <c r="B80" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -6600,7 +6600,7 @@
         <v>580</v>
       </c>
       <c r="B81" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -6608,7 +6608,7 @@
         <v>688</v>
       </c>
       <c r="B82" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -6616,7 +6616,7 @@
         <v>774</v>
       </c>
       <c r="B83" s="1">
-        <v>2280</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -6624,7 +6624,7 @@
         <v>484</v>
       </c>
       <c r="B84" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -6632,7 +6632,7 @@
         <v>775</v>
       </c>
       <c r="B85" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -6640,7 +6640,7 @@
         <v>735</v>
       </c>
       <c r="B86" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -6648,7 +6648,7 @@
         <v>3</v>
       </c>
       <c r="B87" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -6656,7 +6656,7 @@
         <v>17</v>
       </c>
       <c r="B88" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -6664,7 +6664,7 @@
         <v>128</v>
       </c>
       <c r="B89" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -6672,7 +6672,7 @@
         <v>715</v>
       </c>
       <c r="B90" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -6680,7 +6680,7 @@
         <v>499</v>
       </c>
       <c r="B91" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -6688,7 +6688,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -6696,7 +6696,7 @@
         <v>623</v>
       </c>
       <c r="B93" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -6704,7 +6704,7 @@
         <v>776</v>
       </c>
       <c r="B94" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -6712,7 +6712,7 @@
         <v>18</v>
       </c>
       <c r="B95" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -6720,7 +6720,7 @@
         <v>19</v>
       </c>
       <c r="B96" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -6728,7 +6728,7 @@
         <v>500</v>
       </c>
       <c r="B97" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -6736,7 +6736,7 @@
         <v>501</v>
       </c>
       <c r="B98" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -6744,7 +6744,7 @@
         <v>25</v>
       </c>
       <c r="B99" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -6752,7 +6752,7 @@
         <v>553</v>
       </c>
       <c r="B100" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -6760,7 +6760,7 @@
         <v>777</v>
       </c>
       <c r="B101" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -6768,7 +6768,7 @@
         <v>778</v>
       </c>
       <c r="B102" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -6776,7 +6776,7 @@
         <v>779</v>
       </c>
       <c r="B103" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -6784,7 +6784,7 @@
         <v>780</v>
       </c>
       <c r="B104" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -6792,7 +6792,7 @@
         <v>129</v>
       </c>
       <c r="B105" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -6800,7 +6800,7 @@
         <v>502</v>
       </c>
       <c r="B106" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -6808,7 +6808,7 @@
         <v>781</v>
       </c>
       <c r="B107" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -6816,7 +6816,7 @@
         <v>752</v>
       </c>
       <c r="B108" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -6824,7 +6824,7 @@
         <v>723</v>
       </c>
       <c r="B109" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -6832,7 +6832,7 @@
         <v>720</v>
       </c>
       <c r="B110" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -6840,7 +6840,7 @@
         <v>721</v>
       </c>
       <c r="B111" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -6848,7 +6848,7 @@
         <v>503</v>
       </c>
       <c r="B112" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -6856,7 +6856,7 @@
         <v>100</v>
       </c>
       <c r="B113" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -6864,7 +6864,7 @@
         <v>826</v>
       </c>
       <c r="B114" s="1">
-        <v>199500</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -6872,7 +6872,7 @@
         <v>654</v>
       </c>
       <c r="B115" s="1">
-        <v>199500</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -6880,7 +6880,7 @@
         <v>24</v>
       </c>
       <c r="B116" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -6888,7 +6888,7 @@
         <v>782</v>
       </c>
       <c r="B117" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -6896,7 +6896,7 @@
         <v>740</v>
       </c>
       <c r="B118" s="1">
-        <v>125400</v>
+        <v>127600</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -6904,7 +6904,7 @@
         <v>20</v>
       </c>
       <c r="B119" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -6912,7 +6912,7 @@
         <v>433</v>
       </c>
       <c r="B120" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -6920,7 +6920,7 @@
         <v>783</v>
       </c>
       <c r="B121" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -6928,7 +6928,7 @@
         <v>115</v>
       </c>
       <c r="B122" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -6936,7 +6936,7 @@
         <v>504</v>
       </c>
       <c r="B123" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -6944,7 +6944,7 @@
         <v>505</v>
       </c>
       <c r="B124" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -6952,7 +6952,7 @@
         <v>784</v>
       </c>
       <c r="B125" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -6960,7 +6960,7 @@
         <v>716</v>
       </c>
       <c r="B126" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -6968,7 +6968,7 @@
         <v>785</v>
       </c>
       <c r="B127" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -6976,7 +6976,7 @@
         <v>506</v>
       </c>
       <c r="B128" s="1">
-        <v>42750</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -6984,7 +6984,7 @@
         <v>21</v>
       </c>
       <c r="B129" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -6992,7 +6992,7 @@
         <v>756</v>
       </c>
       <c r="B130" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7000,7 +7000,7 @@
         <v>480</v>
       </c>
       <c r="B131" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7008,7 +7008,7 @@
         <v>786</v>
       </c>
       <c r="B132" s="1">
-        <v>74100</v>
+        <v>75400</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7016,7 +7016,7 @@
         <v>787</v>
       </c>
       <c r="B133" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7024,7 +7024,7 @@
         <v>788</v>
       </c>
       <c r="B134" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7032,7 +7032,7 @@
         <v>789</v>
       </c>
       <c r="B135" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7040,7 +7040,7 @@
         <v>73</v>
       </c>
       <c r="B136" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7048,7 +7048,7 @@
         <v>74</v>
       </c>
       <c r="B137" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7056,7 +7056,7 @@
         <v>162</v>
       </c>
       <c r="B138" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7064,7 +7064,7 @@
         <v>790</v>
       </c>
       <c r="B139" s="1">
-        <v>42750</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7072,7 +7072,7 @@
         <v>130</v>
       </c>
       <c r="B140" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7080,7 +7080,7 @@
         <v>791</v>
       </c>
       <c r="B141" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7088,7 +7088,7 @@
         <v>709</v>
       </c>
       <c r="B142" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7096,7 +7096,7 @@
         <v>432</v>
       </c>
       <c r="B143" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7104,7 +7104,7 @@
         <v>507</v>
       </c>
       <c r="B144" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7112,7 +7112,7 @@
         <v>508</v>
       </c>
       <c r="B145" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7120,7 +7120,7 @@
         <v>437</v>
       </c>
       <c r="B146" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7128,7 +7128,7 @@
         <v>509</v>
       </c>
       <c r="B147" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7136,7 +7136,7 @@
         <v>792</v>
       </c>
       <c r="B148" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7144,7 +7144,7 @@
         <v>4</v>
       </c>
       <c r="B149" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7152,7 +7152,7 @@
         <v>793</v>
       </c>
       <c r="B150" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7160,7 +7160,7 @@
         <v>650</v>
       </c>
       <c r="B151" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7168,7 +7168,7 @@
         <v>651</v>
       </c>
       <c r="B152" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7176,7 +7176,7 @@
         <v>588</v>
       </c>
       <c r="B153" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7184,7 +7184,7 @@
         <v>554</v>
       </c>
       <c r="B154" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7192,7 +7192,7 @@
         <v>510</v>
       </c>
       <c r="B155" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7200,7 +7200,7 @@
         <v>403</v>
       </c>
       <c r="B156" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7208,7 +7208,7 @@
         <v>546</v>
       </c>
       <c r="B157" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7216,7 +7216,7 @@
         <v>441</v>
       </c>
       <c r="B158" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7224,7 +7224,7 @@
         <v>556</v>
       </c>
       <c r="B159" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7232,7 +7232,7 @@
         <v>557</v>
       </c>
       <c r="B160" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7240,7 +7240,7 @@
         <v>794</v>
       </c>
       <c r="B161" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7248,7 +7248,7 @@
         <v>435</v>
       </c>
       <c r="B162" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7256,7 +7256,7 @@
         <v>795</v>
       </c>
       <c r="B163" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7264,7 +7264,7 @@
         <v>796</v>
       </c>
       <c r="B164" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -7272,7 +7272,7 @@
         <v>624</v>
       </c>
       <c r="B165" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -7280,7 +7280,7 @@
         <v>10</v>
       </c>
       <c r="B166" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -7288,7 +7288,7 @@
         <v>797</v>
       </c>
       <c r="B167" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
   </sheetData>
@@ -7318,7 +7318,7 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>79800</v>
+        <v>81200</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7326,7 +7326,7 @@
         <v>745</v>
       </c>
       <c r="B3" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7334,7 +7334,7 @@
         <v>746</v>
       </c>
       <c r="B4" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7342,7 +7342,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1">
-        <v>79800</v>
+        <v>81200</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7350,7 +7350,7 @@
         <v>747</v>
       </c>
       <c r="B6" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7358,7 +7358,7 @@
         <v>122</v>
       </c>
       <c r="B7" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7366,7 +7366,7 @@
         <v>131</v>
       </c>
       <c r="B8" s="1">
-        <v>142500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7374,7 +7374,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7382,7 +7382,7 @@
         <v>567</v>
       </c>
       <c r="B10" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7390,7 +7390,7 @@
         <v>82</v>
       </c>
       <c r="B11" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7398,7 +7398,7 @@
         <v>165</v>
       </c>
       <c r="B12" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7406,7 +7406,7 @@
         <v>589</v>
       </c>
       <c r="B13" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7414,7 +7414,7 @@
         <v>798</v>
       </c>
       <c r="B14" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7422,7 +7422,7 @@
         <v>132</v>
       </c>
       <c r="B15" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -7430,7 +7430,7 @@
         <v>133</v>
       </c>
       <c r="B16" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -7438,7 +7438,7 @@
         <v>753</v>
       </c>
       <c r="B17" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -7446,7 +7446,7 @@
         <v>625</v>
       </c>
       <c r="B18" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -7454,7 +7454,7 @@
         <v>823</v>
       </c>
       <c r="B19" s="1">
-        <v>48450</v>
+        <v>49300</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7462,7 +7462,7 @@
         <v>430</v>
       </c>
       <c r="B20" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7470,7 +7470,7 @@
         <v>163</v>
       </c>
       <c r="B21" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7478,7 +7478,7 @@
         <v>647</v>
       </c>
       <c r="B22" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7486,7 +7486,7 @@
         <v>581</v>
       </c>
       <c r="B23" s="1">
-        <v>62700</v>
+        <v>63800</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7494,7 +7494,7 @@
         <v>648</v>
       </c>
       <c r="B24" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7502,7 +7502,7 @@
         <v>83</v>
       </c>
       <c r="B25" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7510,7 +7510,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7518,7 +7518,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7526,7 +7526,7 @@
         <v>121</v>
       </c>
       <c r="B28" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7534,7 +7534,7 @@
         <v>134</v>
       </c>
       <c r="B29" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7542,7 +7542,7 @@
         <v>698</v>
       </c>
       <c r="B30" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7550,7 +7550,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7558,7 +7558,7 @@
         <v>477</v>
       </c>
       <c r="B32" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7566,7 +7566,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7574,7 +7574,7 @@
         <v>158</v>
       </c>
       <c r="B34" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7582,7 +7582,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7590,7 +7590,7 @@
         <v>692</v>
       </c>
       <c r="B36" s="1">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7598,7 +7598,7 @@
         <v>406</v>
       </c>
       <c r="B37" s="1">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7606,7 +7606,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="1">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7614,7 +7614,7 @@
         <v>626</v>
       </c>
       <c r="B39" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7622,7 +7622,7 @@
         <v>627</v>
       </c>
       <c r="B40" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7630,7 +7630,7 @@
         <v>628</v>
       </c>
       <c r="B41" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7638,7 +7638,7 @@
         <v>629</v>
       </c>
       <c r="B42" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -7646,7 +7646,7 @@
         <v>511</v>
       </c>
       <c r="B43" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7654,7 +7654,7 @@
         <v>85</v>
       </c>
       <c r="B44" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -7662,7 +7662,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -7670,7 +7670,7 @@
         <v>86</v>
       </c>
       <c r="B46" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7678,7 +7678,7 @@
         <v>135</v>
       </c>
       <c r="B47" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7686,7 +7686,7 @@
         <v>136</v>
       </c>
       <c r="B48" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -7694,7 +7694,7 @@
         <v>87</v>
       </c>
       <c r="B49" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -7702,7 +7702,7 @@
         <v>444</v>
       </c>
       <c r="B50" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -7710,7 +7710,7 @@
         <v>512</v>
       </c>
       <c r="B51" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -7718,7 +7718,7 @@
         <v>137</v>
       </c>
       <c r="B52" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -7726,7 +7726,7 @@
         <v>513</v>
       </c>
       <c r="B53" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -7734,7 +7734,7 @@
         <v>451</v>
       </c>
       <c r="B54" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -7742,7 +7742,7 @@
         <v>452</v>
       </c>
       <c r="B55" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -7750,7 +7750,7 @@
         <v>138</v>
       </c>
       <c r="B56" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -7758,7 +7758,7 @@
         <v>699</v>
       </c>
       <c r="B57" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -7766,7 +7766,7 @@
         <v>583</v>
       </c>
       <c r="B58" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -7774,7 +7774,7 @@
         <v>584</v>
       </c>
       <c r="B59" s="1">
-        <v>42750</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -7782,7 +7782,7 @@
         <v>139</v>
       </c>
       <c r="B60" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -7790,7 +7790,7 @@
         <v>551</v>
       </c>
       <c r="B61" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -7798,7 +7798,7 @@
         <v>140</v>
       </c>
       <c r="B62" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -7806,7 +7806,7 @@
         <v>89</v>
       </c>
       <c r="B63" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -7814,7 +7814,7 @@
         <v>88</v>
       </c>
       <c r="B64" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -7822,7 +7822,7 @@
         <v>559</v>
       </c>
       <c r="B65" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -7830,7 +7830,7 @@
         <v>722</v>
       </c>
       <c r="B66" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -7838,7 +7838,7 @@
         <v>118</v>
       </c>
       <c r="B67" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -7846,7 +7846,7 @@
         <v>799</v>
       </c>
       <c r="B68" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -7854,7 +7854,7 @@
         <v>39</v>
       </c>
       <c r="B69" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -7862,7 +7862,7 @@
         <v>40</v>
       </c>
       <c r="B70" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -7870,7 +7870,7 @@
         <v>800</v>
       </c>
       <c r="B71" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -7878,7 +7878,7 @@
         <v>120</v>
       </c>
       <c r="B72" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7886,7 +7886,7 @@
         <v>41</v>
       </c>
       <c r="B73" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7894,7 +7894,7 @@
         <v>42</v>
       </c>
       <c r="B74" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7902,7 +7902,7 @@
         <v>43</v>
       </c>
       <c r="B75" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7910,7 +7910,7 @@
         <v>44</v>
       </c>
       <c r="B76" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7918,7 +7918,7 @@
         <v>45</v>
       </c>
       <c r="B77" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7926,7 +7926,7 @@
         <v>46</v>
       </c>
       <c r="B78" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7934,7 +7934,7 @@
         <v>687</v>
       </c>
       <c r="B79" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7942,7 +7942,7 @@
         <v>90</v>
       </c>
       <c r="B80" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7950,7 +7950,7 @@
         <v>32</v>
       </c>
       <c r="B81" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7958,7 +7958,7 @@
         <v>27</v>
       </c>
       <c r="B82" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7966,7 +7966,7 @@
         <v>33</v>
       </c>
       <c r="B83" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7974,7 +7974,7 @@
         <v>141</v>
       </c>
       <c r="B84" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7982,7 +7982,7 @@
         <v>49</v>
       </c>
       <c r="B85" s="1">
-        <v>142500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7990,7 +7990,7 @@
         <v>48</v>
       </c>
       <c r="B86" s="1">
-        <v>142500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7998,7 +7998,7 @@
         <v>47</v>
       </c>
       <c r="B87" s="1">
-        <v>131100</v>
+        <v>133400</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -8006,7 +8006,7 @@
         <v>50</v>
       </c>
       <c r="B88" s="1">
-        <v>142500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -8014,7 +8014,7 @@
         <v>51</v>
       </c>
       <c r="B89" s="1">
-        <v>142500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -8022,7 +8022,7 @@
         <v>474</v>
       </c>
       <c r="B90" s="1">
-        <v>142500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -8030,7 +8030,7 @@
         <v>55</v>
       </c>
       <c r="B91" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -8038,7 +8038,7 @@
         <v>52</v>
       </c>
       <c r="B92" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -8046,7 +8046,7 @@
         <v>53</v>
       </c>
       <c r="B93" s="1">
-        <v>125400</v>
+        <v>127600</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -8054,7 +8054,7 @@
         <v>54</v>
       </c>
       <c r="B94" s="1">
-        <v>125400</v>
+        <v>127600</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -8062,7 +8062,7 @@
         <v>56</v>
       </c>
       <c r="B95" s="1">
-        <v>125400</v>
+        <v>127600</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -8070,7 +8070,7 @@
         <v>475</v>
       </c>
       <c r="B96" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -8078,7 +8078,7 @@
         <v>514</v>
       </c>
       <c r="B97" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -8086,7 +8086,7 @@
         <v>700</v>
       </c>
       <c r="B98" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -8094,7 +8094,7 @@
         <v>701</v>
       </c>
       <c r="B99" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -8102,7 +8102,7 @@
         <v>142</v>
       </c>
       <c r="B100" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -8110,7 +8110,7 @@
         <v>801</v>
       </c>
       <c r="B101" s="1">
-        <v>79800</v>
+        <v>81200</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -8118,7 +8118,7 @@
         <v>544</v>
       </c>
       <c r="B102" s="1">
-        <v>79800</v>
+        <v>81200</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -8126,7 +8126,7 @@
         <v>802</v>
       </c>
       <c r="B103" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -8134,7 +8134,7 @@
         <v>643</v>
       </c>
       <c r="B104" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -8142,7 +8142,7 @@
         <v>515</v>
       </c>
       <c r="B105" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -8150,7 +8150,7 @@
         <v>428</v>
       </c>
       <c r="B106" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -8158,7 +8158,7 @@
         <v>693</v>
       </c>
       <c r="B107" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -8166,7 +8166,7 @@
         <v>552</v>
       </c>
       <c r="B108" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -8174,7 +8174,7 @@
         <v>825</v>
       </c>
       <c r="B109" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -8182,7 +8182,7 @@
         <v>702</v>
       </c>
       <c r="B110" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -8190,7 +8190,7 @@
         <v>93</v>
       </c>
       <c r="B111" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -8198,7 +8198,7 @@
         <v>92</v>
       </c>
       <c r="B112" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -8206,7 +8206,7 @@
         <v>91</v>
       </c>
       <c r="B113" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -8214,7 +8214,7 @@
         <v>94</v>
       </c>
       <c r="B114" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -8222,7 +8222,7 @@
         <v>585</v>
       </c>
       <c r="B115" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -8230,7 +8230,7 @@
         <v>646</v>
       </c>
       <c r="B116" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -8238,7 +8238,7 @@
         <v>560</v>
       </c>
       <c r="B117" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -8246,7 +8246,7 @@
         <v>57</v>
       </c>
       <c r="B118" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -8254,7 +8254,7 @@
         <v>58</v>
       </c>
       <c r="B119" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -8262,7 +8262,7 @@
         <v>59</v>
       </c>
       <c r="B120" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -8270,7 +8270,7 @@
         <v>561</v>
       </c>
       <c r="B121" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -8278,7 +8278,7 @@
         <v>562</v>
       </c>
       <c r="B122" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -8286,7 +8286,7 @@
         <v>677</v>
       </c>
       <c r="B123" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -8294,7 +8294,7 @@
         <v>685</v>
       </c>
       <c r="B124" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -8302,7 +8302,7 @@
         <v>686</v>
       </c>
       <c r="B125" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -8310,7 +8310,7 @@
         <v>484</v>
       </c>
       <c r="B126" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -8318,7 +8318,7 @@
         <v>735</v>
       </c>
       <c r="B127" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -8326,7 +8326,7 @@
         <v>60</v>
       </c>
       <c r="B128" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -8334,7 +8334,7 @@
         <v>61</v>
       </c>
       <c r="B129" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -8342,7 +8342,7 @@
         <v>157</v>
       </c>
       <c r="B130" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -8350,7 +8350,7 @@
         <v>62</v>
       </c>
       <c r="B131" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -8358,7 +8358,7 @@
         <v>754</v>
       </c>
       <c r="B132" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -8366,7 +8366,7 @@
         <v>694</v>
       </c>
       <c r="B133" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -8374,7 +8374,7 @@
         <v>563</v>
       </c>
       <c r="B134" s="1">
-        <v>79800</v>
+        <v>81200</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -8382,7 +8382,7 @@
         <v>697</v>
       </c>
       <c r="B135" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -8390,7 +8390,7 @@
         <v>455</v>
       </c>
       <c r="B136" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -8398,7 +8398,7 @@
         <v>623</v>
       </c>
       <c r="B137" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -8406,7 +8406,7 @@
         <v>630</v>
       </c>
       <c r="B138" s="1">
-        <v>313500</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -8414,7 +8414,7 @@
         <v>631</v>
       </c>
       <c r="B139" s="1">
-        <v>324900</v>
+        <v>330600</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -8422,7 +8422,7 @@
         <v>449</v>
       </c>
       <c r="B140" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -8430,7 +8430,7 @@
         <v>448</v>
       </c>
       <c r="B141" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -8438,7 +8438,7 @@
         <v>450</v>
       </c>
       <c r="B142" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -8446,7 +8446,7 @@
         <v>447</v>
       </c>
       <c r="B143" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -8454,7 +8454,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -8462,7 +8462,7 @@
         <v>446</v>
       </c>
       <c r="B145" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -8470,7 +8470,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -8478,7 +8478,7 @@
         <v>591</v>
       </c>
       <c r="B147" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -8486,7 +8486,7 @@
         <v>96</v>
       </c>
       <c r="B148" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -8494,7 +8494,7 @@
         <v>95</v>
       </c>
       <c r="B149" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -8502,7 +8502,7 @@
         <v>97</v>
       </c>
       <c r="B150" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -8510,7 +8510,7 @@
         <v>553</v>
       </c>
       <c r="B151" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -8518,7 +8518,7 @@
         <v>803</v>
       </c>
       <c r="B152" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -8526,7 +8526,7 @@
         <v>804</v>
       </c>
       <c r="B153" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -8534,7 +8534,7 @@
         <v>145</v>
       </c>
       <c r="B154" s="1">
-        <v>142500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -8542,7 +8542,7 @@
         <v>119</v>
       </c>
       <c r="B155" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -8550,7 +8550,7 @@
         <v>703</v>
       </c>
       <c r="B156" s="1">
-        <v>42750</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -8558,7 +8558,7 @@
         <v>704</v>
       </c>
       <c r="B157" s="1">
-        <v>42750</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -8566,7 +8566,7 @@
         <v>98</v>
       </c>
       <c r="B158" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -8574,7 +8574,7 @@
         <v>63</v>
       </c>
       <c r="B159" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -8582,7 +8582,7 @@
         <v>472</v>
       </c>
       <c r="B160" s="1">
-        <v>79800</v>
+        <v>81200</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -8590,7 +8590,7 @@
         <v>99</v>
       </c>
       <c r="B161" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -8598,7 +8598,7 @@
         <v>720</v>
       </c>
       <c r="B162" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -8606,7 +8606,7 @@
         <v>724</v>
       </c>
       <c r="B163" s="1">
-        <v>42750</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -8614,7 +8614,7 @@
         <v>721</v>
       </c>
       <c r="B164" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -8622,7 +8622,7 @@
         <v>725</v>
       </c>
       <c r="B165" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -8630,7 +8630,7 @@
         <v>695</v>
       </c>
       <c r="B166" s="1">
-        <v>855</v>
+        <v>870</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -8638,7 +8638,7 @@
         <v>101</v>
       </c>
       <c r="B167" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -8646,7 +8646,7 @@
         <v>102</v>
       </c>
       <c r="B168" s="1">
-        <v>131100</v>
+        <v>133400</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -8654,7 +8654,7 @@
         <v>103</v>
       </c>
       <c r="B169" s="1">
-        <v>199500</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -8662,7 +8662,7 @@
         <v>632</v>
       </c>
       <c r="B170" s="1">
-        <v>199500</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -8670,7 +8670,7 @@
         <v>633</v>
       </c>
       <c r="B171" s="1">
-        <v>205200</v>
+        <v>208800</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -8678,7 +8678,7 @@
         <v>678</v>
       </c>
       <c r="B172" s="1">
-        <v>210900</v>
+        <v>214600</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -8686,7 +8686,7 @@
         <v>679</v>
       </c>
       <c r="B173" s="1">
-        <v>199500</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -8694,7 +8694,7 @@
         <v>680</v>
       </c>
       <c r="B174" s="1">
-        <v>199500</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8702,7 +8702,7 @@
         <v>681</v>
       </c>
       <c r="B175" s="1">
-        <v>199500</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -8710,7 +8710,7 @@
         <v>740</v>
       </c>
       <c r="B176" s="1">
-        <v>125400</v>
+        <v>127600</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -8718,7 +8718,7 @@
         <v>23</v>
       </c>
       <c r="B177" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -8726,7 +8726,7 @@
         <v>442</v>
       </c>
       <c r="B178" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -8734,7 +8734,7 @@
         <v>564</v>
       </c>
       <c r="B179" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -8742,7 +8742,7 @@
         <v>146</v>
       </c>
       <c r="B180" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -8750,7 +8750,7 @@
         <v>147</v>
       </c>
       <c r="B181" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -8758,7 +8758,7 @@
         <v>755</v>
       </c>
       <c r="B182" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -8766,7 +8766,7 @@
         <v>705</v>
       </c>
       <c r="B183" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -8774,7 +8774,7 @@
         <v>652</v>
       </c>
       <c r="B184" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -8782,7 +8782,7 @@
         <v>805</v>
       </c>
       <c r="B185" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -8790,7 +8790,7 @@
         <v>748</v>
       </c>
       <c r="B186" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -8798,7 +8798,7 @@
         <v>148</v>
       </c>
       <c r="B187" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -8806,7 +8806,7 @@
         <v>706</v>
       </c>
       <c r="B188" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -8814,7 +8814,7 @@
         <v>516</v>
       </c>
       <c r="B189" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -8822,7 +8822,7 @@
         <v>749</v>
       </c>
       <c r="B190" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -8830,7 +8830,7 @@
         <v>149</v>
       </c>
       <c r="B191" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -8838,7 +8838,7 @@
         <v>565</v>
       </c>
       <c r="B192" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -8846,7 +8846,7 @@
         <v>707</v>
       </c>
       <c r="B193" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -8854,7 +8854,7 @@
         <v>150</v>
       </c>
       <c r="B194" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -8862,7 +8862,7 @@
         <v>104</v>
       </c>
       <c r="B195" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -8870,7 +8870,7 @@
         <v>517</v>
       </c>
       <c r="B196" s="1">
-        <v>42750</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -8878,7 +8878,7 @@
         <v>151</v>
       </c>
       <c r="B197" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -8886,7 +8886,7 @@
         <v>481</v>
       </c>
       <c r="B198" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -8894,7 +8894,7 @@
         <v>708</v>
       </c>
       <c r="B199" s="1">
-        <v>96900</v>
+        <v>98600</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -8902,7 +8902,7 @@
         <v>64</v>
       </c>
       <c r="B200" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -8910,7 +8910,7 @@
         <v>152</v>
       </c>
       <c r="B201" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -8918,7 +8918,7 @@
         <v>65</v>
       </c>
       <c r="B202" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -8926,7 +8926,7 @@
         <v>545</v>
       </c>
       <c r="B203" s="1">
-        <v>79800</v>
+        <v>81200</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -8934,7 +8934,7 @@
         <v>547</v>
       </c>
       <c r="B204" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -8942,7 +8942,7 @@
         <v>66</v>
       </c>
       <c r="B205" s="1">
-        <v>74100</v>
+        <v>75400</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -8950,7 +8950,7 @@
         <v>67</v>
       </c>
       <c r="B206" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -8958,7 +8958,7 @@
         <v>68</v>
       </c>
       <c r="B207" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -8966,7 +8966,7 @@
         <v>69</v>
       </c>
       <c r="B208" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -8974,7 +8974,7 @@
         <v>70</v>
       </c>
       <c r="B209" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -8982,7 +8982,7 @@
         <v>71</v>
       </c>
       <c r="B210" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -8990,7 +8990,7 @@
         <v>72</v>
       </c>
       <c r="B211" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -8998,7 +8998,7 @@
         <v>473</v>
       </c>
       <c r="B212" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -9006,7 +9006,7 @@
         <v>160</v>
       </c>
       <c r="B213" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -9014,7 +9014,7 @@
         <v>161</v>
       </c>
       <c r="B214" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -9022,7 +9022,7 @@
         <v>75</v>
       </c>
       <c r="B215" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -9030,7 +9030,7 @@
         <v>159</v>
       </c>
       <c r="B216" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -9038,7 +9038,7 @@
         <v>107</v>
       </c>
       <c r="B217" s="1">
-        <v>142500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -9046,7 +9046,7 @@
         <v>108</v>
       </c>
       <c r="B218" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -9054,7 +9054,7 @@
         <v>110</v>
       </c>
       <c r="B219" s="1">
-        <v>114000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -9062,7 +9062,7 @@
         <v>105</v>
       </c>
       <c r="B220" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -9070,7 +9070,7 @@
         <v>106</v>
       </c>
       <c r="B221" s="1">
-        <v>85500</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -9078,7 +9078,7 @@
         <v>109</v>
       </c>
       <c r="B222" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -9086,7 +9086,7 @@
         <v>111</v>
       </c>
       <c r="B223" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -9094,7 +9094,7 @@
         <v>153</v>
       </c>
       <c r="B224" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -9102,7 +9102,7 @@
         <v>154</v>
       </c>
       <c r="B225" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -9110,7 +9110,7 @@
         <v>76</v>
       </c>
       <c r="B226" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -9118,7 +9118,7 @@
         <v>77</v>
       </c>
       <c r="B227" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -9126,7 +9126,7 @@
         <v>714</v>
       </c>
       <c r="B228" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -9134,7 +9134,7 @@
         <v>78</v>
       </c>
       <c r="B229" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -9142,7 +9142,7 @@
         <v>443</v>
       </c>
       <c r="B230" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -9150,7 +9150,7 @@
         <v>79</v>
       </c>
       <c r="B231" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -9158,7 +9158,7 @@
         <v>518</v>
       </c>
       <c r="B232" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -9166,7 +9166,7 @@
         <v>80</v>
       </c>
       <c r="B233" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -9174,7 +9174,7 @@
         <v>81</v>
       </c>
       <c r="B234" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -9182,7 +9182,7 @@
         <v>519</v>
       </c>
       <c r="B235" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -9190,7 +9190,7 @@
         <v>113</v>
       </c>
       <c r="B236" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -9198,7 +9198,7 @@
         <v>114</v>
       </c>
       <c r="B237" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -9206,7 +9206,7 @@
         <v>453</v>
       </c>
       <c r="B238" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -9214,7 +9214,7 @@
         <v>710</v>
       </c>
       <c r="B239" s="1">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -9222,7 +9222,7 @@
         <v>750</v>
       </c>
       <c r="B240" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -9230,7 +9230,7 @@
         <v>650</v>
       </c>
       <c r="B241" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -9238,7 +9238,7 @@
         <v>588</v>
       </c>
       <c r="B242" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -9246,7 +9246,7 @@
         <v>555</v>
       </c>
       <c r="B243" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -9254,7 +9254,7 @@
         <v>117</v>
       </c>
       <c r="B244" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -9262,7 +9262,7 @@
         <v>403</v>
       </c>
       <c r="B245" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -9270,7 +9270,7 @@
         <v>546</v>
       </c>
       <c r="B246" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -9278,7 +9278,7 @@
         <v>568</v>
       </c>
       <c r="B247" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -9286,7 +9286,7 @@
         <v>566</v>
       </c>
       <c r="B248" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -9294,7 +9294,7 @@
         <v>556</v>
       </c>
       <c r="B249" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -9302,7 +9302,7 @@
         <v>557</v>
       </c>
       <c r="B250" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -9310,7 +9310,7 @@
         <v>634</v>
       </c>
       <c r="B251" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -9318,7 +9318,7 @@
         <v>711</v>
       </c>
       <c r="B252" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -9326,7 +9326,7 @@
         <v>712</v>
       </c>
       <c r="B253" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -9334,7 +9334,7 @@
         <v>558</v>
       </c>
       <c r="B254" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -9342,7 +9342,7 @@
         <v>635</v>
       </c>
       <c r="B255" s="1">
-        <v>131100</v>
+        <v>133400</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -9350,7 +9350,7 @@
         <v>713</v>
       </c>
       <c r="B256" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -9358,7 +9358,7 @@
         <v>794</v>
       </c>
       <c r="B257" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -9366,7 +9366,7 @@
         <v>445</v>
       </c>
       <c r="B258" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -9374,7 +9374,7 @@
         <v>682</v>
       </c>
       <c r="B259" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -9382,7 +9382,7 @@
         <v>112</v>
       </c>
       <c r="B260" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -9390,7 +9390,7 @@
         <v>155</v>
       </c>
       <c r="B261" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -9398,7 +9398,7 @@
         <v>156</v>
       </c>
       <c r="B262" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
   </sheetData>
@@ -9428,7 +9428,7 @@
         <v>592</v>
       </c>
       <c r="B2" s="1">
-        <v>102600</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9436,7 +9436,7 @@
         <v>806</v>
       </c>
       <c r="B3" s="1">
-        <v>76950</v>
+        <v>78300</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9444,7 +9444,7 @@
         <v>807</v>
       </c>
       <c r="B4" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9452,7 +9452,7 @@
         <v>589</v>
       </c>
       <c r="B5" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9460,7 +9460,7 @@
         <v>808</v>
       </c>
       <c r="B6" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9468,7 +9468,7 @@
         <v>581</v>
       </c>
       <c r="B7" s="1">
-        <v>62700</v>
+        <v>63800</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9476,7 +9476,7 @@
         <v>648</v>
       </c>
       <c r="B8" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9484,7 +9484,7 @@
         <v>520</v>
       </c>
       <c r="B9" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -9492,7 +9492,7 @@
         <v>521</v>
       </c>
       <c r="B10" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9500,7 +9500,7 @@
         <v>522</v>
       </c>
       <c r="B11" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9508,7 +9508,7 @@
         <v>523</v>
       </c>
       <c r="B12" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -9516,7 +9516,7 @@
         <v>809</v>
       </c>
       <c r="B13" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -9524,7 +9524,7 @@
         <v>551</v>
       </c>
       <c r="B14" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -9532,7 +9532,7 @@
         <v>722</v>
       </c>
       <c r="B15" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -9540,7 +9540,7 @@
         <v>524</v>
       </c>
       <c r="B16" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -9548,7 +9548,7 @@
         <v>525</v>
       </c>
       <c r="B17" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -9556,7 +9556,7 @@
         <v>691</v>
       </c>
       <c r="B18" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -9564,7 +9564,7 @@
         <v>526</v>
       </c>
       <c r="B19" s="1">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -9572,7 +9572,7 @@
         <v>810</v>
       </c>
       <c r="B20" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -9580,7 +9580,7 @@
         <v>527</v>
       </c>
       <c r="B21" s="1">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -9588,7 +9588,7 @@
         <v>552</v>
       </c>
       <c r="B22" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -9596,7 +9596,7 @@
         <v>825</v>
       </c>
       <c r="B23" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -9604,7 +9604,7 @@
         <v>528</v>
       </c>
       <c r="B24" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -9612,7 +9612,7 @@
         <v>821</v>
       </c>
       <c r="B25" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -9620,7 +9620,7 @@
         <v>529</v>
       </c>
       <c r="B26" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -9628,7 +9628,7 @@
         <v>684</v>
       </c>
       <c r="B27" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -9636,7 +9636,7 @@
         <v>484</v>
       </c>
       <c r="B28">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -9644,7 +9644,7 @@
         <v>735</v>
       </c>
       <c r="B29">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -9652,7 +9652,7 @@
         <v>530</v>
       </c>
       <c r="B30">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -9660,7 +9660,7 @@
         <v>531</v>
       </c>
       <c r="B31">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -9668,7 +9668,7 @@
         <v>532</v>
       </c>
       <c r="B32">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -9676,7 +9676,7 @@
         <v>533</v>
       </c>
       <c r="B33">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -9684,7 +9684,7 @@
         <v>534</v>
       </c>
       <c r="B34">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -9692,7 +9692,7 @@
         <v>535</v>
       </c>
       <c r="B35">
-        <v>62700</v>
+        <v>63800</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -9700,7 +9700,7 @@
         <v>631</v>
       </c>
       <c r="B36">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -9708,7 +9708,7 @@
         <v>553</v>
       </c>
       <c r="B37">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -9716,7 +9716,7 @@
         <v>726</v>
       </c>
       <c r="B38">
-        <v>48450</v>
+        <v>49300</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -9724,7 +9724,7 @@
         <v>727</v>
       </c>
       <c r="B39">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -9732,7 +9732,7 @@
         <v>536</v>
       </c>
       <c r="B40">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -9740,7 +9740,7 @@
         <v>683</v>
       </c>
       <c r="B41">
-        <v>205200</v>
+        <v>208800</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -9748,7 +9748,7 @@
         <v>636</v>
       </c>
       <c r="B42">
-        <v>210900</v>
+        <v>214600</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -9756,7 +9756,7 @@
         <v>740</v>
       </c>
       <c r="B43">
-        <v>125400</v>
+        <v>127600</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -9764,7 +9764,7 @@
         <v>537</v>
       </c>
       <c r="B44">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -9772,7 +9772,7 @@
         <v>538</v>
       </c>
       <c r="B45">
-        <v>28500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -9780,7 +9780,7 @@
         <v>811</v>
       </c>
       <c r="B46">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -9788,7 +9788,7 @@
         <v>812</v>
       </c>
       <c r="B47">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -9796,7 +9796,7 @@
         <v>813</v>
       </c>
       <c r="B48">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -9804,7 +9804,7 @@
         <v>539</v>
       </c>
       <c r="B49">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -9812,7 +9812,7 @@
         <v>814</v>
       </c>
       <c r="B50">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -9820,7 +9820,7 @@
         <v>815</v>
       </c>
       <c r="B51">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -9828,7 +9828,7 @@
         <v>816</v>
       </c>
       <c r="B52">
-        <v>14250</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -9836,7 +9836,7 @@
         <v>588</v>
       </c>
       <c r="B53">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -9844,7 +9844,7 @@
         <v>817</v>
       </c>
       <c r="B54">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -9852,7 +9852,7 @@
         <v>818</v>
       </c>
       <c r="B55">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -9860,7 +9860,7 @@
         <v>819</v>
       </c>
       <c r="B56">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -9868,7 +9868,7 @@
         <v>548</v>
       </c>
       <c r="B57">
-        <v>39900</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -9876,7 +9876,7 @@
         <v>549</v>
       </c>
       <c r="B58">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -9884,7 +9884,7 @@
         <v>403</v>
       </c>
       <c r="B59">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -9892,7 +9892,7 @@
         <v>546</v>
       </c>
       <c r="B60">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -9900,7 +9900,7 @@
         <v>556</v>
       </c>
       <c r="B61">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -9908,7 +9908,7 @@
         <v>557</v>
       </c>
       <c r="B62">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -9916,7 +9916,7 @@
         <v>540</v>
       </c>
       <c r="B63">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -9924,7 +9924,7 @@
         <v>541</v>
       </c>
       <c r="B64">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -9932,7 +9932,7 @@
         <v>637</v>
       </c>
       <c r="B65">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -9940,7 +9940,7 @@
         <v>542</v>
       </c>
       <c r="B66">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
   </sheetData>
@@ -9970,7 +9970,7 @@
         <v>383</v>
       </c>
       <c r="B2" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9978,7 +9978,7 @@
         <v>384</v>
       </c>
       <c r="B3" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9986,7 +9986,7 @@
         <v>385</v>
       </c>
       <c r="B4" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9994,7 +9994,7 @@
         <v>386</v>
       </c>
       <c r="B5" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -10002,7 +10002,7 @@
         <v>640</v>
       </c>
       <c r="B6" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -10010,7 +10010,7 @@
         <v>387</v>
       </c>
       <c r="B7" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -10018,7 +10018,7 @@
         <v>660</v>
       </c>
       <c r="B8" s="1">
-        <v>22800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -10026,7 +10026,7 @@
         <v>662</v>
       </c>
       <c r="B9" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -10034,7 +10034,7 @@
         <v>661</v>
       </c>
       <c r="B10" s="1">
-        <v>18240</v>
+        <v>18560</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -10042,7 +10042,7 @@
         <v>388</v>
       </c>
       <c r="B11" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -10050,7 +10050,7 @@
         <v>405</v>
       </c>
       <c r="B12" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -10058,7 +10058,7 @@
         <v>659</v>
       </c>
       <c r="B13" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -10066,7 +10066,7 @@
         <v>665</v>
       </c>
       <c r="B14" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -10074,7 +10074,7 @@
         <v>745</v>
       </c>
       <c r="B15" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -10082,7 +10082,7 @@
         <v>389</v>
       </c>
       <c r="B16" s="1">
-        <v>5130</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -10090,7 +10090,7 @@
         <v>589</v>
       </c>
       <c r="B17" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -10098,7 +10098,7 @@
         <v>823</v>
       </c>
       <c r="B18" s="1">
-        <v>48450</v>
+        <v>49300</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -10106,7 +10106,7 @@
         <v>663</v>
       </c>
       <c r="B19" s="1">
-        <v>99750</v>
+        <v>101500</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -10114,7 +10114,7 @@
         <v>655</v>
       </c>
       <c r="B20" s="1">
-        <v>111150</v>
+        <v>113100</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -10122,7 +10122,7 @@
         <v>656</v>
       </c>
       <c r="B21" s="1">
-        <v>125400</v>
+        <v>127600</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -10130,7 +10130,7 @@
         <v>430</v>
       </c>
       <c r="B22" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -10138,7 +10138,7 @@
         <v>163</v>
       </c>
       <c r="B23" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -10146,7 +10146,7 @@
         <v>647</v>
       </c>
       <c r="B24" s="1">
-        <v>57000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -10154,7 +10154,7 @@
         <v>581</v>
       </c>
       <c r="B25" s="1">
-        <v>62700</v>
+        <v>63800</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -10162,7 +10162,7 @@
         <v>648</v>
       </c>
       <c r="B26" s="1">
-        <v>68400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -10170,7 +10170,7 @@
         <v>657</v>
       </c>
       <c r="B27" s="1">
-        <v>76950</v>
+        <v>78300</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -10178,7 +10178,7 @@
         <v>658</v>
       </c>
       <c r="B28" s="1">
-        <v>91200</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -10186,7 +10186,7 @@
         <v>664</v>
       </c>
       <c r="B29" s="1">
-        <v>96900</v>
+        <v>98600</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -10194,7 +10194,7 @@
         <v>692</v>
       </c>
       <c r="B30" s="1">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -10202,7 +10202,7 @@
         <v>406</v>
       </c>
       <c r="B31" s="1">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -10210,7 +10210,7 @@
         <v>402</v>
       </c>
       <c r="B32" s="1">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -10218,7 +10218,7 @@
         <v>429</v>
       </c>
       <c r="B33" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -10226,7 +10226,7 @@
         <v>551</v>
       </c>
       <c r="B34" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -10234,7 +10234,7 @@
         <v>390</v>
       </c>
       <c r="B35" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -10242,7 +10242,7 @@
         <v>552</v>
       </c>
       <c r="B36" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -10250,7 +10250,7 @@
         <v>825</v>
       </c>
       <c r="B37" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -10258,7 +10258,7 @@
         <v>820</v>
       </c>
       <c r="B38" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -10266,7 +10266,7 @@
         <v>404</v>
       </c>
       <c r="B39" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -10274,7 +10274,7 @@
         <v>259</v>
       </c>
       <c r="B40" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -10282,7 +10282,7 @@
         <v>425</v>
       </c>
       <c r="B41" s="1">
-        <v>2280</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -10290,7 +10290,7 @@
         <v>484</v>
       </c>
       <c r="B42" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -10298,7 +10298,7 @@
         <v>735</v>
       </c>
       <c r="B43" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -10306,7 +10306,7 @@
         <v>391</v>
       </c>
       <c r="B44" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -10314,7 +10314,7 @@
         <v>392</v>
       </c>
       <c r="B45" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -10322,7 +10322,7 @@
         <v>393</v>
       </c>
       <c r="B46" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -10330,7 +10330,7 @@
         <v>638</v>
       </c>
       <c r="B47" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -10338,7 +10338,7 @@
         <v>394</v>
       </c>
       <c r="B48" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -10346,7 +10346,7 @@
         <v>395</v>
       </c>
       <c r="B49" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -10354,7 +10354,7 @@
         <v>396</v>
       </c>
       <c r="B50" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -10362,7 +10362,7 @@
         <v>728</v>
       </c>
       <c r="B51" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -10370,7 +10370,7 @@
         <v>553</v>
       </c>
       <c r="B52" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -10378,7 +10378,7 @@
         <v>718</v>
       </c>
       <c r="B53" s="1">
-        <v>31350</v>
+        <v>31900</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -10386,7 +10386,7 @@
         <v>719</v>
       </c>
       <c r="B54" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -10394,7 +10394,7 @@
         <v>752</v>
       </c>
       <c r="B55" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -10402,7 +10402,7 @@
         <v>723</v>
       </c>
       <c r="B56" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -10410,7 +10410,7 @@
         <v>720</v>
       </c>
       <c r="B57" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -10418,7 +10418,7 @@
         <v>724</v>
       </c>
       <c r="B58" s="1">
-        <v>42750</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -10426,7 +10426,7 @@
         <v>721</v>
       </c>
       <c r="B59" s="1">
-        <v>37050</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -10434,7 +10434,7 @@
         <v>725</v>
       </c>
       <c r="B60" s="1">
-        <v>45600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -10442,7 +10442,7 @@
         <v>726</v>
       </c>
       <c r="B61" s="1">
-        <v>48450</v>
+        <v>49300</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -10450,7 +10450,7 @@
         <v>727</v>
       </c>
       <c r="B62" s="1">
-        <v>51300</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -10458,7 +10458,7 @@
         <v>740</v>
       </c>
       <c r="B63" s="1">
-        <v>125400</v>
+        <v>127600</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -10466,7 +10466,7 @@
         <v>827</v>
       </c>
       <c r="B64" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -10474,7 +10474,7 @@
         <v>639</v>
       </c>
       <c r="B65" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -10482,7 +10482,7 @@
         <v>543</v>
       </c>
       <c r="B66" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -10490,7 +10490,7 @@
         <v>397</v>
       </c>
       <c r="B67" s="1">
-        <v>10260</v>
+        <v>10440</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -10498,7 +10498,7 @@
         <v>653</v>
       </c>
       <c r="B68" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -10506,7 +10506,7 @@
         <v>398</v>
       </c>
       <c r="B69" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -10514,7 +10514,7 @@
         <v>399</v>
       </c>
       <c r="B70" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -10522,7 +10522,7 @@
         <v>400</v>
       </c>
       <c r="B71" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -10530,7 +10530,7 @@
         <v>582</v>
       </c>
       <c r="B72" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -10538,7 +10538,7 @@
         <v>401</v>
       </c>
       <c r="B73" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -10546,7 +10546,7 @@
         <v>588</v>
       </c>
       <c r="B74" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -10554,7 +10554,7 @@
         <v>554</v>
       </c>
       <c r="B75" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -10562,7 +10562,7 @@
         <v>555</v>
       </c>
       <c r="B76" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -10570,7 +10570,7 @@
         <v>644</v>
       </c>
       <c r="B77" s="1">
-        <v>3990</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -10578,7 +10578,7 @@
         <v>645</v>
       </c>
       <c r="B78" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -10586,7 +10586,7 @@
         <v>403</v>
       </c>
       <c r="B79" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -10594,7 +10594,7 @@
         <v>546</v>
       </c>
       <c r="B80" s="1">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -10602,7 +10602,7 @@
         <v>556</v>
       </c>
       <c r="B81" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -10610,7 +10610,7 @@
         <v>557</v>
       </c>
       <c r="B82" s="1">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -10618,7 +10618,7 @@
         <v>558</v>
       </c>
       <c r="B83" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
   </sheetData>

--- a/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\580 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\590 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F12C0C4-F4AF-4A63-9F69-0732BC182CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D26C5F1-3E1F-4633-AB0B-D7D5C7710607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAEWOO TICO" sheetId="1" r:id="rId1"/>
@@ -3034,7 +3034,7 @@
         <v>166</v>
       </c>
       <c r="B2" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3042,7 +3042,7 @@
         <v>421</v>
       </c>
       <c r="B3" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3050,7 +3050,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3058,7 +3058,7 @@
         <v>459</v>
       </c>
       <c r="B5" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3066,7 +3066,7 @@
         <v>460</v>
       </c>
       <c r="B6" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3074,7 +3074,7 @@
         <v>593</v>
       </c>
       <c r="B7" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3082,7 +3082,7 @@
         <v>168</v>
       </c>
       <c r="B8" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3090,7 +3090,7 @@
         <v>461</v>
       </c>
       <c r="B9" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3098,7 +3098,7 @@
         <v>169</v>
       </c>
       <c r="B10" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3106,7 +3106,7 @@
         <v>170</v>
       </c>
       <c r="B11" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3114,7 +3114,7 @@
         <v>171</v>
       </c>
       <c r="B12" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3122,7 +3122,7 @@
         <v>174</v>
       </c>
       <c r="B13" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3130,7 +3130,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3138,7 +3138,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="1">
-        <v>63800</v>
+        <v>64900</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3146,7 +3146,7 @@
         <v>666</v>
       </c>
       <c r="B16" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3154,7 +3154,7 @@
         <v>175</v>
       </c>
       <c r="B17" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3162,7 +3162,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3170,7 +3170,7 @@
         <v>589</v>
       </c>
       <c r="B19" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3178,7 +3178,7 @@
         <v>462</v>
       </c>
       <c r="B20" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3186,7 +3186,7 @@
         <v>177</v>
       </c>
       <c r="B21" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3194,7 +3194,7 @@
         <v>178</v>
       </c>
       <c r="B22" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3202,7 +3202,7 @@
         <v>179</v>
       </c>
       <c r="B23" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3210,7 +3210,7 @@
         <v>550</v>
       </c>
       <c r="B24" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3218,7 +3218,7 @@
         <v>180</v>
       </c>
       <c r="B25" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3226,7 +3226,7 @@
         <v>181</v>
       </c>
       <c r="B26" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3234,7 +3234,7 @@
         <v>182</v>
       </c>
       <c r="B27" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3242,7 +3242,7 @@
         <v>183</v>
       </c>
       <c r="B28" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3250,7 +3250,7 @@
         <v>184</v>
       </c>
       <c r="B29" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3258,7 +3258,7 @@
         <v>185</v>
       </c>
       <c r="B30" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3266,7 +3266,7 @@
         <v>186</v>
       </c>
       <c r="B31" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3274,7 +3274,7 @@
         <v>187</v>
       </c>
       <c r="B32" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3282,7 +3282,7 @@
         <v>188</v>
       </c>
       <c r="B33" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3290,7 +3290,7 @@
         <v>606</v>
       </c>
       <c r="B34" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3298,7 +3298,7 @@
         <v>569</v>
       </c>
       <c r="B35" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3306,7 +3306,7 @@
         <v>594</v>
       </c>
       <c r="B36" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3314,7 +3314,7 @@
         <v>823</v>
       </c>
       <c r="B37" s="1">
-        <v>49300</v>
+        <v>50150</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3322,7 +3322,7 @@
         <v>430</v>
       </c>
       <c r="B38" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3330,7 +3330,7 @@
         <v>163</v>
       </c>
       <c r="B39" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3338,7 +3338,7 @@
         <v>647</v>
       </c>
       <c r="B40" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3346,7 +3346,7 @@
         <v>581</v>
       </c>
       <c r="B41" s="1">
-        <v>63800</v>
+        <v>64900</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3354,7 +3354,7 @@
         <v>648</v>
       </c>
       <c r="B42" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3362,7 +3362,7 @@
         <v>189</v>
       </c>
       <c r="B43" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3370,7 +3370,7 @@
         <v>419</v>
       </c>
       <c r="B44" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3378,7 +3378,7 @@
         <v>408</v>
       </c>
       <c r="B45" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3386,7 +3386,7 @@
         <v>729</v>
       </c>
       <c r="B46" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3394,7 +3394,7 @@
         <v>730</v>
       </c>
       <c r="B47" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3402,7 +3402,7 @@
         <v>190</v>
       </c>
       <c r="B48" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3410,7 +3410,7 @@
         <v>191</v>
       </c>
       <c r="B49" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3418,7 +3418,7 @@
         <v>192</v>
       </c>
       <c r="B50" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3426,7 +3426,7 @@
         <v>193</v>
       </c>
       <c r="B51" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3434,7 +3434,7 @@
         <v>692</v>
       </c>
       <c r="B52" s="1">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3442,7 +3442,7 @@
         <v>194</v>
       </c>
       <c r="B53" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3450,7 +3450,7 @@
         <v>406</v>
       </c>
       <c r="B54" s="1">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3458,7 +3458,7 @@
         <v>402</v>
       </c>
       <c r="B55" s="1">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3466,7 +3466,7 @@
         <v>429</v>
       </c>
       <c r="B56" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3474,7 +3474,7 @@
         <v>195</v>
       </c>
       <c r="B57" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3482,7 +3482,7 @@
         <v>196</v>
       </c>
       <c r="B58" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3490,7 +3490,7 @@
         <v>197</v>
       </c>
       <c r="B59" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3498,7 +3498,7 @@
         <v>595</v>
       </c>
       <c r="B60" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3506,7 +3506,7 @@
         <v>596</v>
       </c>
       <c r="B61" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3514,7 +3514,7 @@
         <v>198</v>
       </c>
       <c r="B62" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3522,7 +3522,7 @@
         <v>199</v>
       </c>
       <c r="B63" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3530,7 +3530,7 @@
         <v>200</v>
       </c>
       <c r="B64" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3538,7 +3538,7 @@
         <v>201</v>
       </c>
       <c r="B65" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3546,7 +3546,7 @@
         <v>202</v>
       </c>
       <c r="B66" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3554,7 +3554,7 @@
         <v>203</v>
       </c>
       <c r="B67" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3562,7 +3562,7 @@
         <v>204</v>
       </c>
       <c r="B68" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3570,7 +3570,7 @@
         <v>205</v>
       </c>
       <c r="B69" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3578,7 +3578,7 @@
         <v>206</v>
       </c>
       <c r="B70" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3586,7 +3586,7 @@
         <v>208</v>
       </c>
       <c r="B71" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3594,7 +3594,7 @@
         <v>212</v>
       </c>
       <c r="B72" s="1">
-        <v>1160</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3602,7 +3602,7 @@
         <v>209</v>
       </c>
       <c r="B73" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3610,7 +3610,7 @@
         <v>210</v>
       </c>
       <c r="B74" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3618,7 +3618,7 @@
         <v>211</v>
       </c>
       <c r="B75" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3626,7 +3626,7 @@
         <v>476</v>
       </c>
       <c r="B76" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3634,7 +3634,7 @@
         <v>207</v>
       </c>
       <c r="B77" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3642,7 +3642,7 @@
         <v>213</v>
       </c>
       <c r="B78" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3650,7 +3650,7 @@
         <v>214</v>
       </c>
       <c r="B79" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3658,7 +3658,7 @@
         <v>215</v>
       </c>
       <c r="B80" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3666,7 +3666,7 @@
         <v>216</v>
       </c>
       <c r="B81" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3674,7 +3674,7 @@
         <v>217</v>
       </c>
       <c r="B82" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3682,7 +3682,7 @@
         <v>218</v>
       </c>
       <c r="B83" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3690,7 +3690,7 @@
         <v>219</v>
       </c>
       <c r="B84" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3698,7 +3698,7 @@
         <v>220</v>
       </c>
       <c r="B85" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3706,7 +3706,7 @@
         <v>607</v>
       </c>
       <c r="B86" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3714,7 +3714,7 @@
         <v>221</v>
       </c>
       <c r="B87" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3722,7 +3722,7 @@
         <v>608</v>
       </c>
       <c r="B88" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3730,7 +3730,7 @@
         <v>417</v>
       </c>
       <c r="B89" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3738,7 +3738,7 @@
         <v>418</v>
       </c>
       <c r="B90" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3746,7 +3746,7 @@
         <v>222</v>
       </c>
       <c r="B91" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3754,7 +3754,7 @@
         <v>223</v>
       </c>
       <c r="B92" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3762,7 +3762,7 @@
         <v>224</v>
       </c>
       <c r="B93" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3770,7 +3770,7 @@
         <v>225</v>
       </c>
       <c r="B94" s="1">
-        <v>203000</v>
+        <v>206500</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3778,7 +3778,7 @@
         <v>226</v>
       </c>
       <c r="B95" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3786,7 +3786,7 @@
         <v>824</v>
       </c>
       <c r="B96" s="1">
-        <v>174000</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3794,7 +3794,7 @@
         <v>227</v>
       </c>
       <c r="B97" s="1">
-        <v>162400</v>
+        <v>165200</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3802,7 +3802,7 @@
         <v>228</v>
       </c>
       <c r="B98" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3810,7 +3810,7 @@
         <v>551</v>
       </c>
       <c r="B99" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3818,7 +3818,7 @@
         <v>667</v>
       </c>
       <c r="B100" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3826,7 +3826,7 @@
         <v>409</v>
       </c>
       <c r="B101" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3834,7 +3834,7 @@
         <v>229</v>
       </c>
       <c r="B102" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3842,7 +3842,7 @@
         <v>230</v>
       </c>
       <c r="B103" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3850,7 +3850,7 @@
         <v>231</v>
       </c>
       <c r="B104" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3858,7 +3858,7 @@
         <v>424</v>
       </c>
       <c r="B105" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3866,7 +3866,7 @@
         <v>232</v>
       </c>
       <c r="B106" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3874,7 +3874,7 @@
         <v>570</v>
       </c>
       <c r="B107" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3882,7 +3882,7 @@
         <v>483</v>
       </c>
       <c r="B108" s="1">
-        <v>145000</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3890,7 +3890,7 @@
         <v>587</v>
       </c>
       <c r="B109" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3898,7 +3898,7 @@
         <v>233</v>
       </c>
       <c r="B110" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3906,7 +3906,7 @@
         <v>234</v>
       </c>
       <c r="B111" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3914,7 +3914,7 @@
         <v>731</v>
       </c>
       <c r="B112" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3922,7 +3922,7 @@
         <v>717</v>
       </c>
       <c r="B113" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3930,7 +3930,7 @@
         <v>571</v>
       </c>
       <c r="B114" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3938,7 +3938,7 @@
         <v>590</v>
       </c>
       <c r="B115" s="1">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3946,7 +3946,7 @@
         <v>235</v>
       </c>
       <c r="B116" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3954,7 +3954,7 @@
         <v>732</v>
       </c>
       <c r="B117" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3962,7 +3962,7 @@
         <v>236</v>
       </c>
       <c r="B118" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3970,7 +3970,7 @@
         <v>733</v>
       </c>
       <c r="B119" s="1">
-        <v>1160</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3978,7 +3978,7 @@
         <v>237</v>
       </c>
       <c r="B120" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3986,7 +3986,7 @@
         <v>410</v>
       </c>
       <c r="B121" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3994,7 +3994,7 @@
         <v>238</v>
       </c>
       <c r="B122" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4002,7 +4002,7 @@
         <v>239</v>
       </c>
       <c r="B123" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4010,7 +4010,7 @@
         <v>240</v>
       </c>
       <c r="B124" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4018,7 +4018,7 @@
         <v>241</v>
       </c>
       <c r="B125" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4026,7 +4026,7 @@
         <v>242</v>
       </c>
       <c r="B126" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4034,7 +4034,7 @@
         <v>243</v>
       </c>
       <c r="B127" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4042,7 +4042,7 @@
         <v>668</v>
       </c>
       <c r="B128" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4050,7 +4050,7 @@
         <v>669</v>
       </c>
       <c r="B129" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4058,7 +4058,7 @@
         <v>431</v>
       </c>
       <c r="B130" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4066,7 +4066,7 @@
         <v>244</v>
       </c>
       <c r="B131" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4074,7 +4074,7 @@
         <v>597</v>
       </c>
       <c r="B132" s="1">
-        <v>249400</v>
+        <v>253700</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4082,7 +4082,7 @@
         <v>245</v>
       </c>
       <c r="B133" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4090,7 +4090,7 @@
         <v>456</v>
       </c>
       <c r="B134" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4098,7 +4098,7 @@
         <v>457</v>
       </c>
       <c r="B135" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4106,7 +4106,7 @@
         <v>458</v>
       </c>
       <c r="B136" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4114,7 +4114,7 @@
         <v>246</v>
       </c>
       <c r="B137" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4122,7 +4122,7 @@
         <v>247</v>
       </c>
       <c r="B138" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4130,7 +4130,7 @@
         <v>248</v>
       </c>
       <c r="B139" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4138,7 +4138,7 @@
         <v>250</v>
       </c>
       <c r="B140" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4146,7 +4146,7 @@
         <v>420</v>
       </c>
       <c r="B141" s="1">
-        <v>145000</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4154,7 +4154,7 @@
         <v>14</v>
       </c>
       <c r="B142" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4162,7 +4162,7 @@
         <v>602</v>
       </c>
       <c r="B143" s="1">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4170,7 +4170,7 @@
         <v>249</v>
       </c>
       <c r="B144" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4178,7 +4178,7 @@
         <v>552</v>
       </c>
       <c r="B145" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4186,7 +4186,7 @@
         <v>251</v>
       </c>
       <c r="B146" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4194,7 +4194,7 @@
         <v>825</v>
       </c>
       <c r="B147" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4202,7 +4202,7 @@
         <v>252</v>
       </c>
       <c r="B148" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4210,7 +4210,7 @@
         <v>253</v>
       </c>
       <c r="B149" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4218,7 +4218,7 @@
         <v>598</v>
       </c>
       <c r="B150" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4226,7 +4226,7 @@
         <v>254</v>
       </c>
       <c r="B151" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4234,7 +4234,7 @@
         <v>255</v>
       </c>
       <c r="B152" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4242,7 +4242,7 @@
         <v>256</v>
       </c>
       <c r="B153" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4250,7 +4250,7 @@
         <v>257</v>
       </c>
       <c r="B154" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4258,7 +4258,7 @@
         <v>258</v>
       </c>
       <c r="B155" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4266,7 +4266,7 @@
         <v>261</v>
       </c>
       <c r="B156" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4274,7 +4274,7 @@
         <v>262</v>
       </c>
       <c r="B157" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4282,7 +4282,7 @@
         <v>263</v>
       </c>
       <c r="B158" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4290,7 +4290,7 @@
         <v>404</v>
       </c>
       <c r="B159" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4298,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="B160" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4306,7 +4306,7 @@
         <v>463</v>
       </c>
       <c r="B161" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4314,7 +4314,7 @@
         <v>260</v>
       </c>
       <c r="B162" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4322,7 +4322,7 @@
         <v>264</v>
       </c>
       <c r="B163" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4330,7 +4330,7 @@
         <v>689</v>
       </c>
       <c r="B164" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4338,7 +4338,7 @@
         <v>641</v>
       </c>
       <c r="B165" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4346,7 +4346,7 @@
         <v>642</v>
       </c>
       <c r="B166" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4354,7 +4354,7 @@
         <v>603</v>
       </c>
       <c r="B167" s="1">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4362,7 +4362,7 @@
         <v>604</v>
       </c>
       <c r="B168" s="1">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4370,7 +4370,7 @@
         <v>484</v>
       </c>
       <c r="B169" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4378,7 +4378,7 @@
         <v>265</v>
       </c>
       <c r="B170" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4386,7 +4386,7 @@
         <v>609</v>
       </c>
       <c r="B171" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4394,7 +4394,7 @@
         <v>734</v>
       </c>
       <c r="B172" s="1">
-        <v>2320</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4402,7 +4402,7 @@
         <v>735</v>
       </c>
       <c r="B173" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4410,7 +4410,7 @@
         <v>266</v>
       </c>
       <c r="B174" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4418,7 +4418,7 @@
         <v>267</v>
       </c>
       <c r="B175" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4426,7 +4426,7 @@
         <v>268</v>
       </c>
       <c r="B176" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4434,7 +4434,7 @@
         <v>269</v>
       </c>
       <c r="B177" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4442,7 +4442,7 @@
         <v>270</v>
       </c>
       <c r="B178" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4450,7 +4450,7 @@
         <v>271</v>
       </c>
       <c r="B179" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4458,7 +4458,7 @@
         <v>272</v>
       </c>
       <c r="B180" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4466,7 +4466,7 @@
         <v>273</v>
       </c>
       <c r="B181" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4474,7 +4474,7 @@
         <v>422</v>
       </c>
       <c r="B182" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4482,7 +4482,7 @@
         <v>423</v>
       </c>
       <c r="B183" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4490,7 +4490,7 @@
         <v>610</v>
       </c>
       <c r="B184" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4498,7 +4498,7 @@
         <v>611</v>
       </c>
       <c r="B185" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4506,7 +4506,7 @@
         <v>612</v>
       </c>
       <c r="B186" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4514,7 +4514,7 @@
         <v>613</v>
       </c>
       <c r="B187" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4522,7 +4522,7 @@
         <v>614</v>
       </c>
       <c r="B188" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4530,7 +4530,7 @@
         <v>615</v>
       </c>
       <c r="B189" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4538,7 +4538,7 @@
         <v>274</v>
       </c>
       <c r="B190" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4546,7 +4546,7 @@
         <v>276</v>
       </c>
       <c r="B191" s="1">
-        <v>1160</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4554,7 +4554,7 @@
         <v>275</v>
       </c>
       <c r="B192" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4562,7 +4562,7 @@
         <v>616</v>
       </c>
       <c r="B193" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4570,7 +4570,7 @@
         <v>277</v>
       </c>
       <c r="B194" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4578,7 +4578,7 @@
         <v>464</v>
       </c>
       <c r="B195" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4586,7 +4586,7 @@
         <v>278</v>
       </c>
       <c r="B196" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4594,7 +4594,7 @@
         <v>736</v>
       </c>
       <c r="B197" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4602,7 +4602,7 @@
         <v>391</v>
       </c>
       <c r="B198" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4610,7 +4610,7 @@
         <v>396</v>
       </c>
       <c r="B199" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4618,7 +4618,7 @@
         <v>466</v>
       </c>
       <c r="B200" s="1">
-        <v>185600</v>
+        <v>188800</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4626,7 +4626,7 @@
         <v>279</v>
       </c>
       <c r="B201" s="1">
-        <v>301600</v>
+        <v>306800</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4634,7 +4634,7 @@
         <v>649</v>
       </c>
       <c r="B202" s="1">
-        <v>307400</v>
+        <v>312700</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4642,7 +4642,7 @@
         <v>280</v>
       </c>
       <c r="B203" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4650,7 +4650,7 @@
         <v>696</v>
       </c>
       <c r="B204" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4658,7 +4658,7 @@
         <v>737</v>
       </c>
       <c r="B205" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4666,7 +4666,7 @@
         <v>411</v>
       </c>
       <c r="B206" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4674,7 +4674,7 @@
         <v>281</v>
       </c>
       <c r="B207" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4682,7 +4682,7 @@
         <v>412</v>
       </c>
       <c r="B208" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4690,7 +4690,7 @@
         <v>282</v>
       </c>
       <c r="B209" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4698,7 +4698,7 @@
         <v>283</v>
       </c>
       <c r="B210" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4706,7 +4706,7 @@
         <v>284</v>
       </c>
       <c r="B211" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4714,7 +4714,7 @@
         <v>285</v>
       </c>
       <c r="B212" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4722,7 +4722,7 @@
         <v>286</v>
       </c>
       <c r="B213" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4730,7 +4730,7 @@
         <v>287</v>
       </c>
       <c r="B214" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4738,7 +4738,7 @@
         <v>288</v>
       </c>
       <c r="B215" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4746,7 +4746,7 @@
         <v>289</v>
       </c>
       <c r="B216" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4754,7 +4754,7 @@
         <v>553</v>
       </c>
       <c r="B217" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4762,7 +4762,7 @@
         <v>290</v>
       </c>
       <c r="B218" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4770,7 +4770,7 @@
         <v>738</v>
       </c>
       <c r="B219" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4778,7 +4778,7 @@
         <v>739</v>
       </c>
       <c r="B220" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4786,7 +4786,7 @@
         <v>291</v>
       </c>
       <c r="B221" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4794,7 +4794,7 @@
         <v>292</v>
       </c>
       <c r="B222" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4802,7 +4802,7 @@
         <v>293</v>
       </c>
       <c r="B223" s="1">
-        <v>162400</v>
+        <v>165200</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4810,7 +4810,7 @@
         <v>294</v>
       </c>
       <c r="B224" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4818,7 +4818,7 @@
         <v>572</v>
       </c>
       <c r="B225" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4826,7 +4826,7 @@
         <v>670</v>
       </c>
       <c r="B226" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4834,7 +4834,7 @@
         <v>295</v>
       </c>
       <c r="B227" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4842,7 +4842,7 @@
         <v>671</v>
       </c>
       <c r="B228" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4850,7 +4850,7 @@
         <v>296</v>
       </c>
       <c r="B229" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4858,7 +4858,7 @@
         <v>718</v>
       </c>
       <c r="B230" s="1">
-        <v>31900</v>
+        <v>32450</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4866,7 +4866,7 @@
         <v>719</v>
       </c>
       <c r="B231" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4874,7 +4874,7 @@
         <v>720</v>
       </c>
       <c r="B232" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4882,7 +4882,7 @@
         <v>721</v>
       </c>
       <c r="B233" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4890,7 +4890,7 @@
         <v>617</v>
       </c>
       <c r="B234" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4898,7 +4898,7 @@
         <v>297</v>
       </c>
       <c r="B235" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4906,7 +4906,7 @@
         <v>573</v>
       </c>
       <c r="B236" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4914,7 +4914,7 @@
         <v>298</v>
       </c>
       <c r="B237" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4922,7 +4922,7 @@
         <v>299</v>
       </c>
       <c r="B238" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4930,7 +4930,7 @@
         <v>300</v>
       </c>
       <c r="B239" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4938,7 +4938,7 @@
         <v>301</v>
       </c>
       <c r="B240" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4946,7 +4946,7 @@
         <v>302</v>
       </c>
       <c r="B241" s="1">
-        <v>174000</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4954,7 +4954,7 @@
         <v>672</v>
       </c>
       <c r="B242" s="1">
-        <v>174000</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4962,7 +4962,7 @@
         <v>303</v>
       </c>
       <c r="B243" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4970,7 +4970,7 @@
         <v>740</v>
       </c>
       <c r="B244" s="1">
-        <v>127600</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4978,7 +4978,7 @@
         <v>304</v>
       </c>
       <c r="B245" s="1">
-        <v>63800</v>
+        <v>64900</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4986,7 +4986,7 @@
         <v>305</v>
       </c>
       <c r="B246" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4994,7 +4994,7 @@
         <v>306</v>
       </c>
       <c r="B247" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5002,7 +5002,7 @@
         <v>618</v>
       </c>
       <c r="B248" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5010,7 +5010,7 @@
         <v>307</v>
       </c>
       <c r="B249" s="1">
-        <v>98600</v>
+        <v>100300</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5018,7 +5018,7 @@
         <v>308</v>
       </c>
       <c r="B250" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5026,7 +5026,7 @@
         <v>309</v>
       </c>
       <c r="B251" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5034,7 +5034,7 @@
         <v>310</v>
       </c>
       <c r="B252" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5042,7 +5042,7 @@
         <v>690</v>
       </c>
       <c r="B253" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5050,7 +5050,7 @@
         <v>311</v>
       </c>
       <c r="B254" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5058,7 +5058,7 @@
         <v>312</v>
       </c>
       <c r="B255" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5066,7 +5066,7 @@
         <v>313</v>
       </c>
       <c r="B256" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5074,7 +5074,7 @@
         <v>467</v>
       </c>
       <c r="B257" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5082,7 +5082,7 @@
         <v>741</v>
       </c>
       <c r="B258" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5090,7 +5090,7 @@
         <v>742</v>
       </c>
       <c r="B259" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5098,7 +5098,7 @@
         <v>468</v>
       </c>
       <c r="B260" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5106,7 +5106,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5114,7 +5114,7 @@
         <v>315</v>
       </c>
       <c r="B262" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5122,7 +5122,7 @@
         <v>316</v>
       </c>
       <c r="B263" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5130,7 +5130,7 @@
         <v>414</v>
       </c>
       <c r="B264" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5138,7 +5138,7 @@
         <v>317</v>
       </c>
       <c r="B265" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5146,7 +5146,7 @@
         <v>318</v>
       </c>
       <c r="B266" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5154,7 +5154,7 @@
         <v>605</v>
       </c>
       <c r="B267" s="1">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5162,7 +5162,7 @@
         <v>319</v>
       </c>
       <c r="B268" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5170,7 +5170,7 @@
         <v>320</v>
       </c>
       <c r="B269" s="1">
-        <v>174000</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5178,7 +5178,7 @@
         <v>321</v>
       </c>
       <c r="B270" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5186,7 +5186,7 @@
         <v>322</v>
       </c>
       <c r="B271" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5194,7 +5194,7 @@
         <v>323</v>
       </c>
       <c r="B272" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5202,7 +5202,7 @@
         <v>324</v>
       </c>
       <c r="B273" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5210,7 +5210,7 @@
         <v>325</v>
       </c>
       <c r="B274" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5218,7 +5218,7 @@
         <v>326</v>
       </c>
       <c r="B275" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5226,7 +5226,7 @@
         <v>327</v>
       </c>
       <c r="B276" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5234,7 +5234,7 @@
         <v>328</v>
       </c>
       <c r="B277" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5242,7 +5242,7 @@
         <v>329</v>
       </c>
       <c r="B278" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5250,7 +5250,7 @@
         <v>330</v>
       </c>
       <c r="B279" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5258,7 +5258,7 @@
         <v>331</v>
       </c>
       <c r="B280" s="1">
-        <v>75400</v>
+        <v>76700</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5266,7 +5266,7 @@
         <v>332</v>
       </c>
       <c r="B281" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5274,7 +5274,7 @@
         <v>333</v>
       </c>
       <c r="B282" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5282,7 +5282,7 @@
         <v>334</v>
       </c>
       <c r="B283" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5290,7 +5290,7 @@
         <v>574</v>
       </c>
       <c r="B284" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5298,7 +5298,7 @@
         <v>599</v>
       </c>
       <c r="B285" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5306,7 +5306,7 @@
         <v>600</v>
       </c>
       <c r="B286" s="1">
-        <v>55100</v>
+        <v>56050</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5314,7 +5314,7 @@
         <v>743</v>
       </c>
       <c r="B287" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5322,7 +5322,7 @@
         <v>619</v>
       </c>
       <c r="B288" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5330,7 +5330,7 @@
         <v>335</v>
       </c>
       <c r="B289" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5338,7 +5338,7 @@
         <v>620</v>
       </c>
       <c r="B290" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5346,7 +5346,7 @@
         <v>336</v>
       </c>
       <c r="B291" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5354,7 +5354,7 @@
         <v>337</v>
       </c>
       <c r="B292" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5362,7 +5362,7 @@
         <v>338</v>
       </c>
       <c r="B293" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5370,7 +5370,7 @@
         <v>339</v>
       </c>
       <c r="B294" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5378,7 +5378,7 @@
         <v>340</v>
       </c>
       <c r="B295" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5386,7 +5386,7 @@
         <v>341</v>
       </c>
       <c r="B296" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5394,7 +5394,7 @@
         <v>342</v>
       </c>
       <c r="B297" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5402,7 +5402,7 @@
         <v>343</v>
       </c>
       <c r="B298" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5410,7 +5410,7 @@
         <v>415</v>
       </c>
       <c r="B299" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5418,7 +5418,7 @@
         <v>416</v>
       </c>
       <c r="B300" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5426,7 +5426,7 @@
         <v>601</v>
       </c>
       <c r="B301" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5434,7 +5434,7 @@
         <v>344</v>
       </c>
       <c r="B302" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5442,7 +5442,7 @@
         <v>345</v>
       </c>
       <c r="B303" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5450,7 +5450,7 @@
         <v>346</v>
       </c>
       <c r="B304" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5458,7 +5458,7 @@
         <v>347</v>
       </c>
       <c r="B305" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5466,7 +5466,7 @@
         <v>348</v>
       </c>
       <c r="B306" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5474,7 +5474,7 @@
         <v>349</v>
       </c>
       <c r="B307" s="1">
-        <v>2320</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5482,7 +5482,7 @@
         <v>744</v>
       </c>
       <c r="B308" s="1">
-        <v>1160</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5490,7 +5490,7 @@
         <v>673</v>
       </c>
       <c r="B309" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5498,7 +5498,7 @@
         <v>350</v>
       </c>
       <c r="B310" s="1">
-        <v>43500</v>
+        <v>44250</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5506,7 +5506,7 @@
         <v>351</v>
       </c>
       <c r="B311" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5514,7 +5514,7 @@
         <v>352</v>
       </c>
       <c r="B312" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5522,7 +5522,7 @@
         <v>575</v>
       </c>
       <c r="B313" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5530,7 +5530,7 @@
         <v>353</v>
       </c>
       <c r="B314" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5538,7 +5538,7 @@
         <v>354</v>
       </c>
       <c r="B315" s="1">
-        <v>145000</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5546,7 +5546,7 @@
         <v>407</v>
       </c>
       <c r="B316" s="1">
-        <v>319000</v>
+        <v>324500</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5554,7 +5554,7 @@
         <v>355</v>
       </c>
       <c r="B317" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5562,7 +5562,7 @@
         <v>356</v>
       </c>
       <c r="B318" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5570,7 +5570,7 @@
         <v>576</v>
       </c>
       <c r="B319" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5578,7 +5578,7 @@
         <v>357</v>
       </c>
       <c r="B320" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5586,7 +5586,7 @@
         <v>358</v>
       </c>
       <c r="B321" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5594,7 +5594,7 @@
         <v>651</v>
       </c>
       <c r="B322" s="1">
-        <v>2320</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5602,7 +5602,7 @@
         <v>577</v>
       </c>
       <c r="B323" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5610,7 +5610,7 @@
         <v>588</v>
       </c>
       <c r="B324" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5618,7 +5618,7 @@
         <v>359</v>
       </c>
       <c r="B325" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5626,7 +5626,7 @@
         <v>360</v>
       </c>
       <c r="B326" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5634,7 +5634,7 @@
         <v>361</v>
       </c>
       <c r="B327" s="1">
-        <v>2320</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5642,7 +5642,7 @@
         <v>362</v>
       </c>
       <c r="B328" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5650,7 +5650,7 @@
         <v>363</v>
       </c>
       <c r="B329" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5658,7 +5658,7 @@
         <v>364</v>
       </c>
       <c r="B330" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5666,7 +5666,7 @@
         <v>365</v>
       </c>
       <c r="B331" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5674,7 +5674,7 @@
         <v>403</v>
       </c>
       <c r="B332" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5682,7 +5682,7 @@
         <v>546</v>
       </c>
       <c r="B333" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5690,7 +5690,7 @@
         <v>822</v>
       </c>
       <c r="B334" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5698,7 +5698,7 @@
         <v>366</v>
       </c>
       <c r="B335" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5706,7 +5706,7 @@
         <v>556</v>
       </c>
       <c r="B336" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5714,7 +5714,7 @@
         <v>557</v>
       </c>
       <c r="B337" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5722,7 +5722,7 @@
         <v>367</v>
       </c>
       <c r="B338" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5730,7 +5730,7 @@
         <v>368</v>
       </c>
       <c r="B339" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5738,7 +5738,7 @@
         <v>369</v>
       </c>
       <c r="B340" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5746,7 +5746,7 @@
         <v>370</v>
       </c>
       <c r="B341" s="1">
-        <v>1160</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5754,7 +5754,7 @@
         <v>371</v>
       </c>
       <c r="B342" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5762,7 +5762,7 @@
         <v>372</v>
       </c>
       <c r="B343" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5770,7 +5770,7 @@
         <v>373</v>
       </c>
       <c r="B344" s="1">
-        <v>2320</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5778,7 +5778,7 @@
         <v>413</v>
       </c>
       <c r="B345" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5786,7 +5786,7 @@
         <v>465</v>
       </c>
       <c r="B346" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5794,7 +5794,7 @@
         <v>621</v>
       </c>
       <c r="B347" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5802,7 +5802,7 @@
         <v>374</v>
       </c>
       <c r="B348" s="1">
-        <v>1160</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5810,7 +5810,7 @@
         <v>485</v>
       </c>
       <c r="B349" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5818,7 +5818,7 @@
         <v>469</v>
       </c>
       <c r="B350" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5826,7 +5826,7 @@
         <v>375</v>
       </c>
       <c r="B351" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5834,7 +5834,7 @@
         <v>674</v>
       </c>
       <c r="B352" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5842,7 +5842,7 @@
         <v>675</v>
       </c>
       <c r="B353" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5850,7 +5850,7 @@
         <v>376</v>
       </c>
       <c r="B354" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5858,7 +5858,7 @@
         <v>377</v>
       </c>
       <c r="B355" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5866,7 +5866,7 @@
         <v>378</v>
       </c>
       <c r="B356" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5874,7 +5874,7 @@
         <v>622</v>
       </c>
       <c r="B357" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5882,7 +5882,7 @@
         <v>379</v>
       </c>
       <c r="B358" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5890,7 +5890,7 @@
         <v>470</v>
       </c>
       <c r="B359" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5898,7 +5898,7 @@
         <v>471</v>
       </c>
       <c r="B360" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5906,7 +5906,7 @@
         <v>676</v>
       </c>
       <c r="B361" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5914,7 +5914,7 @@
         <v>380</v>
       </c>
       <c r="B362" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5922,7 +5922,7 @@
         <v>381</v>
       </c>
       <c r="B363" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5930,7 +5930,7 @@
         <v>454</v>
       </c>
       <c r="B364" s="1">
-        <v>2320</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5938,7 +5938,7 @@
         <v>382</v>
       </c>
       <c r="B365" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
   </sheetData>
@@ -5968,7 +5968,7 @@
         <v>486</v>
       </c>
       <c r="B2" s="1">
-        <v>81200</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5976,7 +5976,7 @@
         <v>123</v>
       </c>
       <c r="B3" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5984,7 +5984,7 @@
         <v>757</v>
       </c>
       <c r="B4" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5992,7 +5992,7 @@
         <v>578</v>
       </c>
       <c r="B5" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6000,7 +6000,7 @@
         <v>164</v>
       </c>
       <c r="B6" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6008,7 +6008,7 @@
         <v>579</v>
       </c>
       <c r="B7" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6016,7 +6016,7 @@
         <v>589</v>
       </c>
       <c r="B8" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6024,7 +6024,7 @@
         <v>758</v>
       </c>
       <c r="B9" s="1">
-        <v>75400</v>
+        <v>76700</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6032,7 +6032,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6040,7 +6040,7 @@
         <v>759</v>
       </c>
       <c r="B11" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6048,7 +6048,7 @@
         <v>124</v>
       </c>
       <c r="B12" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6056,7 +6056,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6064,7 +6064,7 @@
         <v>823</v>
       </c>
       <c r="B14" s="1">
-        <v>49300</v>
+        <v>50150</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6072,7 +6072,7 @@
         <v>430</v>
       </c>
       <c r="B15" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6080,7 +6080,7 @@
         <v>163</v>
       </c>
       <c r="B16" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6088,7 +6088,7 @@
         <v>647</v>
       </c>
       <c r="B17" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6096,7 +6096,7 @@
         <v>581</v>
       </c>
       <c r="B18" s="1">
-        <v>63800</v>
+        <v>64900</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6104,7 +6104,7 @@
         <v>648</v>
       </c>
       <c r="B19" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6112,7 +6112,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6120,7 +6120,7 @@
         <v>125</v>
       </c>
       <c r="B21" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6128,7 +6128,7 @@
         <v>478</v>
       </c>
       <c r="B22" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6136,7 +6136,7 @@
         <v>36</v>
       </c>
       <c r="B23" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6144,7 +6144,7 @@
         <v>487</v>
       </c>
       <c r="B24" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6152,7 +6152,7 @@
         <v>488</v>
       </c>
       <c r="B25" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6160,7 +6160,7 @@
         <v>692</v>
       </c>
       <c r="B26" s="1">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6168,7 +6168,7 @@
         <v>406</v>
       </c>
       <c r="B27" s="1">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6176,7 +6176,7 @@
         <v>402</v>
       </c>
       <c r="B28" s="1">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6184,7 +6184,7 @@
         <v>439</v>
       </c>
       <c r="B29" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6192,7 +6192,7 @@
         <v>760</v>
       </c>
       <c r="B30" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6200,7 +6200,7 @@
         <v>489</v>
       </c>
       <c r="B31" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6208,7 +6208,7 @@
         <v>490</v>
       </c>
       <c r="B32" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6216,7 +6216,7 @@
         <v>761</v>
       </c>
       <c r="B33" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6224,7 +6224,7 @@
         <v>12</v>
       </c>
       <c r="B34" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6232,7 +6232,7 @@
         <v>762</v>
       </c>
       <c r="B35" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="1">
-        <v>1450</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6248,7 +6248,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6256,7 +6256,7 @@
         <v>434</v>
       </c>
       <c r="B38" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6264,7 +6264,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6272,7 +6272,7 @@
         <v>491</v>
       </c>
       <c r="B40" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6280,7 +6280,7 @@
         <v>479</v>
       </c>
       <c r="B41" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6288,7 +6288,7 @@
         <v>763</v>
       </c>
       <c r="B42" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6296,7 +6296,7 @@
         <v>438</v>
       </c>
       <c r="B43" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6304,7 +6304,7 @@
         <v>440</v>
       </c>
       <c r="B44" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6312,7 +6312,7 @@
         <v>492</v>
       </c>
       <c r="B45" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6320,7 +6320,7 @@
         <v>493</v>
       </c>
       <c r="B46" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6328,7 +6328,7 @@
         <v>494</v>
       </c>
       <c r="B47" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6336,7 +6336,7 @@
         <v>764</v>
       </c>
       <c r="B48" s="1">
-        <v>203000</v>
+        <v>206500</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -6344,7 +6344,7 @@
         <v>551</v>
       </c>
       <c r="B49" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -6352,7 +6352,7 @@
         <v>765</v>
       </c>
       <c r="B50" s="1">
-        <v>75400</v>
+        <v>76700</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -6360,7 +6360,7 @@
         <v>751</v>
       </c>
       <c r="B51" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -6368,7 +6368,7 @@
         <v>722</v>
       </c>
       <c r="B52" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -6376,7 +6376,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -6384,7 +6384,7 @@
         <v>766</v>
       </c>
       <c r="B54" s="1">
-        <v>81200</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -6392,7 +6392,7 @@
         <v>495</v>
       </c>
       <c r="B55" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -6400,7 +6400,7 @@
         <v>436</v>
       </c>
       <c r="B56" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -6408,7 +6408,7 @@
         <v>126</v>
       </c>
       <c r="B57" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -6416,7 +6416,7 @@
         <v>496</v>
       </c>
       <c r="B58" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -6424,7 +6424,7 @@
         <v>767</v>
       </c>
       <c r="B59" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -6432,7 +6432,7 @@
         <v>30</v>
       </c>
       <c r="B60" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -6440,7 +6440,7 @@
         <v>427</v>
       </c>
       <c r="B61" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -6448,7 +6448,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -6456,7 +6456,7 @@
         <v>768</v>
       </c>
       <c r="B63" s="1">
-        <v>145000</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -6464,7 +6464,7 @@
         <v>769</v>
       </c>
       <c r="B64" s="1">
-        <v>127600</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -6472,7 +6472,7 @@
         <v>127</v>
       </c>
       <c r="B65" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -6480,7 +6480,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -6488,7 +6488,7 @@
         <v>116</v>
       </c>
       <c r="B67" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6496,7 +6496,7 @@
         <v>14</v>
       </c>
       <c r="B68" s="1">
-        <v>75400</v>
+        <v>76700</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6504,7 +6504,7 @@
         <v>770</v>
       </c>
       <c r="B69" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -6512,7 +6512,7 @@
         <v>771</v>
       </c>
       <c r="B70" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -6520,7 +6520,7 @@
         <v>426</v>
       </c>
       <c r="B71" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -6528,7 +6528,7 @@
         <v>552</v>
       </c>
       <c r="B72" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -6536,7 +6536,7 @@
         <v>825</v>
       </c>
       <c r="B73" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -6544,7 +6544,7 @@
         <v>497</v>
       </c>
       <c r="B74" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -6552,7 +6552,7 @@
         <v>498</v>
       </c>
       <c r="B75" s="1">
-        <v>31900</v>
+        <v>32450</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -6560,7 +6560,7 @@
         <v>772</v>
       </c>
       <c r="B76" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -6568,7 +6568,7 @@
         <v>773</v>
       </c>
       <c r="B77" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -6576,7 +6576,7 @@
         <v>586</v>
       </c>
       <c r="B78" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -6584,7 +6584,7 @@
         <v>15</v>
       </c>
       <c r="B79" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -6592,7 +6592,7 @@
         <v>16</v>
       </c>
       <c r="B80" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -6600,7 +6600,7 @@
         <v>580</v>
       </c>
       <c r="B81" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -6608,7 +6608,7 @@
         <v>688</v>
       </c>
       <c r="B82" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -6616,7 +6616,7 @@
         <v>774</v>
       </c>
       <c r="B83" s="1">
-        <v>2320</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -6624,7 +6624,7 @@
         <v>484</v>
       </c>
       <c r="B84" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -6632,7 +6632,7 @@
         <v>775</v>
       </c>
       <c r="B85" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -6640,7 +6640,7 @@
         <v>735</v>
       </c>
       <c r="B86" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -6648,7 +6648,7 @@
         <v>3</v>
       </c>
       <c r="B87" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -6656,7 +6656,7 @@
         <v>17</v>
       </c>
       <c r="B88" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -6664,7 +6664,7 @@
         <v>128</v>
       </c>
       <c r="B89" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -6672,7 +6672,7 @@
         <v>715</v>
       </c>
       <c r="B90" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -6680,7 +6680,7 @@
         <v>499</v>
       </c>
       <c r="B91" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -6688,7 +6688,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -6696,7 +6696,7 @@
         <v>623</v>
       </c>
       <c r="B93" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -6704,7 +6704,7 @@
         <v>776</v>
       </c>
       <c r="B94" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -6712,7 +6712,7 @@
         <v>18</v>
       </c>
       <c r="B95" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -6720,7 +6720,7 @@
         <v>19</v>
       </c>
       <c r="B96" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -6728,7 +6728,7 @@
         <v>500</v>
       </c>
       <c r="B97" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -6736,7 +6736,7 @@
         <v>501</v>
       </c>
       <c r="B98" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -6744,7 +6744,7 @@
         <v>25</v>
       </c>
       <c r="B99" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -6752,7 +6752,7 @@
         <v>553</v>
       </c>
       <c r="B100" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -6760,7 +6760,7 @@
         <v>777</v>
       </c>
       <c r="B101" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -6768,7 +6768,7 @@
         <v>778</v>
       </c>
       <c r="B102" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -6776,7 +6776,7 @@
         <v>779</v>
       </c>
       <c r="B103" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -6784,7 +6784,7 @@
         <v>780</v>
       </c>
       <c r="B104" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -6792,7 +6792,7 @@
         <v>129</v>
       </c>
       <c r="B105" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -6800,7 +6800,7 @@
         <v>502</v>
       </c>
       <c r="B106" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -6808,7 +6808,7 @@
         <v>781</v>
       </c>
       <c r="B107" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -6816,7 +6816,7 @@
         <v>752</v>
       </c>
       <c r="B108" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -6824,7 +6824,7 @@
         <v>723</v>
       </c>
       <c r="B109" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -6832,7 +6832,7 @@
         <v>720</v>
       </c>
       <c r="B110" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -6840,7 +6840,7 @@
         <v>721</v>
       </c>
       <c r="B111" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -6848,7 +6848,7 @@
         <v>503</v>
       </c>
       <c r="B112" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -6856,7 +6856,7 @@
         <v>100</v>
       </c>
       <c r="B113" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -6864,7 +6864,7 @@
         <v>826</v>
       </c>
       <c r="B114" s="1">
-        <v>203000</v>
+        <v>206500</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -6872,7 +6872,7 @@
         <v>654</v>
       </c>
       <c r="B115" s="1">
-        <v>203000</v>
+        <v>206500</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -6880,7 +6880,7 @@
         <v>24</v>
       </c>
       <c r="B116" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -6888,7 +6888,7 @@
         <v>782</v>
       </c>
       <c r="B117" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -6896,7 +6896,7 @@
         <v>740</v>
       </c>
       <c r="B118" s="1">
-        <v>127600</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -6904,7 +6904,7 @@
         <v>20</v>
       </c>
       <c r="B119" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -6912,7 +6912,7 @@
         <v>433</v>
       </c>
       <c r="B120" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -6920,7 +6920,7 @@
         <v>783</v>
       </c>
       <c r="B121" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -6928,7 +6928,7 @@
         <v>115</v>
       </c>
       <c r="B122" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -6936,7 +6936,7 @@
         <v>504</v>
       </c>
       <c r="B123" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -6944,7 +6944,7 @@
         <v>505</v>
       </c>
       <c r="B124" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -6952,7 +6952,7 @@
         <v>784</v>
       </c>
       <c r="B125" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -6960,7 +6960,7 @@
         <v>716</v>
       </c>
       <c r="B126" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -6968,7 +6968,7 @@
         <v>785</v>
       </c>
       <c r="B127" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -6976,7 +6976,7 @@
         <v>506</v>
       </c>
       <c r="B128" s="1">
-        <v>43500</v>
+        <v>44250</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -6984,7 +6984,7 @@
         <v>21</v>
       </c>
       <c r="B129" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -6992,7 +6992,7 @@
         <v>756</v>
       </c>
       <c r="B130" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7000,7 +7000,7 @@
         <v>480</v>
       </c>
       <c r="B131" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7008,7 +7008,7 @@
         <v>786</v>
       </c>
       <c r="B132" s="1">
-        <v>75400</v>
+        <v>76700</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7016,7 +7016,7 @@
         <v>787</v>
       </c>
       <c r="B133" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7024,7 +7024,7 @@
         <v>788</v>
       </c>
       <c r="B134" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7032,7 +7032,7 @@
         <v>789</v>
       </c>
       <c r="B135" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7040,7 +7040,7 @@
         <v>73</v>
       </c>
       <c r="B136" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7048,7 +7048,7 @@
         <v>74</v>
       </c>
       <c r="B137" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7056,7 +7056,7 @@
         <v>162</v>
       </c>
       <c r="B138" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7064,7 +7064,7 @@
         <v>790</v>
       </c>
       <c r="B139" s="1">
-        <v>43500</v>
+        <v>44250</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7072,7 +7072,7 @@
         <v>130</v>
       </c>
       <c r="B140" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7080,7 +7080,7 @@
         <v>791</v>
       </c>
       <c r="B141" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7088,7 +7088,7 @@
         <v>709</v>
       </c>
       <c r="B142" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7096,7 +7096,7 @@
         <v>432</v>
       </c>
       <c r="B143" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7104,7 +7104,7 @@
         <v>507</v>
       </c>
       <c r="B144" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7112,7 +7112,7 @@
         <v>508</v>
       </c>
       <c r="B145" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7120,7 +7120,7 @@
         <v>437</v>
       </c>
       <c r="B146" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7128,7 +7128,7 @@
         <v>509</v>
       </c>
       <c r="B147" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7136,7 +7136,7 @@
         <v>792</v>
       </c>
       <c r="B148" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7144,7 +7144,7 @@
         <v>4</v>
       </c>
       <c r="B149" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7152,7 +7152,7 @@
         <v>793</v>
       </c>
       <c r="B150" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7160,7 +7160,7 @@
         <v>650</v>
       </c>
       <c r="B151" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7168,7 +7168,7 @@
         <v>651</v>
       </c>
       <c r="B152" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7176,7 +7176,7 @@
         <v>588</v>
       </c>
       <c r="B153" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7184,7 +7184,7 @@
         <v>554</v>
       </c>
       <c r="B154" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7192,7 +7192,7 @@
         <v>510</v>
       </c>
       <c r="B155" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7200,7 +7200,7 @@
         <v>403</v>
       </c>
       <c r="B156" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7208,7 +7208,7 @@
         <v>546</v>
       </c>
       <c r="B157" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7216,7 +7216,7 @@
         <v>441</v>
       </c>
       <c r="B158" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7224,7 +7224,7 @@
         <v>556</v>
       </c>
       <c r="B159" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7232,7 +7232,7 @@
         <v>557</v>
       </c>
       <c r="B160" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7240,7 +7240,7 @@
         <v>794</v>
       </c>
       <c r="B161" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7248,7 +7248,7 @@
         <v>435</v>
       </c>
       <c r="B162" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7256,7 +7256,7 @@
         <v>795</v>
       </c>
       <c r="B163" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7264,7 +7264,7 @@
         <v>796</v>
       </c>
       <c r="B164" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -7272,7 +7272,7 @@
         <v>624</v>
       </c>
       <c r="B165" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -7280,7 +7280,7 @@
         <v>10</v>
       </c>
       <c r="B166" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -7288,7 +7288,7 @@
         <v>797</v>
       </c>
       <c r="B167" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
   </sheetData>
@@ -7318,7 +7318,7 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>81200</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7326,7 +7326,7 @@
         <v>745</v>
       </c>
       <c r="B3" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7334,7 +7334,7 @@
         <v>746</v>
       </c>
       <c r="B4" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7342,7 +7342,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1">
-        <v>81200</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7350,7 +7350,7 @@
         <v>747</v>
       </c>
       <c r="B6" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7358,7 +7358,7 @@
         <v>122</v>
       </c>
       <c r="B7" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7366,7 +7366,7 @@
         <v>131</v>
       </c>
       <c r="B8" s="1">
-        <v>145000</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7374,7 +7374,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7382,7 +7382,7 @@
         <v>567</v>
       </c>
       <c r="B10" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7390,7 +7390,7 @@
         <v>82</v>
       </c>
       <c r="B11" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7398,7 +7398,7 @@
         <v>165</v>
       </c>
       <c r="B12" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7406,7 +7406,7 @@
         <v>589</v>
       </c>
       <c r="B13" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7414,7 +7414,7 @@
         <v>798</v>
       </c>
       <c r="B14" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7422,7 +7422,7 @@
         <v>132</v>
       </c>
       <c r="B15" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -7430,7 +7430,7 @@
         <v>133</v>
       </c>
       <c r="B16" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -7438,7 +7438,7 @@
         <v>753</v>
       </c>
       <c r="B17" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -7446,7 +7446,7 @@
         <v>625</v>
       </c>
       <c r="B18" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -7454,7 +7454,7 @@
         <v>823</v>
       </c>
       <c r="B19" s="1">
-        <v>49300</v>
+        <v>50150</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7462,7 +7462,7 @@
         <v>430</v>
       </c>
       <c r="B20" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7470,7 +7470,7 @@
         <v>163</v>
       </c>
       <c r="B21" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7478,7 +7478,7 @@
         <v>647</v>
       </c>
       <c r="B22" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7486,7 +7486,7 @@
         <v>581</v>
       </c>
       <c r="B23" s="1">
-        <v>63800</v>
+        <v>64900</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7494,7 +7494,7 @@
         <v>648</v>
       </c>
       <c r="B24" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7502,7 +7502,7 @@
         <v>83</v>
       </c>
       <c r="B25" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7510,7 +7510,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7518,7 +7518,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7526,7 +7526,7 @@
         <v>121</v>
       </c>
       <c r="B28" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7534,7 +7534,7 @@
         <v>134</v>
       </c>
       <c r="B29" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7542,7 +7542,7 @@
         <v>698</v>
       </c>
       <c r="B30" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7550,7 +7550,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7558,7 +7558,7 @@
         <v>477</v>
       </c>
       <c r="B32" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7566,7 +7566,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7574,7 +7574,7 @@
         <v>158</v>
       </c>
       <c r="B34" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7582,7 +7582,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7590,7 +7590,7 @@
         <v>692</v>
       </c>
       <c r="B36" s="1">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7598,7 +7598,7 @@
         <v>406</v>
       </c>
       <c r="B37" s="1">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7606,7 +7606,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="1">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7614,7 +7614,7 @@
         <v>626</v>
       </c>
       <c r="B39" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7622,7 +7622,7 @@
         <v>627</v>
       </c>
       <c r="B40" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7630,7 +7630,7 @@
         <v>628</v>
       </c>
       <c r="B41" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7638,7 +7638,7 @@
         <v>629</v>
       </c>
       <c r="B42" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -7646,7 +7646,7 @@
         <v>511</v>
       </c>
       <c r="B43" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7654,7 +7654,7 @@
         <v>85</v>
       </c>
       <c r="B44" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -7662,7 +7662,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -7670,7 +7670,7 @@
         <v>86</v>
       </c>
       <c r="B46" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7678,7 +7678,7 @@
         <v>135</v>
       </c>
       <c r="B47" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7686,7 +7686,7 @@
         <v>136</v>
       </c>
       <c r="B48" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -7694,7 +7694,7 @@
         <v>87</v>
       </c>
       <c r="B49" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -7702,7 +7702,7 @@
         <v>444</v>
       </c>
       <c r="B50" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -7710,7 +7710,7 @@
         <v>512</v>
       </c>
       <c r="B51" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -7718,7 +7718,7 @@
         <v>137</v>
       </c>
       <c r="B52" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -7726,7 +7726,7 @@
         <v>513</v>
       </c>
       <c r="B53" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -7734,7 +7734,7 @@
         <v>451</v>
       </c>
       <c r="B54" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -7742,7 +7742,7 @@
         <v>452</v>
       </c>
       <c r="B55" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -7750,7 +7750,7 @@
         <v>138</v>
       </c>
       <c r="B56" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -7758,7 +7758,7 @@
         <v>699</v>
       </c>
       <c r="B57" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -7766,7 +7766,7 @@
         <v>583</v>
       </c>
       <c r="B58" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -7774,7 +7774,7 @@
         <v>584</v>
       </c>
       <c r="B59" s="1">
-        <v>43500</v>
+        <v>44250</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -7782,7 +7782,7 @@
         <v>139</v>
       </c>
       <c r="B60" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -7790,7 +7790,7 @@
         <v>551</v>
       </c>
       <c r="B61" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -7798,7 +7798,7 @@
         <v>140</v>
       </c>
       <c r="B62" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -7806,7 +7806,7 @@
         <v>89</v>
       </c>
       <c r="B63" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -7814,7 +7814,7 @@
         <v>88</v>
       </c>
       <c r="B64" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -7822,7 +7822,7 @@
         <v>559</v>
       </c>
       <c r="B65" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -7830,7 +7830,7 @@
         <v>722</v>
       </c>
       <c r="B66" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -7838,7 +7838,7 @@
         <v>118</v>
       </c>
       <c r="B67" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -7846,7 +7846,7 @@
         <v>799</v>
       </c>
       <c r="B68" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -7854,7 +7854,7 @@
         <v>39</v>
       </c>
       <c r="B69" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -7862,7 +7862,7 @@
         <v>40</v>
       </c>
       <c r="B70" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -7870,7 +7870,7 @@
         <v>800</v>
       </c>
       <c r="B71" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -7878,7 +7878,7 @@
         <v>120</v>
       </c>
       <c r="B72" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7886,7 +7886,7 @@
         <v>41</v>
       </c>
       <c r="B73" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7894,7 +7894,7 @@
         <v>42</v>
       </c>
       <c r="B74" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7902,7 +7902,7 @@
         <v>43</v>
       </c>
       <c r="B75" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7910,7 +7910,7 @@
         <v>44</v>
       </c>
       <c r="B76" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7918,7 +7918,7 @@
         <v>45</v>
       </c>
       <c r="B77" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7926,7 +7926,7 @@
         <v>46</v>
       </c>
       <c r="B78" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7934,7 +7934,7 @@
         <v>687</v>
       </c>
       <c r="B79" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7942,7 +7942,7 @@
         <v>90</v>
       </c>
       <c r="B80" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7950,7 +7950,7 @@
         <v>32</v>
       </c>
       <c r="B81" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7958,7 +7958,7 @@
         <v>27</v>
       </c>
       <c r="B82" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7966,7 +7966,7 @@
         <v>33</v>
       </c>
       <c r="B83" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7974,7 +7974,7 @@
         <v>141</v>
       </c>
       <c r="B84" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7982,7 +7982,7 @@
         <v>49</v>
       </c>
       <c r="B85" s="1">
-        <v>145000</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7990,7 +7990,7 @@
         <v>48</v>
       </c>
       <c r="B86" s="1">
-        <v>145000</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7998,7 +7998,7 @@
         <v>47</v>
       </c>
       <c r="B87" s="1">
-        <v>133400</v>
+        <v>135700</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -8006,7 +8006,7 @@
         <v>50</v>
       </c>
       <c r="B88" s="1">
-        <v>145000</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -8014,7 +8014,7 @@
         <v>51</v>
       </c>
       <c r="B89" s="1">
-        <v>145000</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -8022,7 +8022,7 @@
         <v>474</v>
       </c>
       <c r="B90" s="1">
-        <v>145000</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -8030,7 +8030,7 @@
         <v>55</v>
       </c>
       <c r="B91" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -8038,7 +8038,7 @@
         <v>52</v>
       </c>
       <c r="B92" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -8046,7 +8046,7 @@
         <v>53</v>
       </c>
       <c r="B93" s="1">
-        <v>127600</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -8054,7 +8054,7 @@
         <v>54</v>
       </c>
       <c r="B94" s="1">
-        <v>127600</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -8062,7 +8062,7 @@
         <v>56</v>
       </c>
       <c r="B95" s="1">
-        <v>127600</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -8070,7 +8070,7 @@
         <v>475</v>
       </c>
       <c r="B96" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -8078,7 +8078,7 @@
         <v>514</v>
       </c>
       <c r="B97" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -8086,7 +8086,7 @@
         <v>700</v>
       </c>
       <c r="B98" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -8094,7 +8094,7 @@
         <v>701</v>
       </c>
       <c r="B99" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -8102,7 +8102,7 @@
         <v>142</v>
       </c>
       <c r="B100" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -8110,7 +8110,7 @@
         <v>801</v>
       </c>
       <c r="B101" s="1">
-        <v>81200</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -8118,7 +8118,7 @@
         <v>544</v>
       </c>
       <c r="B102" s="1">
-        <v>81200</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -8126,7 +8126,7 @@
         <v>802</v>
       </c>
       <c r="B103" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -8134,7 +8134,7 @@
         <v>643</v>
       </c>
       <c r="B104" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -8142,7 +8142,7 @@
         <v>515</v>
       </c>
       <c r="B105" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -8150,7 +8150,7 @@
         <v>428</v>
       </c>
       <c r="B106" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -8158,7 +8158,7 @@
         <v>693</v>
       </c>
       <c r="B107" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -8166,7 +8166,7 @@
         <v>552</v>
       </c>
       <c r="B108" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -8174,7 +8174,7 @@
         <v>825</v>
       </c>
       <c r="B109" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -8182,7 +8182,7 @@
         <v>702</v>
       </c>
       <c r="B110" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -8190,7 +8190,7 @@
         <v>93</v>
       </c>
       <c r="B111" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -8198,7 +8198,7 @@
         <v>92</v>
       </c>
       <c r="B112" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -8206,7 +8206,7 @@
         <v>91</v>
       </c>
       <c r="B113" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -8214,7 +8214,7 @@
         <v>94</v>
       </c>
       <c r="B114" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -8222,7 +8222,7 @@
         <v>585</v>
       </c>
       <c r="B115" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -8230,7 +8230,7 @@
         <v>646</v>
       </c>
       <c r="B116" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -8238,7 +8238,7 @@
         <v>560</v>
       </c>
       <c r="B117" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -8246,7 +8246,7 @@
         <v>57</v>
       </c>
       <c r="B118" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -8254,7 +8254,7 @@
         <v>58</v>
       </c>
       <c r="B119" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -8262,7 +8262,7 @@
         <v>59</v>
       </c>
       <c r="B120" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -8270,7 +8270,7 @@
         <v>561</v>
       </c>
       <c r="B121" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -8278,7 +8278,7 @@
         <v>562</v>
       </c>
       <c r="B122" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -8286,7 +8286,7 @@
         <v>677</v>
       </c>
       <c r="B123" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -8294,7 +8294,7 @@
         <v>685</v>
       </c>
       <c r="B124" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -8302,7 +8302,7 @@
         <v>686</v>
       </c>
       <c r="B125" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -8310,7 +8310,7 @@
         <v>484</v>
       </c>
       <c r="B126" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -8318,7 +8318,7 @@
         <v>735</v>
       </c>
       <c r="B127" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -8326,7 +8326,7 @@
         <v>60</v>
       </c>
       <c r="B128" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -8334,7 +8334,7 @@
         <v>61</v>
       </c>
       <c r="B129" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -8342,7 +8342,7 @@
         <v>157</v>
       </c>
       <c r="B130" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -8350,7 +8350,7 @@
         <v>62</v>
       </c>
       <c r="B131" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -8358,7 +8358,7 @@
         <v>754</v>
       </c>
       <c r="B132" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -8366,7 +8366,7 @@
         <v>694</v>
       </c>
       <c r="B133" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -8374,7 +8374,7 @@
         <v>563</v>
       </c>
       <c r="B134" s="1">
-        <v>81200</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -8382,7 +8382,7 @@
         <v>697</v>
       </c>
       <c r="B135" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -8390,7 +8390,7 @@
         <v>455</v>
       </c>
       <c r="B136" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -8398,7 +8398,7 @@
         <v>623</v>
       </c>
       <c r="B137" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -8406,7 +8406,7 @@
         <v>630</v>
       </c>
       <c r="B138" s="1">
-        <v>319000</v>
+        <v>324500</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -8414,7 +8414,7 @@
         <v>631</v>
       </c>
       <c r="B139" s="1">
-        <v>330600</v>
+        <v>336300</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -8422,7 +8422,7 @@
         <v>449</v>
       </c>
       <c r="B140" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -8430,7 +8430,7 @@
         <v>448</v>
       </c>
       <c r="B141" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -8438,7 +8438,7 @@
         <v>450</v>
       </c>
       <c r="B142" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -8446,7 +8446,7 @@
         <v>447</v>
       </c>
       <c r="B143" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -8454,7 +8454,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -8462,7 +8462,7 @@
         <v>446</v>
       </c>
       <c r="B145" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -8470,7 +8470,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -8478,7 +8478,7 @@
         <v>591</v>
       </c>
       <c r="B147" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -8486,7 +8486,7 @@
         <v>96</v>
       </c>
       <c r="B148" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -8494,7 +8494,7 @@
         <v>95</v>
       </c>
       <c r="B149" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -8502,7 +8502,7 @@
         <v>97</v>
       </c>
       <c r="B150" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -8510,7 +8510,7 @@
         <v>553</v>
       </c>
       <c r="B151" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -8518,7 +8518,7 @@
         <v>803</v>
       </c>
       <c r="B152" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -8526,7 +8526,7 @@
         <v>804</v>
       </c>
       <c r="B153" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -8534,7 +8534,7 @@
         <v>145</v>
       </c>
       <c r="B154" s="1">
-        <v>145000</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -8542,7 +8542,7 @@
         <v>119</v>
       </c>
       <c r="B155" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -8550,7 +8550,7 @@
         <v>703</v>
       </c>
       <c r="B156" s="1">
-        <v>43500</v>
+        <v>44250</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -8558,7 +8558,7 @@
         <v>704</v>
       </c>
       <c r="B157" s="1">
-        <v>43500</v>
+        <v>44250</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -8566,7 +8566,7 @@
         <v>98</v>
       </c>
       <c r="B158" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -8574,7 +8574,7 @@
         <v>63</v>
       </c>
       <c r="B159" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -8582,7 +8582,7 @@
         <v>472</v>
       </c>
       <c r="B160" s="1">
-        <v>81200</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -8590,7 +8590,7 @@
         <v>99</v>
       </c>
       <c r="B161" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -8598,7 +8598,7 @@
         <v>720</v>
       </c>
       <c r="B162" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -8606,7 +8606,7 @@
         <v>724</v>
       </c>
       <c r="B163" s="1">
-        <v>43500</v>
+        <v>44250</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -8614,7 +8614,7 @@
         <v>721</v>
       </c>
       <c r="B164" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -8622,7 +8622,7 @@
         <v>725</v>
       </c>
       <c r="B165" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -8630,7 +8630,7 @@
         <v>695</v>
       </c>
       <c r="B166" s="1">
-        <v>870</v>
+        <v>885</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -8638,7 +8638,7 @@
         <v>101</v>
       </c>
       <c r="B167" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -8646,7 +8646,7 @@
         <v>102</v>
       </c>
       <c r="B168" s="1">
-        <v>133400</v>
+        <v>135700</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -8654,7 +8654,7 @@
         <v>103</v>
       </c>
       <c r="B169" s="1">
-        <v>203000</v>
+        <v>206500</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -8662,7 +8662,7 @@
         <v>632</v>
       </c>
       <c r="B170" s="1">
-        <v>203000</v>
+        <v>206500</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -8670,7 +8670,7 @@
         <v>633</v>
       </c>
       <c r="B171" s="1">
-        <v>208800</v>
+        <v>212400</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -8678,7 +8678,7 @@
         <v>678</v>
       </c>
       <c r="B172" s="1">
-        <v>214600</v>
+        <v>218300</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -8686,7 +8686,7 @@
         <v>679</v>
       </c>
       <c r="B173" s="1">
-        <v>203000</v>
+        <v>206500</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -8694,7 +8694,7 @@
         <v>680</v>
       </c>
       <c r="B174" s="1">
-        <v>203000</v>
+        <v>206500</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8702,7 +8702,7 @@
         <v>681</v>
       </c>
       <c r="B175" s="1">
-        <v>203000</v>
+        <v>206500</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -8710,7 +8710,7 @@
         <v>740</v>
       </c>
       <c r="B176" s="1">
-        <v>127600</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -8718,7 +8718,7 @@
         <v>23</v>
       </c>
       <c r="B177" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -8726,7 +8726,7 @@
         <v>442</v>
       </c>
       <c r="B178" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -8734,7 +8734,7 @@
         <v>564</v>
       </c>
       <c r="B179" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -8742,7 +8742,7 @@
         <v>146</v>
       </c>
       <c r="B180" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -8750,7 +8750,7 @@
         <v>147</v>
       </c>
       <c r="B181" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -8758,7 +8758,7 @@
         <v>755</v>
       </c>
       <c r="B182" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -8766,7 +8766,7 @@
         <v>705</v>
       </c>
       <c r="B183" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -8774,7 +8774,7 @@
         <v>652</v>
       </c>
       <c r="B184" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -8782,7 +8782,7 @@
         <v>805</v>
       </c>
       <c r="B185" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -8790,7 +8790,7 @@
         <v>748</v>
       </c>
       <c r="B186" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -8798,7 +8798,7 @@
         <v>148</v>
       </c>
       <c r="B187" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -8806,7 +8806,7 @@
         <v>706</v>
       </c>
       <c r="B188" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -8814,7 +8814,7 @@
         <v>516</v>
       </c>
       <c r="B189" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -8822,7 +8822,7 @@
         <v>749</v>
       </c>
       <c r="B190" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -8830,7 +8830,7 @@
         <v>149</v>
       </c>
       <c r="B191" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -8838,7 +8838,7 @@
         <v>565</v>
       </c>
       <c r="B192" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -8846,7 +8846,7 @@
         <v>707</v>
       </c>
       <c r="B193" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -8854,7 +8854,7 @@
         <v>150</v>
       </c>
       <c r="B194" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -8862,7 +8862,7 @@
         <v>104</v>
       </c>
       <c r="B195" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -8870,7 +8870,7 @@
         <v>517</v>
       </c>
       <c r="B196" s="1">
-        <v>43500</v>
+        <v>44250</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -8878,7 +8878,7 @@
         <v>151</v>
       </c>
       <c r="B197" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -8886,7 +8886,7 @@
         <v>481</v>
       </c>
       <c r="B198" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -8894,7 +8894,7 @@
         <v>708</v>
       </c>
       <c r="B199" s="1">
-        <v>98600</v>
+        <v>100300</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -8902,7 +8902,7 @@
         <v>64</v>
       </c>
       <c r="B200" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -8910,7 +8910,7 @@
         <v>152</v>
       </c>
       <c r="B201" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -8918,7 +8918,7 @@
         <v>65</v>
       </c>
       <c r="B202" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -8926,7 +8926,7 @@
         <v>545</v>
       </c>
       <c r="B203" s="1">
-        <v>81200</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -8934,7 +8934,7 @@
         <v>547</v>
       </c>
       <c r="B204" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -8942,7 +8942,7 @@
         <v>66</v>
       </c>
       <c r="B205" s="1">
-        <v>75400</v>
+        <v>76700</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -8950,7 +8950,7 @@
         <v>67</v>
       </c>
       <c r="B206" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -8958,7 +8958,7 @@
         <v>68</v>
       </c>
       <c r="B207" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -8966,7 +8966,7 @@
         <v>69</v>
       </c>
       <c r="B208" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -8974,7 +8974,7 @@
         <v>70</v>
       </c>
       <c r="B209" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -8982,7 +8982,7 @@
         <v>71</v>
       </c>
       <c r="B210" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -8990,7 +8990,7 @@
         <v>72</v>
       </c>
       <c r="B211" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -8998,7 +8998,7 @@
         <v>473</v>
       </c>
       <c r="B212" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -9006,7 +9006,7 @@
         <v>160</v>
       </c>
       <c r="B213" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -9014,7 +9014,7 @@
         <v>161</v>
       </c>
       <c r="B214" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -9022,7 +9022,7 @@
         <v>75</v>
       </c>
       <c r="B215" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -9030,7 +9030,7 @@
         <v>159</v>
       </c>
       <c r="B216" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -9038,7 +9038,7 @@
         <v>107</v>
       </c>
       <c r="B217" s="1">
-        <v>145000</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -9046,7 +9046,7 @@
         <v>108</v>
       </c>
       <c r="B218" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -9054,7 +9054,7 @@
         <v>110</v>
       </c>
       <c r="B219" s="1">
-        <v>116000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -9062,7 +9062,7 @@
         <v>105</v>
       </c>
       <c r="B220" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -9070,7 +9070,7 @@
         <v>106</v>
       </c>
       <c r="B221" s="1">
-        <v>87000</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -9078,7 +9078,7 @@
         <v>109</v>
       </c>
       <c r="B222" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -9086,7 +9086,7 @@
         <v>111</v>
       </c>
       <c r="B223" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -9094,7 +9094,7 @@
         <v>153</v>
       </c>
       <c r="B224" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -9102,7 +9102,7 @@
         <v>154</v>
       </c>
       <c r="B225" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -9110,7 +9110,7 @@
         <v>76</v>
       </c>
       <c r="B226" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -9118,7 +9118,7 @@
         <v>77</v>
       </c>
       <c r="B227" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -9126,7 +9126,7 @@
         <v>714</v>
       </c>
       <c r="B228" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -9134,7 +9134,7 @@
         <v>78</v>
       </c>
       <c r="B229" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -9142,7 +9142,7 @@
         <v>443</v>
       </c>
       <c r="B230" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -9150,7 +9150,7 @@
         <v>79</v>
       </c>
       <c r="B231" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -9158,7 +9158,7 @@
         <v>518</v>
       </c>
       <c r="B232" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -9166,7 +9166,7 @@
         <v>80</v>
       </c>
       <c r="B233" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -9174,7 +9174,7 @@
         <v>81</v>
       </c>
       <c r="B234" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -9182,7 +9182,7 @@
         <v>519</v>
       </c>
       <c r="B235" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -9190,7 +9190,7 @@
         <v>113</v>
       </c>
       <c r="B236" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -9198,7 +9198,7 @@
         <v>114</v>
       </c>
       <c r="B237" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -9206,7 +9206,7 @@
         <v>453</v>
       </c>
       <c r="B238" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -9214,7 +9214,7 @@
         <v>710</v>
       </c>
       <c r="B239" s="1">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -9222,7 +9222,7 @@
         <v>750</v>
       </c>
       <c r="B240" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -9230,7 +9230,7 @@
         <v>650</v>
       </c>
       <c r="B241" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -9238,7 +9238,7 @@
         <v>588</v>
       </c>
       <c r="B242" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -9246,7 +9246,7 @@
         <v>555</v>
       </c>
       <c r="B243" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -9254,7 +9254,7 @@
         <v>117</v>
       </c>
       <c r="B244" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -9262,7 +9262,7 @@
         <v>403</v>
       </c>
       <c r="B245" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -9270,7 +9270,7 @@
         <v>546</v>
       </c>
       <c r="B246" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -9278,7 +9278,7 @@
         <v>568</v>
       </c>
       <c r="B247" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -9286,7 +9286,7 @@
         <v>566</v>
       </c>
       <c r="B248" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -9294,7 +9294,7 @@
         <v>556</v>
       </c>
       <c r="B249" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -9302,7 +9302,7 @@
         <v>557</v>
       </c>
       <c r="B250" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -9310,7 +9310,7 @@
         <v>634</v>
       </c>
       <c r="B251" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -9318,7 +9318,7 @@
         <v>711</v>
       </c>
       <c r="B252" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -9326,7 +9326,7 @@
         <v>712</v>
       </c>
       <c r="B253" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -9334,7 +9334,7 @@
         <v>558</v>
       </c>
       <c r="B254" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -9342,7 +9342,7 @@
         <v>635</v>
       </c>
       <c r="B255" s="1">
-        <v>133400</v>
+        <v>135700</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -9350,7 +9350,7 @@
         <v>713</v>
       </c>
       <c r="B256" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -9358,7 +9358,7 @@
         <v>794</v>
       </c>
       <c r="B257" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -9366,7 +9366,7 @@
         <v>445</v>
       </c>
       <c r="B258" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -9374,7 +9374,7 @@
         <v>682</v>
       </c>
       <c r="B259" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -9382,7 +9382,7 @@
         <v>112</v>
       </c>
       <c r="B260" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -9390,7 +9390,7 @@
         <v>155</v>
       </c>
       <c r="B261" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -9398,7 +9398,7 @@
         <v>156</v>
       </c>
       <c r="B262" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
   </sheetData>
@@ -9428,7 +9428,7 @@
         <v>592</v>
       </c>
       <c r="B2" s="1">
-        <v>104400</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9436,7 +9436,7 @@
         <v>806</v>
       </c>
       <c r="B3" s="1">
-        <v>78300</v>
+        <v>79650</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9444,7 +9444,7 @@
         <v>807</v>
       </c>
       <c r="B4" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9452,7 +9452,7 @@
         <v>589</v>
       </c>
       <c r="B5" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9460,7 +9460,7 @@
         <v>808</v>
       </c>
       <c r="B6" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9468,7 +9468,7 @@
         <v>581</v>
       </c>
       <c r="B7" s="1">
-        <v>63800</v>
+        <v>64900</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9476,7 +9476,7 @@
         <v>648</v>
       </c>
       <c r="B8" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9484,7 +9484,7 @@
         <v>520</v>
       </c>
       <c r="B9" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -9492,7 +9492,7 @@
         <v>521</v>
       </c>
       <c r="B10" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9500,7 +9500,7 @@
         <v>522</v>
       </c>
       <c r="B11" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9508,7 +9508,7 @@
         <v>523</v>
       </c>
       <c r="B12" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -9516,7 +9516,7 @@
         <v>809</v>
       </c>
       <c r="B13" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -9524,7 +9524,7 @@
         <v>551</v>
       </c>
       <c r="B14" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -9532,7 +9532,7 @@
         <v>722</v>
       </c>
       <c r="B15" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -9540,7 +9540,7 @@
         <v>524</v>
       </c>
       <c r="B16" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -9548,7 +9548,7 @@
         <v>525</v>
       </c>
       <c r="B17" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -9556,7 +9556,7 @@
         <v>691</v>
       </c>
       <c r="B18" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -9564,7 +9564,7 @@
         <v>526</v>
       </c>
       <c r="B19" s="1">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -9572,7 +9572,7 @@
         <v>810</v>
       </c>
       <c r="B20" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -9580,7 +9580,7 @@
         <v>527</v>
       </c>
       <c r="B21" s="1">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -9588,7 +9588,7 @@
         <v>552</v>
       </c>
       <c r="B22" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -9596,7 +9596,7 @@
         <v>825</v>
       </c>
       <c r="B23" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -9604,7 +9604,7 @@
         <v>528</v>
       </c>
       <c r="B24" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -9612,7 +9612,7 @@
         <v>821</v>
       </c>
       <c r="B25" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -9620,7 +9620,7 @@
         <v>529</v>
       </c>
       <c r="B26" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -9628,7 +9628,7 @@
         <v>684</v>
       </c>
       <c r="B27" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -9636,7 +9636,7 @@
         <v>484</v>
       </c>
       <c r="B28">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -9644,7 +9644,7 @@
         <v>735</v>
       </c>
       <c r="B29">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -9652,7 +9652,7 @@
         <v>530</v>
       </c>
       <c r="B30">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -9660,7 +9660,7 @@
         <v>531</v>
       </c>
       <c r="B31">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -9668,7 +9668,7 @@
         <v>532</v>
       </c>
       <c r="B32">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -9676,7 +9676,7 @@
         <v>533</v>
       </c>
       <c r="B33">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -9684,7 +9684,7 @@
         <v>534</v>
       </c>
       <c r="B34">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -9692,7 +9692,7 @@
         <v>535</v>
       </c>
       <c r="B35">
-        <v>63800</v>
+        <v>64900</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -9700,7 +9700,7 @@
         <v>631</v>
       </c>
       <c r="B36">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -9708,7 +9708,7 @@
         <v>553</v>
       </c>
       <c r="B37">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -9716,7 +9716,7 @@
         <v>726</v>
       </c>
       <c r="B38">
-        <v>49300</v>
+        <v>50150</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -9724,7 +9724,7 @@
         <v>727</v>
       </c>
       <c r="B39">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -9732,7 +9732,7 @@
         <v>536</v>
       </c>
       <c r="B40">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -9740,7 +9740,7 @@
         <v>683</v>
       </c>
       <c r="B41">
-        <v>208800</v>
+        <v>212400</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -9748,7 +9748,7 @@
         <v>636</v>
       </c>
       <c r="B42">
-        <v>214600</v>
+        <v>218300</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -9756,7 +9756,7 @@
         <v>740</v>
       </c>
       <c r="B43">
-        <v>127600</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -9764,7 +9764,7 @@
         <v>537</v>
       </c>
       <c r="B44">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -9772,7 +9772,7 @@
         <v>538</v>
       </c>
       <c r="B45">
-        <v>29000</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -9780,7 +9780,7 @@
         <v>811</v>
       </c>
       <c r="B46">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -9788,7 +9788,7 @@
         <v>812</v>
       </c>
       <c r="B47">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -9796,7 +9796,7 @@
         <v>813</v>
       </c>
       <c r="B48">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -9804,7 +9804,7 @@
         <v>539</v>
       </c>
       <c r="B49">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -9812,7 +9812,7 @@
         <v>814</v>
       </c>
       <c r="B50">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -9820,7 +9820,7 @@
         <v>815</v>
       </c>
       <c r="B51">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -9828,7 +9828,7 @@
         <v>816</v>
       </c>
       <c r="B52">
-        <v>14500</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -9836,7 +9836,7 @@
         <v>588</v>
       </c>
       <c r="B53">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -9844,7 +9844,7 @@
         <v>817</v>
       </c>
       <c r="B54">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -9852,7 +9852,7 @@
         <v>818</v>
       </c>
       <c r="B55">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -9860,7 +9860,7 @@
         <v>819</v>
       </c>
       <c r="B56">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -9868,7 +9868,7 @@
         <v>548</v>
       </c>
       <c r="B57">
-        <v>40600</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -9876,7 +9876,7 @@
         <v>549</v>
       </c>
       <c r="B58">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -9884,7 +9884,7 @@
         <v>403</v>
       </c>
       <c r="B59">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -9892,7 +9892,7 @@
         <v>546</v>
       </c>
       <c r="B60">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -9900,7 +9900,7 @@
         <v>556</v>
       </c>
       <c r="B61">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -9908,7 +9908,7 @@
         <v>557</v>
       </c>
       <c r="B62">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -9916,7 +9916,7 @@
         <v>540</v>
       </c>
       <c r="B63">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -9924,7 +9924,7 @@
         <v>541</v>
       </c>
       <c r="B64">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -9932,7 +9932,7 @@
         <v>637</v>
       </c>
       <c r="B65">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -9940,7 +9940,7 @@
         <v>542</v>
       </c>
       <c r="B66">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
   </sheetData>
@@ -9970,7 +9970,7 @@
         <v>383</v>
       </c>
       <c r="B2" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9978,7 +9978,7 @@
         <v>384</v>
       </c>
       <c r="B3" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9986,7 +9986,7 @@
         <v>385</v>
       </c>
       <c r="B4" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9994,7 +9994,7 @@
         <v>386</v>
       </c>
       <c r="B5" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -10002,7 +10002,7 @@
         <v>640</v>
       </c>
       <c r="B6" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -10010,7 +10010,7 @@
         <v>387</v>
       </c>
       <c r="B7" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -10018,7 +10018,7 @@
         <v>660</v>
       </c>
       <c r="B8" s="1">
-        <v>23200</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -10026,7 +10026,7 @@
         <v>662</v>
       </c>
       <c r="B9" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -10034,7 +10034,7 @@
         <v>661</v>
       </c>
       <c r="B10" s="1">
-        <v>18560</v>
+        <v>18880</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -10042,7 +10042,7 @@
         <v>388</v>
       </c>
       <c r="B11" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -10050,7 +10050,7 @@
         <v>405</v>
       </c>
       <c r="B12" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -10058,7 +10058,7 @@
         <v>659</v>
       </c>
       <c r="B13" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -10066,7 +10066,7 @@
         <v>665</v>
       </c>
       <c r="B14" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -10074,7 +10074,7 @@
         <v>745</v>
       </c>
       <c r="B15" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -10082,7 +10082,7 @@
         <v>389</v>
       </c>
       <c r="B16" s="1">
-        <v>5220</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -10090,7 +10090,7 @@
         <v>589</v>
       </c>
       <c r="B17" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -10098,7 +10098,7 @@
         <v>823</v>
       </c>
       <c r="B18" s="1">
-        <v>49300</v>
+        <v>50150</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -10106,7 +10106,7 @@
         <v>663</v>
       </c>
       <c r="B19" s="1">
-        <v>101500</v>
+        <v>103250</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -10114,7 +10114,7 @@
         <v>655</v>
       </c>
       <c r="B20" s="1">
-        <v>113100</v>
+        <v>115050</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -10122,7 +10122,7 @@
         <v>656</v>
       </c>
       <c r="B21" s="1">
-        <v>127600</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -10130,7 +10130,7 @@
         <v>430</v>
       </c>
       <c r="B22" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -10138,7 +10138,7 @@
         <v>163</v>
       </c>
       <c r="B23" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -10146,7 +10146,7 @@
         <v>647</v>
       </c>
       <c r="B24" s="1">
-        <v>58000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -10154,7 +10154,7 @@
         <v>581</v>
       </c>
       <c r="B25" s="1">
-        <v>63800</v>
+        <v>64900</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -10162,7 +10162,7 @@
         <v>648</v>
       </c>
       <c r="B26" s="1">
-        <v>69600</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -10170,7 +10170,7 @@
         <v>657</v>
       </c>
       <c r="B27" s="1">
-        <v>78300</v>
+        <v>79650</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -10178,7 +10178,7 @@
         <v>658</v>
       </c>
       <c r="B28" s="1">
-        <v>92800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -10186,7 +10186,7 @@
         <v>664</v>
       </c>
       <c r="B29" s="1">
-        <v>98600</v>
+        <v>100300</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -10194,7 +10194,7 @@
         <v>692</v>
       </c>
       <c r="B30" s="1">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -10202,7 +10202,7 @@
         <v>406</v>
       </c>
       <c r="B31" s="1">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -10210,7 +10210,7 @@
         <v>402</v>
       </c>
       <c r="B32" s="1">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -10218,7 +10218,7 @@
         <v>429</v>
       </c>
       <c r="B33" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -10226,7 +10226,7 @@
         <v>551</v>
       </c>
       <c r="B34" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -10234,7 +10234,7 @@
         <v>390</v>
       </c>
       <c r="B35" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -10242,7 +10242,7 @@
         <v>552</v>
       </c>
       <c r="B36" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -10250,7 +10250,7 @@
         <v>825</v>
       </c>
       <c r="B37" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -10258,7 +10258,7 @@
         <v>820</v>
       </c>
       <c r="B38" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -10266,7 +10266,7 @@
         <v>404</v>
       </c>
       <c r="B39" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -10274,7 +10274,7 @@
         <v>259</v>
       </c>
       <c r="B40" s="1">
-        <v>17400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -10282,7 +10282,7 @@
         <v>425</v>
       </c>
       <c r="B41" s="1">
-        <v>2320</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -10290,7 +10290,7 @@
         <v>484</v>
       </c>
       <c r="B42" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -10298,7 +10298,7 @@
         <v>735</v>
       </c>
       <c r="B43" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -10306,7 +10306,7 @@
         <v>391</v>
       </c>
       <c r="B44" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -10314,7 +10314,7 @@
         <v>392</v>
       </c>
       <c r="B45" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -10322,7 +10322,7 @@
         <v>393</v>
       </c>
       <c r="B46" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -10330,7 +10330,7 @@
         <v>638</v>
       </c>
       <c r="B47" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -10338,7 +10338,7 @@
         <v>394</v>
       </c>
       <c r="B48" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -10346,7 +10346,7 @@
         <v>395</v>
       </c>
       <c r="B49" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -10354,7 +10354,7 @@
         <v>396</v>
       </c>
       <c r="B50" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -10362,7 +10362,7 @@
         <v>728</v>
       </c>
       <c r="B51" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -10370,7 +10370,7 @@
         <v>553</v>
       </c>
       <c r="B52" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -10378,7 +10378,7 @@
         <v>718</v>
       </c>
       <c r="B53" s="1">
-        <v>31900</v>
+        <v>32450</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -10386,7 +10386,7 @@
         <v>719</v>
       </c>
       <c r="B54" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -10394,7 +10394,7 @@
         <v>752</v>
       </c>
       <c r="B55" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -10402,7 +10402,7 @@
         <v>723</v>
       </c>
       <c r="B56" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -10410,7 +10410,7 @@
         <v>720</v>
       </c>
       <c r="B57" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -10418,7 +10418,7 @@
         <v>724</v>
       </c>
       <c r="B58" s="1">
-        <v>43500</v>
+        <v>44250</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -10426,7 +10426,7 @@
         <v>721</v>
       </c>
       <c r="B59" s="1">
-        <v>37700</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -10434,7 +10434,7 @@
         <v>725</v>
       </c>
       <c r="B60" s="1">
-        <v>46400</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -10442,7 +10442,7 @@
         <v>726</v>
       </c>
       <c r="B61" s="1">
-        <v>49300</v>
+        <v>50150</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -10450,7 +10450,7 @@
         <v>727</v>
       </c>
       <c r="B62" s="1">
-        <v>52200</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -10458,7 +10458,7 @@
         <v>740</v>
       </c>
       <c r="B63" s="1">
-        <v>127600</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -10466,7 +10466,7 @@
         <v>827</v>
       </c>
       <c r="B64" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -10474,7 +10474,7 @@
         <v>639</v>
       </c>
       <c r="B65" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -10482,7 +10482,7 @@
         <v>543</v>
       </c>
       <c r="B66" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -10490,7 +10490,7 @@
         <v>397</v>
       </c>
       <c r="B67" s="1">
-        <v>10440</v>
+        <v>10620</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -10498,7 +10498,7 @@
         <v>653</v>
       </c>
       <c r="B68" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -10506,7 +10506,7 @@
         <v>398</v>
       </c>
       <c r="B69" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -10514,7 +10514,7 @@
         <v>399</v>
       </c>
       <c r="B70" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -10522,7 +10522,7 @@
         <v>400</v>
       </c>
       <c r="B71" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -10530,7 +10530,7 @@
         <v>582</v>
       </c>
       <c r="B72" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -10538,7 +10538,7 @@
         <v>401</v>
       </c>
       <c r="B73" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -10546,7 +10546,7 @@
         <v>588</v>
       </c>
       <c r="B74" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -10554,7 +10554,7 @@
         <v>554</v>
       </c>
       <c r="B75" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -10562,7 +10562,7 @@
         <v>555</v>
       </c>
       <c r="B76" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -10570,7 +10570,7 @@
         <v>644</v>
       </c>
       <c r="B77" s="1">
-        <v>4060</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -10578,7 +10578,7 @@
         <v>645</v>
       </c>
       <c r="B78" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -10586,7 +10586,7 @@
         <v>403</v>
       </c>
       <c r="B79" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -10594,7 +10594,7 @@
         <v>546</v>
       </c>
       <c r="B80" s="1">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -10602,7 +10602,7 @@
         <v>556</v>
       </c>
       <c r="B81" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -10610,7 +10610,7 @@
         <v>557</v>
       </c>
       <c r="B82" s="1">
-        <v>5800</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -10618,7 +10618,7 @@
         <v>558</v>
       </c>
       <c r="B83" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
   </sheetData>

--- a/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\590 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\600 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D26C5F1-3E1F-4633-AB0B-D7D5C7710607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D2D2BB-09EA-47C6-88B9-1AB68DF7E8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAEWOO TICO" sheetId="1" r:id="rId1"/>
@@ -3034,7 +3034,7 @@
         <v>166</v>
       </c>
       <c r="B2" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3042,7 +3042,7 @@
         <v>421</v>
       </c>
       <c r="B3" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3050,7 +3050,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3058,7 +3058,7 @@
         <v>459</v>
       </c>
       <c r="B5" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3066,7 +3066,7 @@
         <v>460</v>
       </c>
       <c r="B6" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3074,7 +3074,7 @@
         <v>593</v>
       </c>
       <c r="B7" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3082,7 +3082,7 @@
         <v>168</v>
       </c>
       <c r="B8" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3090,7 +3090,7 @@
         <v>461</v>
       </c>
       <c r="B9" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3098,7 +3098,7 @@
         <v>169</v>
       </c>
       <c r="B10" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3106,7 +3106,7 @@
         <v>170</v>
       </c>
       <c r="B11" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3114,7 +3114,7 @@
         <v>171</v>
       </c>
       <c r="B12" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3122,7 +3122,7 @@
         <v>174</v>
       </c>
       <c r="B13" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3130,7 +3130,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3138,7 +3138,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="1">
-        <v>64900</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3146,7 +3146,7 @@
         <v>666</v>
       </c>
       <c r="B16" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3154,7 +3154,7 @@
         <v>175</v>
       </c>
       <c r="B17" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3162,7 +3162,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3170,7 +3170,7 @@
         <v>589</v>
       </c>
       <c r="B19" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3178,7 +3178,7 @@
         <v>462</v>
       </c>
       <c r="B20" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3186,7 +3186,7 @@
         <v>177</v>
       </c>
       <c r="B21" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3194,7 +3194,7 @@
         <v>178</v>
       </c>
       <c r="B22" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3202,7 +3202,7 @@
         <v>179</v>
       </c>
       <c r="B23" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3210,7 +3210,7 @@
         <v>550</v>
       </c>
       <c r="B24" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3218,7 +3218,7 @@
         <v>180</v>
       </c>
       <c r="B25" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3226,7 +3226,7 @@
         <v>181</v>
       </c>
       <c r="B26" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3234,7 +3234,7 @@
         <v>182</v>
       </c>
       <c r="B27" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3242,7 +3242,7 @@
         <v>183</v>
       </c>
       <c r="B28" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3250,7 +3250,7 @@
         <v>184</v>
       </c>
       <c r="B29" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3258,7 +3258,7 @@
         <v>185</v>
       </c>
       <c r="B30" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3266,7 +3266,7 @@
         <v>186</v>
       </c>
       <c r="B31" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3274,7 +3274,7 @@
         <v>187</v>
       </c>
       <c r="B32" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3282,7 +3282,7 @@
         <v>188</v>
       </c>
       <c r="B33" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3290,7 +3290,7 @@
         <v>606</v>
       </c>
       <c r="B34" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3298,7 +3298,7 @@
         <v>569</v>
       </c>
       <c r="B35" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3306,7 +3306,7 @@
         <v>594</v>
       </c>
       <c r="B36" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3314,7 +3314,7 @@
         <v>823</v>
       </c>
       <c r="B37" s="1">
-        <v>50150</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3322,7 +3322,7 @@
         <v>430</v>
       </c>
       <c r="B38" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3330,7 +3330,7 @@
         <v>163</v>
       </c>
       <c r="B39" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3338,7 +3338,7 @@
         <v>647</v>
       </c>
       <c r="B40" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3346,7 +3346,7 @@
         <v>581</v>
       </c>
       <c r="B41" s="1">
-        <v>64900</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3354,7 +3354,7 @@
         <v>648</v>
       </c>
       <c r="B42" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3362,7 +3362,7 @@
         <v>189</v>
       </c>
       <c r="B43" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3370,7 +3370,7 @@
         <v>419</v>
       </c>
       <c r="B44" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3378,7 +3378,7 @@
         <v>408</v>
       </c>
       <c r="B45" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3386,7 +3386,7 @@
         <v>729</v>
       </c>
       <c r="B46" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3394,7 +3394,7 @@
         <v>730</v>
       </c>
       <c r="B47" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3402,7 +3402,7 @@
         <v>190</v>
       </c>
       <c r="B48" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3410,7 +3410,7 @@
         <v>191</v>
       </c>
       <c r="B49" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3418,7 +3418,7 @@
         <v>192</v>
       </c>
       <c r="B50" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3426,7 +3426,7 @@
         <v>193</v>
       </c>
       <c r="B51" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3434,7 +3434,7 @@
         <v>692</v>
       </c>
       <c r="B52" s="1">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3442,7 +3442,7 @@
         <v>194</v>
       </c>
       <c r="B53" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3450,7 +3450,7 @@
         <v>406</v>
       </c>
       <c r="B54" s="1">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3458,7 +3458,7 @@
         <v>402</v>
       </c>
       <c r="B55" s="1">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3466,7 +3466,7 @@
         <v>429</v>
       </c>
       <c r="B56" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3474,7 +3474,7 @@
         <v>195</v>
       </c>
       <c r="B57" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3482,7 +3482,7 @@
         <v>196</v>
       </c>
       <c r="B58" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3490,7 +3490,7 @@
         <v>197</v>
       </c>
       <c r="B59" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3498,7 +3498,7 @@
         <v>595</v>
       </c>
       <c r="B60" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3506,7 +3506,7 @@
         <v>596</v>
       </c>
       <c r="B61" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3514,7 +3514,7 @@
         <v>198</v>
       </c>
       <c r="B62" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3522,7 +3522,7 @@
         <v>199</v>
       </c>
       <c r="B63" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3530,7 +3530,7 @@
         <v>200</v>
       </c>
       <c r="B64" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3538,7 +3538,7 @@
         <v>201</v>
       </c>
       <c r="B65" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3546,7 +3546,7 @@
         <v>202</v>
       </c>
       <c r="B66" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3554,7 +3554,7 @@
         <v>203</v>
       </c>
       <c r="B67" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3562,7 +3562,7 @@
         <v>204</v>
       </c>
       <c r="B68" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3570,7 +3570,7 @@
         <v>205</v>
       </c>
       <c r="B69" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3578,7 +3578,7 @@
         <v>206</v>
       </c>
       <c r="B70" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3586,7 +3586,7 @@
         <v>208</v>
       </c>
       <c r="B71" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3594,7 +3594,7 @@
         <v>212</v>
       </c>
       <c r="B72" s="1">
-        <v>1180</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3602,7 +3602,7 @@
         <v>209</v>
       </c>
       <c r="B73" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3610,7 +3610,7 @@
         <v>210</v>
       </c>
       <c r="B74" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3618,7 +3618,7 @@
         <v>211</v>
       </c>
       <c r="B75" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3626,7 +3626,7 @@
         <v>476</v>
       </c>
       <c r="B76" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3634,7 +3634,7 @@
         <v>207</v>
       </c>
       <c r="B77" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3642,7 +3642,7 @@
         <v>213</v>
       </c>
       <c r="B78" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3650,7 +3650,7 @@
         <v>214</v>
       </c>
       <c r="B79" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3658,7 +3658,7 @@
         <v>215</v>
       </c>
       <c r="B80" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3666,7 +3666,7 @@
         <v>216</v>
       </c>
       <c r="B81" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3674,7 +3674,7 @@
         <v>217</v>
       </c>
       <c r="B82" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3682,7 +3682,7 @@
         <v>218</v>
       </c>
       <c r="B83" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3690,7 +3690,7 @@
         <v>219</v>
       </c>
       <c r="B84" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3698,7 +3698,7 @@
         <v>220</v>
       </c>
       <c r="B85" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3706,7 +3706,7 @@
         <v>607</v>
       </c>
       <c r="B86" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3714,7 +3714,7 @@
         <v>221</v>
       </c>
       <c r="B87" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3722,7 +3722,7 @@
         <v>608</v>
       </c>
       <c r="B88" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3730,7 +3730,7 @@
         <v>417</v>
       </c>
       <c r="B89" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3738,7 +3738,7 @@
         <v>418</v>
       </c>
       <c r="B90" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3746,7 +3746,7 @@
         <v>222</v>
       </c>
       <c r="B91" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3754,7 +3754,7 @@
         <v>223</v>
       </c>
       <c r="B92" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3762,7 +3762,7 @@
         <v>224</v>
       </c>
       <c r="B93" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3770,7 +3770,7 @@
         <v>225</v>
       </c>
       <c r="B94" s="1">
-        <v>206500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3778,7 +3778,7 @@
         <v>226</v>
       </c>
       <c r="B95" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3786,7 +3786,7 @@
         <v>824</v>
       </c>
       <c r="B96" s="1">
-        <v>177000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3794,7 +3794,7 @@
         <v>227</v>
       </c>
       <c r="B97" s="1">
-        <v>165200</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3802,7 +3802,7 @@
         <v>228</v>
       </c>
       <c r="B98" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3810,7 +3810,7 @@
         <v>551</v>
       </c>
       <c r="B99" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3818,7 +3818,7 @@
         <v>667</v>
       </c>
       <c r="B100" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3826,7 +3826,7 @@
         <v>409</v>
       </c>
       <c r="B101" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3834,7 +3834,7 @@
         <v>229</v>
       </c>
       <c r="B102" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3842,7 +3842,7 @@
         <v>230</v>
       </c>
       <c r="B103" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3850,7 +3850,7 @@
         <v>231</v>
       </c>
       <c r="B104" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3858,7 +3858,7 @@
         <v>424</v>
       </c>
       <c r="B105" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3866,7 +3866,7 @@
         <v>232</v>
       </c>
       <c r="B106" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3874,7 +3874,7 @@
         <v>570</v>
       </c>
       <c r="B107" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3882,7 +3882,7 @@
         <v>483</v>
       </c>
       <c r="B108" s="1">
-        <v>147500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3890,7 +3890,7 @@
         <v>587</v>
       </c>
       <c r="B109" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3898,7 +3898,7 @@
         <v>233</v>
       </c>
       <c r="B110" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3906,7 +3906,7 @@
         <v>234</v>
       </c>
       <c r="B111" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3914,7 +3914,7 @@
         <v>731</v>
       </c>
       <c r="B112" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3922,7 +3922,7 @@
         <v>717</v>
       </c>
       <c r="B113" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3930,7 +3930,7 @@
         <v>571</v>
       </c>
       <c r="B114" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3938,7 +3938,7 @@
         <v>590</v>
       </c>
       <c r="B115" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3946,7 +3946,7 @@
         <v>235</v>
       </c>
       <c r="B116" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3954,7 +3954,7 @@
         <v>732</v>
       </c>
       <c r="B117" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3962,7 +3962,7 @@
         <v>236</v>
       </c>
       <c r="B118" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3970,7 +3970,7 @@
         <v>733</v>
       </c>
       <c r="B119" s="1">
-        <v>1180</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3978,7 +3978,7 @@
         <v>237</v>
       </c>
       <c r="B120" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3986,7 +3986,7 @@
         <v>410</v>
       </c>
       <c r="B121" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3994,7 +3994,7 @@
         <v>238</v>
       </c>
       <c r="B122" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4002,7 +4002,7 @@
         <v>239</v>
       </c>
       <c r="B123" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4010,7 +4010,7 @@
         <v>240</v>
       </c>
       <c r="B124" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4018,7 +4018,7 @@
         <v>241</v>
       </c>
       <c r="B125" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4026,7 +4026,7 @@
         <v>242</v>
       </c>
       <c r="B126" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4034,7 +4034,7 @@
         <v>243</v>
       </c>
       <c r="B127" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4042,7 +4042,7 @@
         <v>668</v>
       </c>
       <c r="B128" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4050,7 +4050,7 @@
         <v>669</v>
       </c>
       <c r="B129" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4058,7 +4058,7 @@
         <v>431</v>
       </c>
       <c r="B130" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4066,7 +4066,7 @@
         <v>244</v>
       </c>
       <c r="B131" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4074,7 +4074,7 @@
         <v>597</v>
       </c>
       <c r="B132" s="1">
-        <v>253700</v>
+        <v>258000</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4082,7 +4082,7 @@
         <v>245</v>
       </c>
       <c r="B133" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4090,7 +4090,7 @@
         <v>456</v>
       </c>
       <c r="B134" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4098,7 +4098,7 @@
         <v>457</v>
       </c>
       <c r="B135" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4106,7 +4106,7 @@
         <v>458</v>
       </c>
       <c r="B136" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4114,7 +4114,7 @@
         <v>246</v>
       </c>
       <c r="B137" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4122,7 +4122,7 @@
         <v>247</v>
       </c>
       <c r="B138" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4130,7 +4130,7 @@
         <v>248</v>
       </c>
       <c r="B139" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4138,7 +4138,7 @@
         <v>250</v>
       </c>
       <c r="B140" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4146,7 +4146,7 @@
         <v>420</v>
       </c>
       <c r="B141" s="1">
-        <v>147500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4154,7 +4154,7 @@
         <v>14</v>
       </c>
       <c r="B142" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4162,7 +4162,7 @@
         <v>602</v>
       </c>
       <c r="B143" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4170,7 +4170,7 @@
         <v>249</v>
       </c>
       <c r="B144" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4178,7 +4178,7 @@
         <v>552</v>
       </c>
       <c r="B145" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4186,7 +4186,7 @@
         <v>251</v>
       </c>
       <c r="B146" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4194,7 +4194,7 @@
         <v>825</v>
       </c>
       <c r="B147" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4202,7 +4202,7 @@
         <v>252</v>
       </c>
       <c r="B148" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4210,7 +4210,7 @@
         <v>253</v>
       </c>
       <c r="B149" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4218,7 +4218,7 @@
         <v>598</v>
       </c>
       <c r="B150" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4226,7 +4226,7 @@
         <v>254</v>
       </c>
       <c r="B151" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4234,7 +4234,7 @@
         <v>255</v>
       </c>
       <c r="B152" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4242,7 +4242,7 @@
         <v>256</v>
       </c>
       <c r="B153" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4250,7 +4250,7 @@
         <v>257</v>
       </c>
       <c r="B154" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4258,7 +4258,7 @@
         <v>258</v>
       </c>
       <c r="B155" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4266,7 +4266,7 @@
         <v>261</v>
       </c>
       <c r="B156" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4274,7 +4274,7 @@
         <v>262</v>
       </c>
       <c r="B157" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4282,7 +4282,7 @@
         <v>263</v>
       </c>
       <c r="B158" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4290,7 +4290,7 @@
         <v>404</v>
       </c>
       <c r="B159" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4298,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="B160" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4306,7 +4306,7 @@
         <v>463</v>
       </c>
       <c r="B161" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4314,7 +4314,7 @@
         <v>260</v>
       </c>
       <c r="B162" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4322,7 +4322,7 @@
         <v>264</v>
       </c>
       <c r="B163" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4330,7 +4330,7 @@
         <v>689</v>
       </c>
       <c r="B164" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4338,7 +4338,7 @@
         <v>641</v>
       </c>
       <c r="B165" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4346,7 +4346,7 @@
         <v>642</v>
       </c>
       <c r="B166" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4354,7 +4354,7 @@
         <v>603</v>
       </c>
       <c r="B167" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4362,7 +4362,7 @@
         <v>604</v>
       </c>
       <c r="B168" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4370,7 +4370,7 @@
         <v>484</v>
       </c>
       <c r="B169" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4378,7 +4378,7 @@
         <v>265</v>
       </c>
       <c r="B170" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4386,7 +4386,7 @@
         <v>609</v>
       </c>
       <c r="B171" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4394,7 +4394,7 @@
         <v>734</v>
       </c>
       <c r="B172" s="1">
-        <v>2360</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4402,7 +4402,7 @@
         <v>735</v>
       </c>
       <c r="B173" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4410,7 +4410,7 @@
         <v>266</v>
       </c>
       <c r="B174" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4418,7 +4418,7 @@
         <v>267</v>
       </c>
       <c r="B175" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4426,7 +4426,7 @@
         <v>268</v>
       </c>
       <c r="B176" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4434,7 +4434,7 @@
         <v>269</v>
       </c>
       <c r="B177" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4442,7 +4442,7 @@
         <v>270</v>
       </c>
       <c r="B178" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4450,7 +4450,7 @@
         <v>271</v>
       </c>
       <c r="B179" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4458,7 +4458,7 @@
         <v>272</v>
       </c>
       <c r="B180" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4466,7 +4466,7 @@
         <v>273</v>
       </c>
       <c r="B181" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4474,7 +4474,7 @@
         <v>422</v>
       </c>
       <c r="B182" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4482,7 +4482,7 @@
         <v>423</v>
       </c>
       <c r="B183" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4490,7 +4490,7 @@
         <v>610</v>
       </c>
       <c r="B184" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4498,7 +4498,7 @@
         <v>611</v>
       </c>
       <c r="B185" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4506,7 +4506,7 @@
         <v>612</v>
       </c>
       <c r="B186" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4514,7 +4514,7 @@
         <v>613</v>
       </c>
       <c r="B187" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4522,7 +4522,7 @@
         <v>614</v>
       </c>
       <c r="B188" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4530,7 +4530,7 @@
         <v>615</v>
       </c>
       <c r="B189" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4538,7 +4538,7 @@
         <v>274</v>
       </c>
       <c r="B190" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4546,7 +4546,7 @@
         <v>276</v>
       </c>
       <c r="B191" s="1">
-        <v>1180</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4554,7 +4554,7 @@
         <v>275</v>
       </c>
       <c r="B192" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4562,7 +4562,7 @@
         <v>616</v>
       </c>
       <c r="B193" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4570,7 +4570,7 @@
         <v>277</v>
       </c>
       <c r="B194" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4578,7 +4578,7 @@
         <v>464</v>
       </c>
       <c r="B195" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4586,7 +4586,7 @@
         <v>278</v>
       </c>
       <c r="B196" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4594,7 +4594,7 @@
         <v>736</v>
       </c>
       <c r="B197" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4602,7 +4602,7 @@
         <v>391</v>
       </c>
       <c r="B198" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4610,7 +4610,7 @@
         <v>396</v>
       </c>
       <c r="B199" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4618,7 +4618,7 @@
         <v>466</v>
       </c>
       <c r="B200" s="1">
-        <v>188800</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4626,7 +4626,7 @@
         <v>279</v>
       </c>
       <c r="B201" s="1">
-        <v>306800</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4634,7 +4634,7 @@
         <v>649</v>
       </c>
       <c r="B202" s="1">
-        <v>312700</v>
+        <v>318000</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4642,7 +4642,7 @@
         <v>280</v>
       </c>
       <c r="B203" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4650,7 +4650,7 @@
         <v>696</v>
       </c>
       <c r="B204" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4658,7 +4658,7 @@
         <v>737</v>
       </c>
       <c r="B205" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4666,7 +4666,7 @@
         <v>411</v>
       </c>
       <c r="B206" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4674,7 +4674,7 @@
         <v>281</v>
       </c>
       <c r="B207" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4682,7 +4682,7 @@
         <v>412</v>
       </c>
       <c r="B208" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4690,7 +4690,7 @@
         <v>282</v>
       </c>
       <c r="B209" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4698,7 +4698,7 @@
         <v>283</v>
       </c>
       <c r="B210" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4706,7 +4706,7 @@
         <v>284</v>
       </c>
       <c r="B211" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4714,7 +4714,7 @@
         <v>285</v>
       </c>
       <c r="B212" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4722,7 +4722,7 @@
         <v>286</v>
       </c>
       <c r="B213" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4730,7 +4730,7 @@
         <v>287</v>
       </c>
       <c r="B214" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4738,7 +4738,7 @@
         <v>288</v>
       </c>
       <c r="B215" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4746,7 +4746,7 @@
         <v>289</v>
       </c>
       <c r="B216" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4754,7 +4754,7 @@
         <v>553</v>
       </c>
       <c r="B217" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4762,7 +4762,7 @@
         <v>290</v>
       </c>
       <c r="B218" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4770,7 +4770,7 @@
         <v>738</v>
       </c>
       <c r="B219" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4778,7 +4778,7 @@
         <v>739</v>
       </c>
       <c r="B220" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4786,7 +4786,7 @@
         <v>291</v>
       </c>
       <c r="B221" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4794,7 +4794,7 @@
         <v>292</v>
       </c>
       <c r="B222" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4802,7 +4802,7 @@
         <v>293</v>
       </c>
       <c r="B223" s="1">
-        <v>165200</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4810,7 +4810,7 @@
         <v>294</v>
       </c>
       <c r="B224" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4818,7 +4818,7 @@
         <v>572</v>
       </c>
       <c r="B225" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4826,7 +4826,7 @@
         <v>670</v>
       </c>
       <c r="B226" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4834,7 +4834,7 @@
         <v>295</v>
       </c>
       <c r="B227" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4842,7 +4842,7 @@
         <v>671</v>
       </c>
       <c r="B228" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4850,7 +4850,7 @@
         <v>296</v>
       </c>
       <c r="B229" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4858,7 +4858,7 @@
         <v>718</v>
       </c>
       <c r="B230" s="1">
-        <v>32450</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4866,7 +4866,7 @@
         <v>719</v>
       </c>
       <c r="B231" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4874,7 +4874,7 @@
         <v>720</v>
       </c>
       <c r="B232" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4882,7 +4882,7 @@
         <v>721</v>
       </c>
       <c r="B233" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4890,7 +4890,7 @@
         <v>617</v>
       </c>
       <c r="B234" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4898,7 +4898,7 @@
         <v>297</v>
       </c>
       <c r="B235" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4906,7 +4906,7 @@
         <v>573</v>
       </c>
       <c r="B236" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4914,7 +4914,7 @@
         <v>298</v>
       </c>
       <c r="B237" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4922,7 +4922,7 @@
         <v>299</v>
       </c>
       <c r="B238" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4930,7 +4930,7 @@
         <v>300</v>
       </c>
       <c r="B239" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4938,7 +4938,7 @@
         <v>301</v>
       </c>
       <c r="B240" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4946,7 +4946,7 @@
         <v>302</v>
       </c>
       <c r="B241" s="1">
-        <v>177000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4954,7 +4954,7 @@
         <v>672</v>
       </c>
       <c r="B242" s="1">
-        <v>177000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4962,7 +4962,7 @@
         <v>303</v>
       </c>
       <c r="B243" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4970,7 +4970,7 @@
         <v>740</v>
       </c>
       <c r="B244" s="1">
-        <v>129800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4978,7 +4978,7 @@
         <v>304</v>
       </c>
       <c r="B245" s="1">
-        <v>64900</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4986,7 +4986,7 @@
         <v>305</v>
       </c>
       <c r="B246" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4994,7 +4994,7 @@
         <v>306</v>
       </c>
       <c r="B247" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5002,7 +5002,7 @@
         <v>618</v>
       </c>
       <c r="B248" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5010,7 +5010,7 @@
         <v>307</v>
       </c>
       <c r="B249" s="1">
-        <v>100300</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5018,7 +5018,7 @@
         <v>308</v>
       </c>
       <c r="B250" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5026,7 +5026,7 @@
         <v>309</v>
       </c>
       <c r="B251" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5034,7 +5034,7 @@
         <v>310</v>
       </c>
       <c r="B252" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5042,7 +5042,7 @@
         <v>690</v>
       </c>
       <c r="B253" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5050,7 +5050,7 @@
         <v>311</v>
       </c>
       <c r="B254" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5058,7 +5058,7 @@
         <v>312</v>
       </c>
       <c r="B255" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5066,7 +5066,7 @@
         <v>313</v>
       </c>
       <c r="B256" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5074,7 +5074,7 @@
         <v>467</v>
       </c>
       <c r="B257" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5082,7 +5082,7 @@
         <v>741</v>
       </c>
       <c r="B258" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5090,7 +5090,7 @@
         <v>742</v>
       </c>
       <c r="B259" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5098,7 +5098,7 @@
         <v>468</v>
       </c>
       <c r="B260" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5106,7 +5106,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5114,7 +5114,7 @@
         <v>315</v>
       </c>
       <c r="B262" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5122,7 +5122,7 @@
         <v>316</v>
       </c>
       <c r="B263" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5130,7 +5130,7 @@
         <v>414</v>
       </c>
       <c r="B264" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5138,7 +5138,7 @@
         <v>317</v>
       </c>
       <c r="B265" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5146,7 +5146,7 @@
         <v>318</v>
       </c>
       <c r="B266" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5154,7 +5154,7 @@
         <v>605</v>
       </c>
       <c r="B267" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5162,7 +5162,7 @@
         <v>319</v>
       </c>
       <c r="B268" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5170,7 +5170,7 @@
         <v>320</v>
       </c>
       <c r="B269" s="1">
-        <v>177000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5178,7 +5178,7 @@
         <v>321</v>
       </c>
       <c r="B270" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5186,7 +5186,7 @@
         <v>322</v>
       </c>
       <c r="B271" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5194,7 +5194,7 @@
         <v>323</v>
       </c>
       <c r="B272" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5202,7 +5202,7 @@
         <v>324</v>
       </c>
       <c r="B273" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5210,7 +5210,7 @@
         <v>325</v>
       </c>
       <c r="B274" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5218,7 +5218,7 @@
         <v>326</v>
       </c>
       <c r="B275" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5226,7 +5226,7 @@
         <v>327</v>
       </c>
       <c r="B276" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5234,7 +5234,7 @@
         <v>328</v>
       </c>
       <c r="B277" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5242,7 +5242,7 @@
         <v>329</v>
       </c>
       <c r="B278" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5250,7 +5250,7 @@
         <v>330</v>
       </c>
       <c r="B279" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5258,7 +5258,7 @@
         <v>331</v>
       </c>
       <c r="B280" s="1">
-        <v>76700</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5266,7 +5266,7 @@
         <v>332</v>
       </c>
       <c r="B281" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5274,7 +5274,7 @@
         <v>333</v>
       </c>
       <c r="B282" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5282,7 +5282,7 @@
         <v>334</v>
       </c>
       <c r="B283" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5290,7 +5290,7 @@
         <v>574</v>
       </c>
       <c r="B284" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5298,7 +5298,7 @@
         <v>599</v>
       </c>
       <c r="B285" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5306,7 +5306,7 @@
         <v>600</v>
       </c>
       <c r="B286" s="1">
-        <v>56050</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5314,7 +5314,7 @@
         <v>743</v>
       </c>
       <c r="B287" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5322,7 +5322,7 @@
         <v>619</v>
       </c>
       <c r="B288" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5330,7 +5330,7 @@
         <v>335</v>
       </c>
       <c r="B289" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5338,7 +5338,7 @@
         <v>620</v>
       </c>
       <c r="B290" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5346,7 +5346,7 @@
         <v>336</v>
       </c>
       <c r="B291" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5354,7 +5354,7 @@
         <v>337</v>
       </c>
       <c r="B292" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5362,7 +5362,7 @@
         <v>338</v>
       </c>
       <c r="B293" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5370,7 +5370,7 @@
         <v>339</v>
       </c>
       <c r="B294" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5378,7 +5378,7 @@
         <v>340</v>
       </c>
       <c r="B295" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5386,7 +5386,7 @@
         <v>341</v>
       </c>
       <c r="B296" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5394,7 +5394,7 @@
         <v>342</v>
       </c>
       <c r="B297" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5402,7 +5402,7 @@
         <v>343</v>
       </c>
       <c r="B298" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5410,7 +5410,7 @@
         <v>415</v>
       </c>
       <c r="B299" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5418,7 +5418,7 @@
         <v>416</v>
       </c>
       <c r="B300" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5426,7 +5426,7 @@
         <v>601</v>
       </c>
       <c r="B301" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5434,7 +5434,7 @@
         <v>344</v>
       </c>
       <c r="B302" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5442,7 +5442,7 @@
         <v>345</v>
       </c>
       <c r="B303" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5450,7 +5450,7 @@
         <v>346</v>
       </c>
       <c r="B304" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5458,7 +5458,7 @@
         <v>347</v>
       </c>
       <c r="B305" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5466,7 +5466,7 @@
         <v>348</v>
       </c>
       <c r="B306" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5474,7 +5474,7 @@
         <v>349</v>
       </c>
       <c r="B307" s="1">
-        <v>2360</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5482,7 +5482,7 @@
         <v>744</v>
       </c>
       <c r="B308" s="1">
-        <v>1180</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5490,7 +5490,7 @@
         <v>673</v>
       </c>
       <c r="B309" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5498,7 +5498,7 @@
         <v>350</v>
       </c>
       <c r="B310" s="1">
-        <v>44250</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5506,7 +5506,7 @@
         <v>351</v>
       </c>
       <c r="B311" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5514,7 +5514,7 @@
         <v>352</v>
       </c>
       <c r="B312" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5522,7 +5522,7 @@
         <v>575</v>
       </c>
       <c r="B313" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5530,7 +5530,7 @@
         <v>353</v>
       </c>
       <c r="B314" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5538,7 +5538,7 @@
         <v>354</v>
       </c>
       <c r="B315" s="1">
-        <v>147500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5546,7 +5546,7 @@
         <v>407</v>
       </c>
       <c r="B316" s="1">
-        <v>324500</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5554,7 +5554,7 @@
         <v>355</v>
       </c>
       <c r="B317" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5562,7 +5562,7 @@
         <v>356</v>
       </c>
       <c r="B318" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5570,7 +5570,7 @@
         <v>576</v>
       </c>
       <c r="B319" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5578,7 +5578,7 @@
         <v>357</v>
       </c>
       <c r="B320" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5586,7 +5586,7 @@
         <v>358</v>
       </c>
       <c r="B321" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5594,7 +5594,7 @@
         <v>651</v>
       </c>
       <c r="B322" s="1">
-        <v>2360</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5602,7 +5602,7 @@
         <v>577</v>
       </c>
       <c r="B323" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5610,7 +5610,7 @@
         <v>588</v>
       </c>
       <c r="B324" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5618,7 +5618,7 @@
         <v>359</v>
       </c>
       <c r="B325" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5626,7 +5626,7 @@
         <v>360</v>
       </c>
       <c r="B326" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5634,7 +5634,7 @@
         <v>361</v>
       </c>
       <c r="B327" s="1">
-        <v>2360</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5642,7 +5642,7 @@
         <v>362</v>
       </c>
       <c r="B328" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5650,7 +5650,7 @@
         <v>363</v>
       </c>
       <c r="B329" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5658,7 +5658,7 @@
         <v>364</v>
       </c>
       <c r="B330" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5666,7 +5666,7 @@
         <v>365</v>
       </c>
       <c r="B331" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5674,7 +5674,7 @@
         <v>403</v>
       </c>
       <c r="B332" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5682,7 +5682,7 @@
         <v>546</v>
       </c>
       <c r="B333" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5690,7 +5690,7 @@
         <v>822</v>
       </c>
       <c r="B334" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5698,7 +5698,7 @@
         <v>366</v>
       </c>
       <c r="B335" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5706,7 +5706,7 @@
         <v>556</v>
       </c>
       <c r="B336" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5714,7 +5714,7 @@
         <v>557</v>
       </c>
       <c r="B337" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5722,7 +5722,7 @@
         <v>367</v>
       </c>
       <c r="B338" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5730,7 +5730,7 @@
         <v>368</v>
       </c>
       <c r="B339" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5738,7 +5738,7 @@
         <v>369</v>
       </c>
       <c r="B340" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5746,7 +5746,7 @@
         <v>370</v>
       </c>
       <c r="B341" s="1">
-        <v>1180</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5754,7 +5754,7 @@
         <v>371</v>
       </c>
       <c r="B342" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5762,7 +5762,7 @@
         <v>372</v>
       </c>
       <c r="B343" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5770,7 +5770,7 @@
         <v>373</v>
       </c>
       <c r="B344" s="1">
-        <v>2360</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5778,7 +5778,7 @@
         <v>413</v>
       </c>
       <c r="B345" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5786,7 +5786,7 @@
         <v>465</v>
       </c>
       <c r="B346" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5794,7 +5794,7 @@
         <v>621</v>
       </c>
       <c r="B347" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5802,7 +5802,7 @@
         <v>374</v>
       </c>
       <c r="B348" s="1">
-        <v>1180</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5810,7 +5810,7 @@
         <v>485</v>
       </c>
       <c r="B349" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5818,7 +5818,7 @@
         <v>469</v>
       </c>
       <c r="B350" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5826,7 +5826,7 @@
         <v>375</v>
       </c>
       <c r="B351" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5834,7 +5834,7 @@
         <v>674</v>
       </c>
       <c r="B352" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5842,7 +5842,7 @@
         <v>675</v>
       </c>
       <c r="B353" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5850,7 +5850,7 @@
         <v>376</v>
       </c>
       <c r="B354" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5858,7 +5858,7 @@
         <v>377</v>
       </c>
       <c r="B355" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5866,7 +5866,7 @@
         <v>378</v>
       </c>
       <c r="B356" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5874,7 +5874,7 @@
         <v>622</v>
       </c>
       <c r="B357" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5882,7 +5882,7 @@
         <v>379</v>
       </c>
       <c r="B358" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5890,7 +5890,7 @@
         <v>470</v>
       </c>
       <c r="B359" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5898,7 +5898,7 @@
         <v>471</v>
       </c>
       <c r="B360" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5906,7 +5906,7 @@
         <v>676</v>
       </c>
       <c r="B361" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5914,7 +5914,7 @@
         <v>380</v>
       </c>
       <c r="B362" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5922,7 +5922,7 @@
         <v>381</v>
       </c>
       <c r="B363" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5930,7 +5930,7 @@
         <v>454</v>
       </c>
       <c r="B364" s="1">
-        <v>2360</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5938,7 +5938,7 @@
         <v>382</v>
       </c>
       <c r="B365" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
   </sheetData>
@@ -5968,7 +5968,7 @@
         <v>486</v>
       </c>
       <c r="B2" s="1">
-        <v>82600</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5976,7 +5976,7 @@
         <v>123</v>
       </c>
       <c r="B3" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5984,7 +5984,7 @@
         <v>757</v>
       </c>
       <c r="B4" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5992,7 +5992,7 @@
         <v>578</v>
       </c>
       <c r="B5" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6000,7 +6000,7 @@
         <v>164</v>
       </c>
       <c r="B6" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6008,7 +6008,7 @@
         <v>579</v>
       </c>
       <c r="B7" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6016,7 +6016,7 @@
         <v>589</v>
       </c>
       <c r="B8" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6024,7 +6024,7 @@
         <v>758</v>
       </c>
       <c r="B9" s="1">
-        <v>76700</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6032,7 +6032,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6040,7 +6040,7 @@
         <v>759</v>
       </c>
       <c r="B11" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6048,7 +6048,7 @@
         <v>124</v>
       </c>
       <c r="B12" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6056,7 +6056,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6064,7 +6064,7 @@
         <v>823</v>
       </c>
       <c r="B14" s="1">
-        <v>50150</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6072,7 +6072,7 @@
         <v>430</v>
       </c>
       <c r="B15" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6080,7 +6080,7 @@
         <v>163</v>
       </c>
       <c r="B16" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6088,7 +6088,7 @@
         <v>647</v>
       </c>
       <c r="B17" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6096,7 +6096,7 @@
         <v>581</v>
       </c>
       <c r="B18" s="1">
-        <v>64900</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6104,7 +6104,7 @@
         <v>648</v>
       </c>
       <c r="B19" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6112,7 +6112,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6120,7 +6120,7 @@
         <v>125</v>
       </c>
       <c r="B21" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6128,7 +6128,7 @@
         <v>478</v>
       </c>
       <c r="B22" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6136,7 +6136,7 @@
         <v>36</v>
       </c>
       <c r="B23" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6144,7 +6144,7 @@
         <v>487</v>
       </c>
       <c r="B24" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6152,7 +6152,7 @@
         <v>488</v>
       </c>
       <c r="B25" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6160,7 +6160,7 @@
         <v>692</v>
       </c>
       <c r="B26" s="1">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6168,7 +6168,7 @@
         <v>406</v>
       </c>
       <c r="B27" s="1">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6176,7 +6176,7 @@
         <v>402</v>
       </c>
       <c r="B28" s="1">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6184,7 +6184,7 @@
         <v>439</v>
       </c>
       <c r="B29" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6192,7 +6192,7 @@
         <v>760</v>
       </c>
       <c r="B30" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6200,7 +6200,7 @@
         <v>489</v>
       </c>
       <c r="B31" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6208,7 +6208,7 @@
         <v>490</v>
       </c>
       <c r="B32" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6216,7 +6216,7 @@
         <v>761</v>
       </c>
       <c r="B33" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6224,7 +6224,7 @@
         <v>12</v>
       </c>
       <c r="B34" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6232,7 +6232,7 @@
         <v>762</v>
       </c>
       <c r="B35" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="1">
-        <v>1475</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6248,7 +6248,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6256,7 +6256,7 @@
         <v>434</v>
       </c>
       <c r="B38" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6264,7 +6264,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6272,7 +6272,7 @@
         <v>491</v>
       </c>
       <c r="B40" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6280,7 +6280,7 @@
         <v>479</v>
       </c>
       <c r="B41" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6288,7 +6288,7 @@
         <v>763</v>
       </c>
       <c r="B42" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6296,7 +6296,7 @@
         <v>438</v>
       </c>
       <c r="B43" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6304,7 +6304,7 @@
         <v>440</v>
       </c>
       <c r="B44" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6312,7 +6312,7 @@
         <v>492</v>
       </c>
       <c r="B45" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6320,7 +6320,7 @@
         <v>493</v>
       </c>
       <c r="B46" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6328,7 +6328,7 @@
         <v>494</v>
       </c>
       <c r="B47" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6336,7 +6336,7 @@
         <v>764</v>
       </c>
       <c r="B48" s="1">
-        <v>206500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -6344,7 +6344,7 @@
         <v>551</v>
       </c>
       <c r="B49" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -6352,7 +6352,7 @@
         <v>765</v>
       </c>
       <c r="B50" s="1">
-        <v>76700</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -6360,7 +6360,7 @@
         <v>751</v>
       </c>
       <c r="B51" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -6368,7 +6368,7 @@
         <v>722</v>
       </c>
       <c r="B52" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -6376,7 +6376,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -6384,7 +6384,7 @@
         <v>766</v>
       </c>
       <c r="B54" s="1">
-        <v>82600</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -6392,7 +6392,7 @@
         <v>495</v>
       </c>
       <c r="B55" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -6400,7 +6400,7 @@
         <v>436</v>
       </c>
       <c r="B56" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -6408,7 +6408,7 @@
         <v>126</v>
       </c>
       <c r="B57" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -6416,7 +6416,7 @@
         <v>496</v>
       </c>
       <c r="B58" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -6424,7 +6424,7 @@
         <v>767</v>
       </c>
       <c r="B59" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -6432,7 +6432,7 @@
         <v>30</v>
       </c>
       <c r="B60" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -6440,7 +6440,7 @@
         <v>427</v>
       </c>
       <c r="B61" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -6448,7 +6448,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -6456,7 +6456,7 @@
         <v>768</v>
       </c>
       <c r="B63" s="1">
-        <v>147500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -6464,7 +6464,7 @@
         <v>769</v>
       </c>
       <c r="B64" s="1">
-        <v>129800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -6472,7 +6472,7 @@
         <v>127</v>
       </c>
       <c r="B65" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -6480,7 +6480,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -6488,7 +6488,7 @@
         <v>116</v>
       </c>
       <c r="B67" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6496,7 +6496,7 @@
         <v>14</v>
       </c>
       <c r="B68" s="1">
-        <v>76700</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6504,7 +6504,7 @@
         <v>770</v>
       </c>
       <c r="B69" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -6512,7 +6512,7 @@
         <v>771</v>
       </c>
       <c r="B70" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -6520,7 +6520,7 @@
         <v>426</v>
       </c>
       <c r="B71" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -6528,7 +6528,7 @@
         <v>552</v>
       </c>
       <c r="B72" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -6536,7 +6536,7 @@
         <v>825</v>
       </c>
       <c r="B73" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -6544,7 +6544,7 @@
         <v>497</v>
       </c>
       <c r="B74" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -6552,7 +6552,7 @@
         <v>498</v>
       </c>
       <c r="B75" s="1">
-        <v>32450</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -6560,7 +6560,7 @@
         <v>772</v>
       </c>
       <c r="B76" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -6568,7 +6568,7 @@
         <v>773</v>
       </c>
       <c r="B77" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -6576,7 +6576,7 @@
         <v>586</v>
       </c>
       <c r="B78" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -6584,7 +6584,7 @@
         <v>15</v>
       </c>
       <c r="B79" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -6592,7 +6592,7 @@
         <v>16</v>
       </c>
       <c r="B80" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -6600,7 +6600,7 @@
         <v>580</v>
       </c>
       <c r="B81" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -6608,7 +6608,7 @@
         <v>688</v>
       </c>
       <c r="B82" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -6616,7 +6616,7 @@
         <v>774</v>
       </c>
       <c r="B83" s="1">
-        <v>2360</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -6624,7 +6624,7 @@
         <v>484</v>
       </c>
       <c r="B84" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -6632,7 +6632,7 @@
         <v>775</v>
       </c>
       <c r="B85" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -6640,7 +6640,7 @@
         <v>735</v>
       </c>
       <c r="B86" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -6648,7 +6648,7 @@
         <v>3</v>
       </c>
       <c r="B87" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -6656,7 +6656,7 @@
         <v>17</v>
       </c>
       <c r="B88" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -6664,7 +6664,7 @@
         <v>128</v>
       </c>
       <c r="B89" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -6672,7 +6672,7 @@
         <v>715</v>
       </c>
       <c r="B90" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -6680,7 +6680,7 @@
         <v>499</v>
       </c>
       <c r="B91" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -6688,7 +6688,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -6696,7 +6696,7 @@
         <v>623</v>
       </c>
       <c r="B93" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -6704,7 +6704,7 @@
         <v>776</v>
       </c>
       <c r="B94" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -6712,7 +6712,7 @@
         <v>18</v>
       </c>
       <c r="B95" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -6720,7 +6720,7 @@
         <v>19</v>
       </c>
       <c r="B96" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -6728,7 +6728,7 @@
         <v>500</v>
       </c>
       <c r="B97" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -6736,7 +6736,7 @@
         <v>501</v>
       </c>
       <c r="B98" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -6744,7 +6744,7 @@
         <v>25</v>
       </c>
       <c r="B99" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -6752,7 +6752,7 @@
         <v>553</v>
       </c>
       <c r="B100" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -6760,7 +6760,7 @@
         <v>777</v>
       </c>
       <c r="B101" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -6768,7 +6768,7 @@
         <v>778</v>
       </c>
       <c r="B102" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -6776,7 +6776,7 @@
         <v>779</v>
       </c>
       <c r="B103" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -6784,7 +6784,7 @@
         <v>780</v>
       </c>
       <c r="B104" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -6792,7 +6792,7 @@
         <v>129</v>
       </c>
       <c r="B105" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -6800,7 +6800,7 @@
         <v>502</v>
       </c>
       <c r="B106" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -6808,7 +6808,7 @@
         <v>781</v>
       </c>
       <c r="B107" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -6816,7 +6816,7 @@
         <v>752</v>
       </c>
       <c r="B108" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -6824,7 +6824,7 @@
         <v>723</v>
       </c>
       <c r="B109" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -6832,7 +6832,7 @@
         <v>720</v>
       </c>
       <c r="B110" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -6840,7 +6840,7 @@
         <v>721</v>
       </c>
       <c r="B111" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -6848,7 +6848,7 @@
         <v>503</v>
       </c>
       <c r="B112" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -6856,7 +6856,7 @@
         <v>100</v>
       </c>
       <c r="B113" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -6864,7 +6864,7 @@
         <v>826</v>
       </c>
       <c r="B114" s="1">
-        <v>206500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -6872,7 +6872,7 @@
         <v>654</v>
       </c>
       <c r="B115" s="1">
-        <v>206500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -6880,7 +6880,7 @@
         <v>24</v>
       </c>
       <c r="B116" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -6888,7 +6888,7 @@
         <v>782</v>
       </c>
       <c r="B117" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -6896,7 +6896,7 @@
         <v>740</v>
       </c>
       <c r="B118" s="1">
-        <v>129800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -6904,7 +6904,7 @@
         <v>20</v>
       </c>
       <c r="B119" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -6912,7 +6912,7 @@
         <v>433</v>
       </c>
       <c r="B120" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -6920,7 +6920,7 @@
         <v>783</v>
       </c>
       <c r="B121" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -6928,7 +6928,7 @@
         <v>115</v>
       </c>
       <c r="B122" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -6936,7 +6936,7 @@
         <v>504</v>
       </c>
       <c r="B123" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -6944,7 +6944,7 @@
         <v>505</v>
       </c>
       <c r="B124" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -6952,7 +6952,7 @@
         <v>784</v>
       </c>
       <c r="B125" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -6960,7 +6960,7 @@
         <v>716</v>
       </c>
       <c r="B126" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -6968,7 +6968,7 @@
         <v>785</v>
       </c>
       <c r="B127" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -6976,7 +6976,7 @@
         <v>506</v>
       </c>
       <c r="B128" s="1">
-        <v>44250</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -6984,7 +6984,7 @@
         <v>21</v>
       </c>
       <c r="B129" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -6992,7 +6992,7 @@
         <v>756</v>
       </c>
       <c r="B130" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7000,7 +7000,7 @@
         <v>480</v>
       </c>
       <c r="B131" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7008,7 +7008,7 @@
         <v>786</v>
       </c>
       <c r="B132" s="1">
-        <v>76700</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7016,7 +7016,7 @@
         <v>787</v>
       </c>
       <c r="B133" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7024,7 +7024,7 @@
         <v>788</v>
       </c>
       <c r="B134" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7032,7 +7032,7 @@
         <v>789</v>
       </c>
       <c r="B135" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7040,7 +7040,7 @@
         <v>73</v>
       </c>
       <c r="B136" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7048,7 +7048,7 @@
         <v>74</v>
       </c>
       <c r="B137" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7056,7 +7056,7 @@
         <v>162</v>
       </c>
       <c r="B138" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7064,7 +7064,7 @@
         <v>790</v>
       </c>
       <c r="B139" s="1">
-        <v>44250</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7072,7 +7072,7 @@
         <v>130</v>
       </c>
       <c r="B140" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7080,7 +7080,7 @@
         <v>791</v>
       </c>
       <c r="B141" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7088,7 +7088,7 @@
         <v>709</v>
       </c>
       <c r="B142" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7096,7 +7096,7 @@
         <v>432</v>
       </c>
       <c r="B143" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7104,7 +7104,7 @@
         <v>507</v>
       </c>
       <c r="B144" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7112,7 +7112,7 @@
         <v>508</v>
       </c>
       <c r="B145" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7120,7 +7120,7 @@
         <v>437</v>
       </c>
       <c r="B146" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7128,7 +7128,7 @@
         <v>509</v>
       </c>
       <c r="B147" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7136,7 +7136,7 @@
         <v>792</v>
       </c>
       <c r="B148" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7144,7 +7144,7 @@
         <v>4</v>
       </c>
       <c r="B149" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7152,7 +7152,7 @@
         <v>793</v>
       </c>
       <c r="B150" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7160,7 +7160,7 @@
         <v>650</v>
       </c>
       <c r="B151" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7168,7 +7168,7 @@
         <v>651</v>
       </c>
       <c r="B152" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7176,7 +7176,7 @@
         <v>588</v>
       </c>
       <c r="B153" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7184,7 +7184,7 @@
         <v>554</v>
       </c>
       <c r="B154" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7192,7 +7192,7 @@
         <v>510</v>
       </c>
       <c r="B155" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7200,7 +7200,7 @@
         <v>403</v>
       </c>
       <c r="B156" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7208,7 +7208,7 @@
         <v>546</v>
       </c>
       <c r="B157" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7216,7 +7216,7 @@
         <v>441</v>
       </c>
       <c r="B158" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7224,7 +7224,7 @@
         <v>556</v>
       </c>
       <c r="B159" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7232,7 +7232,7 @@
         <v>557</v>
       </c>
       <c r="B160" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7240,7 +7240,7 @@
         <v>794</v>
       </c>
       <c r="B161" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7248,7 +7248,7 @@
         <v>435</v>
       </c>
       <c r="B162" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7256,7 +7256,7 @@
         <v>795</v>
       </c>
       <c r="B163" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7264,7 +7264,7 @@
         <v>796</v>
       </c>
       <c r="B164" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -7272,7 +7272,7 @@
         <v>624</v>
       </c>
       <c r="B165" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -7280,7 +7280,7 @@
         <v>10</v>
       </c>
       <c r="B166" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -7288,7 +7288,7 @@
         <v>797</v>
       </c>
       <c r="B167" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
   </sheetData>
@@ -7318,7 +7318,7 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>82600</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7326,7 +7326,7 @@
         <v>745</v>
       </c>
       <c r="B3" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7334,7 +7334,7 @@
         <v>746</v>
       </c>
       <c r="B4" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7342,7 +7342,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1">
-        <v>82600</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7350,7 +7350,7 @@
         <v>747</v>
       </c>
       <c r="B6" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7358,7 +7358,7 @@
         <v>122</v>
       </c>
       <c r="B7" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7366,7 +7366,7 @@
         <v>131</v>
       </c>
       <c r="B8" s="1">
-        <v>147500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7374,7 +7374,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7382,7 +7382,7 @@
         <v>567</v>
       </c>
       <c r="B10" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7390,7 +7390,7 @@
         <v>82</v>
       </c>
       <c r="B11" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7398,7 +7398,7 @@
         <v>165</v>
       </c>
       <c r="B12" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7406,7 +7406,7 @@
         <v>589</v>
       </c>
       <c r="B13" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7414,7 +7414,7 @@
         <v>798</v>
       </c>
       <c r="B14" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7422,7 +7422,7 @@
         <v>132</v>
       </c>
       <c r="B15" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -7430,7 +7430,7 @@
         <v>133</v>
       </c>
       <c r="B16" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -7438,7 +7438,7 @@
         <v>753</v>
       </c>
       <c r="B17" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -7446,7 +7446,7 @@
         <v>625</v>
       </c>
       <c r="B18" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -7454,7 +7454,7 @@
         <v>823</v>
       </c>
       <c r="B19" s="1">
-        <v>50150</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7462,7 +7462,7 @@
         <v>430</v>
       </c>
       <c r="B20" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7470,7 +7470,7 @@
         <v>163</v>
       </c>
       <c r="B21" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7478,7 +7478,7 @@
         <v>647</v>
       </c>
       <c r="B22" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7486,7 +7486,7 @@
         <v>581</v>
       </c>
       <c r="B23" s="1">
-        <v>64900</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7494,7 +7494,7 @@
         <v>648</v>
       </c>
       <c r="B24" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7502,7 +7502,7 @@
         <v>83</v>
       </c>
       <c r="B25" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7510,7 +7510,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7518,7 +7518,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7526,7 +7526,7 @@
         <v>121</v>
       </c>
       <c r="B28" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7534,7 +7534,7 @@
         <v>134</v>
       </c>
       <c r="B29" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7542,7 +7542,7 @@
         <v>698</v>
       </c>
       <c r="B30" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7550,7 +7550,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7558,7 +7558,7 @@
         <v>477</v>
       </c>
       <c r="B32" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7566,7 +7566,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7574,7 +7574,7 @@
         <v>158</v>
       </c>
       <c r="B34" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7582,7 +7582,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7590,7 +7590,7 @@
         <v>692</v>
       </c>
       <c r="B36" s="1">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7598,7 +7598,7 @@
         <v>406</v>
       </c>
       <c r="B37" s="1">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7606,7 +7606,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="1">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7614,7 +7614,7 @@
         <v>626</v>
       </c>
       <c r="B39" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7622,7 +7622,7 @@
         <v>627</v>
       </c>
       <c r="B40" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7630,7 +7630,7 @@
         <v>628</v>
       </c>
       <c r="B41" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7638,7 +7638,7 @@
         <v>629</v>
       </c>
       <c r="B42" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -7646,7 +7646,7 @@
         <v>511</v>
       </c>
       <c r="B43" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7654,7 +7654,7 @@
         <v>85</v>
       </c>
       <c r="B44" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -7662,7 +7662,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -7670,7 +7670,7 @@
         <v>86</v>
       </c>
       <c r="B46" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7678,7 +7678,7 @@
         <v>135</v>
       </c>
       <c r="B47" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7686,7 +7686,7 @@
         <v>136</v>
       </c>
       <c r="B48" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -7694,7 +7694,7 @@
         <v>87</v>
       </c>
       <c r="B49" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -7702,7 +7702,7 @@
         <v>444</v>
       </c>
       <c r="B50" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -7710,7 +7710,7 @@
         <v>512</v>
       </c>
       <c r="B51" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -7718,7 +7718,7 @@
         <v>137</v>
       </c>
       <c r="B52" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -7726,7 +7726,7 @@
         <v>513</v>
       </c>
       <c r="B53" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -7734,7 +7734,7 @@
         <v>451</v>
       </c>
       <c r="B54" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -7742,7 +7742,7 @@
         <v>452</v>
       </c>
       <c r="B55" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -7750,7 +7750,7 @@
         <v>138</v>
       </c>
       <c r="B56" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -7758,7 +7758,7 @@
         <v>699</v>
       </c>
       <c r="B57" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -7766,7 +7766,7 @@
         <v>583</v>
       </c>
       <c r="B58" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -7774,7 +7774,7 @@
         <v>584</v>
       </c>
       <c r="B59" s="1">
-        <v>44250</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -7782,7 +7782,7 @@
         <v>139</v>
       </c>
       <c r="B60" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -7790,7 +7790,7 @@
         <v>551</v>
       </c>
       <c r="B61" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -7798,7 +7798,7 @@
         <v>140</v>
       </c>
       <c r="B62" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -7806,7 +7806,7 @@
         <v>89</v>
       </c>
       <c r="B63" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -7814,7 +7814,7 @@
         <v>88</v>
       </c>
       <c r="B64" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -7822,7 +7822,7 @@
         <v>559</v>
       </c>
       <c r="B65" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -7830,7 +7830,7 @@
         <v>722</v>
       </c>
       <c r="B66" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -7838,7 +7838,7 @@
         <v>118</v>
       </c>
       <c r="B67" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -7846,7 +7846,7 @@
         <v>799</v>
       </c>
       <c r="B68" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -7854,7 +7854,7 @@
         <v>39</v>
       </c>
       <c r="B69" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -7862,7 +7862,7 @@
         <v>40</v>
       </c>
       <c r="B70" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -7870,7 +7870,7 @@
         <v>800</v>
       </c>
       <c r="B71" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -7878,7 +7878,7 @@
         <v>120</v>
       </c>
       <c r="B72" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7886,7 +7886,7 @@
         <v>41</v>
       </c>
       <c r="B73" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7894,7 +7894,7 @@
         <v>42</v>
       </c>
       <c r="B74" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7902,7 +7902,7 @@
         <v>43</v>
       </c>
       <c r="B75" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7910,7 +7910,7 @@
         <v>44</v>
       </c>
       <c r="B76" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7918,7 +7918,7 @@
         <v>45</v>
       </c>
       <c r="B77" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7926,7 +7926,7 @@
         <v>46</v>
       </c>
       <c r="B78" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7934,7 +7934,7 @@
         <v>687</v>
       </c>
       <c r="B79" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7942,7 +7942,7 @@
         <v>90</v>
       </c>
       <c r="B80" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7950,7 +7950,7 @@
         <v>32</v>
       </c>
       <c r="B81" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7958,7 +7958,7 @@
         <v>27</v>
       </c>
       <c r="B82" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7966,7 +7966,7 @@
         <v>33</v>
       </c>
       <c r="B83" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7974,7 +7974,7 @@
         <v>141</v>
       </c>
       <c r="B84" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7982,7 +7982,7 @@
         <v>49</v>
       </c>
       <c r="B85" s="1">
-        <v>147500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7990,7 +7990,7 @@
         <v>48</v>
       </c>
       <c r="B86" s="1">
-        <v>147500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7998,7 +7998,7 @@
         <v>47</v>
       </c>
       <c r="B87" s="1">
-        <v>135700</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -8006,7 +8006,7 @@
         <v>50</v>
       </c>
       <c r="B88" s="1">
-        <v>147500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -8014,7 +8014,7 @@
         <v>51</v>
       </c>
       <c r="B89" s="1">
-        <v>147500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -8022,7 +8022,7 @@
         <v>474</v>
       </c>
       <c r="B90" s="1">
-        <v>147500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -8030,7 +8030,7 @@
         <v>55</v>
       </c>
       <c r="B91" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -8038,7 +8038,7 @@
         <v>52</v>
       </c>
       <c r="B92" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -8046,7 +8046,7 @@
         <v>53</v>
       </c>
       <c r="B93" s="1">
-        <v>129800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -8054,7 +8054,7 @@
         <v>54</v>
       </c>
       <c r="B94" s="1">
-        <v>129800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -8062,7 +8062,7 @@
         <v>56</v>
       </c>
       <c r="B95" s="1">
-        <v>129800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -8070,7 +8070,7 @@
         <v>475</v>
       </c>
       <c r="B96" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -8078,7 +8078,7 @@
         <v>514</v>
       </c>
       <c r="B97" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -8086,7 +8086,7 @@
         <v>700</v>
       </c>
       <c r="B98" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -8094,7 +8094,7 @@
         <v>701</v>
       </c>
       <c r="B99" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -8102,7 +8102,7 @@
         <v>142</v>
       </c>
       <c r="B100" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -8110,7 +8110,7 @@
         <v>801</v>
       </c>
       <c r="B101" s="1">
-        <v>82600</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -8118,7 +8118,7 @@
         <v>544</v>
       </c>
       <c r="B102" s="1">
-        <v>82600</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -8126,7 +8126,7 @@
         <v>802</v>
       </c>
       <c r="B103" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -8134,7 +8134,7 @@
         <v>643</v>
       </c>
       <c r="B104" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -8142,7 +8142,7 @@
         <v>515</v>
       </c>
       <c r="B105" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -8150,7 +8150,7 @@
         <v>428</v>
       </c>
       <c r="B106" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -8158,7 +8158,7 @@
         <v>693</v>
       </c>
       <c r="B107" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -8166,7 +8166,7 @@
         <v>552</v>
       </c>
       <c r="B108" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -8174,7 +8174,7 @@
         <v>825</v>
       </c>
       <c r="B109" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -8182,7 +8182,7 @@
         <v>702</v>
       </c>
       <c r="B110" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -8190,7 +8190,7 @@
         <v>93</v>
       </c>
       <c r="B111" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -8198,7 +8198,7 @@
         <v>92</v>
       </c>
       <c r="B112" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -8206,7 +8206,7 @@
         <v>91</v>
       </c>
       <c r="B113" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -8214,7 +8214,7 @@
         <v>94</v>
       </c>
       <c r="B114" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -8222,7 +8222,7 @@
         <v>585</v>
       </c>
       <c r="B115" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -8230,7 +8230,7 @@
         <v>646</v>
       </c>
       <c r="B116" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -8238,7 +8238,7 @@
         <v>560</v>
       </c>
       <c r="B117" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -8246,7 +8246,7 @@
         <v>57</v>
       </c>
       <c r="B118" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -8254,7 +8254,7 @@
         <v>58</v>
       </c>
       <c r="B119" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -8262,7 +8262,7 @@
         <v>59</v>
       </c>
       <c r="B120" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -8270,7 +8270,7 @@
         <v>561</v>
       </c>
       <c r="B121" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -8278,7 +8278,7 @@
         <v>562</v>
       </c>
       <c r="B122" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -8286,7 +8286,7 @@
         <v>677</v>
       </c>
       <c r="B123" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -8294,7 +8294,7 @@
         <v>685</v>
       </c>
       <c r="B124" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -8302,7 +8302,7 @@
         <v>686</v>
       </c>
       <c r="B125" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -8310,7 +8310,7 @@
         <v>484</v>
       </c>
       <c r="B126" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -8318,7 +8318,7 @@
         <v>735</v>
       </c>
       <c r="B127" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -8326,7 +8326,7 @@
         <v>60</v>
       </c>
       <c r="B128" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -8334,7 +8334,7 @@
         <v>61</v>
       </c>
       <c r="B129" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -8342,7 +8342,7 @@
         <v>157</v>
       </c>
       <c r="B130" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -8350,7 +8350,7 @@
         <v>62</v>
       </c>
       <c r="B131" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -8358,7 +8358,7 @@
         <v>754</v>
       </c>
       <c r="B132" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -8366,7 +8366,7 @@
         <v>694</v>
       </c>
       <c r="B133" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -8374,7 +8374,7 @@
         <v>563</v>
       </c>
       <c r="B134" s="1">
-        <v>82600</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -8382,7 +8382,7 @@
         <v>697</v>
       </c>
       <c r="B135" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -8390,7 +8390,7 @@
         <v>455</v>
       </c>
       <c r="B136" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -8398,7 +8398,7 @@
         <v>623</v>
       </c>
       <c r="B137" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -8406,7 +8406,7 @@
         <v>630</v>
       </c>
       <c r="B138" s="1">
-        <v>324500</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -8414,7 +8414,7 @@
         <v>631</v>
       </c>
       <c r="B139" s="1">
-        <v>336300</v>
+        <v>342000</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -8422,7 +8422,7 @@
         <v>449</v>
       </c>
       <c r="B140" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -8430,7 +8430,7 @@
         <v>448</v>
       </c>
       <c r="B141" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -8438,7 +8438,7 @@
         <v>450</v>
       </c>
       <c r="B142" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -8446,7 +8446,7 @@
         <v>447</v>
       </c>
       <c r="B143" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -8454,7 +8454,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -8462,7 +8462,7 @@
         <v>446</v>
       </c>
       <c r="B145" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -8470,7 +8470,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -8478,7 +8478,7 @@
         <v>591</v>
       </c>
       <c r="B147" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -8486,7 +8486,7 @@
         <v>96</v>
       </c>
       <c r="B148" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -8494,7 +8494,7 @@
         <v>95</v>
       </c>
       <c r="B149" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -8502,7 +8502,7 @@
         <v>97</v>
       </c>
       <c r="B150" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -8510,7 +8510,7 @@
         <v>553</v>
       </c>
       <c r="B151" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -8518,7 +8518,7 @@
         <v>803</v>
       </c>
       <c r="B152" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -8526,7 +8526,7 @@
         <v>804</v>
       </c>
       <c r="B153" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -8534,7 +8534,7 @@
         <v>145</v>
       </c>
       <c r="B154" s="1">
-        <v>147500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -8542,7 +8542,7 @@
         <v>119</v>
       </c>
       <c r="B155" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -8550,7 +8550,7 @@
         <v>703</v>
       </c>
       <c r="B156" s="1">
-        <v>44250</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -8558,7 +8558,7 @@
         <v>704</v>
       </c>
       <c r="B157" s="1">
-        <v>44250</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -8566,7 +8566,7 @@
         <v>98</v>
       </c>
       <c r="B158" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -8574,7 +8574,7 @@
         <v>63</v>
       </c>
       <c r="B159" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -8582,7 +8582,7 @@
         <v>472</v>
       </c>
       <c r="B160" s="1">
-        <v>82600</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -8590,7 +8590,7 @@
         <v>99</v>
       </c>
       <c r="B161" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -8598,7 +8598,7 @@
         <v>720</v>
       </c>
       <c r="B162" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -8606,7 +8606,7 @@
         <v>724</v>
       </c>
       <c r="B163" s="1">
-        <v>44250</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -8614,7 +8614,7 @@
         <v>721</v>
       </c>
       <c r="B164" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -8622,7 +8622,7 @@
         <v>725</v>
       </c>
       <c r="B165" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -8630,7 +8630,7 @@
         <v>695</v>
       </c>
       <c r="B166" s="1">
-        <v>885</v>
+        <v>900</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -8638,7 +8638,7 @@
         <v>101</v>
       </c>
       <c r="B167" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -8646,7 +8646,7 @@
         <v>102</v>
       </c>
       <c r="B168" s="1">
-        <v>135700</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -8654,7 +8654,7 @@
         <v>103</v>
       </c>
       <c r="B169" s="1">
-        <v>206500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -8662,7 +8662,7 @@
         <v>632</v>
       </c>
       <c r="B170" s="1">
-        <v>206500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -8670,7 +8670,7 @@
         <v>633</v>
       </c>
       <c r="B171" s="1">
-        <v>212400</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -8678,7 +8678,7 @@
         <v>678</v>
       </c>
       <c r="B172" s="1">
-        <v>218300</v>
+        <v>222000</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -8686,7 +8686,7 @@
         <v>679</v>
       </c>
       <c r="B173" s="1">
-        <v>206500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -8694,7 +8694,7 @@
         <v>680</v>
       </c>
       <c r="B174" s="1">
-        <v>206500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8702,7 +8702,7 @@
         <v>681</v>
       </c>
       <c r="B175" s="1">
-        <v>206500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -8710,7 +8710,7 @@
         <v>740</v>
       </c>
       <c r="B176" s="1">
-        <v>129800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -8718,7 +8718,7 @@
         <v>23</v>
       </c>
       <c r="B177" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -8726,7 +8726,7 @@
         <v>442</v>
       </c>
       <c r="B178" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -8734,7 +8734,7 @@
         <v>564</v>
       </c>
       <c r="B179" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -8742,7 +8742,7 @@
         <v>146</v>
       </c>
       <c r="B180" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -8750,7 +8750,7 @@
         <v>147</v>
       </c>
       <c r="B181" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -8758,7 +8758,7 @@
         <v>755</v>
       </c>
       <c r="B182" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -8766,7 +8766,7 @@
         <v>705</v>
       </c>
       <c r="B183" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -8774,7 +8774,7 @@
         <v>652</v>
       </c>
       <c r="B184" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -8782,7 +8782,7 @@
         <v>805</v>
       </c>
       <c r="B185" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -8790,7 +8790,7 @@
         <v>748</v>
       </c>
       <c r="B186" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -8798,7 +8798,7 @@
         <v>148</v>
       </c>
       <c r="B187" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -8806,7 +8806,7 @@
         <v>706</v>
       </c>
       <c r="B188" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -8814,7 +8814,7 @@
         <v>516</v>
       </c>
       <c r="B189" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -8822,7 +8822,7 @@
         <v>749</v>
       </c>
       <c r="B190" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -8830,7 +8830,7 @@
         <v>149</v>
       </c>
       <c r="B191" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -8838,7 +8838,7 @@
         <v>565</v>
       </c>
       <c r="B192" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -8846,7 +8846,7 @@
         <v>707</v>
       </c>
       <c r="B193" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -8854,7 +8854,7 @@
         <v>150</v>
       </c>
       <c r="B194" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -8862,7 +8862,7 @@
         <v>104</v>
       </c>
       <c r="B195" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -8870,7 +8870,7 @@
         <v>517</v>
       </c>
       <c r="B196" s="1">
-        <v>44250</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -8878,7 +8878,7 @@
         <v>151</v>
       </c>
       <c r="B197" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -8886,7 +8886,7 @@
         <v>481</v>
       </c>
       <c r="B198" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -8894,7 +8894,7 @@
         <v>708</v>
       </c>
       <c r="B199" s="1">
-        <v>100300</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -8902,7 +8902,7 @@
         <v>64</v>
       </c>
       <c r="B200" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -8910,7 +8910,7 @@
         <v>152</v>
       </c>
       <c r="B201" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -8918,7 +8918,7 @@
         <v>65</v>
       </c>
       <c r="B202" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -8926,7 +8926,7 @@
         <v>545</v>
       </c>
       <c r="B203" s="1">
-        <v>82600</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -8934,7 +8934,7 @@
         <v>547</v>
       </c>
       <c r="B204" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -8942,7 +8942,7 @@
         <v>66</v>
       </c>
       <c r="B205" s="1">
-        <v>76700</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -8950,7 +8950,7 @@
         <v>67</v>
       </c>
       <c r="B206" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -8958,7 +8958,7 @@
         <v>68</v>
       </c>
       <c r="B207" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -8966,7 +8966,7 @@
         <v>69</v>
       </c>
       <c r="B208" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -8974,7 +8974,7 @@
         <v>70</v>
       </c>
       <c r="B209" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -8982,7 +8982,7 @@
         <v>71</v>
       </c>
       <c r="B210" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -8990,7 +8990,7 @@
         <v>72</v>
       </c>
       <c r="B211" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -8998,7 +8998,7 @@
         <v>473</v>
       </c>
       <c r="B212" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -9006,7 +9006,7 @@
         <v>160</v>
       </c>
       <c r="B213" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -9014,7 +9014,7 @@
         <v>161</v>
       </c>
       <c r="B214" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -9022,7 +9022,7 @@
         <v>75</v>
       </c>
       <c r="B215" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -9030,7 +9030,7 @@
         <v>159</v>
       </c>
       <c r="B216" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -9038,7 +9038,7 @@
         <v>107</v>
       </c>
       <c r="B217" s="1">
-        <v>147500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -9046,7 +9046,7 @@
         <v>108</v>
       </c>
       <c r="B218" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -9054,7 +9054,7 @@
         <v>110</v>
       </c>
       <c r="B219" s="1">
-        <v>118000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -9062,7 +9062,7 @@
         <v>105</v>
       </c>
       <c r="B220" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -9070,7 +9070,7 @@
         <v>106</v>
       </c>
       <c r="B221" s="1">
-        <v>88500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -9078,7 +9078,7 @@
         <v>109</v>
       </c>
       <c r="B222" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -9086,7 +9086,7 @@
         <v>111</v>
       </c>
       <c r="B223" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -9094,7 +9094,7 @@
         <v>153</v>
       </c>
       <c r="B224" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -9102,7 +9102,7 @@
         <v>154</v>
       </c>
       <c r="B225" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -9110,7 +9110,7 @@
         <v>76</v>
       </c>
       <c r="B226" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -9118,7 +9118,7 @@
         <v>77</v>
       </c>
       <c r="B227" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -9126,7 +9126,7 @@
         <v>714</v>
       </c>
       <c r="B228" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -9134,7 +9134,7 @@
         <v>78</v>
       </c>
       <c r="B229" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -9142,7 +9142,7 @@
         <v>443</v>
       </c>
       <c r="B230" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -9150,7 +9150,7 @@
         <v>79</v>
       </c>
       <c r="B231" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -9158,7 +9158,7 @@
         <v>518</v>
       </c>
       <c r="B232" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -9166,7 +9166,7 @@
         <v>80</v>
       </c>
       <c r="B233" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -9174,7 +9174,7 @@
         <v>81</v>
       </c>
       <c r="B234" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -9182,7 +9182,7 @@
         <v>519</v>
       </c>
       <c r="B235" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -9190,7 +9190,7 @@
         <v>113</v>
       </c>
       <c r="B236" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -9198,7 +9198,7 @@
         <v>114</v>
       </c>
       <c r="B237" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -9206,7 +9206,7 @@
         <v>453</v>
       </c>
       <c r="B238" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -9214,7 +9214,7 @@
         <v>710</v>
       </c>
       <c r="B239" s="1">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -9222,7 +9222,7 @@
         <v>750</v>
       </c>
       <c r="B240" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -9230,7 +9230,7 @@
         <v>650</v>
       </c>
       <c r="B241" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -9238,7 +9238,7 @@
         <v>588</v>
       </c>
       <c r="B242" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -9246,7 +9246,7 @@
         <v>555</v>
       </c>
       <c r="B243" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -9254,7 +9254,7 @@
         <v>117</v>
       </c>
       <c r="B244" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -9262,7 +9262,7 @@
         <v>403</v>
       </c>
       <c r="B245" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -9270,7 +9270,7 @@
         <v>546</v>
       </c>
       <c r="B246" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -9278,7 +9278,7 @@
         <v>568</v>
       </c>
       <c r="B247" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -9286,7 +9286,7 @@
         <v>566</v>
       </c>
       <c r="B248" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -9294,7 +9294,7 @@
         <v>556</v>
       </c>
       <c r="B249" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -9302,7 +9302,7 @@
         <v>557</v>
       </c>
       <c r="B250" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -9310,7 +9310,7 @@
         <v>634</v>
       </c>
       <c r="B251" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -9318,7 +9318,7 @@
         <v>711</v>
       </c>
       <c r="B252" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -9326,7 +9326,7 @@
         <v>712</v>
       </c>
       <c r="B253" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -9334,7 +9334,7 @@
         <v>558</v>
       </c>
       <c r="B254" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -9342,7 +9342,7 @@
         <v>635</v>
       </c>
       <c r="B255" s="1">
-        <v>135700</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -9350,7 +9350,7 @@
         <v>713</v>
       </c>
       <c r="B256" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -9358,7 +9358,7 @@
         <v>794</v>
       </c>
       <c r="B257" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -9366,7 +9366,7 @@
         <v>445</v>
       </c>
       <c r="B258" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -9374,7 +9374,7 @@
         <v>682</v>
       </c>
       <c r="B259" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -9382,7 +9382,7 @@
         <v>112</v>
       </c>
       <c r="B260" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -9390,7 +9390,7 @@
         <v>155</v>
       </c>
       <c r="B261" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -9398,7 +9398,7 @@
         <v>156</v>
       </c>
       <c r="B262" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
   </sheetData>
@@ -9428,7 +9428,7 @@
         <v>592</v>
       </c>
       <c r="B2" s="1">
-        <v>106200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9436,7 +9436,7 @@
         <v>806</v>
       </c>
       <c r="B3" s="1">
-        <v>79650</v>
+        <v>81000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9444,7 +9444,7 @@
         <v>807</v>
       </c>
       <c r="B4" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9452,7 +9452,7 @@
         <v>589</v>
       </c>
       <c r="B5" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9460,7 +9460,7 @@
         <v>808</v>
       </c>
       <c r="B6" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9468,7 +9468,7 @@
         <v>581</v>
       </c>
       <c r="B7" s="1">
-        <v>64900</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9476,7 +9476,7 @@
         <v>648</v>
       </c>
       <c r="B8" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9484,7 +9484,7 @@
         <v>520</v>
       </c>
       <c r="B9" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -9492,7 +9492,7 @@
         <v>521</v>
       </c>
       <c r="B10" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9500,7 +9500,7 @@
         <v>522</v>
       </c>
       <c r="B11" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9508,7 +9508,7 @@
         <v>523</v>
       </c>
       <c r="B12" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -9516,7 +9516,7 @@
         <v>809</v>
       </c>
       <c r="B13" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -9524,7 +9524,7 @@
         <v>551</v>
       </c>
       <c r="B14" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -9532,7 +9532,7 @@
         <v>722</v>
       </c>
       <c r="B15" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -9540,7 +9540,7 @@
         <v>524</v>
       </c>
       <c r="B16" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -9548,7 +9548,7 @@
         <v>525</v>
       </c>
       <c r="B17" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -9556,7 +9556,7 @@
         <v>691</v>
       </c>
       <c r="B18" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -9564,7 +9564,7 @@
         <v>526</v>
       </c>
       <c r="B19" s="1">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -9572,7 +9572,7 @@
         <v>810</v>
       </c>
       <c r="B20" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -9580,7 +9580,7 @@
         <v>527</v>
       </c>
       <c r="B21" s="1">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -9588,7 +9588,7 @@
         <v>552</v>
       </c>
       <c r="B22" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -9596,7 +9596,7 @@
         <v>825</v>
       </c>
       <c r="B23" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -9604,7 +9604,7 @@
         <v>528</v>
       </c>
       <c r="B24" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -9612,7 +9612,7 @@
         <v>821</v>
       </c>
       <c r="B25" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -9620,7 +9620,7 @@
         <v>529</v>
       </c>
       <c r="B26" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -9628,7 +9628,7 @@
         <v>684</v>
       </c>
       <c r="B27" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -9636,7 +9636,7 @@
         <v>484</v>
       </c>
       <c r="B28">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -9644,7 +9644,7 @@
         <v>735</v>
       </c>
       <c r="B29">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -9652,7 +9652,7 @@
         <v>530</v>
       </c>
       <c r="B30">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -9660,7 +9660,7 @@
         <v>531</v>
       </c>
       <c r="B31">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -9668,7 +9668,7 @@
         <v>532</v>
       </c>
       <c r="B32">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -9676,7 +9676,7 @@
         <v>533</v>
       </c>
       <c r="B33">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -9684,7 +9684,7 @@
         <v>534</v>
       </c>
       <c r="B34">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -9692,7 +9692,7 @@
         <v>535</v>
       </c>
       <c r="B35">
-        <v>64900</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -9700,7 +9700,7 @@
         <v>631</v>
       </c>
       <c r="B36">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -9708,7 +9708,7 @@
         <v>553</v>
       </c>
       <c r="B37">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -9716,7 +9716,7 @@
         <v>726</v>
       </c>
       <c r="B38">
-        <v>50150</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -9724,7 +9724,7 @@
         <v>727</v>
       </c>
       <c r="B39">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -9732,7 +9732,7 @@
         <v>536</v>
       </c>
       <c r="B40">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -9740,7 +9740,7 @@
         <v>683</v>
       </c>
       <c r="B41">
-        <v>212400</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -9748,7 +9748,7 @@
         <v>636</v>
       </c>
       <c r="B42">
-        <v>218300</v>
+        <v>222000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -9756,7 +9756,7 @@
         <v>740</v>
       </c>
       <c r="B43">
-        <v>129800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -9764,7 +9764,7 @@
         <v>537</v>
       </c>
       <c r="B44">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -9772,7 +9772,7 @@
         <v>538</v>
       </c>
       <c r="B45">
-        <v>29500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -9780,7 +9780,7 @@
         <v>811</v>
       </c>
       <c r="B46">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -9788,7 +9788,7 @@
         <v>812</v>
       </c>
       <c r="B47">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -9796,7 +9796,7 @@
         <v>813</v>
       </c>
       <c r="B48">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -9804,7 +9804,7 @@
         <v>539</v>
       </c>
       <c r="B49">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -9812,7 +9812,7 @@
         <v>814</v>
       </c>
       <c r="B50">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -9820,7 +9820,7 @@
         <v>815</v>
       </c>
       <c r="B51">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -9828,7 +9828,7 @@
         <v>816</v>
       </c>
       <c r="B52">
-        <v>14750</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -9836,7 +9836,7 @@
         <v>588</v>
       </c>
       <c r="B53">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -9844,7 +9844,7 @@
         <v>817</v>
       </c>
       <c r="B54">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -9852,7 +9852,7 @@
         <v>818</v>
       </c>
       <c r="B55">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -9860,7 +9860,7 @@
         <v>819</v>
       </c>
       <c r="B56">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -9868,7 +9868,7 @@
         <v>548</v>
       </c>
       <c r="B57">
-        <v>41300</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -9876,7 +9876,7 @@
         <v>549</v>
       </c>
       <c r="B58">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -9884,7 +9884,7 @@
         <v>403</v>
       </c>
       <c r="B59">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -9892,7 +9892,7 @@
         <v>546</v>
       </c>
       <c r="B60">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -9900,7 +9900,7 @@
         <v>556</v>
       </c>
       <c r="B61">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -9908,7 +9908,7 @@
         <v>557</v>
       </c>
       <c r="B62">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -9916,7 +9916,7 @@
         <v>540</v>
       </c>
       <c r="B63">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -9924,7 +9924,7 @@
         <v>541</v>
       </c>
       <c r="B64">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -9932,7 +9932,7 @@
         <v>637</v>
       </c>
       <c r="B65">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -9940,7 +9940,7 @@
         <v>542</v>
       </c>
       <c r="B66">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
   </sheetData>
@@ -9970,7 +9970,7 @@
         <v>383</v>
       </c>
       <c r="B2" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9978,7 +9978,7 @@
         <v>384</v>
       </c>
       <c r="B3" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9986,7 +9986,7 @@
         <v>385</v>
       </c>
       <c r="B4" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9994,7 +9994,7 @@
         <v>386</v>
       </c>
       <c r="B5" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -10002,7 +10002,7 @@
         <v>640</v>
       </c>
       <c r="B6" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -10010,7 +10010,7 @@
         <v>387</v>
       </c>
       <c r="B7" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -10018,7 +10018,7 @@
         <v>660</v>
       </c>
       <c r="B8" s="1">
-        <v>23600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -10026,7 +10026,7 @@
         <v>662</v>
       </c>
       <c r="B9" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -10034,7 +10034,7 @@
         <v>661</v>
       </c>
       <c r="B10" s="1">
-        <v>18880</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -10042,7 +10042,7 @@
         <v>388</v>
       </c>
       <c r="B11" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -10050,7 +10050,7 @@
         <v>405</v>
       </c>
       <c r="B12" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -10058,7 +10058,7 @@
         <v>659</v>
       </c>
       <c r="B13" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -10066,7 +10066,7 @@
         <v>665</v>
       </c>
       <c r="B14" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -10074,7 +10074,7 @@
         <v>745</v>
       </c>
       <c r="B15" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -10082,7 +10082,7 @@
         <v>389</v>
       </c>
       <c r="B16" s="1">
-        <v>5310</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -10090,7 +10090,7 @@
         <v>589</v>
       </c>
       <c r="B17" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -10098,7 +10098,7 @@
         <v>823</v>
       </c>
       <c r="B18" s="1">
-        <v>50150</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -10106,7 +10106,7 @@
         <v>663</v>
       </c>
       <c r="B19" s="1">
-        <v>103250</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -10114,7 +10114,7 @@
         <v>655</v>
       </c>
       <c r="B20" s="1">
-        <v>115050</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -10122,7 +10122,7 @@
         <v>656</v>
       </c>
       <c r="B21" s="1">
-        <v>129800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -10130,7 +10130,7 @@
         <v>430</v>
       </c>
       <c r="B22" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -10138,7 +10138,7 @@
         <v>163</v>
       </c>
       <c r="B23" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -10146,7 +10146,7 @@
         <v>647</v>
       </c>
       <c r="B24" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -10154,7 +10154,7 @@
         <v>581</v>
       </c>
       <c r="B25" s="1">
-        <v>64900</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -10162,7 +10162,7 @@
         <v>648</v>
       </c>
       <c r="B26" s="1">
-        <v>70800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -10170,7 +10170,7 @@
         <v>657</v>
       </c>
       <c r="B27" s="1">
-        <v>79650</v>
+        <v>81000</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -10178,7 +10178,7 @@
         <v>658</v>
       </c>
       <c r="B28" s="1">
-        <v>94400</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -10186,7 +10186,7 @@
         <v>664</v>
       </c>
       <c r="B29" s="1">
-        <v>100300</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -10194,7 +10194,7 @@
         <v>692</v>
       </c>
       <c r="B30" s="1">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -10202,7 +10202,7 @@
         <v>406</v>
       </c>
       <c r="B31" s="1">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -10210,7 +10210,7 @@
         <v>402</v>
       </c>
       <c r="B32" s="1">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -10218,7 +10218,7 @@
         <v>429</v>
       </c>
       <c r="B33" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -10226,7 +10226,7 @@
         <v>551</v>
       </c>
       <c r="B34" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -10234,7 +10234,7 @@
         <v>390</v>
       </c>
       <c r="B35" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -10242,7 +10242,7 @@
         <v>552</v>
       </c>
       <c r="B36" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -10250,7 +10250,7 @@
         <v>825</v>
       </c>
       <c r="B37" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -10258,7 +10258,7 @@
         <v>820</v>
       </c>
       <c r="B38" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -10266,7 +10266,7 @@
         <v>404</v>
       </c>
       <c r="B39" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -10274,7 +10274,7 @@
         <v>259</v>
       </c>
       <c r="B40" s="1">
-        <v>17700</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -10282,7 +10282,7 @@
         <v>425</v>
       </c>
       <c r="B41" s="1">
-        <v>2360</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -10290,7 +10290,7 @@
         <v>484</v>
       </c>
       <c r="B42" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -10298,7 +10298,7 @@
         <v>735</v>
       </c>
       <c r="B43" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -10306,7 +10306,7 @@
         <v>391</v>
       </c>
       <c r="B44" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -10314,7 +10314,7 @@
         <v>392</v>
       </c>
       <c r="B45" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -10322,7 +10322,7 @@
         <v>393</v>
       </c>
       <c r="B46" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -10330,7 +10330,7 @@
         <v>638</v>
       </c>
       <c r="B47" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -10338,7 +10338,7 @@
         <v>394</v>
       </c>
       <c r="B48" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -10346,7 +10346,7 @@
         <v>395</v>
       </c>
       <c r="B49" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -10354,7 +10354,7 @@
         <v>396</v>
       </c>
       <c r="B50" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -10362,7 +10362,7 @@
         <v>728</v>
       </c>
       <c r="B51" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -10370,7 +10370,7 @@
         <v>553</v>
       </c>
       <c r="B52" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -10378,7 +10378,7 @@
         <v>718</v>
       </c>
       <c r="B53" s="1">
-        <v>32450</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -10386,7 +10386,7 @@
         <v>719</v>
       </c>
       <c r="B54" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -10394,7 +10394,7 @@
         <v>752</v>
       </c>
       <c r="B55" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -10402,7 +10402,7 @@
         <v>723</v>
       </c>
       <c r="B56" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -10410,7 +10410,7 @@
         <v>720</v>
       </c>
       <c r="B57" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -10418,7 +10418,7 @@
         <v>724</v>
       </c>
       <c r="B58" s="1">
-        <v>44250</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -10426,7 +10426,7 @@
         <v>721</v>
       </c>
       <c r="B59" s="1">
-        <v>38350</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -10434,7 +10434,7 @@
         <v>725</v>
       </c>
       <c r="B60" s="1">
-        <v>47200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -10442,7 +10442,7 @@
         <v>726</v>
       </c>
       <c r="B61" s="1">
-        <v>50150</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -10450,7 +10450,7 @@
         <v>727</v>
       </c>
       <c r="B62" s="1">
-        <v>53100</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -10458,7 +10458,7 @@
         <v>740</v>
       </c>
       <c r="B63" s="1">
-        <v>129800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -10466,7 +10466,7 @@
         <v>827</v>
       </c>
       <c r="B64" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -10474,7 +10474,7 @@
         <v>639</v>
       </c>
       <c r="B65" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -10482,7 +10482,7 @@
         <v>543</v>
       </c>
       <c r="B66" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -10490,7 +10490,7 @@
         <v>397</v>
       </c>
       <c r="B67" s="1">
-        <v>10620</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -10498,7 +10498,7 @@
         <v>653</v>
       </c>
       <c r="B68" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -10506,7 +10506,7 @@
         <v>398</v>
       </c>
       <c r="B69" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -10514,7 +10514,7 @@
         <v>399</v>
       </c>
       <c r="B70" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -10522,7 +10522,7 @@
         <v>400</v>
       </c>
       <c r="B71" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -10530,7 +10530,7 @@
         <v>582</v>
       </c>
       <c r="B72" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -10538,7 +10538,7 @@
         <v>401</v>
       </c>
       <c r="B73" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -10546,7 +10546,7 @@
         <v>588</v>
       </c>
       <c r="B74" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -10554,7 +10554,7 @@
         <v>554</v>
       </c>
       <c r="B75" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -10562,7 +10562,7 @@
         <v>555</v>
       </c>
       <c r="B76" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -10570,7 +10570,7 @@
         <v>644</v>
       </c>
       <c r="B77" s="1">
-        <v>4130</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -10578,7 +10578,7 @@
         <v>645</v>
       </c>
       <c r="B78" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -10586,7 +10586,7 @@
         <v>403</v>
       </c>
       <c r="B79" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -10594,7 +10594,7 @@
         <v>546</v>
       </c>
       <c r="B80" s="1">
-        <v>7080</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -10602,7 +10602,7 @@
         <v>556</v>
       </c>
       <c r="B81" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -10610,7 +10610,7 @@
         <v>557</v>
       </c>
       <c r="B82" s="1">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -10618,7 +10618,7 @@
         <v>558</v>
       </c>
       <c r="B83" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
   </sheetData>

--- a/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\600 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\610 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D2D2BB-09EA-47C6-88B9-1AB68DF7E8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571E3D6E-3AD2-4E37-9BE7-A8526FF952E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3034,7 +3034,7 @@
         <v>166</v>
       </c>
       <c r="B2" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3042,7 +3042,7 @@
         <v>421</v>
       </c>
       <c r="B3" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3050,7 +3050,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3058,7 +3058,7 @@
         <v>459</v>
       </c>
       <c r="B5" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3066,7 +3066,7 @@
         <v>460</v>
       </c>
       <c r="B6" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3074,7 +3074,7 @@
         <v>593</v>
       </c>
       <c r="B7" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3082,7 +3082,7 @@
         <v>168</v>
       </c>
       <c r="B8" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3090,7 +3090,7 @@
         <v>461</v>
       </c>
       <c r="B9" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3098,7 +3098,7 @@
         <v>169</v>
       </c>
       <c r="B10" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3106,7 +3106,7 @@
         <v>170</v>
       </c>
       <c r="B11" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3114,7 +3114,7 @@
         <v>171</v>
       </c>
       <c r="B12" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3122,7 +3122,7 @@
         <v>174</v>
       </c>
       <c r="B13" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3130,7 +3130,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3138,7 +3138,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="1">
-        <v>66000</v>
+        <v>67100</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3146,7 +3146,7 @@
         <v>666</v>
       </c>
       <c r="B16" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3154,7 +3154,7 @@
         <v>175</v>
       </c>
       <c r="B17" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3162,7 +3162,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3170,7 +3170,7 @@
         <v>589</v>
       </c>
       <c r="B19" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3178,7 +3178,7 @@
         <v>462</v>
       </c>
       <c r="B20" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3186,7 +3186,7 @@
         <v>177</v>
       </c>
       <c r="B21" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3194,7 +3194,7 @@
         <v>178</v>
       </c>
       <c r="B22" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3202,7 +3202,7 @@
         <v>179</v>
       </c>
       <c r="B23" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3210,7 +3210,7 @@
         <v>550</v>
       </c>
       <c r="B24" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3218,7 +3218,7 @@
         <v>180</v>
       </c>
       <c r="B25" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3226,7 +3226,7 @@
         <v>181</v>
       </c>
       <c r="B26" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3234,7 +3234,7 @@
         <v>182</v>
       </c>
       <c r="B27" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3242,7 +3242,7 @@
         <v>183</v>
       </c>
       <c r="B28" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3250,7 +3250,7 @@
         <v>184</v>
       </c>
       <c r="B29" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3258,7 +3258,7 @@
         <v>185</v>
       </c>
       <c r="B30" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3266,7 +3266,7 @@
         <v>186</v>
       </c>
       <c r="B31" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3274,7 +3274,7 @@
         <v>187</v>
       </c>
       <c r="B32" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3282,7 +3282,7 @@
         <v>188</v>
       </c>
       <c r="B33" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3290,7 +3290,7 @@
         <v>606</v>
       </c>
       <c r="B34" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3298,7 +3298,7 @@
         <v>569</v>
       </c>
       <c r="B35" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3306,7 +3306,7 @@
         <v>594</v>
       </c>
       <c r="B36" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3314,7 +3314,7 @@
         <v>823</v>
       </c>
       <c r="B37" s="1">
-        <v>51000</v>
+        <v>51850</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3322,7 +3322,7 @@
         <v>430</v>
       </c>
       <c r="B38" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3330,7 +3330,7 @@
         <v>163</v>
       </c>
       <c r="B39" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3338,7 +3338,7 @@
         <v>647</v>
       </c>
       <c r="B40" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3346,7 +3346,7 @@
         <v>581</v>
       </c>
       <c r="B41" s="1">
-        <v>66000</v>
+        <v>67100</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3354,7 +3354,7 @@
         <v>648</v>
       </c>
       <c r="B42" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3362,7 +3362,7 @@
         <v>189</v>
       </c>
       <c r="B43" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3370,7 +3370,7 @@
         <v>419</v>
       </c>
       <c r="B44" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3378,7 +3378,7 @@
         <v>408</v>
       </c>
       <c r="B45" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3386,7 +3386,7 @@
         <v>729</v>
       </c>
       <c r="B46" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3394,7 +3394,7 @@
         <v>730</v>
       </c>
       <c r="B47" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3402,7 +3402,7 @@
         <v>190</v>
       </c>
       <c r="B48" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3410,7 +3410,7 @@
         <v>191</v>
       </c>
       <c r="B49" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3418,7 +3418,7 @@
         <v>192</v>
       </c>
       <c r="B50" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3426,7 +3426,7 @@
         <v>193</v>
       </c>
       <c r="B51" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3434,7 +3434,7 @@
         <v>692</v>
       </c>
       <c r="B52" s="1">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3442,7 +3442,7 @@
         <v>194</v>
       </c>
       <c r="B53" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3450,7 +3450,7 @@
         <v>406</v>
       </c>
       <c r="B54" s="1">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3458,7 +3458,7 @@
         <v>402</v>
       </c>
       <c r="B55" s="1">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3466,7 +3466,7 @@
         <v>429</v>
       </c>
       <c r="B56" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3474,7 +3474,7 @@
         <v>195</v>
       </c>
       <c r="B57" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3482,7 +3482,7 @@
         <v>196</v>
       </c>
       <c r="B58" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3490,7 +3490,7 @@
         <v>197</v>
       </c>
       <c r="B59" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3498,7 +3498,7 @@
         <v>595</v>
       </c>
       <c r="B60" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3506,7 +3506,7 @@
         <v>596</v>
       </c>
       <c r="B61" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3514,7 +3514,7 @@
         <v>198</v>
       </c>
       <c r="B62" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3522,7 +3522,7 @@
         <v>199</v>
       </c>
       <c r="B63" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3530,7 +3530,7 @@
         <v>200</v>
       </c>
       <c r="B64" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3538,7 +3538,7 @@
         <v>201</v>
       </c>
       <c r="B65" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3546,7 +3546,7 @@
         <v>202</v>
       </c>
       <c r="B66" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3554,7 +3554,7 @@
         <v>203</v>
       </c>
       <c r="B67" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3562,7 +3562,7 @@
         <v>204</v>
       </c>
       <c r="B68" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3570,7 +3570,7 @@
         <v>205</v>
       </c>
       <c r="B69" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3578,7 +3578,7 @@
         <v>206</v>
       </c>
       <c r="B70" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3586,7 +3586,7 @@
         <v>208</v>
       </c>
       <c r="B71" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3594,7 +3594,7 @@
         <v>212</v>
       </c>
       <c r="B72" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3602,7 +3602,7 @@
         <v>209</v>
       </c>
       <c r="B73" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3610,7 +3610,7 @@
         <v>210</v>
       </c>
       <c r="B74" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3618,7 +3618,7 @@
         <v>211</v>
       </c>
       <c r="B75" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3626,7 +3626,7 @@
         <v>476</v>
       </c>
       <c r="B76" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3634,7 +3634,7 @@
         <v>207</v>
       </c>
       <c r="B77" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3642,7 +3642,7 @@
         <v>213</v>
       </c>
       <c r="B78" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3650,7 +3650,7 @@
         <v>214</v>
       </c>
       <c r="B79" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3658,7 +3658,7 @@
         <v>215</v>
       </c>
       <c r="B80" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3666,7 +3666,7 @@
         <v>216</v>
       </c>
       <c r="B81" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3674,7 +3674,7 @@
         <v>217</v>
       </c>
       <c r="B82" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3682,7 +3682,7 @@
         <v>218</v>
       </c>
       <c r="B83" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3690,7 +3690,7 @@
         <v>219</v>
       </c>
       <c r="B84" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3698,7 +3698,7 @@
         <v>220</v>
       </c>
       <c r="B85" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3706,7 +3706,7 @@
         <v>607</v>
       </c>
       <c r="B86" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3714,7 +3714,7 @@
         <v>221</v>
       </c>
       <c r="B87" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3722,7 +3722,7 @@
         <v>608</v>
       </c>
       <c r="B88" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3730,7 +3730,7 @@
         <v>417</v>
       </c>
       <c r="B89" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3738,7 +3738,7 @@
         <v>418</v>
       </c>
       <c r="B90" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3746,7 +3746,7 @@
         <v>222</v>
       </c>
       <c r="B91" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3754,7 +3754,7 @@
         <v>223</v>
       </c>
       <c r="B92" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3762,7 +3762,7 @@
         <v>224</v>
       </c>
       <c r="B93" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3770,7 +3770,7 @@
         <v>225</v>
       </c>
       <c r="B94" s="1">
-        <v>210000</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3778,7 +3778,7 @@
         <v>226</v>
       </c>
       <c r="B95" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3786,7 +3786,7 @@
         <v>824</v>
       </c>
       <c r="B96" s="1">
-        <v>180000</v>
+        <v>183000</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3794,7 +3794,7 @@
         <v>227</v>
       </c>
       <c r="B97" s="1">
-        <v>168000</v>
+        <v>170800</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3802,7 +3802,7 @@
         <v>228</v>
       </c>
       <c r="B98" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3810,7 +3810,7 @@
         <v>551</v>
       </c>
       <c r="B99" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3818,7 +3818,7 @@
         <v>667</v>
       </c>
       <c r="B100" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3826,7 +3826,7 @@
         <v>409</v>
       </c>
       <c r="B101" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3834,7 +3834,7 @@
         <v>229</v>
       </c>
       <c r="B102" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3842,7 +3842,7 @@
         <v>230</v>
       </c>
       <c r="B103" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3850,7 +3850,7 @@
         <v>231</v>
       </c>
       <c r="B104" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3858,7 +3858,7 @@
         <v>424</v>
       </c>
       <c r="B105" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3866,7 +3866,7 @@
         <v>232</v>
       </c>
       <c r="B106" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3874,7 +3874,7 @@
         <v>570</v>
       </c>
       <c r="B107" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3882,7 +3882,7 @@
         <v>483</v>
       </c>
       <c r="B108" s="1">
-        <v>150000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3890,7 +3890,7 @@
         <v>587</v>
       </c>
       <c r="B109" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3898,7 +3898,7 @@
         <v>233</v>
       </c>
       <c r="B110" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3906,7 +3906,7 @@
         <v>234</v>
       </c>
       <c r="B111" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3914,7 +3914,7 @@
         <v>731</v>
       </c>
       <c r="B112" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3922,7 +3922,7 @@
         <v>717</v>
       </c>
       <c r="B113" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3930,7 +3930,7 @@
         <v>571</v>
       </c>
       <c r="B114" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3938,7 +3938,7 @@
         <v>590</v>
       </c>
       <c r="B115" s="1">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3946,7 +3946,7 @@
         <v>235</v>
       </c>
       <c r="B116" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3954,7 +3954,7 @@
         <v>732</v>
       </c>
       <c r="B117" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3962,7 +3962,7 @@
         <v>236</v>
       </c>
       <c r="B118" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3970,7 +3970,7 @@
         <v>733</v>
       </c>
       <c r="B119" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3978,7 +3978,7 @@
         <v>237</v>
       </c>
       <c r="B120" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3986,7 +3986,7 @@
         <v>410</v>
       </c>
       <c r="B121" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3994,7 +3994,7 @@
         <v>238</v>
       </c>
       <c r="B122" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4002,7 +4002,7 @@
         <v>239</v>
       </c>
       <c r="B123" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4010,7 +4010,7 @@
         <v>240</v>
       </c>
       <c r="B124" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4018,7 +4018,7 @@
         <v>241</v>
       </c>
       <c r="B125" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4026,7 +4026,7 @@
         <v>242</v>
       </c>
       <c r="B126" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4034,7 +4034,7 @@
         <v>243</v>
       </c>
       <c r="B127" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4042,7 +4042,7 @@
         <v>668</v>
       </c>
       <c r="B128" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4050,7 +4050,7 @@
         <v>669</v>
       </c>
       <c r="B129" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4058,7 +4058,7 @@
         <v>431</v>
       </c>
       <c r="B130" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4066,7 +4066,7 @@
         <v>244</v>
       </c>
       <c r="B131" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4074,7 +4074,7 @@
         <v>597</v>
       </c>
       <c r="B132" s="1">
-        <v>258000</v>
+        <v>262300</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4082,7 +4082,7 @@
         <v>245</v>
       </c>
       <c r="B133" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4090,7 +4090,7 @@
         <v>456</v>
       </c>
       <c r="B134" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4098,7 +4098,7 @@
         <v>457</v>
       </c>
       <c r="B135" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4106,7 +4106,7 @@
         <v>458</v>
       </c>
       <c r="B136" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4114,7 +4114,7 @@
         <v>246</v>
       </c>
       <c r="B137" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4122,7 +4122,7 @@
         <v>247</v>
       </c>
       <c r="B138" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4130,7 +4130,7 @@
         <v>248</v>
       </c>
       <c r="B139" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4138,7 +4138,7 @@
         <v>250</v>
       </c>
       <c r="B140" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4146,7 +4146,7 @@
         <v>420</v>
       </c>
       <c r="B141" s="1">
-        <v>150000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4154,7 +4154,7 @@
         <v>14</v>
       </c>
       <c r="B142" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4162,7 +4162,7 @@
         <v>602</v>
       </c>
       <c r="B143" s="1">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4170,7 +4170,7 @@
         <v>249</v>
       </c>
       <c r="B144" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4178,7 +4178,7 @@
         <v>552</v>
       </c>
       <c r="B145" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4186,7 +4186,7 @@
         <v>251</v>
       </c>
       <c r="B146" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4194,7 +4194,7 @@
         <v>825</v>
       </c>
       <c r="B147" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4202,7 +4202,7 @@
         <v>252</v>
       </c>
       <c r="B148" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4210,7 +4210,7 @@
         <v>253</v>
       </c>
       <c r="B149" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4218,7 +4218,7 @@
         <v>598</v>
       </c>
       <c r="B150" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4226,7 +4226,7 @@
         <v>254</v>
       </c>
       <c r="B151" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4234,7 +4234,7 @@
         <v>255</v>
       </c>
       <c r="B152" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4242,7 +4242,7 @@
         <v>256</v>
       </c>
       <c r="B153" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4250,7 +4250,7 @@
         <v>257</v>
       </c>
       <c r="B154" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4258,7 +4258,7 @@
         <v>258</v>
       </c>
       <c r="B155" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4266,7 +4266,7 @@
         <v>261</v>
       </c>
       <c r="B156" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4274,7 +4274,7 @@
         <v>262</v>
       </c>
       <c r="B157" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4282,7 +4282,7 @@
         <v>263</v>
       </c>
       <c r="B158" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4290,7 +4290,7 @@
         <v>404</v>
       </c>
       <c r="B159" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4298,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="B160" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4306,7 +4306,7 @@
         <v>463</v>
       </c>
       <c r="B161" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4314,7 +4314,7 @@
         <v>260</v>
       </c>
       <c r="B162" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4322,7 +4322,7 @@
         <v>264</v>
       </c>
       <c r="B163" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4330,7 +4330,7 @@
         <v>689</v>
       </c>
       <c r="B164" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4338,7 +4338,7 @@
         <v>641</v>
       </c>
       <c r="B165" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4346,7 +4346,7 @@
         <v>642</v>
       </c>
       <c r="B166" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4354,7 +4354,7 @@
         <v>603</v>
       </c>
       <c r="B167" s="1">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4362,7 +4362,7 @@
         <v>604</v>
       </c>
       <c r="B168" s="1">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4370,7 +4370,7 @@
         <v>484</v>
       </c>
       <c r="B169" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4378,7 +4378,7 @@
         <v>265</v>
       </c>
       <c r="B170" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4386,7 +4386,7 @@
         <v>609</v>
       </c>
       <c r="B171" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4394,7 +4394,7 @@
         <v>734</v>
       </c>
       <c r="B172" s="1">
-        <v>2400</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4402,7 +4402,7 @@
         <v>735</v>
       </c>
       <c r="B173" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4410,7 +4410,7 @@
         <v>266</v>
       </c>
       <c r="B174" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4418,7 +4418,7 @@
         <v>267</v>
       </c>
       <c r="B175" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4426,7 +4426,7 @@
         <v>268</v>
       </c>
       <c r="B176" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4434,7 +4434,7 @@
         <v>269</v>
       </c>
       <c r="B177" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4442,7 +4442,7 @@
         <v>270</v>
       </c>
       <c r="B178" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4450,7 +4450,7 @@
         <v>271</v>
       </c>
       <c r="B179" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4458,7 +4458,7 @@
         <v>272</v>
       </c>
       <c r="B180" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4466,7 +4466,7 @@
         <v>273</v>
       </c>
       <c r="B181" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4474,7 +4474,7 @@
         <v>422</v>
       </c>
       <c r="B182" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4482,7 +4482,7 @@
         <v>423</v>
       </c>
       <c r="B183" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4490,7 +4490,7 @@
         <v>610</v>
       </c>
       <c r="B184" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4498,7 +4498,7 @@
         <v>611</v>
       </c>
       <c r="B185" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4506,7 +4506,7 @@
         <v>612</v>
       </c>
       <c r="B186" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4514,7 +4514,7 @@
         <v>613</v>
       </c>
       <c r="B187" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4522,7 +4522,7 @@
         <v>614</v>
       </c>
       <c r="B188" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4530,7 +4530,7 @@
         <v>615</v>
       </c>
       <c r="B189" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4538,7 +4538,7 @@
         <v>274</v>
       </c>
       <c r="B190" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4546,7 +4546,7 @@
         <v>276</v>
       </c>
       <c r="B191" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4554,7 +4554,7 @@
         <v>275</v>
       </c>
       <c r="B192" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4562,7 +4562,7 @@
         <v>616</v>
       </c>
       <c r="B193" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4570,7 +4570,7 @@
         <v>277</v>
       </c>
       <c r="B194" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4578,7 +4578,7 @@
         <v>464</v>
       </c>
       <c r="B195" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4586,7 +4586,7 @@
         <v>278</v>
       </c>
       <c r="B196" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4594,7 +4594,7 @@
         <v>736</v>
       </c>
       <c r="B197" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4602,7 +4602,7 @@
         <v>391</v>
       </c>
       <c r="B198" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4610,7 +4610,7 @@
         <v>396</v>
       </c>
       <c r="B199" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4618,7 +4618,7 @@
         <v>466</v>
       </c>
       <c r="B200" s="1">
-        <v>192000</v>
+        <v>195200</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4626,7 +4626,7 @@
         <v>279</v>
       </c>
       <c r="B201" s="1">
-        <v>312000</v>
+        <v>317200</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4634,7 +4634,7 @@
         <v>649</v>
       </c>
       <c r="B202" s="1">
-        <v>318000</v>
+        <v>323300</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4642,7 +4642,7 @@
         <v>280</v>
       </c>
       <c r="B203" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4650,7 +4650,7 @@
         <v>696</v>
       </c>
       <c r="B204" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4658,7 +4658,7 @@
         <v>737</v>
       </c>
       <c r="B205" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4666,7 +4666,7 @@
         <v>411</v>
       </c>
       <c r="B206" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4674,7 +4674,7 @@
         <v>281</v>
       </c>
       <c r="B207" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4682,7 +4682,7 @@
         <v>412</v>
       </c>
       <c r="B208" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4690,7 +4690,7 @@
         <v>282</v>
       </c>
       <c r="B209" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4698,7 +4698,7 @@
         <v>283</v>
       </c>
       <c r="B210" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4706,7 +4706,7 @@
         <v>284</v>
       </c>
       <c r="B211" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4714,7 +4714,7 @@
         <v>285</v>
       </c>
       <c r="B212" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4722,7 +4722,7 @@
         <v>286</v>
       </c>
       <c r="B213" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4730,7 +4730,7 @@
         <v>287</v>
       </c>
       <c r="B214" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4738,7 +4738,7 @@
         <v>288</v>
       </c>
       <c r="B215" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4746,7 +4746,7 @@
         <v>289</v>
       </c>
       <c r="B216" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4754,7 +4754,7 @@
         <v>553</v>
       </c>
       <c r="B217" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4762,7 +4762,7 @@
         <v>290</v>
       </c>
       <c r="B218" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4770,7 +4770,7 @@
         <v>738</v>
       </c>
       <c r="B219" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4778,7 +4778,7 @@
         <v>739</v>
       </c>
       <c r="B220" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4786,7 +4786,7 @@
         <v>291</v>
       </c>
       <c r="B221" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4794,7 +4794,7 @@
         <v>292</v>
       </c>
       <c r="B222" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4802,7 +4802,7 @@
         <v>293</v>
       </c>
       <c r="B223" s="1">
-        <v>168000</v>
+        <v>170800</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4810,7 +4810,7 @@
         <v>294</v>
       </c>
       <c r="B224" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4818,7 +4818,7 @@
         <v>572</v>
       </c>
       <c r="B225" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4826,7 +4826,7 @@
         <v>670</v>
       </c>
       <c r="B226" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4834,7 +4834,7 @@
         <v>295</v>
       </c>
       <c r="B227" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4842,7 +4842,7 @@
         <v>671</v>
       </c>
       <c r="B228" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4850,7 +4850,7 @@
         <v>296</v>
       </c>
       <c r="B229" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4858,7 +4858,7 @@
         <v>718</v>
       </c>
       <c r="B230" s="1">
-        <v>33000</v>
+        <v>33550</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4866,7 +4866,7 @@
         <v>719</v>
       </c>
       <c r="B231" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4874,7 +4874,7 @@
         <v>720</v>
       </c>
       <c r="B232" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4882,7 +4882,7 @@
         <v>721</v>
       </c>
       <c r="B233" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4890,7 +4890,7 @@
         <v>617</v>
       </c>
       <c r="B234" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4898,7 +4898,7 @@
         <v>297</v>
       </c>
       <c r="B235" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4906,7 +4906,7 @@
         <v>573</v>
       </c>
       <c r="B236" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4914,7 +4914,7 @@
         <v>298</v>
       </c>
       <c r="B237" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4922,7 +4922,7 @@
         <v>299</v>
       </c>
       <c r="B238" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4930,7 +4930,7 @@
         <v>300</v>
       </c>
       <c r="B239" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4938,7 +4938,7 @@
         <v>301</v>
       </c>
       <c r="B240" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4946,7 +4946,7 @@
         <v>302</v>
       </c>
       <c r="B241" s="1">
-        <v>180000</v>
+        <v>183000</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4954,7 +4954,7 @@
         <v>672</v>
       </c>
       <c r="B242" s="1">
-        <v>180000</v>
+        <v>183000</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4962,7 +4962,7 @@
         <v>303</v>
       </c>
       <c r="B243" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4970,7 +4970,7 @@
         <v>740</v>
       </c>
       <c r="B244" s="1">
-        <v>132000</v>
+        <v>134200</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4978,7 +4978,7 @@
         <v>304</v>
       </c>
       <c r="B245" s="1">
-        <v>66000</v>
+        <v>67100</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4986,7 +4986,7 @@
         <v>305</v>
       </c>
       <c r="B246" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4994,7 +4994,7 @@
         <v>306</v>
       </c>
       <c r="B247" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5002,7 +5002,7 @@
         <v>618</v>
       </c>
       <c r="B248" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5010,7 +5010,7 @@
         <v>307</v>
       </c>
       <c r="B249" s="1">
-        <v>102000</v>
+        <v>103700</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5018,7 +5018,7 @@
         <v>308</v>
       </c>
       <c r="B250" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5026,7 +5026,7 @@
         <v>309</v>
       </c>
       <c r="B251" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5034,7 +5034,7 @@
         <v>310</v>
       </c>
       <c r="B252" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5042,7 +5042,7 @@
         <v>690</v>
       </c>
       <c r="B253" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5050,7 +5050,7 @@
         <v>311</v>
       </c>
       <c r="B254" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5058,7 +5058,7 @@
         <v>312</v>
       </c>
       <c r="B255" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5066,7 +5066,7 @@
         <v>313</v>
       </c>
       <c r="B256" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5074,7 +5074,7 @@
         <v>467</v>
       </c>
       <c r="B257" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5082,7 +5082,7 @@
         <v>741</v>
       </c>
       <c r="B258" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5090,7 +5090,7 @@
         <v>742</v>
       </c>
       <c r="B259" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5098,7 +5098,7 @@
         <v>468</v>
       </c>
       <c r="B260" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5106,7 +5106,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5114,7 +5114,7 @@
         <v>315</v>
       </c>
       <c r="B262" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5122,7 +5122,7 @@
         <v>316</v>
       </c>
       <c r="B263" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5130,7 +5130,7 @@
         <v>414</v>
       </c>
       <c r="B264" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5138,7 +5138,7 @@
         <v>317</v>
       </c>
       <c r="B265" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5146,7 +5146,7 @@
         <v>318</v>
       </c>
       <c r="B266" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5154,7 +5154,7 @@
         <v>605</v>
       </c>
       <c r="B267" s="1">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5162,7 +5162,7 @@
         <v>319</v>
       </c>
       <c r="B268" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5170,7 +5170,7 @@
         <v>320</v>
       </c>
       <c r="B269" s="1">
-        <v>180000</v>
+        <v>183000</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5178,7 +5178,7 @@
         <v>321</v>
       </c>
       <c r="B270" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5186,7 +5186,7 @@
         <v>322</v>
       </c>
       <c r="B271" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5194,7 +5194,7 @@
         <v>323</v>
       </c>
       <c r="B272" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5202,7 +5202,7 @@
         <v>324</v>
       </c>
       <c r="B273" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5210,7 +5210,7 @@
         <v>325</v>
       </c>
       <c r="B274" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5218,7 +5218,7 @@
         <v>326</v>
       </c>
       <c r="B275" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5226,7 +5226,7 @@
         <v>327</v>
       </c>
       <c r="B276" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5234,7 +5234,7 @@
         <v>328</v>
       </c>
       <c r="B277" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5242,7 +5242,7 @@
         <v>329</v>
       </c>
       <c r="B278" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5250,7 +5250,7 @@
         <v>330</v>
       </c>
       <c r="B279" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5258,7 +5258,7 @@
         <v>331</v>
       </c>
       <c r="B280" s="1">
-        <v>78000</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5266,7 +5266,7 @@
         <v>332</v>
       </c>
       <c r="B281" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5274,7 +5274,7 @@
         <v>333</v>
       </c>
       <c r="B282" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5282,7 +5282,7 @@
         <v>334</v>
       </c>
       <c r="B283" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5290,7 +5290,7 @@
         <v>574</v>
       </c>
       <c r="B284" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5298,7 +5298,7 @@
         <v>599</v>
       </c>
       <c r="B285" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5306,7 +5306,7 @@
         <v>600</v>
       </c>
       <c r="B286" s="1">
-        <v>57000</v>
+        <v>57950</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5314,7 +5314,7 @@
         <v>743</v>
       </c>
       <c r="B287" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5322,7 +5322,7 @@
         <v>619</v>
       </c>
       <c r="B288" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5330,7 +5330,7 @@
         <v>335</v>
       </c>
       <c r="B289" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5338,7 +5338,7 @@
         <v>620</v>
       </c>
       <c r="B290" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5346,7 +5346,7 @@
         <v>336</v>
       </c>
       <c r="B291" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5354,7 +5354,7 @@
         <v>337</v>
       </c>
       <c r="B292" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5362,7 +5362,7 @@
         <v>338</v>
       </c>
       <c r="B293" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5370,7 +5370,7 @@
         <v>339</v>
       </c>
       <c r="B294" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5378,7 +5378,7 @@
         <v>340</v>
       </c>
       <c r="B295" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5386,7 +5386,7 @@
         <v>341</v>
       </c>
       <c r="B296" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5394,7 +5394,7 @@
         <v>342</v>
       </c>
       <c r="B297" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5402,7 +5402,7 @@
         <v>343</v>
       </c>
       <c r="B298" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5410,7 +5410,7 @@
         <v>415</v>
       </c>
       <c r="B299" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5418,7 +5418,7 @@
         <v>416</v>
       </c>
       <c r="B300" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5426,7 +5426,7 @@
         <v>601</v>
       </c>
       <c r="B301" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5434,7 +5434,7 @@
         <v>344</v>
       </c>
       <c r="B302" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5442,7 +5442,7 @@
         <v>345</v>
       </c>
       <c r="B303" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5450,7 +5450,7 @@
         <v>346</v>
       </c>
       <c r="B304" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5458,7 +5458,7 @@
         <v>347</v>
       </c>
       <c r="B305" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5466,7 +5466,7 @@
         <v>348</v>
       </c>
       <c r="B306" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5474,7 +5474,7 @@
         <v>349</v>
       </c>
       <c r="B307" s="1">
-        <v>2400</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5482,7 +5482,7 @@
         <v>744</v>
       </c>
       <c r="B308" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5490,7 +5490,7 @@
         <v>673</v>
       </c>
       <c r="B309" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5498,7 +5498,7 @@
         <v>350</v>
       </c>
       <c r="B310" s="1">
-        <v>45000</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5506,7 +5506,7 @@
         <v>351</v>
       </c>
       <c r="B311" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5514,7 +5514,7 @@
         <v>352</v>
       </c>
       <c r="B312" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5522,7 +5522,7 @@
         <v>575</v>
       </c>
       <c r="B313" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5530,7 +5530,7 @@
         <v>353</v>
       </c>
       <c r="B314" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5538,7 +5538,7 @@
         <v>354</v>
       </c>
       <c r="B315" s="1">
-        <v>150000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5546,7 +5546,7 @@
         <v>407</v>
       </c>
       <c r="B316" s="1">
-        <v>330000</v>
+        <v>335500</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5554,7 +5554,7 @@
         <v>355</v>
       </c>
       <c r="B317" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5562,7 +5562,7 @@
         <v>356</v>
       </c>
       <c r="B318" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5570,7 +5570,7 @@
         <v>576</v>
       </c>
       <c r="B319" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5578,7 +5578,7 @@
         <v>357</v>
       </c>
       <c r="B320" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5586,7 +5586,7 @@
         <v>358</v>
       </c>
       <c r="B321" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5594,7 +5594,7 @@
         <v>651</v>
       </c>
       <c r="B322" s="1">
-        <v>2400</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5602,7 +5602,7 @@
         <v>577</v>
       </c>
       <c r="B323" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5610,7 +5610,7 @@
         <v>588</v>
       </c>
       <c r="B324" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5618,7 +5618,7 @@
         <v>359</v>
       </c>
       <c r="B325" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5626,7 +5626,7 @@
         <v>360</v>
       </c>
       <c r="B326" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5634,7 +5634,7 @@
         <v>361</v>
       </c>
       <c r="B327" s="1">
-        <v>2400</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5642,7 +5642,7 @@
         <v>362</v>
       </c>
       <c r="B328" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5650,7 +5650,7 @@
         <v>363</v>
       </c>
       <c r="B329" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5658,7 +5658,7 @@
         <v>364</v>
       </c>
       <c r="B330" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5666,7 +5666,7 @@
         <v>365</v>
       </c>
       <c r="B331" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5674,7 +5674,7 @@
         <v>403</v>
       </c>
       <c r="B332" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5682,7 +5682,7 @@
         <v>546</v>
       </c>
       <c r="B333" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5690,7 +5690,7 @@
         <v>822</v>
       </c>
       <c r="B334" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5698,7 +5698,7 @@
         <v>366</v>
       </c>
       <c r="B335" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5706,7 +5706,7 @@
         <v>556</v>
       </c>
       <c r="B336" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5714,7 +5714,7 @@
         <v>557</v>
       </c>
       <c r="B337" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5722,7 +5722,7 @@
         <v>367</v>
       </c>
       <c r="B338" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5730,7 +5730,7 @@
         <v>368</v>
       </c>
       <c r="B339" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5738,7 +5738,7 @@
         <v>369</v>
       </c>
       <c r="B340" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5746,7 +5746,7 @@
         <v>370</v>
       </c>
       <c r="B341" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5754,7 +5754,7 @@
         <v>371</v>
       </c>
       <c r="B342" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5762,7 +5762,7 @@
         <v>372</v>
       </c>
       <c r="B343" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5770,7 +5770,7 @@
         <v>373</v>
       </c>
       <c r="B344" s="1">
-        <v>2400</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5778,7 +5778,7 @@
         <v>413</v>
       </c>
       <c r="B345" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5786,7 +5786,7 @@
         <v>465</v>
       </c>
       <c r="B346" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5794,7 +5794,7 @@
         <v>621</v>
       </c>
       <c r="B347" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5802,7 +5802,7 @@
         <v>374</v>
       </c>
       <c r="B348" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5810,7 +5810,7 @@
         <v>485</v>
       </c>
       <c r="B349" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5818,7 +5818,7 @@
         <v>469</v>
       </c>
       <c r="B350" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5826,7 +5826,7 @@
         <v>375</v>
       </c>
       <c r="B351" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5834,7 +5834,7 @@
         <v>674</v>
       </c>
       <c r="B352" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5842,7 +5842,7 @@
         <v>675</v>
       </c>
       <c r="B353" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5850,7 +5850,7 @@
         <v>376</v>
       </c>
       <c r="B354" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5858,7 +5858,7 @@
         <v>377</v>
       </c>
       <c r="B355" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5866,7 +5866,7 @@
         <v>378</v>
       </c>
       <c r="B356" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5874,7 +5874,7 @@
         <v>622</v>
       </c>
       <c r="B357" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5882,7 +5882,7 @@
         <v>379</v>
       </c>
       <c r="B358" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5890,7 +5890,7 @@
         <v>470</v>
       </c>
       <c r="B359" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5898,7 +5898,7 @@
         <v>471</v>
       </c>
       <c r="B360" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5906,7 +5906,7 @@
         <v>676</v>
       </c>
       <c r="B361" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5914,7 +5914,7 @@
         <v>380</v>
       </c>
       <c r="B362" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5922,7 +5922,7 @@
         <v>381</v>
       </c>
       <c r="B363" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5930,7 +5930,7 @@
         <v>454</v>
       </c>
       <c r="B364" s="1">
-        <v>2400</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5938,7 +5938,7 @@
         <v>382</v>
       </c>
       <c r="B365" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
   </sheetData>
@@ -5968,7 +5968,7 @@
         <v>486</v>
       </c>
       <c r="B2" s="1">
-        <v>84000</v>
+        <v>85400</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5976,7 +5976,7 @@
         <v>123</v>
       </c>
       <c r="B3" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5984,7 +5984,7 @@
         <v>757</v>
       </c>
       <c r="B4" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5992,7 +5992,7 @@
         <v>578</v>
       </c>
       <c r="B5" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6000,7 +6000,7 @@
         <v>164</v>
       </c>
       <c r="B6" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6008,7 +6008,7 @@
         <v>579</v>
       </c>
       <c r="B7" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6016,7 +6016,7 @@
         <v>589</v>
       </c>
       <c r="B8" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6024,7 +6024,7 @@
         <v>758</v>
       </c>
       <c r="B9" s="1">
-        <v>78000</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6032,7 +6032,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6040,7 +6040,7 @@
         <v>759</v>
       </c>
       <c r="B11" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6048,7 +6048,7 @@
         <v>124</v>
       </c>
       <c r="B12" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6056,7 +6056,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6064,7 +6064,7 @@
         <v>823</v>
       </c>
       <c r="B14" s="1">
-        <v>51000</v>
+        <v>51850</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6072,7 +6072,7 @@
         <v>430</v>
       </c>
       <c r="B15" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6080,7 +6080,7 @@
         <v>163</v>
       </c>
       <c r="B16" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6088,7 +6088,7 @@
         <v>647</v>
       </c>
       <c r="B17" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6096,7 +6096,7 @@
         <v>581</v>
       </c>
       <c r="B18" s="1">
-        <v>66000</v>
+        <v>67100</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6104,7 +6104,7 @@
         <v>648</v>
       </c>
       <c r="B19" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6112,7 +6112,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6120,7 +6120,7 @@
         <v>125</v>
       </c>
       <c r="B21" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6128,7 +6128,7 @@
         <v>478</v>
       </c>
       <c r="B22" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6136,7 +6136,7 @@
         <v>36</v>
       </c>
       <c r="B23" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6144,7 +6144,7 @@
         <v>487</v>
       </c>
       <c r="B24" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6152,7 +6152,7 @@
         <v>488</v>
       </c>
       <c r="B25" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6160,7 +6160,7 @@
         <v>692</v>
       </c>
       <c r="B26" s="1">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6168,7 +6168,7 @@
         <v>406</v>
       </c>
       <c r="B27" s="1">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6176,7 +6176,7 @@
         <v>402</v>
       </c>
       <c r="B28" s="1">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6184,7 +6184,7 @@
         <v>439</v>
       </c>
       <c r="B29" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6192,7 +6192,7 @@
         <v>760</v>
       </c>
       <c r="B30" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6200,7 +6200,7 @@
         <v>489</v>
       </c>
       <c r="B31" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6208,7 +6208,7 @@
         <v>490</v>
       </c>
       <c r="B32" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6216,7 +6216,7 @@
         <v>761</v>
       </c>
       <c r="B33" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6224,7 +6224,7 @@
         <v>12</v>
       </c>
       <c r="B34" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6232,7 +6232,7 @@
         <v>762</v>
       </c>
       <c r="B35" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="1">
-        <v>1500</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6248,7 +6248,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6256,7 +6256,7 @@
         <v>434</v>
       </c>
       <c r="B38" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6264,7 +6264,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6272,7 +6272,7 @@
         <v>491</v>
       </c>
       <c r="B40" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6280,7 +6280,7 @@
         <v>479</v>
       </c>
       <c r="B41" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6288,7 +6288,7 @@
         <v>763</v>
       </c>
       <c r="B42" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6296,7 +6296,7 @@
         <v>438</v>
       </c>
       <c r="B43" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6304,7 +6304,7 @@
         <v>440</v>
       </c>
       <c r="B44" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6312,7 +6312,7 @@
         <v>492</v>
       </c>
       <c r="B45" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6320,7 +6320,7 @@
         <v>493</v>
       </c>
       <c r="B46" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6328,7 +6328,7 @@
         <v>494</v>
       </c>
       <c r="B47" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6336,7 +6336,7 @@
         <v>764</v>
       </c>
       <c r="B48" s="1">
-        <v>210000</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -6344,7 +6344,7 @@
         <v>551</v>
       </c>
       <c r="B49" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -6352,7 +6352,7 @@
         <v>765</v>
       </c>
       <c r="B50" s="1">
-        <v>78000</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -6360,7 +6360,7 @@
         <v>751</v>
       </c>
       <c r="B51" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -6368,7 +6368,7 @@
         <v>722</v>
       </c>
       <c r="B52" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -6376,7 +6376,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -6384,7 +6384,7 @@
         <v>766</v>
       </c>
       <c r="B54" s="1">
-        <v>84000</v>
+        <v>85400</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -6392,7 +6392,7 @@
         <v>495</v>
       </c>
       <c r="B55" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -6400,7 +6400,7 @@
         <v>436</v>
       </c>
       <c r="B56" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -6408,7 +6408,7 @@
         <v>126</v>
       </c>
       <c r="B57" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -6416,7 +6416,7 @@
         <v>496</v>
       </c>
       <c r="B58" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -6424,7 +6424,7 @@
         <v>767</v>
       </c>
       <c r="B59" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -6432,7 +6432,7 @@
         <v>30</v>
       </c>
       <c r="B60" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -6440,7 +6440,7 @@
         <v>427</v>
       </c>
       <c r="B61" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -6448,7 +6448,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -6456,7 +6456,7 @@
         <v>768</v>
       </c>
       <c r="B63" s="1">
-        <v>150000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -6464,7 +6464,7 @@
         <v>769</v>
       </c>
       <c r="B64" s="1">
-        <v>132000</v>
+        <v>134200</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -6472,7 +6472,7 @@
         <v>127</v>
       </c>
       <c r="B65" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -6480,7 +6480,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -6488,7 +6488,7 @@
         <v>116</v>
       </c>
       <c r="B67" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6496,7 +6496,7 @@
         <v>14</v>
       </c>
       <c r="B68" s="1">
-        <v>78000</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6504,7 +6504,7 @@
         <v>770</v>
       </c>
       <c r="B69" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -6512,7 +6512,7 @@
         <v>771</v>
       </c>
       <c r="B70" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -6520,7 +6520,7 @@
         <v>426</v>
       </c>
       <c r="B71" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -6528,7 +6528,7 @@
         <v>552</v>
       </c>
       <c r="B72" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -6536,7 +6536,7 @@
         <v>825</v>
       </c>
       <c r="B73" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -6544,7 +6544,7 @@
         <v>497</v>
       </c>
       <c r="B74" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -6552,7 +6552,7 @@
         <v>498</v>
       </c>
       <c r="B75" s="1">
-        <v>33000</v>
+        <v>33550</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -6560,7 +6560,7 @@
         <v>772</v>
       </c>
       <c r="B76" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -6568,7 +6568,7 @@
         <v>773</v>
       </c>
       <c r="B77" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -6576,7 +6576,7 @@
         <v>586</v>
       </c>
       <c r="B78" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -6584,7 +6584,7 @@
         <v>15</v>
       </c>
       <c r="B79" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -6592,7 +6592,7 @@
         <v>16</v>
       </c>
       <c r="B80" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -6600,7 +6600,7 @@
         <v>580</v>
       </c>
       <c r="B81" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -6608,7 +6608,7 @@
         <v>688</v>
       </c>
       <c r="B82" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -6616,7 +6616,7 @@
         <v>774</v>
       </c>
       <c r="B83" s="1">
-        <v>2400</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -6624,7 +6624,7 @@
         <v>484</v>
       </c>
       <c r="B84" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -6632,7 +6632,7 @@
         <v>775</v>
       </c>
       <c r="B85" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -6640,7 +6640,7 @@
         <v>735</v>
       </c>
       <c r="B86" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -6648,7 +6648,7 @@
         <v>3</v>
       </c>
       <c r="B87" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -6656,7 +6656,7 @@
         <v>17</v>
       </c>
       <c r="B88" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -6664,7 +6664,7 @@
         <v>128</v>
       </c>
       <c r="B89" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -6672,7 +6672,7 @@
         <v>715</v>
       </c>
       <c r="B90" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -6680,7 +6680,7 @@
         <v>499</v>
       </c>
       <c r="B91" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -6688,7 +6688,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -6696,7 +6696,7 @@
         <v>623</v>
       </c>
       <c r="B93" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -6704,7 +6704,7 @@
         <v>776</v>
       </c>
       <c r="B94" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -6712,7 +6712,7 @@
         <v>18</v>
       </c>
       <c r="B95" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -6720,7 +6720,7 @@
         <v>19</v>
       </c>
       <c r="B96" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -6728,7 +6728,7 @@
         <v>500</v>
       </c>
       <c r="B97" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -6736,7 +6736,7 @@
         <v>501</v>
       </c>
       <c r="B98" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -6744,7 +6744,7 @@
         <v>25</v>
       </c>
       <c r="B99" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -6752,7 +6752,7 @@
         <v>553</v>
       </c>
       <c r="B100" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -6760,7 +6760,7 @@
         <v>777</v>
       </c>
       <c r="B101" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -6768,7 +6768,7 @@
         <v>778</v>
       </c>
       <c r="B102" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -6776,7 +6776,7 @@
         <v>779</v>
       </c>
       <c r="B103" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -6784,7 +6784,7 @@
         <v>780</v>
       </c>
       <c r="B104" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -6792,7 +6792,7 @@
         <v>129</v>
       </c>
       <c r="B105" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -6800,7 +6800,7 @@
         <v>502</v>
       </c>
       <c r="B106" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -6808,7 +6808,7 @@
         <v>781</v>
       </c>
       <c r="B107" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -6816,7 +6816,7 @@
         <v>752</v>
       </c>
       <c r="B108" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -6824,7 +6824,7 @@
         <v>723</v>
       </c>
       <c r="B109" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -6832,7 +6832,7 @@
         <v>720</v>
       </c>
       <c r="B110" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -6840,7 +6840,7 @@
         <v>721</v>
       </c>
       <c r="B111" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -6848,7 +6848,7 @@
         <v>503</v>
       </c>
       <c r="B112" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -6856,7 +6856,7 @@
         <v>100</v>
       </c>
       <c r="B113" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -6864,7 +6864,7 @@
         <v>826</v>
       </c>
       <c r="B114" s="1">
-        <v>210000</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -6872,7 +6872,7 @@
         <v>654</v>
       </c>
       <c r="B115" s="1">
-        <v>210000</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -6880,7 +6880,7 @@
         <v>24</v>
       </c>
       <c r="B116" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -6888,7 +6888,7 @@
         <v>782</v>
       </c>
       <c r="B117" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -6896,7 +6896,7 @@
         <v>740</v>
       </c>
       <c r="B118" s="1">
-        <v>132000</v>
+        <v>134200</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -6904,7 +6904,7 @@
         <v>20</v>
       </c>
       <c r="B119" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -6912,7 +6912,7 @@
         <v>433</v>
       </c>
       <c r="B120" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -6920,7 +6920,7 @@
         <v>783</v>
       </c>
       <c r="B121" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -6928,7 +6928,7 @@
         <v>115</v>
       </c>
       <c r="B122" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -6936,7 +6936,7 @@
         <v>504</v>
       </c>
       <c r="B123" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -6944,7 +6944,7 @@
         <v>505</v>
       </c>
       <c r="B124" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -6952,7 +6952,7 @@
         <v>784</v>
       </c>
       <c r="B125" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -6960,7 +6960,7 @@
         <v>716</v>
       </c>
       <c r="B126" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -6968,7 +6968,7 @@
         <v>785</v>
       </c>
       <c r="B127" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -6976,7 +6976,7 @@
         <v>506</v>
       </c>
       <c r="B128" s="1">
-        <v>45000</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -6984,7 +6984,7 @@
         <v>21</v>
       </c>
       <c r="B129" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -6992,7 +6992,7 @@
         <v>756</v>
       </c>
       <c r="B130" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7000,7 +7000,7 @@
         <v>480</v>
       </c>
       <c r="B131" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7008,7 +7008,7 @@
         <v>786</v>
       </c>
       <c r="B132" s="1">
-        <v>78000</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7016,7 +7016,7 @@
         <v>787</v>
       </c>
       <c r="B133" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7024,7 +7024,7 @@
         <v>788</v>
       </c>
       <c r="B134" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7032,7 +7032,7 @@
         <v>789</v>
       </c>
       <c r="B135" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7040,7 +7040,7 @@
         <v>73</v>
       </c>
       <c r="B136" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7048,7 +7048,7 @@
         <v>74</v>
       </c>
       <c r="B137" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7056,7 +7056,7 @@
         <v>162</v>
       </c>
       <c r="B138" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7064,7 +7064,7 @@
         <v>790</v>
       </c>
       <c r="B139" s="1">
-        <v>45000</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7072,7 +7072,7 @@
         <v>130</v>
       </c>
       <c r="B140" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7080,7 +7080,7 @@
         <v>791</v>
       </c>
       <c r="B141" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7088,7 +7088,7 @@
         <v>709</v>
       </c>
       <c r="B142" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7096,7 +7096,7 @@
         <v>432</v>
       </c>
       <c r="B143" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7104,7 +7104,7 @@
         <v>507</v>
       </c>
       <c r="B144" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7112,7 +7112,7 @@
         <v>508</v>
       </c>
       <c r="B145" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7120,7 +7120,7 @@
         <v>437</v>
       </c>
       <c r="B146" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7128,7 +7128,7 @@
         <v>509</v>
       </c>
       <c r="B147" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7136,7 +7136,7 @@
         <v>792</v>
       </c>
       <c r="B148" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7144,7 +7144,7 @@
         <v>4</v>
       </c>
       <c r="B149" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7152,7 +7152,7 @@
         <v>793</v>
       </c>
       <c r="B150" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7160,7 +7160,7 @@
         <v>650</v>
       </c>
       <c r="B151" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7168,7 +7168,7 @@
         <v>651</v>
       </c>
       <c r="B152" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7176,7 +7176,7 @@
         <v>588</v>
       </c>
       <c r="B153" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7184,7 +7184,7 @@
         <v>554</v>
       </c>
       <c r="B154" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7192,7 +7192,7 @@
         <v>510</v>
       </c>
       <c r="B155" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7200,7 +7200,7 @@
         <v>403</v>
       </c>
       <c r="B156" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7208,7 +7208,7 @@
         <v>546</v>
       </c>
       <c r="B157" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7216,7 +7216,7 @@
         <v>441</v>
       </c>
       <c r="B158" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7224,7 +7224,7 @@
         <v>556</v>
       </c>
       <c r="B159" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7232,7 +7232,7 @@
         <v>557</v>
       </c>
       <c r="B160" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7240,7 +7240,7 @@
         <v>794</v>
       </c>
       <c r="B161" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7248,7 +7248,7 @@
         <v>435</v>
       </c>
       <c r="B162" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7256,7 +7256,7 @@
         <v>795</v>
       </c>
       <c r="B163" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7264,7 +7264,7 @@
         <v>796</v>
       </c>
       <c r="B164" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -7272,7 +7272,7 @@
         <v>624</v>
       </c>
       <c r="B165" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -7280,7 +7280,7 @@
         <v>10</v>
       </c>
       <c r="B166" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -7288,7 +7288,7 @@
         <v>797</v>
       </c>
       <c r="B167" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
   </sheetData>
@@ -7318,7 +7318,7 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>84000</v>
+        <v>85400</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7326,7 +7326,7 @@
         <v>745</v>
       </c>
       <c r="B3" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7334,7 +7334,7 @@
         <v>746</v>
       </c>
       <c r="B4" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7342,7 +7342,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1">
-        <v>84000</v>
+        <v>85400</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7350,7 +7350,7 @@
         <v>747</v>
       </c>
       <c r="B6" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7358,7 +7358,7 @@
         <v>122</v>
       </c>
       <c r="B7" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7366,7 +7366,7 @@
         <v>131</v>
       </c>
       <c r="B8" s="1">
-        <v>150000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7374,7 +7374,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7382,7 +7382,7 @@
         <v>567</v>
       </c>
       <c r="B10" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7390,7 +7390,7 @@
         <v>82</v>
       </c>
       <c r="B11" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7398,7 +7398,7 @@
         <v>165</v>
       </c>
       <c r="B12" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7406,7 +7406,7 @@
         <v>589</v>
       </c>
       <c r="B13" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7414,7 +7414,7 @@
         <v>798</v>
       </c>
       <c r="B14" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7422,7 +7422,7 @@
         <v>132</v>
       </c>
       <c r="B15" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -7430,7 +7430,7 @@
         <v>133</v>
       </c>
       <c r="B16" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -7438,7 +7438,7 @@
         <v>753</v>
       </c>
       <c r="B17" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -7446,7 +7446,7 @@
         <v>625</v>
       </c>
       <c r="B18" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -7454,7 +7454,7 @@
         <v>823</v>
       </c>
       <c r="B19" s="1">
-        <v>51000</v>
+        <v>51850</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7462,7 +7462,7 @@
         <v>430</v>
       </c>
       <c r="B20" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7470,7 +7470,7 @@
         <v>163</v>
       </c>
       <c r="B21" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7478,7 +7478,7 @@
         <v>647</v>
       </c>
       <c r="B22" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7486,7 +7486,7 @@
         <v>581</v>
       </c>
       <c r="B23" s="1">
-        <v>66000</v>
+        <v>67100</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7494,7 +7494,7 @@
         <v>648</v>
       </c>
       <c r="B24" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7502,7 +7502,7 @@
         <v>83</v>
       </c>
       <c r="B25" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7510,7 +7510,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7518,7 +7518,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7526,7 +7526,7 @@
         <v>121</v>
       </c>
       <c r="B28" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7534,7 +7534,7 @@
         <v>134</v>
       </c>
       <c r="B29" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7542,7 +7542,7 @@
         <v>698</v>
       </c>
       <c r="B30" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7550,7 +7550,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7558,7 +7558,7 @@
         <v>477</v>
       </c>
       <c r="B32" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7566,7 +7566,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7574,7 +7574,7 @@
         <v>158</v>
       </c>
       <c r="B34" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7582,7 +7582,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7590,7 +7590,7 @@
         <v>692</v>
       </c>
       <c r="B36" s="1">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7598,7 +7598,7 @@
         <v>406</v>
       </c>
       <c r="B37" s="1">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7606,7 +7606,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="1">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7614,7 +7614,7 @@
         <v>626</v>
       </c>
       <c r="B39" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7622,7 +7622,7 @@
         <v>627</v>
       </c>
       <c r="B40" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7630,7 +7630,7 @@
         <v>628</v>
       </c>
       <c r="B41" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7638,7 +7638,7 @@
         <v>629</v>
       </c>
       <c r="B42" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -7646,7 +7646,7 @@
         <v>511</v>
       </c>
       <c r="B43" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7654,7 +7654,7 @@
         <v>85</v>
       </c>
       <c r="B44" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -7662,7 +7662,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -7670,7 +7670,7 @@
         <v>86</v>
       </c>
       <c r="B46" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7678,7 +7678,7 @@
         <v>135</v>
       </c>
       <c r="B47" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7686,7 +7686,7 @@
         <v>136</v>
       </c>
       <c r="B48" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -7694,7 +7694,7 @@
         <v>87</v>
       </c>
       <c r="B49" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -7702,7 +7702,7 @@
         <v>444</v>
       </c>
       <c r="B50" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -7710,7 +7710,7 @@
         <v>512</v>
       </c>
       <c r="B51" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -7718,7 +7718,7 @@
         <v>137</v>
       </c>
       <c r="B52" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -7726,7 +7726,7 @@
         <v>513</v>
       </c>
       <c r="B53" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -7734,7 +7734,7 @@
         <v>451</v>
       </c>
       <c r="B54" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -7742,7 +7742,7 @@
         <v>452</v>
       </c>
       <c r="B55" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -7750,7 +7750,7 @@
         <v>138</v>
       </c>
       <c r="B56" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -7758,7 +7758,7 @@
         <v>699</v>
       </c>
       <c r="B57" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -7766,7 +7766,7 @@
         <v>583</v>
       </c>
       <c r="B58" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -7774,7 +7774,7 @@
         <v>584</v>
       </c>
       <c r="B59" s="1">
-        <v>45000</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -7782,7 +7782,7 @@
         <v>139</v>
       </c>
       <c r="B60" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -7790,7 +7790,7 @@
         <v>551</v>
       </c>
       <c r="B61" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -7798,7 +7798,7 @@
         <v>140</v>
       </c>
       <c r="B62" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -7806,7 +7806,7 @@
         <v>89</v>
       </c>
       <c r="B63" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -7814,7 +7814,7 @@
         <v>88</v>
       </c>
       <c r="B64" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -7822,7 +7822,7 @@
         <v>559</v>
       </c>
       <c r="B65" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -7830,7 +7830,7 @@
         <v>722</v>
       </c>
       <c r="B66" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -7838,7 +7838,7 @@
         <v>118</v>
       </c>
       <c r="B67" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -7846,7 +7846,7 @@
         <v>799</v>
       </c>
       <c r="B68" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -7854,7 +7854,7 @@
         <v>39</v>
       </c>
       <c r="B69" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -7862,7 +7862,7 @@
         <v>40</v>
       </c>
       <c r="B70" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -7870,7 +7870,7 @@
         <v>800</v>
       </c>
       <c r="B71" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -7878,7 +7878,7 @@
         <v>120</v>
       </c>
       <c r="B72" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7886,7 +7886,7 @@
         <v>41</v>
       </c>
       <c r="B73" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7894,7 +7894,7 @@
         <v>42</v>
       </c>
       <c r="B74" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7902,7 +7902,7 @@
         <v>43</v>
       </c>
       <c r="B75" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7910,7 +7910,7 @@
         <v>44</v>
       </c>
       <c r="B76" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7918,7 +7918,7 @@
         <v>45</v>
       </c>
       <c r="B77" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7926,7 +7926,7 @@
         <v>46</v>
       </c>
       <c r="B78" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7934,7 +7934,7 @@
         <v>687</v>
       </c>
       <c r="B79" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7942,7 +7942,7 @@
         <v>90</v>
       </c>
       <c r="B80" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7950,7 +7950,7 @@
         <v>32</v>
       </c>
       <c r="B81" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7958,7 +7958,7 @@
         <v>27</v>
       </c>
       <c r="B82" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7966,7 +7966,7 @@
         <v>33</v>
       </c>
       <c r="B83" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7974,7 +7974,7 @@
         <v>141</v>
       </c>
       <c r="B84" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7982,7 +7982,7 @@
         <v>49</v>
       </c>
       <c r="B85" s="1">
-        <v>150000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7990,7 +7990,7 @@
         <v>48</v>
       </c>
       <c r="B86" s="1">
-        <v>150000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7998,7 +7998,7 @@
         <v>47</v>
       </c>
       <c r="B87" s="1">
-        <v>138000</v>
+        <v>140300</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -8006,7 +8006,7 @@
         <v>50</v>
       </c>
       <c r="B88" s="1">
-        <v>150000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -8014,7 +8014,7 @@
         <v>51</v>
       </c>
       <c r="B89" s="1">
-        <v>150000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -8022,7 +8022,7 @@
         <v>474</v>
       </c>
       <c r="B90" s="1">
-        <v>150000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -8030,7 +8030,7 @@
         <v>55</v>
       </c>
       <c r="B91" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -8038,7 +8038,7 @@
         <v>52</v>
       </c>
       <c r="B92" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -8046,7 +8046,7 @@
         <v>53</v>
       </c>
       <c r="B93" s="1">
-        <v>132000</v>
+        <v>134200</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -8054,7 +8054,7 @@
         <v>54</v>
       </c>
       <c r="B94" s="1">
-        <v>132000</v>
+        <v>134200</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -8062,7 +8062,7 @@
         <v>56</v>
       </c>
       <c r="B95" s="1">
-        <v>132000</v>
+        <v>134200</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -8070,7 +8070,7 @@
         <v>475</v>
       </c>
       <c r="B96" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -8078,7 +8078,7 @@
         <v>514</v>
       </c>
       <c r="B97" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -8086,7 +8086,7 @@
         <v>700</v>
       </c>
       <c r="B98" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -8094,7 +8094,7 @@
         <v>701</v>
       </c>
       <c r="B99" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -8102,7 +8102,7 @@
         <v>142</v>
       </c>
       <c r="B100" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -8110,7 +8110,7 @@
         <v>801</v>
       </c>
       <c r="B101" s="1">
-        <v>84000</v>
+        <v>85400</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -8118,7 +8118,7 @@
         <v>544</v>
       </c>
       <c r="B102" s="1">
-        <v>84000</v>
+        <v>85400</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -8126,7 +8126,7 @@
         <v>802</v>
       </c>
       <c r="B103" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -8134,7 +8134,7 @@
         <v>643</v>
       </c>
       <c r="B104" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -8142,7 +8142,7 @@
         <v>515</v>
       </c>
       <c r="B105" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -8150,7 +8150,7 @@
         <v>428</v>
       </c>
       <c r="B106" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -8158,7 +8158,7 @@
         <v>693</v>
       </c>
       <c r="B107" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -8166,7 +8166,7 @@
         <v>552</v>
       </c>
       <c r="B108" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -8174,7 +8174,7 @@
         <v>825</v>
       </c>
       <c r="B109" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -8182,7 +8182,7 @@
         <v>702</v>
       </c>
       <c r="B110" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -8190,7 +8190,7 @@
         <v>93</v>
       </c>
       <c r="B111" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -8198,7 +8198,7 @@
         <v>92</v>
       </c>
       <c r="B112" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -8206,7 +8206,7 @@
         <v>91</v>
       </c>
       <c r="B113" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -8214,7 +8214,7 @@
         <v>94</v>
       </c>
       <c r="B114" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -8222,7 +8222,7 @@
         <v>585</v>
       </c>
       <c r="B115" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -8230,7 +8230,7 @@
         <v>646</v>
       </c>
       <c r="B116" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -8238,7 +8238,7 @@
         <v>560</v>
       </c>
       <c r="B117" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -8246,7 +8246,7 @@
         <v>57</v>
       </c>
       <c r="B118" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -8254,7 +8254,7 @@
         <v>58</v>
       </c>
       <c r="B119" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -8262,7 +8262,7 @@
         <v>59</v>
       </c>
       <c r="B120" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -8270,7 +8270,7 @@
         <v>561</v>
       </c>
       <c r="B121" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -8278,7 +8278,7 @@
         <v>562</v>
       </c>
       <c r="B122" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -8286,7 +8286,7 @@
         <v>677</v>
       </c>
       <c r="B123" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -8294,7 +8294,7 @@
         <v>685</v>
       </c>
       <c r="B124" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -8302,7 +8302,7 @@
         <v>686</v>
       </c>
       <c r="B125" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -8310,7 +8310,7 @@
         <v>484</v>
       </c>
       <c r="B126" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -8318,7 +8318,7 @@
         <v>735</v>
       </c>
       <c r="B127" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -8326,7 +8326,7 @@
         <v>60</v>
       </c>
       <c r="B128" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -8334,7 +8334,7 @@
         <v>61</v>
       </c>
       <c r="B129" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -8342,7 +8342,7 @@
         <v>157</v>
       </c>
       <c r="B130" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -8350,7 +8350,7 @@
         <v>62</v>
       </c>
       <c r="B131" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -8358,7 +8358,7 @@
         <v>754</v>
       </c>
       <c r="B132" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -8366,7 +8366,7 @@
         <v>694</v>
       </c>
       <c r="B133" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -8374,7 +8374,7 @@
         <v>563</v>
       </c>
       <c r="B134" s="1">
-        <v>84000</v>
+        <v>85400</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -8382,7 +8382,7 @@
         <v>697</v>
       </c>
       <c r="B135" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -8390,7 +8390,7 @@
         <v>455</v>
       </c>
       <c r="B136" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -8398,7 +8398,7 @@
         <v>623</v>
       </c>
       <c r="B137" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -8406,7 +8406,7 @@
         <v>630</v>
       </c>
       <c r="B138" s="1">
-        <v>330000</v>
+        <v>335500</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -8414,7 +8414,7 @@
         <v>631</v>
       </c>
       <c r="B139" s="1">
-        <v>342000</v>
+        <v>347700</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -8422,7 +8422,7 @@
         <v>449</v>
       </c>
       <c r="B140" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -8430,7 +8430,7 @@
         <v>448</v>
       </c>
       <c r="B141" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -8438,7 +8438,7 @@
         <v>450</v>
       </c>
       <c r="B142" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -8446,7 +8446,7 @@
         <v>447</v>
       </c>
       <c r="B143" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -8454,7 +8454,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -8462,7 +8462,7 @@
         <v>446</v>
       </c>
       <c r="B145" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -8470,7 +8470,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -8478,7 +8478,7 @@
         <v>591</v>
       </c>
       <c r="B147" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -8486,7 +8486,7 @@
         <v>96</v>
       </c>
       <c r="B148" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -8494,7 +8494,7 @@
         <v>95</v>
       </c>
       <c r="B149" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -8502,7 +8502,7 @@
         <v>97</v>
       </c>
       <c r="B150" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -8510,7 +8510,7 @@
         <v>553</v>
       </c>
       <c r="B151" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -8518,7 +8518,7 @@
         <v>803</v>
       </c>
       <c r="B152" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -8526,7 +8526,7 @@
         <v>804</v>
       </c>
       <c r="B153" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -8534,7 +8534,7 @@
         <v>145</v>
       </c>
       <c r="B154" s="1">
-        <v>150000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -8542,7 +8542,7 @@
         <v>119</v>
       </c>
       <c r="B155" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -8550,7 +8550,7 @@
         <v>703</v>
       </c>
       <c r="B156" s="1">
-        <v>45000</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -8558,7 +8558,7 @@
         <v>704</v>
       </c>
       <c r="B157" s="1">
-        <v>45000</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -8566,7 +8566,7 @@
         <v>98</v>
       </c>
       <c r="B158" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -8574,7 +8574,7 @@
         <v>63</v>
       </c>
       <c r="B159" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -8582,7 +8582,7 @@
         <v>472</v>
       </c>
       <c r="B160" s="1">
-        <v>84000</v>
+        <v>85400</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -8590,7 +8590,7 @@
         <v>99</v>
       </c>
       <c r="B161" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -8598,7 +8598,7 @@
         <v>720</v>
       </c>
       <c r="B162" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -8606,7 +8606,7 @@
         <v>724</v>
       </c>
       <c r="B163" s="1">
-        <v>45000</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -8614,7 +8614,7 @@
         <v>721</v>
       </c>
       <c r="B164" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -8622,7 +8622,7 @@
         <v>725</v>
       </c>
       <c r="B165" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -8630,7 +8630,7 @@
         <v>695</v>
       </c>
       <c r="B166" s="1">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -8638,7 +8638,7 @@
         <v>101</v>
       </c>
       <c r="B167" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -8646,7 +8646,7 @@
         <v>102</v>
       </c>
       <c r="B168" s="1">
-        <v>138000</v>
+        <v>140300</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -8654,7 +8654,7 @@
         <v>103</v>
       </c>
       <c r="B169" s="1">
-        <v>210000</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -8662,7 +8662,7 @@
         <v>632</v>
       </c>
       <c r="B170" s="1">
-        <v>210000</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -8670,7 +8670,7 @@
         <v>633</v>
       </c>
       <c r="B171" s="1">
-        <v>216000</v>
+        <v>219600</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -8678,7 +8678,7 @@
         <v>678</v>
       </c>
       <c r="B172" s="1">
-        <v>222000</v>
+        <v>225700</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -8686,7 +8686,7 @@
         <v>679</v>
       </c>
       <c r="B173" s="1">
-        <v>210000</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -8694,7 +8694,7 @@
         <v>680</v>
       </c>
       <c r="B174" s="1">
-        <v>210000</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8702,7 +8702,7 @@
         <v>681</v>
       </c>
       <c r="B175" s="1">
-        <v>210000</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -8710,7 +8710,7 @@
         <v>740</v>
       </c>
       <c r="B176" s="1">
-        <v>132000</v>
+        <v>134200</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -8718,7 +8718,7 @@
         <v>23</v>
       </c>
       <c r="B177" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -8726,7 +8726,7 @@
         <v>442</v>
       </c>
       <c r="B178" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -8734,7 +8734,7 @@
         <v>564</v>
       </c>
       <c r="B179" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -8742,7 +8742,7 @@
         <v>146</v>
       </c>
       <c r="B180" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -8750,7 +8750,7 @@
         <v>147</v>
       </c>
       <c r="B181" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -8758,7 +8758,7 @@
         <v>755</v>
       </c>
       <c r="B182" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -8766,7 +8766,7 @@
         <v>705</v>
       </c>
       <c r="B183" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -8774,7 +8774,7 @@
         <v>652</v>
       </c>
       <c r="B184" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -8782,7 +8782,7 @@
         <v>805</v>
       </c>
       <c r="B185" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -8790,7 +8790,7 @@
         <v>748</v>
       </c>
       <c r="B186" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -8798,7 +8798,7 @@
         <v>148</v>
       </c>
       <c r="B187" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -8806,7 +8806,7 @@
         <v>706</v>
       </c>
       <c r="B188" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -8814,7 +8814,7 @@
         <v>516</v>
       </c>
       <c r="B189" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -8822,7 +8822,7 @@
         <v>749</v>
       </c>
       <c r="B190" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -8830,7 +8830,7 @@
         <v>149</v>
       </c>
       <c r="B191" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -8838,7 +8838,7 @@
         <v>565</v>
       </c>
       <c r="B192" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -8846,7 +8846,7 @@
         <v>707</v>
       </c>
       <c r="B193" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -8854,7 +8854,7 @@
         <v>150</v>
       </c>
       <c r="B194" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -8862,7 +8862,7 @@
         <v>104</v>
       </c>
       <c r="B195" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -8870,7 +8870,7 @@
         <v>517</v>
       </c>
       <c r="B196" s="1">
-        <v>45000</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -8878,7 +8878,7 @@
         <v>151</v>
       </c>
       <c r="B197" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -8886,7 +8886,7 @@
         <v>481</v>
       </c>
       <c r="B198" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -8894,7 +8894,7 @@
         <v>708</v>
       </c>
       <c r="B199" s="1">
-        <v>102000</v>
+        <v>103700</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -8902,7 +8902,7 @@
         <v>64</v>
       </c>
       <c r="B200" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -8910,7 +8910,7 @@
         <v>152</v>
       </c>
       <c r="B201" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -8918,7 +8918,7 @@
         <v>65</v>
       </c>
       <c r="B202" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -8926,7 +8926,7 @@
         <v>545</v>
       </c>
       <c r="B203" s="1">
-        <v>84000</v>
+        <v>85400</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -8934,7 +8934,7 @@
         <v>547</v>
       </c>
       <c r="B204" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -8942,7 +8942,7 @@
         <v>66</v>
       </c>
       <c r="B205" s="1">
-        <v>78000</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -8950,7 +8950,7 @@
         <v>67</v>
       </c>
       <c r="B206" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -8958,7 +8958,7 @@
         <v>68</v>
       </c>
       <c r="B207" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -8966,7 +8966,7 @@
         <v>69</v>
       </c>
       <c r="B208" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -8974,7 +8974,7 @@
         <v>70</v>
       </c>
       <c r="B209" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -8982,7 +8982,7 @@
         <v>71</v>
       </c>
       <c r="B210" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -8990,7 +8990,7 @@
         <v>72</v>
       </c>
       <c r="B211" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -8998,7 +8998,7 @@
         <v>473</v>
       </c>
       <c r="B212" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -9006,7 +9006,7 @@
         <v>160</v>
       </c>
       <c r="B213" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -9014,7 +9014,7 @@
         <v>161</v>
       </c>
       <c r="B214" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -9022,7 +9022,7 @@
         <v>75</v>
       </c>
       <c r="B215" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -9030,7 +9030,7 @@
         <v>159</v>
       </c>
       <c r="B216" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -9038,7 +9038,7 @@
         <v>107</v>
       </c>
       <c r="B217" s="1">
-        <v>150000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -9046,7 +9046,7 @@
         <v>108</v>
       </c>
       <c r="B218" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -9054,7 +9054,7 @@
         <v>110</v>
       </c>
       <c r="B219" s="1">
-        <v>120000</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -9062,7 +9062,7 @@
         <v>105</v>
       </c>
       <c r="B220" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -9070,7 +9070,7 @@
         <v>106</v>
       </c>
       <c r="B221" s="1">
-        <v>90000</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -9078,7 +9078,7 @@
         <v>109</v>
       </c>
       <c r="B222" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -9086,7 +9086,7 @@
         <v>111</v>
       </c>
       <c r="B223" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -9094,7 +9094,7 @@
         <v>153</v>
       </c>
       <c r="B224" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -9102,7 +9102,7 @@
         <v>154</v>
       </c>
       <c r="B225" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -9110,7 +9110,7 @@
         <v>76</v>
       </c>
       <c r="B226" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -9118,7 +9118,7 @@
         <v>77</v>
       </c>
       <c r="B227" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -9126,7 +9126,7 @@
         <v>714</v>
       </c>
       <c r="B228" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -9134,7 +9134,7 @@
         <v>78</v>
       </c>
       <c r="B229" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -9142,7 +9142,7 @@
         <v>443</v>
       </c>
       <c r="B230" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -9150,7 +9150,7 @@
         <v>79</v>
       </c>
       <c r="B231" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -9158,7 +9158,7 @@
         <v>518</v>
       </c>
       <c r="B232" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -9166,7 +9166,7 @@
         <v>80</v>
       </c>
       <c r="B233" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -9174,7 +9174,7 @@
         <v>81</v>
       </c>
       <c r="B234" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -9182,7 +9182,7 @@
         <v>519</v>
       </c>
       <c r="B235" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -9190,7 +9190,7 @@
         <v>113</v>
       </c>
       <c r="B236" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -9198,7 +9198,7 @@
         <v>114</v>
       </c>
       <c r="B237" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -9206,7 +9206,7 @@
         <v>453</v>
       </c>
       <c r="B238" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -9214,7 +9214,7 @@
         <v>710</v>
       </c>
       <c r="B239" s="1">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -9222,7 +9222,7 @@
         <v>750</v>
       </c>
       <c r="B240" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -9230,7 +9230,7 @@
         <v>650</v>
       </c>
       <c r="B241" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -9238,7 +9238,7 @@
         <v>588</v>
       </c>
       <c r="B242" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -9246,7 +9246,7 @@
         <v>555</v>
       </c>
       <c r="B243" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -9254,7 +9254,7 @@
         <v>117</v>
       </c>
       <c r="B244" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -9262,7 +9262,7 @@
         <v>403</v>
       </c>
       <c r="B245" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -9270,7 +9270,7 @@
         <v>546</v>
       </c>
       <c r="B246" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -9278,7 +9278,7 @@
         <v>568</v>
       </c>
       <c r="B247" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -9286,7 +9286,7 @@
         <v>566</v>
       </c>
       <c r="B248" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -9294,7 +9294,7 @@
         <v>556</v>
       </c>
       <c r="B249" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -9302,7 +9302,7 @@
         <v>557</v>
       </c>
       <c r="B250" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -9310,7 +9310,7 @@
         <v>634</v>
       </c>
       <c r="B251" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -9318,7 +9318,7 @@
         <v>711</v>
       </c>
       <c r="B252" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -9326,7 +9326,7 @@
         <v>712</v>
       </c>
       <c r="B253" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -9334,7 +9334,7 @@
         <v>558</v>
       </c>
       <c r="B254" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -9342,7 +9342,7 @@
         <v>635</v>
       </c>
       <c r="B255" s="1">
-        <v>138000</v>
+        <v>140300</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -9350,7 +9350,7 @@
         <v>713</v>
       </c>
       <c r="B256" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -9358,7 +9358,7 @@
         <v>794</v>
       </c>
       <c r="B257" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -9366,7 +9366,7 @@
         <v>445</v>
       </c>
       <c r="B258" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -9374,7 +9374,7 @@
         <v>682</v>
       </c>
       <c r="B259" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -9382,7 +9382,7 @@
         <v>112</v>
       </c>
       <c r="B260" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -9390,7 +9390,7 @@
         <v>155</v>
       </c>
       <c r="B261" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -9398,7 +9398,7 @@
         <v>156</v>
       </c>
       <c r="B262" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
   </sheetData>
@@ -9428,7 +9428,7 @@
         <v>592</v>
       </c>
       <c r="B2" s="1">
-        <v>108000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9436,7 +9436,7 @@
         <v>806</v>
       </c>
       <c r="B3" s="1">
-        <v>81000</v>
+        <v>82350</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9444,7 +9444,7 @@
         <v>807</v>
       </c>
       <c r="B4" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9452,7 +9452,7 @@
         <v>589</v>
       </c>
       <c r="B5" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9460,7 +9460,7 @@
         <v>808</v>
       </c>
       <c r="B6" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9468,7 +9468,7 @@
         <v>581</v>
       </c>
       <c r="B7" s="1">
-        <v>66000</v>
+        <v>67100</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9476,7 +9476,7 @@
         <v>648</v>
       </c>
       <c r="B8" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9484,7 +9484,7 @@
         <v>520</v>
       </c>
       <c r="B9" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -9492,7 +9492,7 @@
         <v>521</v>
       </c>
       <c r="B10" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9500,7 +9500,7 @@
         <v>522</v>
       </c>
       <c r="B11" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9508,7 +9508,7 @@
         <v>523</v>
       </c>
       <c r="B12" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -9516,7 +9516,7 @@
         <v>809</v>
       </c>
       <c r="B13" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -9524,7 +9524,7 @@
         <v>551</v>
       </c>
       <c r="B14" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -9532,7 +9532,7 @@
         <v>722</v>
       </c>
       <c r="B15" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -9540,7 +9540,7 @@
         <v>524</v>
       </c>
       <c r="B16" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -9548,7 +9548,7 @@
         <v>525</v>
       </c>
       <c r="B17" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -9556,7 +9556,7 @@
         <v>691</v>
       </c>
       <c r="B18" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -9564,7 +9564,7 @@
         <v>526</v>
       </c>
       <c r="B19" s="1">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -9572,7 +9572,7 @@
         <v>810</v>
       </c>
       <c r="B20" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -9580,7 +9580,7 @@
         <v>527</v>
       </c>
       <c r="B21" s="1">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -9588,7 +9588,7 @@
         <v>552</v>
       </c>
       <c r="B22" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -9596,7 +9596,7 @@
         <v>825</v>
       </c>
       <c r="B23" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -9604,7 +9604,7 @@
         <v>528</v>
       </c>
       <c r="B24" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -9612,7 +9612,7 @@
         <v>821</v>
       </c>
       <c r="B25" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -9620,7 +9620,7 @@
         <v>529</v>
       </c>
       <c r="B26" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -9628,7 +9628,7 @@
         <v>684</v>
       </c>
       <c r="B27" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -9636,7 +9636,7 @@
         <v>484</v>
       </c>
       <c r="B28">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -9644,7 +9644,7 @@
         <v>735</v>
       </c>
       <c r="B29">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -9652,7 +9652,7 @@
         <v>530</v>
       </c>
       <c r="B30">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -9660,7 +9660,7 @@
         <v>531</v>
       </c>
       <c r="B31">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -9668,7 +9668,7 @@
         <v>532</v>
       </c>
       <c r="B32">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -9676,7 +9676,7 @@
         <v>533</v>
       </c>
       <c r="B33">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -9684,7 +9684,7 @@
         <v>534</v>
       </c>
       <c r="B34">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -9692,7 +9692,7 @@
         <v>535</v>
       </c>
       <c r="B35">
-        <v>66000</v>
+        <v>67100</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -9700,7 +9700,7 @@
         <v>631</v>
       </c>
       <c r="B36">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -9708,7 +9708,7 @@
         <v>553</v>
       </c>
       <c r="B37">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -9716,7 +9716,7 @@
         <v>726</v>
       </c>
       <c r="B38">
-        <v>51000</v>
+        <v>51850</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -9724,7 +9724,7 @@
         <v>727</v>
       </c>
       <c r="B39">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -9732,7 +9732,7 @@
         <v>536</v>
       </c>
       <c r="B40">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -9740,7 +9740,7 @@
         <v>683</v>
       </c>
       <c r="B41">
-        <v>216000</v>
+        <v>219600</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -9748,7 +9748,7 @@
         <v>636</v>
       </c>
       <c r="B42">
-        <v>222000</v>
+        <v>225700</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -9756,7 +9756,7 @@
         <v>740</v>
       </c>
       <c r="B43">
-        <v>132000</v>
+        <v>134200</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -9764,7 +9764,7 @@
         <v>537</v>
       </c>
       <c r="B44">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -9772,7 +9772,7 @@
         <v>538</v>
       </c>
       <c r="B45">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -9780,7 +9780,7 @@
         <v>811</v>
       </c>
       <c r="B46">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -9788,7 +9788,7 @@
         <v>812</v>
       </c>
       <c r="B47">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -9796,7 +9796,7 @@
         <v>813</v>
       </c>
       <c r="B48">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -9804,7 +9804,7 @@
         <v>539</v>
       </c>
       <c r="B49">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -9812,7 +9812,7 @@
         <v>814</v>
       </c>
       <c r="B50">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -9820,7 +9820,7 @@
         <v>815</v>
       </c>
       <c r="B51">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -9828,7 +9828,7 @@
         <v>816</v>
       </c>
       <c r="B52">
-        <v>15000</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -9836,7 +9836,7 @@
         <v>588</v>
       </c>
       <c r="B53">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -9844,7 +9844,7 @@
         <v>817</v>
       </c>
       <c r="B54">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -9852,7 +9852,7 @@
         <v>818</v>
       </c>
       <c r="B55">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -9860,7 +9860,7 @@
         <v>819</v>
       </c>
       <c r="B56">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -9868,7 +9868,7 @@
         <v>548</v>
       </c>
       <c r="B57">
-        <v>42000</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -9876,7 +9876,7 @@
         <v>549</v>
       </c>
       <c r="B58">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -9884,7 +9884,7 @@
         <v>403</v>
       </c>
       <c r="B59">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -9892,7 +9892,7 @@
         <v>546</v>
       </c>
       <c r="B60">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -9900,7 +9900,7 @@
         <v>556</v>
       </c>
       <c r="B61">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -9908,7 +9908,7 @@
         <v>557</v>
       </c>
       <c r="B62">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -9916,7 +9916,7 @@
         <v>540</v>
       </c>
       <c r="B63">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -9924,7 +9924,7 @@
         <v>541</v>
       </c>
       <c r="B64">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -9932,7 +9932,7 @@
         <v>637</v>
       </c>
       <c r="B65">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -9940,7 +9940,7 @@
         <v>542</v>
       </c>
       <c r="B66">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
   </sheetData>
@@ -9970,7 +9970,7 @@
         <v>383</v>
       </c>
       <c r="B2" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9978,7 +9978,7 @@
         <v>384</v>
       </c>
       <c r="B3" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9986,7 +9986,7 @@
         <v>385</v>
       </c>
       <c r="B4" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9994,7 +9994,7 @@
         <v>386</v>
       </c>
       <c r="B5" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -10002,7 +10002,7 @@
         <v>640</v>
       </c>
       <c r="B6" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -10010,7 +10010,7 @@
         <v>387</v>
       </c>
       <c r="B7" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -10018,7 +10018,7 @@
         <v>660</v>
       </c>
       <c r="B8" s="1">
-        <v>24000</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -10026,7 +10026,7 @@
         <v>662</v>
       </c>
       <c r="B9" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -10034,7 +10034,7 @@
         <v>661</v>
       </c>
       <c r="B10" s="1">
-        <v>19200</v>
+        <v>19520</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -10042,7 +10042,7 @@
         <v>388</v>
       </c>
       <c r="B11" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -10050,7 +10050,7 @@
         <v>405</v>
       </c>
       <c r="B12" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -10058,7 +10058,7 @@
         <v>659</v>
       </c>
       <c r="B13" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -10066,7 +10066,7 @@
         <v>665</v>
       </c>
       <c r="B14" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -10074,7 +10074,7 @@
         <v>745</v>
       </c>
       <c r="B15" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -10082,7 +10082,7 @@
         <v>389</v>
       </c>
       <c r="B16" s="1">
-        <v>5400</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -10090,7 +10090,7 @@
         <v>589</v>
       </c>
       <c r="B17" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -10098,7 +10098,7 @@
         <v>823</v>
       </c>
       <c r="B18" s="1">
-        <v>51000</v>
+        <v>51850</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -10106,7 +10106,7 @@
         <v>663</v>
       </c>
       <c r="B19" s="1">
-        <v>105000</v>
+        <v>106750</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -10114,7 +10114,7 @@
         <v>655</v>
       </c>
       <c r="B20" s="1">
-        <v>117000</v>
+        <v>118950</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -10122,7 +10122,7 @@
         <v>656</v>
       </c>
       <c r="B21" s="1">
-        <v>132000</v>
+        <v>134200</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -10130,7 +10130,7 @@
         <v>430</v>
       </c>
       <c r="B22" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -10138,7 +10138,7 @@
         <v>163</v>
       </c>
       <c r="B23" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -10146,7 +10146,7 @@
         <v>647</v>
       </c>
       <c r="B24" s="1">
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -10154,7 +10154,7 @@
         <v>581</v>
       </c>
       <c r="B25" s="1">
-        <v>66000</v>
+        <v>67100</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -10162,7 +10162,7 @@
         <v>648</v>
       </c>
       <c r="B26" s="1">
-        <v>72000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -10170,7 +10170,7 @@
         <v>657</v>
       </c>
       <c r="B27" s="1">
-        <v>81000</v>
+        <v>82350</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -10178,7 +10178,7 @@
         <v>658</v>
       </c>
       <c r="B28" s="1">
-        <v>96000</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -10186,7 +10186,7 @@
         <v>664</v>
       </c>
       <c r="B29" s="1">
-        <v>102000</v>
+        <v>103700</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -10194,7 +10194,7 @@
         <v>692</v>
       </c>
       <c r="B30" s="1">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -10202,7 +10202,7 @@
         <v>406</v>
       </c>
       <c r="B31" s="1">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -10210,7 +10210,7 @@
         <v>402</v>
       </c>
       <c r="B32" s="1">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -10218,7 +10218,7 @@
         <v>429</v>
       </c>
       <c r="B33" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -10226,7 +10226,7 @@
         <v>551</v>
       </c>
       <c r="B34" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -10234,7 +10234,7 @@
         <v>390</v>
       </c>
       <c r="B35" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -10242,7 +10242,7 @@
         <v>552</v>
       </c>
       <c r="B36" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -10250,7 +10250,7 @@
         <v>825</v>
       </c>
       <c r="B37" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -10258,7 +10258,7 @@
         <v>820</v>
       </c>
       <c r="B38" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -10266,7 +10266,7 @@
         <v>404</v>
       </c>
       <c r="B39" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -10274,7 +10274,7 @@
         <v>259</v>
       </c>
       <c r="B40" s="1">
-        <v>18000</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -10282,7 +10282,7 @@
         <v>425</v>
       </c>
       <c r="B41" s="1">
-        <v>2400</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -10290,7 +10290,7 @@
         <v>484</v>
       </c>
       <c r="B42" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -10298,7 +10298,7 @@
         <v>735</v>
       </c>
       <c r="B43" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -10306,7 +10306,7 @@
         <v>391</v>
       </c>
       <c r="B44" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -10314,7 +10314,7 @@
         <v>392</v>
       </c>
       <c r="B45" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -10322,7 +10322,7 @@
         <v>393</v>
       </c>
       <c r="B46" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -10330,7 +10330,7 @@
         <v>638</v>
       </c>
       <c r="B47" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -10338,7 +10338,7 @@
         <v>394</v>
       </c>
       <c r="B48" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -10346,7 +10346,7 @@
         <v>395</v>
       </c>
       <c r="B49" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -10354,7 +10354,7 @@
         <v>396</v>
       </c>
       <c r="B50" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -10362,7 +10362,7 @@
         <v>728</v>
       </c>
       <c r="B51" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -10370,7 +10370,7 @@
         <v>553</v>
       </c>
       <c r="B52" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -10378,7 +10378,7 @@
         <v>718</v>
       </c>
       <c r="B53" s="1">
-        <v>33000</v>
+        <v>33550</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -10386,7 +10386,7 @@
         <v>719</v>
       </c>
       <c r="B54" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -10394,7 +10394,7 @@
         <v>752</v>
       </c>
       <c r="B55" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -10402,7 +10402,7 @@
         <v>723</v>
       </c>
       <c r="B56" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -10410,7 +10410,7 @@
         <v>720</v>
       </c>
       <c r="B57" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -10418,7 +10418,7 @@
         <v>724</v>
       </c>
       <c r="B58" s="1">
-        <v>45000</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -10426,7 +10426,7 @@
         <v>721</v>
       </c>
       <c r="B59" s="1">
-        <v>39000</v>
+        <v>39650</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -10434,7 +10434,7 @@
         <v>725</v>
       </c>
       <c r="B60" s="1">
-        <v>48000</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -10442,7 +10442,7 @@
         <v>726</v>
       </c>
       <c r="B61" s="1">
-        <v>51000</v>
+        <v>51850</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -10450,7 +10450,7 @@
         <v>727</v>
       </c>
       <c r="B62" s="1">
-        <v>54000</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -10458,7 +10458,7 @@
         <v>740</v>
       </c>
       <c r="B63" s="1">
-        <v>132000</v>
+        <v>134200</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -10466,7 +10466,7 @@
         <v>827</v>
       </c>
       <c r="B64" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -10474,7 +10474,7 @@
         <v>639</v>
       </c>
       <c r="B65" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -10482,7 +10482,7 @@
         <v>543</v>
       </c>
       <c r="B66" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -10490,7 +10490,7 @@
         <v>397</v>
       </c>
       <c r="B67" s="1">
-        <v>10800</v>
+        <v>10980</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -10498,7 +10498,7 @@
         <v>653</v>
       </c>
       <c r="B68" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -10506,7 +10506,7 @@
         <v>398</v>
       </c>
       <c r="B69" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -10514,7 +10514,7 @@
         <v>399</v>
       </c>
       <c r="B70" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -10522,7 +10522,7 @@
         <v>400</v>
       </c>
       <c r="B71" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -10530,7 +10530,7 @@
         <v>582</v>
       </c>
       <c r="B72" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -10538,7 +10538,7 @@
         <v>401</v>
       </c>
       <c r="B73" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -10546,7 +10546,7 @@
         <v>588</v>
       </c>
       <c r="B74" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -10554,7 +10554,7 @@
         <v>554</v>
       </c>
       <c r="B75" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -10562,7 +10562,7 @@
         <v>555</v>
       </c>
       <c r="B76" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -10570,7 +10570,7 @@
         <v>644</v>
       </c>
       <c r="B77" s="1">
-        <v>4200</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -10578,7 +10578,7 @@
         <v>645</v>
       </c>
       <c r="B78" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -10586,7 +10586,7 @@
         <v>403</v>
       </c>
       <c r="B79" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -10594,7 +10594,7 @@
         <v>546</v>
       </c>
       <c r="B80" s="1">
-        <v>7200</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -10602,7 +10602,7 @@
         <v>556</v>
       </c>
       <c r="B81" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -10610,7 +10610,7 @@
         <v>557</v>
       </c>
       <c r="B82" s="1">
-        <v>6000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -10618,7 +10618,7 @@
         <v>558</v>
       </c>
       <c r="B83" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
   </sheetData>

--- a/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO_Partes_y_Piezas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\610 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\620 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571E3D6E-3AD2-4E37-9BE7-A8526FF952E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA25DF76-C36B-4E65-AB2C-80BFF642069A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3034,7 +3034,7 @@
         <v>166</v>
       </c>
       <c r="B2" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3042,7 +3042,7 @@
         <v>421</v>
       </c>
       <c r="B3" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3050,7 +3050,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3058,7 +3058,7 @@
         <v>459</v>
       </c>
       <c r="B5" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3066,7 +3066,7 @@
         <v>460</v>
       </c>
       <c r="B6" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3074,7 +3074,7 @@
         <v>593</v>
       </c>
       <c r="B7" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3082,7 +3082,7 @@
         <v>168</v>
       </c>
       <c r="B8" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3090,7 +3090,7 @@
         <v>461</v>
       </c>
       <c r="B9" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3098,7 +3098,7 @@
         <v>169</v>
       </c>
       <c r="B10" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3106,7 +3106,7 @@
         <v>170</v>
       </c>
       <c r="B11" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3114,7 +3114,7 @@
         <v>171</v>
       </c>
       <c r="B12" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3122,7 +3122,7 @@
         <v>174</v>
       </c>
       <c r="B13" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3130,7 +3130,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3138,7 +3138,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="1">
-        <v>67100</v>
+        <v>68200</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3146,7 +3146,7 @@
         <v>666</v>
       </c>
       <c r="B16" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3154,7 +3154,7 @@
         <v>175</v>
       </c>
       <c r="B17" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3162,7 +3162,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3170,7 +3170,7 @@
         <v>589</v>
       </c>
       <c r="B19" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3178,7 +3178,7 @@
         <v>462</v>
       </c>
       <c r="B20" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3186,7 +3186,7 @@
         <v>177</v>
       </c>
       <c r="B21" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3194,7 +3194,7 @@
         <v>178</v>
       </c>
       <c r="B22" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3202,7 +3202,7 @@
         <v>179</v>
       </c>
       <c r="B23" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3210,7 +3210,7 @@
         <v>550</v>
       </c>
       <c r="B24" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3218,7 +3218,7 @@
         <v>180</v>
       </c>
       <c r="B25" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3226,7 +3226,7 @@
         <v>181</v>
       </c>
       <c r="B26" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3234,7 +3234,7 @@
         <v>182</v>
       </c>
       <c r="B27" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3242,7 +3242,7 @@
         <v>183</v>
       </c>
       <c r="B28" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3250,7 +3250,7 @@
         <v>184</v>
       </c>
       <c r="B29" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3258,7 +3258,7 @@
         <v>185</v>
       </c>
       <c r="B30" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3266,7 +3266,7 @@
         <v>186</v>
       </c>
       <c r="B31" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3274,7 +3274,7 @@
         <v>187</v>
       </c>
       <c r="B32" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3282,7 +3282,7 @@
         <v>188</v>
       </c>
       <c r="B33" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3290,7 +3290,7 @@
         <v>606</v>
       </c>
       <c r="B34" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3298,7 +3298,7 @@
         <v>569</v>
       </c>
       <c r="B35" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3306,7 +3306,7 @@
         <v>594</v>
       </c>
       <c r="B36" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3314,7 +3314,7 @@
         <v>823</v>
       </c>
       <c r="B37" s="1">
-        <v>51850</v>
+        <v>52700</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3322,7 +3322,7 @@
         <v>430</v>
       </c>
       <c r="B38" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3330,7 +3330,7 @@
         <v>163</v>
       </c>
       <c r="B39" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3338,7 +3338,7 @@
         <v>647</v>
       </c>
       <c r="B40" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3346,7 +3346,7 @@
         <v>581</v>
       </c>
       <c r="B41" s="1">
-        <v>67100</v>
+        <v>68200</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3354,7 +3354,7 @@
         <v>648</v>
       </c>
       <c r="B42" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3362,7 +3362,7 @@
         <v>189</v>
       </c>
       <c r="B43" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3370,7 +3370,7 @@
         <v>419</v>
       </c>
       <c r="B44" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3378,7 +3378,7 @@
         <v>408</v>
       </c>
       <c r="B45" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3386,7 +3386,7 @@
         <v>729</v>
       </c>
       <c r="B46" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3394,7 +3394,7 @@
         <v>730</v>
       </c>
       <c r="B47" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3402,7 +3402,7 @@
         <v>190</v>
       </c>
       <c r="B48" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3410,7 +3410,7 @@
         <v>191</v>
       </c>
       <c r="B49" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3418,7 +3418,7 @@
         <v>192</v>
       </c>
       <c r="B50" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3426,7 +3426,7 @@
         <v>193</v>
       </c>
       <c r="B51" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3434,7 +3434,7 @@
         <v>692</v>
       </c>
       <c r="B52" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3442,7 +3442,7 @@
         <v>194</v>
       </c>
       <c r="B53" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3450,7 +3450,7 @@
         <v>406</v>
       </c>
       <c r="B54" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3458,7 +3458,7 @@
         <v>402</v>
       </c>
       <c r="B55" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3466,7 +3466,7 @@
         <v>429</v>
       </c>
       <c r="B56" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3474,7 +3474,7 @@
         <v>195</v>
       </c>
       <c r="B57" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3482,7 +3482,7 @@
         <v>196</v>
       </c>
       <c r="B58" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3490,7 +3490,7 @@
         <v>197</v>
       </c>
       <c r="B59" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3498,7 +3498,7 @@
         <v>595</v>
       </c>
       <c r="B60" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3506,7 +3506,7 @@
         <v>596</v>
       </c>
       <c r="B61" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3514,7 +3514,7 @@
         <v>198</v>
       </c>
       <c r="B62" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3522,7 +3522,7 @@
         <v>199</v>
       </c>
       <c r="B63" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3530,7 +3530,7 @@
         <v>200</v>
       </c>
       <c r="B64" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3538,7 +3538,7 @@
         <v>201</v>
       </c>
       <c r="B65" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3546,7 +3546,7 @@
         <v>202</v>
       </c>
       <c r="B66" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3554,7 +3554,7 @@
         <v>203</v>
       </c>
       <c r="B67" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3562,7 +3562,7 @@
         <v>204</v>
       </c>
       <c r="B68" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3570,7 +3570,7 @@
         <v>205</v>
       </c>
       <c r="B69" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3578,7 +3578,7 @@
         <v>206</v>
       </c>
       <c r="B70" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3586,7 +3586,7 @@
         <v>208</v>
       </c>
       <c r="B71" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3594,7 +3594,7 @@
         <v>212</v>
       </c>
       <c r="B72" s="1">
-        <v>1220</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3602,7 +3602,7 @@
         <v>209</v>
       </c>
       <c r="B73" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3610,7 +3610,7 @@
         <v>210</v>
       </c>
       <c r="B74" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3618,7 +3618,7 @@
         <v>211</v>
       </c>
       <c r="B75" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3626,7 +3626,7 @@
         <v>476</v>
       </c>
       <c r="B76" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3634,7 +3634,7 @@
         <v>207</v>
       </c>
       <c r="B77" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3642,7 +3642,7 @@
         <v>213</v>
       </c>
       <c r="B78" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3650,7 +3650,7 @@
         <v>214</v>
       </c>
       <c r="B79" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3658,7 +3658,7 @@
         <v>215</v>
       </c>
       <c r="B80" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3666,7 +3666,7 @@
         <v>216</v>
       </c>
       <c r="B81" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3674,7 +3674,7 @@
         <v>217</v>
       </c>
       <c r="B82" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3682,7 +3682,7 @@
         <v>218</v>
       </c>
       <c r="B83" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3690,7 +3690,7 @@
         <v>219</v>
       </c>
       <c r="B84" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3698,7 +3698,7 @@
         <v>220</v>
       </c>
       <c r="B85" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3706,7 +3706,7 @@
         <v>607</v>
       </c>
       <c r="B86" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3714,7 +3714,7 @@
         <v>221</v>
       </c>
       <c r="B87" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3722,7 +3722,7 @@
         <v>608</v>
       </c>
       <c r="B88" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3730,7 +3730,7 @@
         <v>417</v>
       </c>
       <c r="B89" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3738,7 +3738,7 @@
         <v>418</v>
       </c>
       <c r="B90" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3746,7 +3746,7 @@
         <v>222</v>
       </c>
       <c r="B91" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3754,7 +3754,7 @@
         <v>223</v>
       </c>
       <c r="B92" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3762,7 +3762,7 @@
         <v>224</v>
       </c>
       <c r="B93" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3770,7 +3770,7 @@
         <v>225</v>
       </c>
       <c r="B94" s="1">
-        <v>213500</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3778,7 +3778,7 @@
         <v>226</v>
       </c>
       <c r="B95" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3786,7 +3786,7 @@
         <v>824</v>
       </c>
       <c r="B96" s="1">
-        <v>183000</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3794,7 +3794,7 @@
         <v>227</v>
       </c>
       <c r="B97" s="1">
-        <v>170800</v>
+        <v>173600</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3802,7 +3802,7 @@
         <v>228</v>
       </c>
       <c r="B98" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3810,7 +3810,7 @@
         <v>551</v>
       </c>
       <c r="B99" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3818,7 +3818,7 @@
         <v>667</v>
       </c>
       <c r="B100" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3826,7 +3826,7 @@
         <v>409</v>
       </c>
       <c r="B101" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3834,7 +3834,7 @@
         <v>229</v>
       </c>
       <c r="B102" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3842,7 +3842,7 @@
         <v>230</v>
       </c>
       <c r="B103" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3850,7 +3850,7 @@
         <v>231</v>
       </c>
       <c r="B104" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3858,7 +3858,7 @@
         <v>424</v>
       </c>
       <c r="B105" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3866,7 +3866,7 @@
         <v>232</v>
       </c>
       <c r="B106" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3874,7 +3874,7 @@
         <v>570</v>
       </c>
       <c r="B107" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3882,7 +3882,7 @@
         <v>483</v>
       </c>
       <c r="B108" s="1">
-        <v>152500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3890,7 +3890,7 @@
         <v>587</v>
       </c>
       <c r="B109" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3898,7 +3898,7 @@
         <v>233</v>
       </c>
       <c r="B110" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3906,7 +3906,7 @@
         <v>234</v>
       </c>
       <c r="B111" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3914,7 +3914,7 @@
         <v>731</v>
       </c>
       <c r="B112" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3922,7 +3922,7 @@
         <v>717</v>
       </c>
       <c r="B113" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3930,7 +3930,7 @@
         <v>571</v>
       </c>
       <c r="B114" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3938,7 +3938,7 @@
         <v>590</v>
       </c>
       <c r="B115" s="1">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3946,7 +3946,7 @@
         <v>235</v>
       </c>
       <c r="B116" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3954,7 +3954,7 @@
         <v>732</v>
       </c>
       <c r="B117" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3962,7 +3962,7 @@
         <v>236</v>
       </c>
       <c r="B118" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3970,7 +3970,7 @@
         <v>733</v>
       </c>
       <c r="B119" s="1">
-        <v>1220</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3978,7 +3978,7 @@
         <v>237</v>
       </c>
       <c r="B120" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3986,7 +3986,7 @@
         <v>410</v>
       </c>
       <c r="B121" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3994,7 +3994,7 @@
         <v>238</v>
       </c>
       <c r="B122" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4002,7 +4002,7 @@
         <v>239</v>
       </c>
       <c r="B123" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4010,7 +4010,7 @@
         <v>240</v>
       </c>
       <c r="B124" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4018,7 +4018,7 @@
         <v>241</v>
       </c>
       <c r="B125" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4026,7 +4026,7 @@
         <v>242</v>
       </c>
       <c r="B126" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4034,7 +4034,7 @@
         <v>243</v>
       </c>
       <c r="B127" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4042,7 +4042,7 @@
         <v>668</v>
       </c>
       <c r="B128" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4050,7 +4050,7 @@
         <v>669</v>
       </c>
       <c r="B129" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4058,7 +4058,7 @@
         <v>431</v>
       </c>
       <c r="B130" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4066,7 +4066,7 @@
         <v>244</v>
       </c>
       <c r="B131" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4074,7 +4074,7 @@
         <v>597</v>
       </c>
       <c r="B132" s="1">
-        <v>262300</v>
+        <v>266600</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4082,7 +4082,7 @@
         <v>245</v>
       </c>
       <c r="B133" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4090,7 +4090,7 @@
         <v>456</v>
       </c>
       <c r="B134" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4098,7 +4098,7 @@
         <v>457</v>
       </c>
       <c r="B135" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4106,7 +4106,7 @@
         <v>458</v>
       </c>
       <c r="B136" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4114,7 +4114,7 @@
         <v>246</v>
       </c>
       <c r="B137" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4122,7 +4122,7 @@
         <v>247</v>
       </c>
       <c r="B138" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4130,7 +4130,7 @@
         <v>248</v>
       </c>
       <c r="B139" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4138,7 +4138,7 @@
         <v>250</v>
       </c>
       <c r="B140" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4146,7 +4146,7 @@
         <v>420</v>
       </c>
       <c r="B141" s="1">
-        <v>152500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4154,7 +4154,7 @@
         <v>14</v>
       </c>
       <c r="B142" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4162,7 +4162,7 @@
         <v>602</v>
       </c>
       <c r="B143" s="1">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4170,7 +4170,7 @@
         <v>249</v>
       </c>
       <c r="B144" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4178,7 +4178,7 @@
         <v>552</v>
       </c>
       <c r="B145" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4186,7 +4186,7 @@
         <v>251</v>
       </c>
       <c r="B146" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4194,7 +4194,7 @@
         <v>825</v>
       </c>
       <c r="B147" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4202,7 +4202,7 @@
         <v>252</v>
       </c>
       <c r="B148" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4210,7 +4210,7 @@
         <v>253</v>
       </c>
       <c r="B149" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4218,7 +4218,7 @@
         <v>598</v>
       </c>
       <c r="B150" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4226,7 +4226,7 @@
         <v>254</v>
       </c>
       <c r="B151" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4234,7 +4234,7 @@
         <v>255</v>
       </c>
       <c r="B152" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4242,7 +4242,7 @@
         <v>256</v>
       </c>
       <c r="B153" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4250,7 +4250,7 @@
         <v>257</v>
       </c>
       <c r="B154" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4258,7 +4258,7 @@
         <v>258</v>
       </c>
       <c r="B155" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4266,7 +4266,7 @@
         <v>261</v>
       </c>
       <c r="B156" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4274,7 +4274,7 @@
         <v>262</v>
       </c>
       <c r="B157" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4282,7 +4282,7 @@
         <v>263</v>
       </c>
       <c r="B158" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4290,7 +4290,7 @@
         <v>404</v>
       </c>
       <c r="B159" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4298,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="B160" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4306,7 +4306,7 @@
         <v>463</v>
       </c>
       <c r="B161" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4314,7 +4314,7 @@
         <v>260</v>
       </c>
       <c r="B162" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4322,7 +4322,7 @@
         <v>264</v>
       </c>
       <c r="B163" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4330,7 +4330,7 @@
         <v>689</v>
       </c>
       <c r="B164" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4338,7 +4338,7 @@
         <v>641</v>
       </c>
       <c r="B165" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4346,7 +4346,7 @@
         <v>642</v>
       </c>
       <c r="B166" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4354,7 +4354,7 @@
         <v>603</v>
       </c>
       <c r="B167" s="1">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4362,7 +4362,7 @@
         <v>604</v>
       </c>
       <c r="B168" s="1">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4370,7 +4370,7 @@
         <v>484</v>
       </c>
       <c r="B169" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4378,7 +4378,7 @@
         <v>265</v>
       </c>
       <c r="B170" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4386,7 +4386,7 @@
         <v>609</v>
       </c>
       <c r="B171" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4394,7 +4394,7 @@
         <v>734</v>
       </c>
       <c r="B172" s="1">
-        <v>2440</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4402,7 +4402,7 @@
         <v>735</v>
       </c>
       <c r="B173" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4410,7 +4410,7 @@
         <v>266</v>
       </c>
       <c r="B174" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4418,7 +4418,7 @@
         <v>267</v>
       </c>
       <c r="B175" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4426,7 +4426,7 @@
         <v>268</v>
       </c>
       <c r="B176" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4434,7 +4434,7 @@
         <v>269</v>
       </c>
       <c r="B177" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4442,7 +4442,7 @@
         <v>270</v>
       </c>
       <c r="B178" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4450,7 +4450,7 @@
         <v>271</v>
       </c>
       <c r="B179" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4458,7 +4458,7 @@
         <v>272</v>
       </c>
       <c r="B180" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4466,7 +4466,7 @@
         <v>273</v>
       </c>
       <c r="B181" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4474,7 +4474,7 @@
         <v>422</v>
       </c>
       <c r="B182" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4482,7 +4482,7 @@
         <v>423</v>
       </c>
       <c r="B183" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4490,7 +4490,7 @@
         <v>610</v>
       </c>
       <c r="B184" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4498,7 +4498,7 @@
         <v>611</v>
       </c>
       <c r="B185" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4506,7 +4506,7 @@
         <v>612</v>
       </c>
       <c r="B186" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4514,7 +4514,7 @@
         <v>613</v>
       </c>
       <c r="B187" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4522,7 +4522,7 @@
         <v>614</v>
       </c>
       <c r="B188" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4530,7 +4530,7 @@
         <v>615</v>
       </c>
       <c r="B189" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4538,7 +4538,7 @@
         <v>274</v>
       </c>
       <c r="B190" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4546,7 +4546,7 @@
         <v>276</v>
       </c>
       <c r="B191" s="1">
-        <v>1220</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4554,7 +4554,7 @@
         <v>275</v>
       </c>
       <c r="B192" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4562,7 +4562,7 @@
         <v>616</v>
       </c>
       <c r="B193" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4570,7 +4570,7 @@
         <v>277</v>
       </c>
       <c r="B194" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4578,7 +4578,7 @@
         <v>464</v>
       </c>
       <c r="B195" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4586,7 +4586,7 @@
         <v>278</v>
       </c>
       <c r="B196" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4594,7 +4594,7 @@
         <v>736</v>
       </c>
       <c r="B197" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4602,7 +4602,7 @@
         <v>391</v>
       </c>
       <c r="B198" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4610,7 +4610,7 @@
         <v>396</v>
       </c>
       <c r="B199" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4618,7 +4618,7 @@
         <v>466</v>
       </c>
       <c r="B200" s="1">
-        <v>195200</v>
+        <v>198400</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4626,7 +4626,7 @@
         <v>279</v>
       </c>
       <c r="B201" s="1">
-        <v>317200</v>
+        <v>322400</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4634,7 +4634,7 @@
         <v>649</v>
       </c>
       <c r="B202" s="1">
-        <v>323300</v>
+        <v>328600</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4642,7 +4642,7 @@
         <v>280</v>
       </c>
       <c r="B203" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4650,7 +4650,7 @@
         <v>696</v>
       </c>
       <c r="B204" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4658,7 +4658,7 @@
         <v>737</v>
       </c>
       <c r="B205" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4666,7 +4666,7 @@
         <v>411</v>
       </c>
       <c r="B206" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4674,7 +4674,7 @@
         <v>281</v>
       </c>
       <c r="B207" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4682,7 +4682,7 @@
         <v>412</v>
       </c>
       <c r="B208" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4690,7 +4690,7 @@
         <v>282</v>
       </c>
       <c r="B209" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4698,7 +4698,7 @@
         <v>283</v>
       </c>
       <c r="B210" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4706,7 +4706,7 @@
         <v>284</v>
       </c>
       <c r="B211" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4714,7 +4714,7 @@
         <v>285</v>
       </c>
       <c r="B212" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4722,7 +4722,7 @@
         <v>286</v>
       </c>
       <c r="B213" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4730,7 +4730,7 @@
         <v>287</v>
       </c>
       <c r="B214" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4738,7 +4738,7 @@
         <v>288</v>
       </c>
       <c r="B215" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4746,7 +4746,7 @@
         <v>289</v>
       </c>
       <c r="B216" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4754,7 +4754,7 @@
         <v>553</v>
       </c>
       <c r="B217" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4762,7 +4762,7 @@
         <v>290</v>
       </c>
       <c r="B218" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4770,7 +4770,7 @@
         <v>738</v>
       </c>
       <c r="B219" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4778,7 +4778,7 @@
         <v>739</v>
       </c>
       <c r="B220" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4786,7 +4786,7 @@
         <v>291</v>
       </c>
       <c r="B221" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4794,7 +4794,7 @@
         <v>292</v>
       </c>
       <c r="B222" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4802,7 +4802,7 @@
         <v>293</v>
       </c>
       <c r="B223" s="1">
-        <v>170800</v>
+        <v>173600</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4810,7 +4810,7 @@
         <v>294</v>
       </c>
       <c r="B224" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4818,7 +4818,7 @@
         <v>572</v>
       </c>
       <c r="B225" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4826,7 +4826,7 @@
         <v>670</v>
       </c>
       <c r="B226" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4834,7 +4834,7 @@
         <v>295</v>
       </c>
       <c r="B227" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4842,7 +4842,7 @@
         <v>671</v>
       </c>
       <c r="B228" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4850,7 +4850,7 @@
         <v>296</v>
       </c>
       <c r="B229" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4858,7 +4858,7 @@
         <v>718</v>
       </c>
       <c r="B230" s="1">
-        <v>33550</v>
+        <v>34100</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4866,7 +4866,7 @@
         <v>719</v>
       </c>
       <c r="B231" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4874,7 +4874,7 @@
         <v>720</v>
       </c>
       <c r="B232" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4882,7 +4882,7 @@
         <v>721</v>
       </c>
       <c r="B233" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4890,7 +4890,7 @@
         <v>617</v>
       </c>
       <c r="B234" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4898,7 +4898,7 @@
         <v>297</v>
       </c>
       <c r="B235" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4906,7 +4906,7 @@
         <v>573</v>
       </c>
       <c r="B236" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4914,7 +4914,7 @@
         <v>298</v>
       </c>
       <c r="B237" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4922,7 +4922,7 @@
         <v>299</v>
       </c>
       <c r="B238" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4930,7 +4930,7 @@
         <v>300</v>
       </c>
       <c r="B239" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4938,7 +4938,7 @@
         <v>301</v>
       </c>
       <c r="B240" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4946,7 +4946,7 @@
         <v>302</v>
       </c>
       <c r="B241" s="1">
-        <v>183000</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4954,7 +4954,7 @@
         <v>672</v>
       </c>
       <c r="B242" s="1">
-        <v>183000</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4962,7 +4962,7 @@
         <v>303</v>
       </c>
       <c r="B243" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4970,7 +4970,7 @@
         <v>740</v>
       </c>
       <c r="B244" s="1">
-        <v>134200</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4978,7 +4978,7 @@
         <v>304</v>
       </c>
       <c r="B245" s="1">
-        <v>67100</v>
+        <v>68200</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4986,7 +4986,7 @@
         <v>305</v>
       </c>
       <c r="B246" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4994,7 +4994,7 @@
         <v>306</v>
       </c>
       <c r="B247" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5002,7 +5002,7 @@
         <v>618</v>
       </c>
       <c r="B248" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5010,7 +5010,7 @@
         <v>307</v>
       </c>
       <c r="B249" s="1">
-        <v>103700</v>
+        <v>105400</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5018,7 +5018,7 @@
         <v>308</v>
       </c>
       <c r="B250" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5026,7 +5026,7 @@
         <v>309</v>
       </c>
       <c r="B251" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5034,7 +5034,7 @@
         <v>310</v>
       </c>
       <c r="B252" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5042,7 +5042,7 @@
         <v>690</v>
       </c>
       <c r="B253" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5050,7 +5050,7 @@
         <v>311</v>
       </c>
       <c r="B254" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5058,7 +5058,7 @@
         <v>312</v>
       </c>
       <c r="B255" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5066,7 +5066,7 @@
         <v>313</v>
       </c>
       <c r="B256" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5074,7 +5074,7 @@
         <v>467</v>
       </c>
       <c r="B257" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5082,7 +5082,7 @@
         <v>741</v>
       </c>
       <c r="B258" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5090,7 +5090,7 @@
         <v>742</v>
       </c>
       <c r="B259" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5098,7 +5098,7 @@
         <v>468</v>
       </c>
       <c r="B260" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5106,7 +5106,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5114,7 +5114,7 @@
         <v>315</v>
       </c>
       <c r="B262" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5122,7 +5122,7 @@
         <v>316</v>
       </c>
       <c r="B263" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5130,7 +5130,7 @@
         <v>414</v>
       </c>
       <c r="B264" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5138,7 +5138,7 @@
         <v>317</v>
       </c>
       <c r="B265" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5146,7 +5146,7 @@
         <v>318</v>
       </c>
       <c r="B266" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5154,7 +5154,7 @@
         <v>605</v>
       </c>
       <c r="B267" s="1">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5162,7 +5162,7 @@
         <v>319</v>
       </c>
       <c r="B268" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5170,7 +5170,7 @@
         <v>320</v>
       </c>
       <c r="B269" s="1">
-        <v>183000</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5178,7 +5178,7 @@
         <v>321</v>
       </c>
       <c r="B270" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5186,7 +5186,7 @@
         <v>322</v>
       </c>
       <c r="B271" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5194,7 +5194,7 @@
         <v>323</v>
       </c>
       <c r="B272" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5202,7 +5202,7 @@
         <v>324</v>
       </c>
       <c r="B273" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5210,7 +5210,7 @@
         <v>325</v>
       </c>
       <c r="B274" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5218,7 +5218,7 @@
         <v>326</v>
       </c>
       <c r="B275" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5226,7 +5226,7 @@
         <v>327</v>
       </c>
       <c r="B276" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5234,7 +5234,7 @@
         <v>328</v>
       </c>
       <c r="B277" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5242,7 +5242,7 @@
         <v>329</v>
       </c>
       <c r="B278" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5250,7 +5250,7 @@
         <v>330</v>
       </c>
       <c r="B279" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5258,7 +5258,7 @@
         <v>331</v>
       </c>
       <c r="B280" s="1">
-        <v>79300</v>
+        <v>80600</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5266,7 +5266,7 @@
         <v>332</v>
       </c>
       <c r="B281" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5274,7 +5274,7 @@
         <v>333</v>
       </c>
       <c r="B282" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5282,7 +5282,7 @@
         <v>334</v>
       </c>
       <c r="B283" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5290,7 +5290,7 @@
         <v>574</v>
       </c>
       <c r="B284" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5298,7 +5298,7 @@
         <v>599</v>
       </c>
       <c r="B285" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5306,7 +5306,7 @@
         <v>600</v>
       </c>
       <c r="B286" s="1">
-        <v>57950</v>
+        <v>58900</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5314,7 +5314,7 @@
         <v>743</v>
       </c>
       <c r="B287" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5322,7 +5322,7 @@
         <v>619</v>
       </c>
       <c r="B288" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5330,7 +5330,7 @@
         <v>335</v>
       </c>
       <c r="B289" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5338,7 +5338,7 @@
         <v>620</v>
       </c>
       <c r="B290" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5346,7 +5346,7 @@
         <v>336</v>
       </c>
       <c r="B291" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5354,7 +5354,7 @@
         <v>337</v>
       </c>
       <c r="B292" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5362,7 +5362,7 @@
         <v>338</v>
       </c>
       <c r="B293" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5370,7 +5370,7 @@
         <v>339</v>
       </c>
       <c r="B294" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5378,7 +5378,7 @@
         <v>340</v>
       </c>
       <c r="B295" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5386,7 +5386,7 @@
         <v>341</v>
       </c>
       <c r="B296" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5394,7 +5394,7 @@
         <v>342</v>
       </c>
       <c r="B297" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5402,7 +5402,7 @@
         <v>343</v>
       </c>
       <c r="B298" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5410,7 +5410,7 @@
         <v>415</v>
       </c>
       <c r="B299" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5418,7 +5418,7 @@
         <v>416</v>
       </c>
       <c r="B300" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5426,7 +5426,7 @@
         <v>601</v>
       </c>
       <c r="B301" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5434,7 +5434,7 @@
         <v>344</v>
       </c>
       <c r="B302" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5442,7 +5442,7 @@
         <v>345</v>
       </c>
       <c r="B303" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5450,7 +5450,7 @@
         <v>346</v>
       </c>
       <c r="B304" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5458,7 +5458,7 @@
         <v>347</v>
       </c>
       <c r="B305" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5466,7 +5466,7 @@
         <v>348</v>
       </c>
       <c r="B306" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5474,7 +5474,7 @@
         <v>349</v>
       </c>
       <c r="B307" s="1">
-        <v>2440</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5482,7 +5482,7 @@
         <v>744</v>
       </c>
       <c r="B308" s="1">
-        <v>1220</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5490,7 +5490,7 @@
         <v>673</v>
       </c>
       <c r="B309" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5498,7 +5498,7 @@
         <v>350</v>
       </c>
       <c r="B310" s="1">
-        <v>45750</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5506,7 +5506,7 @@
         <v>351</v>
       </c>
       <c r="B311" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5514,7 +5514,7 @@
         <v>352</v>
       </c>
       <c r="B312" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5522,7 +5522,7 @@
         <v>575</v>
       </c>
       <c r="B313" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5530,7 +5530,7 @@
         <v>353</v>
       </c>
       <c r="B314" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5538,7 +5538,7 @@
         <v>354</v>
       </c>
       <c r="B315" s="1">
-        <v>152500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5546,7 +5546,7 @@
         <v>407</v>
       </c>
       <c r="B316" s="1">
-        <v>335500</v>
+        <v>341000</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5554,7 +5554,7 @@
         <v>355</v>
       </c>
       <c r="B317" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5562,7 +5562,7 @@
         <v>356</v>
       </c>
       <c r="B318" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5570,7 +5570,7 @@
         <v>576</v>
       </c>
       <c r="B319" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5578,7 +5578,7 @@
         <v>357</v>
       </c>
       <c r="B320" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5586,7 +5586,7 @@
         <v>358</v>
       </c>
       <c r="B321" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5594,7 +5594,7 @@
         <v>651</v>
       </c>
       <c r="B322" s="1">
-        <v>2440</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5602,7 +5602,7 @@
         <v>577</v>
       </c>
       <c r="B323" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5610,7 +5610,7 @@
         <v>588</v>
       </c>
       <c r="B324" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5618,7 +5618,7 @@
         <v>359</v>
       </c>
       <c r="B325" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5626,7 +5626,7 @@
         <v>360</v>
       </c>
       <c r="B326" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5634,7 +5634,7 @@
         <v>361</v>
       </c>
       <c r="B327" s="1">
-        <v>2440</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5642,7 +5642,7 @@
         <v>362</v>
       </c>
       <c r="B328" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5650,7 +5650,7 @@
         <v>363</v>
       </c>
       <c r="B329" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5658,7 +5658,7 @@
         <v>364</v>
       </c>
       <c r="B330" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5666,7 +5666,7 @@
         <v>365</v>
       </c>
       <c r="B331" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5674,7 +5674,7 @@
         <v>403</v>
       </c>
       <c r="B332" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5682,7 +5682,7 @@
         <v>546</v>
       </c>
       <c r="B333" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5690,7 +5690,7 @@
         <v>822</v>
       </c>
       <c r="B334" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5698,7 +5698,7 @@
         <v>366</v>
       </c>
       <c r="B335" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5706,7 +5706,7 @@
         <v>556</v>
       </c>
       <c r="B336" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5714,7 +5714,7 @@
         <v>557</v>
       </c>
       <c r="B337" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5722,7 +5722,7 @@
         <v>367</v>
       </c>
       <c r="B338" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5730,7 +5730,7 @@
         <v>368</v>
       </c>
       <c r="B339" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5738,7 +5738,7 @@
         <v>369</v>
       </c>
       <c r="B340" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5746,7 +5746,7 @@
         <v>370</v>
       </c>
       <c r="B341" s="1">
-        <v>1220</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5754,7 +5754,7 @@
         <v>371</v>
       </c>
       <c r="B342" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5762,7 +5762,7 @@
         <v>372</v>
       </c>
       <c r="B343" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5770,7 +5770,7 @@
         <v>373</v>
       </c>
       <c r="B344" s="1">
-        <v>2440</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5778,7 +5778,7 @@
         <v>413</v>
       </c>
       <c r="B345" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5786,7 +5786,7 @@
         <v>465</v>
       </c>
       <c r="B346" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5794,7 +5794,7 @@
         <v>621</v>
       </c>
       <c r="B347" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5802,7 +5802,7 @@
         <v>374</v>
       </c>
       <c r="B348" s="1">
-        <v>1220</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5810,7 +5810,7 @@
         <v>485</v>
       </c>
       <c r="B349" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5818,7 +5818,7 @@
         <v>469</v>
       </c>
       <c r="B350" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5826,7 +5826,7 @@
         <v>375</v>
       </c>
       <c r="B351" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5834,7 +5834,7 @@
         <v>674</v>
       </c>
       <c r="B352" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5842,7 +5842,7 @@
         <v>675</v>
       </c>
       <c r="B353" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5850,7 +5850,7 @@
         <v>376</v>
       </c>
       <c r="B354" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5858,7 +5858,7 @@
         <v>377</v>
       </c>
       <c r="B355" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5866,7 +5866,7 @@
         <v>378</v>
       </c>
       <c r="B356" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5874,7 +5874,7 @@
         <v>622</v>
       </c>
       <c r="B357" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5882,7 +5882,7 @@
         <v>379</v>
       </c>
       <c r="B358" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5890,7 +5890,7 @@
         <v>470</v>
       </c>
       <c r="B359" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5898,7 +5898,7 @@
         <v>471</v>
       </c>
       <c r="B360" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5906,7 +5906,7 @@
         <v>676</v>
       </c>
       <c r="B361" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5914,7 +5914,7 @@
         <v>380</v>
       </c>
       <c r="B362" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5922,7 +5922,7 @@
         <v>381</v>
       </c>
       <c r="B363" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5930,7 +5930,7 @@
         <v>454</v>
       </c>
       <c r="B364" s="1">
-        <v>2440</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5938,7 +5938,7 @@
         <v>382</v>
       </c>
       <c r="B365" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
   </sheetData>
@@ -5968,7 +5968,7 @@
         <v>486</v>
       </c>
       <c r="B2" s="1">
-        <v>85400</v>
+        <v>86800</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5976,7 +5976,7 @@
         <v>123</v>
       </c>
       <c r="B3" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5984,7 +5984,7 @@
         <v>757</v>
       </c>
       <c r="B4" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5992,7 +5992,7 @@
         <v>578</v>
       </c>
       <c r="B5" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6000,7 +6000,7 @@
         <v>164</v>
       </c>
       <c r="B6" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6008,7 +6008,7 @@
         <v>579</v>
       </c>
       <c r="B7" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6016,7 +6016,7 @@
         <v>589</v>
       </c>
       <c r="B8" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6024,7 +6024,7 @@
         <v>758</v>
       </c>
       <c r="B9" s="1">
-        <v>79300</v>
+        <v>80600</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6032,7 +6032,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6040,7 +6040,7 @@
         <v>759</v>
       </c>
       <c r="B11" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6048,7 +6048,7 @@
         <v>124</v>
       </c>
       <c r="B12" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6056,7 +6056,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6064,7 +6064,7 @@
         <v>823</v>
       </c>
       <c r="B14" s="1">
-        <v>51850</v>
+        <v>52700</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6072,7 +6072,7 @@
         <v>430</v>
       </c>
       <c r="B15" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6080,7 +6080,7 @@
         <v>163</v>
       </c>
       <c r="B16" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6088,7 +6088,7 @@
         <v>647</v>
       </c>
       <c r="B17" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6096,7 +6096,7 @@
         <v>581</v>
       </c>
       <c r="B18" s="1">
-        <v>67100</v>
+        <v>68200</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6104,7 +6104,7 @@
         <v>648</v>
       </c>
       <c r="B19" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6112,7 +6112,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6120,7 +6120,7 @@
         <v>125</v>
       </c>
       <c r="B21" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6128,7 +6128,7 @@
         <v>478</v>
       </c>
       <c r="B22" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6136,7 +6136,7 @@
         <v>36</v>
       </c>
       <c r="B23" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6144,7 +6144,7 @@
         <v>487</v>
       </c>
       <c r="B24" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6152,7 +6152,7 @@
         <v>488</v>
       </c>
       <c r="B25" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6160,7 +6160,7 @@
         <v>692</v>
       </c>
       <c r="B26" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6168,7 +6168,7 @@
         <v>406</v>
       </c>
       <c r="B27" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6176,7 +6176,7 @@
         <v>402</v>
       </c>
       <c r="B28" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6184,7 +6184,7 @@
         <v>439</v>
       </c>
       <c r="B29" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6192,7 +6192,7 @@
         <v>760</v>
       </c>
       <c r="B30" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6200,7 +6200,7 @@
         <v>489</v>
       </c>
       <c r="B31" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6208,7 +6208,7 @@
         <v>490</v>
       </c>
       <c r="B32" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6216,7 +6216,7 @@
         <v>761</v>
       </c>
       <c r="B33" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6224,7 +6224,7 @@
         <v>12</v>
       </c>
       <c r="B34" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6232,7 +6232,7 @@
         <v>762</v>
       </c>
       <c r="B35" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="1">
-        <v>1525</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6248,7 +6248,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6256,7 +6256,7 @@
         <v>434</v>
       </c>
       <c r="B38" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6264,7 +6264,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6272,7 +6272,7 @@
         <v>491</v>
       </c>
       <c r="B40" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6280,7 +6280,7 @@
         <v>479</v>
       </c>
       <c r="B41" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6288,7 +6288,7 @@
         <v>763</v>
       </c>
       <c r="B42" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6296,7 +6296,7 @@
         <v>438</v>
       </c>
       <c r="B43" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6304,7 +6304,7 @@
         <v>440</v>
       </c>
       <c r="B44" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6312,7 +6312,7 @@
         <v>492</v>
       </c>
       <c r="B45" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6320,7 +6320,7 @@
         <v>493</v>
       </c>
       <c r="B46" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6328,7 +6328,7 @@
         <v>494</v>
       </c>
       <c r="B47" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6336,7 +6336,7 @@
         <v>764</v>
       </c>
       <c r="B48" s="1">
-        <v>213500</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -6344,7 +6344,7 @@
         <v>551</v>
       </c>
       <c r="B49" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -6352,7 +6352,7 @@
         <v>765</v>
       </c>
       <c r="B50" s="1">
-        <v>79300</v>
+        <v>80600</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -6360,7 +6360,7 @@
         <v>751</v>
       </c>
       <c r="B51" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -6368,7 +6368,7 @@
         <v>722</v>
       </c>
       <c r="B52" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -6376,7 +6376,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -6384,7 +6384,7 @@
         <v>766</v>
       </c>
       <c r="B54" s="1">
-        <v>85400</v>
+        <v>86800</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -6392,7 +6392,7 @@
         <v>495</v>
       </c>
       <c r="B55" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -6400,7 +6400,7 @@
         <v>436</v>
       </c>
       <c r="B56" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -6408,7 +6408,7 @@
         <v>126</v>
       </c>
       <c r="B57" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -6416,7 +6416,7 @@
         <v>496</v>
       </c>
       <c r="B58" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -6424,7 +6424,7 @@
         <v>767</v>
       </c>
       <c r="B59" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -6432,7 +6432,7 @@
         <v>30</v>
       </c>
       <c r="B60" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -6440,7 +6440,7 @@
         <v>427</v>
       </c>
       <c r="B61" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -6448,7 +6448,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -6456,7 +6456,7 @@
         <v>768</v>
       </c>
       <c r="B63" s="1">
-        <v>152500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -6464,7 +6464,7 @@
         <v>769</v>
       </c>
       <c r="B64" s="1">
-        <v>134200</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -6472,7 +6472,7 @@
         <v>127</v>
       </c>
       <c r="B65" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -6480,7 +6480,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -6488,7 +6488,7 @@
         <v>116</v>
       </c>
       <c r="B67" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6496,7 +6496,7 @@
         <v>14</v>
       </c>
       <c r="B68" s="1">
-        <v>79300</v>
+        <v>80600</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6504,7 +6504,7 @@
         <v>770</v>
       </c>
       <c r="B69" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -6512,7 +6512,7 @@
         <v>771</v>
       </c>
       <c r="B70" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -6520,7 +6520,7 @@
         <v>426</v>
       </c>
       <c r="B71" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -6528,7 +6528,7 @@
         <v>552</v>
       </c>
       <c r="B72" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -6536,7 +6536,7 @@
         <v>825</v>
       </c>
       <c r="B73" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -6544,7 +6544,7 @@
         <v>497</v>
       </c>
       <c r="B74" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -6552,7 +6552,7 @@
         <v>498</v>
       </c>
       <c r="B75" s="1">
-        <v>33550</v>
+        <v>34100</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -6560,7 +6560,7 @@
         <v>772</v>
       </c>
       <c r="B76" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -6568,7 +6568,7 @@
         <v>773</v>
       </c>
       <c r="B77" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -6576,7 +6576,7 @@
         <v>586</v>
       </c>
       <c r="B78" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -6584,7 +6584,7 @@
         <v>15</v>
       </c>
       <c r="B79" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -6592,7 +6592,7 @@
         <v>16</v>
       </c>
       <c r="B80" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -6600,7 +6600,7 @@
         <v>580</v>
       </c>
       <c r="B81" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -6608,7 +6608,7 @@
         <v>688</v>
       </c>
       <c r="B82" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -6616,7 +6616,7 @@
         <v>774</v>
       </c>
       <c r="B83" s="1">
-        <v>2440</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -6624,7 +6624,7 @@
         <v>484</v>
       </c>
       <c r="B84" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -6632,7 +6632,7 @@
         <v>775</v>
       </c>
       <c r="B85" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -6640,7 +6640,7 @@
         <v>735</v>
       </c>
       <c r="B86" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -6648,7 +6648,7 @@
         <v>3</v>
       </c>
       <c r="B87" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -6656,7 +6656,7 @@
         <v>17</v>
       </c>
       <c r="B88" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -6664,7 +6664,7 @@
         <v>128</v>
       </c>
       <c r="B89" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -6672,7 +6672,7 @@
         <v>715</v>
       </c>
       <c r="B90" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -6680,7 +6680,7 @@
         <v>499</v>
       </c>
       <c r="B91" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -6688,7 +6688,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -6696,7 +6696,7 @@
         <v>623</v>
       </c>
       <c r="B93" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -6704,7 +6704,7 @@
         <v>776</v>
       </c>
       <c r="B94" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -6712,7 +6712,7 @@
         <v>18</v>
       </c>
       <c r="B95" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -6720,7 +6720,7 @@
         <v>19</v>
       </c>
       <c r="B96" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -6728,7 +6728,7 @@
         <v>500</v>
       </c>
       <c r="B97" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -6736,7 +6736,7 @@
         <v>501</v>
       </c>
       <c r="B98" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -6744,7 +6744,7 @@
         <v>25</v>
       </c>
       <c r="B99" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -6752,7 +6752,7 @@
         <v>553</v>
       </c>
       <c r="B100" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -6760,7 +6760,7 @@
         <v>777</v>
       </c>
       <c r="B101" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -6768,7 +6768,7 @@
         <v>778</v>
       </c>
       <c r="B102" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -6776,7 +6776,7 @@
         <v>779</v>
       </c>
       <c r="B103" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -6784,7 +6784,7 @@
         <v>780</v>
       </c>
       <c r="B104" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -6792,7 +6792,7 @@
         <v>129</v>
       </c>
       <c r="B105" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -6800,7 +6800,7 @@
         <v>502</v>
       </c>
       <c r="B106" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -6808,7 +6808,7 @@
         <v>781</v>
       </c>
       <c r="B107" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -6816,7 +6816,7 @@
         <v>752</v>
       </c>
       <c r="B108" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -6824,7 +6824,7 @@
         <v>723</v>
       </c>
       <c r="B109" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -6832,7 +6832,7 @@
         <v>720</v>
       </c>
       <c r="B110" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -6840,7 +6840,7 @@
         <v>721</v>
       </c>
       <c r="B111" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -6848,7 +6848,7 @@
         <v>503</v>
       </c>
       <c r="B112" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -6856,7 +6856,7 @@
         <v>100</v>
       </c>
       <c r="B113" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -6864,7 +6864,7 @@
         <v>826</v>
       </c>
       <c r="B114" s="1">
-        <v>213500</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -6872,7 +6872,7 @@
         <v>654</v>
       </c>
       <c r="B115" s="1">
-        <v>213500</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -6880,7 +6880,7 @@
         <v>24</v>
       </c>
       <c r="B116" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -6888,7 +6888,7 @@
         <v>782</v>
       </c>
       <c r="B117" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -6896,7 +6896,7 @@
         <v>740</v>
       </c>
       <c r="B118" s="1">
-        <v>134200</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -6904,7 +6904,7 @@
         <v>20</v>
       </c>
       <c r="B119" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -6912,7 +6912,7 @@
         <v>433</v>
       </c>
       <c r="B120" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -6920,7 +6920,7 @@
         <v>783</v>
       </c>
       <c r="B121" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -6928,7 +6928,7 @@
         <v>115</v>
       </c>
       <c r="B122" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -6936,7 +6936,7 @@
         <v>504</v>
       </c>
       <c r="B123" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -6944,7 +6944,7 @@
         <v>505</v>
       </c>
       <c r="B124" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -6952,7 +6952,7 @@
         <v>784</v>
       </c>
       <c r="B125" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -6960,7 +6960,7 @@
         <v>716</v>
       </c>
       <c r="B126" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -6968,7 +6968,7 @@
         <v>785</v>
       </c>
       <c r="B127" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -6976,7 +6976,7 @@
         <v>506</v>
       </c>
       <c r="B128" s="1">
-        <v>45750</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -6984,7 +6984,7 @@
         <v>21</v>
       </c>
       <c r="B129" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -6992,7 +6992,7 @@
         <v>756</v>
       </c>
       <c r="B130" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7000,7 +7000,7 @@
         <v>480</v>
       </c>
       <c r="B131" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7008,7 +7008,7 @@
         <v>786</v>
       </c>
       <c r="B132" s="1">
-        <v>79300</v>
+        <v>80600</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7016,7 +7016,7 @@
         <v>787</v>
       </c>
       <c r="B133" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7024,7 +7024,7 @@
         <v>788</v>
       </c>
       <c r="B134" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7032,7 +7032,7 @@
         <v>789</v>
       </c>
       <c r="B135" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7040,7 +7040,7 @@
         <v>73</v>
       </c>
       <c r="B136" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7048,7 +7048,7 @@
         <v>74</v>
       </c>
       <c r="B137" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7056,7 +7056,7 @@
         <v>162</v>
       </c>
       <c r="B138" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7064,7 +7064,7 @@
         <v>790</v>
       </c>
       <c r="B139" s="1">
-        <v>45750</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7072,7 +7072,7 @@
         <v>130</v>
       </c>
       <c r="B140" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7080,7 +7080,7 @@
         <v>791</v>
       </c>
       <c r="B141" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7088,7 +7088,7 @@
         <v>709</v>
       </c>
       <c r="B142" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7096,7 +7096,7 @@
         <v>432</v>
       </c>
       <c r="B143" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7104,7 +7104,7 @@
         <v>507</v>
       </c>
       <c r="B144" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7112,7 +7112,7 @@
         <v>508</v>
       </c>
       <c r="B145" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7120,7 +7120,7 @@
         <v>437</v>
       </c>
       <c r="B146" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7128,7 +7128,7 @@
         <v>509</v>
       </c>
       <c r="B147" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7136,7 +7136,7 @@
         <v>792</v>
       </c>
       <c r="B148" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7144,7 +7144,7 @@
         <v>4</v>
       </c>
       <c r="B149" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7152,7 +7152,7 @@
         <v>793</v>
       </c>
       <c r="B150" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7160,7 +7160,7 @@
         <v>650</v>
       </c>
       <c r="B151" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7168,7 +7168,7 @@
         <v>651</v>
       </c>
       <c r="B152" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7176,7 +7176,7 @@
         <v>588</v>
       </c>
       <c r="B153" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7184,7 +7184,7 @@
         <v>554</v>
       </c>
       <c r="B154" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7192,7 +7192,7 @@
         <v>510</v>
       </c>
       <c r="B155" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7200,7 +7200,7 @@
         <v>403</v>
       </c>
       <c r="B156" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7208,7 +7208,7 @@
         <v>546</v>
       </c>
       <c r="B157" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7216,7 +7216,7 @@
         <v>441</v>
       </c>
       <c r="B158" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7224,7 +7224,7 @@
         <v>556</v>
       </c>
       <c r="B159" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7232,7 +7232,7 @@
         <v>557</v>
       </c>
       <c r="B160" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7240,7 +7240,7 @@
         <v>794</v>
       </c>
       <c r="B161" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7248,7 +7248,7 @@
         <v>435</v>
       </c>
       <c r="B162" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7256,7 +7256,7 @@
         <v>795</v>
       </c>
       <c r="B163" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7264,7 +7264,7 @@
         <v>796</v>
       </c>
       <c r="B164" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -7272,7 +7272,7 @@
         <v>624</v>
       </c>
       <c r="B165" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -7280,7 +7280,7 @@
         <v>10</v>
       </c>
       <c r="B166" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -7288,7 +7288,7 @@
         <v>797</v>
       </c>
       <c r="B167" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
   </sheetData>
@@ -7318,7 +7318,7 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>85400</v>
+        <v>86800</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7326,7 +7326,7 @@
         <v>745</v>
       </c>
       <c r="B3" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7334,7 +7334,7 @@
         <v>746</v>
       </c>
       <c r="B4" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7342,7 +7342,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1">
-        <v>85400</v>
+        <v>86800</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7350,7 +7350,7 @@
         <v>747</v>
       </c>
       <c r="B6" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7358,7 +7358,7 @@
         <v>122</v>
       </c>
       <c r="B7" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7366,7 +7366,7 @@
         <v>131</v>
       </c>
       <c r="B8" s="1">
-        <v>152500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7374,7 +7374,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7382,7 +7382,7 @@
         <v>567</v>
       </c>
       <c r="B10" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7390,7 +7390,7 @@
         <v>82</v>
       </c>
       <c r="B11" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7398,7 +7398,7 @@
         <v>165</v>
       </c>
       <c r="B12" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7406,7 +7406,7 @@
         <v>589</v>
       </c>
       <c r="B13" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7414,7 +7414,7 @@
         <v>798</v>
       </c>
       <c r="B14" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7422,7 +7422,7 @@
         <v>132</v>
       </c>
       <c r="B15" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -7430,7 +7430,7 @@
         <v>133</v>
       </c>
       <c r="B16" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -7438,7 +7438,7 @@
         <v>753</v>
       </c>
       <c r="B17" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -7446,7 +7446,7 @@
         <v>625</v>
       </c>
       <c r="B18" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -7454,7 +7454,7 @@
         <v>823</v>
       </c>
       <c r="B19" s="1">
-        <v>51850</v>
+        <v>52700</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7462,7 +7462,7 @@
         <v>430</v>
       </c>
       <c r="B20" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7470,7 +7470,7 @@
         <v>163</v>
       </c>
       <c r="B21" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7478,7 +7478,7 @@
         <v>647</v>
       </c>
       <c r="B22" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7486,7 +7486,7 @@
         <v>581</v>
       </c>
       <c r="B23" s="1">
-        <v>67100</v>
+        <v>68200</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7494,7 +7494,7 @@
         <v>648</v>
       </c>
       <c r="B24" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7502,7 +7502,7 @@
         <v>83</v>
       </c>
       <c r="B25" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7510,7 +7510,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7518,7 +7518,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7526,7 +7526,7 @@
         <v>121</v>
       </c>
       <c r="B28" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7534,7 +7534,7 @@
         <v>134</v>
       </c>
       <c r="B29" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7542,7 +7542,7 @@
         <v>698</v>
       </c>
       <c r="B30" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7550,7 +7550,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7558,7 +7558,7 @@
         <v>477</v>
       </c>
       <c r="B32" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7566,7 +7566,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7574,7 +7574,7 @@
         <v>158</v>
       </c>
       <c r="B34" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7582,7 +7582,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7590,7 +7590,7 @@
         <v>692</v>
       </c>
       <c r="B36" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7598,7 +7598,7 @@
         <v>406</v>
       </c>
       <c r="B37" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7606,7 +7606,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7614,7 +7614,7 @@
         <v>626</v>
       </c>
       <c r="B39" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7622,7 +7622,7 @@
         <v>627</v>
       </c>
       <c r="B40" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7630,7 +7630,7 @@
         <v>628</v>
       </c>
       <c r="B41" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7638,7 +7638,7 @@
         <v>629</v>
       </c>
       <c r="B42" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -7646,7 +7646,7 @@
         <v>511</v>
       </c>
       <c r="B43" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7654,7 +7654,7 @@
         <v>85</v>
       </c>
       <c r="B44" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -7662,7 +7662,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -7670,7 +7670,7 @@
         <v>86</v>
       </c>
       <c r="B46" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7678,7 +7678,7 @@
         <v>135</v>
       </c>
       <c r="B47" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7686,7 +7686,7 @@
         <v>136</v>
       </c>
       <c r="B48" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -7694,7 +7694,7 @@
         <v>87</v>
       </c>
       <c r="B49" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -7702,7 +7702,7 @@
         <v>444</v>
       </c>
       <c r="B50" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -7710,7 +7710,7 @@
         <v>512</v>
       </c>
       <c r="B51" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -7718,7 +7718,7 @@
         <v>137</v>
       </c>
       <c r="B52" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -7726,7 +7726,7 @@
         <v>513</v>
       </c>
       <c r="B53" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -7734,7 +7734,7 @@
         <v>451</v>
       </c>
       <c r="B54" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -7742,7 +7742,7 @@
         <v>452</v>
       </c>
       <c r="B55" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -7750,7 +7750,7 @@
         <v>138</v>
       </c>
       <c r="B56" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -7758,7 +7758,7 @@
         <v>699</v>
       </c>
       <c r="B57" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -7766,7 +7766,7 @@
         <v>583</v>
       </c>
       <c r="B58" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -7774,7 +7774,7 @@
         <v>584</v>
       </c>
       <c r="B59" s="1">
-        <v>45750</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -7782,7 +7782,7 @@
         <v>139</v>
       </c>
       <c r="B60" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -7790,7 +7790,7 @@
         <v>551</v>
       </c>
       <c r="B61" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -7798,7 +7798,7 @@
         <v>140</v>
       </c>
       <c r="B62" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -7806,7 +7806,7 @@
         <v>89</v>
       </c>
       <c r="B63" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -7814,7 +7814,7 @@
         <v>88</v>
       </c>
       <c r="B64" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -7822,7 +7822,7 @@
         <v>559</v>
       </c>
       <c r="B65" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -7830,7 +7830,7 @@
         <v>722</v>
       </c>
       <c r="B66" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -7838,7 +7838,7 @@
         <v>118</v>
       </c>
       <c r="B67" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -7846,7 +7846,7 @@
         <v>799</v>
       </c>
       <c r="B68" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -7854,7 +7854,7 @@
         <v>39</v>
       </c>
       <c r="B69" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -7862,7 +7862,7 @@
         <v>40</v>
       </c>
       <c r="B70" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -7870,7 +7870,7 @@
         <v>800</v>
       </c>
       <c r="B71" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -7878,7 +7878,7 @@
         <v>120</v>
       </c>
       <c r="B72" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7886,7 +7886,7 @@
         <v>41</v>
       </c>
       <c r="B73" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7894,7 +7894,7 @@
         <v>42</v>
       </c>
       <c r="B74" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7902,7 +7902,7 @@
         <v>43</v>
       </c>
       <c r="B75" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7910,7 +7910,7 @@
         <v>44</v>
       </c>
       <c r="B76" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7918,7 +7918,7 @@
         <v>45</v>
       </c>
       <c r="B77" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7926,7 +7926,7 @@
         <v>46</v>
       </c>
       <c r="B78" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7934,7 +7934,7 @@
         <v>687</v>
       </c>
       <c r="B79" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7942,7 +7942,7 @@
         <v>90</v>
       </c>
       <c r="B80" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7950,7 +7950,7 @@
         <v>32</v>
       </c>
       <c r="B81" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7958,7 +7958,7 @@
         <v>27</v>
       </c>
       <c r="B82" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7966,7 +7966,7 @@
         <v>33</v>
       </c>
       <c r="B83" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7974,7 +7974,7 @@
         <v>141</v>
       </c>
       <c r="B84" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7982,7 +7982,7 @@
         <v>49</v>
       </c>
       <c r="B85" s="1">
-        <v>152500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7990,7 +7990,7 @@
         <v>48</v>
       </c>
       <c r="B86" s="1">
-        <v>152500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7998,7 +7998,7 @@
         <v>47</v>
       </c>
       <c r="B87" s="1">
-        <v>140300</v>
+        <v>142600</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -8006,7 +8006,7 @@
         <v>50</v>
       </c>
       <c r="B88" s="1">
-        <v>152500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -8014,7 +8014,7 @@
         <v>51</v>
       </c>
       <c r="B89" s="1">
-        <v>152500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -8022,7 +8022,7 @@
         <v>474</v>
       </c>
       <c r="B90" s="1">
-        <v>152500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -8030,7 +8030,7 @@
         <v>55</v>
       </c>
       <c r="B91" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -8038,7 +8038,7 @@
         <v>52</v>
       </c>
       <c r="B92" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -8046,7 +8046,7 @@
         <v>53</v>
       </c>
       <c r="B93" s="1">
-        <v>134200</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -8054,7 +8054,7 @@
         <v>54</v>
       </c>
       <c r="B94" s="1">
-        <v>134200</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -8062,7 +8062,7 @@
         <v>56</v>
       </c>
       <c r="B95" s="1">
-        <v>134200</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -8070,7 +8070,7 @@
         <v>475</v>
       </c>
       <c r="B96" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -8078,7 +8078,7 @@
         <v>514</v>
       </c>
       <c r="B97" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -8086,7 +8086,7 @@
         <v>700</v>
       </c>
       <c r="B98" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -8094,7 +8094,7 @@
         <v>701</v>
       </c>
       <c r="B99" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -8102,7 +8102,7 @@
         <v>142</v>
       </c>
       <c r="B100" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -8110,7 +8110,7 @@
         <v>801</v>
       </c>
       <c r="B101" s="1">
-        <v>85400</v>
+        <v>86800</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -8118,7 +8118,7 @@
         <v>544</v>
       </c>
       <c r="B102" s="1">
-        <v>85400</v>
+        <v>86800</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -8126,7 +8126,7 @@
         <v>802</v>
       </c>
       <c r="B103" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -8134,7 +8134,7 @@
         <v>643</v>
       </c>
       <c r="B104" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -8142,7 +8142,7 @@
         <v>515</v>
       </c>
       <c r="B105" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -8150,7 +8150,7 @@
         <v>428</v>
       </c>
       <c r="B106" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -8158,7 +8158,7 @@
         <v>693</v>
       </c>
       <c r="B107" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -8166,7 +8166,7 @@
         <v>552</v>
       </c>
       <c r="B108" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -8174,7 +8174,7 @@
         <v>825</v>
       </c>
       <c r="B109" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -8182,7 +8182,7 @@
         <v>702</v>
       </c>
       <c r="B110" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -8190,7 +8190,7 @@
         <v>93</v>
       </c>
       <c r="B111" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -8198,7 +8198,7 @@
         <v>92</v>
       </c>
       <c r="B112" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -8206,7 +8206,7 @@
         <v>91</v>
       </c>
       <c r="B113" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -8214,7 +8214,7 @@
         <v>94</v>
       </c>
       <c r="B114" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -8222,7 +8222,7 @@
         <v>585</v>
       </c>
       <c r="B115" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -8230,7 +8230,7 @@
         <v>646</v>
       </c>
       <c r="B116" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -8238,7 +8238,7 @@
         <v>560</v>
       </c>
       <c r="B117" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -8246,7 +8246,7 @@
         <v>57</v>
       </c>
       <c r="B118" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -8254,7 +8254,7 @@
         <v>58</v>
       </c>
       <c r="B119" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -8262,7 +8262,7 @@
         <v>59</v>
       </c>
       <c r="B120" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -8270,7 +8270,7 @@
         <v>561</v>
       </c>
       <c r="B121" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -8278,7 +8278,7 @@
         <v>562</v>
       </c>
       <c r="B122" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -8286,7 +8286,7 @@
         <v>677</v>
       </c>
       <c r="B123" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -8294,7 +8294,7 @@
         <v>685</v>
       </c>
       <c r="B124" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -8302,7 +8302,7 @@
         <v>686</v>
       </c>
       <c r="B125" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -8310,7 +8310,7 @@
         <v>484</v>
       </c>
       <c r="B126" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -8318,7 +8318,7 @@
         <v>735</v>
       </c>
       <c r="B127" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -8326,7 +8326,7 @@
         <v>60</v>
       </c>
       <c r="B128" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -8334,7 +8334,7 @@
         <v>61</v>
       </c>
       <c r="B129" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -8342,7 +8342,7 @@
         <v>157</v>
       </c>
       <c r="B130" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -8350,7 +8350,7 @@
         <v>62</v>
       </c>
       <c r="B131" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -8358,7 +8358,7 @@
         <v>754</v>
       </c>
       <c r="B132" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -8366,7 +8366,7 @@
         <v>694</v>
       </c>
       <c r="B133" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -8374,7 +8374,7 @@
         <v>563</v>
       </c>
       <c r="B134" s="1">
-        <v>85400</v>
+        <v>86800</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -8382,7 +8382,7 @@
         <v>697</v>
       </c>
       <c r="B135" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -8390,7 +8390,7 @@
         <v>455</v>
       </c>
       <c r="B136" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -8398,7 +8398,7 @@
         <v>623</v>
       </c>
       <c r="B137" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -8406,7 +8406,7 @@
         <v>630</v>
       </c>
       <c r="B138" s="1">
-        <v>335500</v>
+        <v>341000</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -8414,7 +8414,7 @@
         <v>631</v>
       </c>
       <c r="B139" s="1">
-        <v>347700</v>
+        <v>353400</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -8422,7 +8422,7 @@
         <v>449</v>
       </c>
       <c r="B140" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -8430,7 +8430,7 @@
         <v>448</v>
       </c>
       <c r="B141" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -8438,7 +8438,7 @@
         <v>450</v>
       </c>
       <c r="B142" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -8446,7 +8446,7 @@
         <v>447</v>
       </c>
       <c r="B143" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -8454,7 +8454,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -8462,7 +8462,7 @@
         <v>446</v>
       </c>
       <c r="B145" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -8470,7 +8470,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -8478,7 +8478,7 @@
         <v>591</v>
       </c>
       <c r="B147" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -8486,7 +8486,7 @@
         <v>96</v>
       </c>
       <c r="B148" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -8494,7 +8494,7 @@
         <v>95</v>
       </c>
       <c r="B149" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -8502,7 +8502,7 @@
         <v>97</v>
       </c>
       <c r="B150" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -8510,7 +8510,7 @@
         <v>553</v>
       </c>
       <c r="B151" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -8518,7 +8518,7 @@
         <v>803</v>
       </c>
       <c r="B152" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -8526,7 +8526,7 @@
         <v>804</v>
       </c>
       <c r="B153" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -8534,7 +8534,7 @@
         <v>145</v>
       </c>
       <c r="B154" s="1">
-        <v>152500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -8542,7 +8542,7 @@
         <v>119</v>
       </c>
       <c r="B155" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -8550,7 +8550,7 @@
         <v>703</v>
       </c>
       <c r="B156" s="1">
-        <v>45750</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -8558,7 +8558,7 @@
         <v>704</v>
       </c>
       <c r="B157" s="1">
-        <v>45750</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -8566,7 +8566,7 @@
         <v>98</v>
       </c>
       <c r="B158" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -8574,7 +8574,7 @@
         <v>63</v>
       </c>
       <c r="B159" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -8582,7 +8582,7 @@
         <v>472</v>
       </c>
       <c r="B160" s="1">
-        <v>85400</v>
+        <v>86800</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -8590,7 +8590,7 @@
         <v>99</v>
       </c>
       <c r="B161" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -8598,7 +8598,7 @@
         <v>720</v>
       </c>
       <c r="B162" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -8606,7 +8606,7 @@
         <v>724</v>
       </c>
       <c r="B163" s="1">
-        <v>45750</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -8614,7 +8614,7 @@
         <v>721</v>
       </c>
       <c r="B164" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -8622,7 +8622,7 @@
         <v>725</v>
       </c>
       <c r="B165" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -8630,7 +8630,7 @@
         <v>695</v>
       </c>
       <c r="B166" s="1">
-        <v>915</v>
+        <v>930</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -8638,7 +8638,7 @@
         <v>101</v>
       </c>
       <c r="B167" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -8646,7 +8646,7 @@
         <v>102</v>
       </c>
       <c r="B168" s="1">
-        <v>140300</v>
+        <v>142600</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -8654,7 +8654,7 @@
         <v>103</v>
       </c>
       <c r="B169" s="1">
-        <v>213500</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -8662,7 +8662,7 @@
         <v>632</v>
       </c>
       <c r="B170" s="1">
-        <v>213500</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -8670,7 +8670,7 @@
         <v>633</v>
       </c>
       <c r="B171" s="1">
-        <v>219600</v>
+        <v>223200</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -8678,7 +8678,7 @@
         <v>678</v>
       </c>
       <c r="B172" s="1">
-        <v>225700</v>
+        <v>229400</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -8686,7 +8686,7 @@
         <v>679</v>
       </c>
       <c r="B173" s="1">
-        <v>213500</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -8694,7 +8694,7 @@
         <v>680</v>
       </c>
       <c r="B174" s="1">
-        <v>213500</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8702,7 +8702,7 @@
         <v>681</v>
       </c>
       <c r="B175" s="1">
-        <v>213500</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -8710,7 +8710,7 @@
         <v>740</v>
       </c>
       <c r="B176" s="1">
-        <v>134200</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -8718,7 +8718,7 @@
         <v>23</v>
       </c>
       <c r="B177" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -8726,7 +8726,7 @@
         <v>442</v>
       </c>
       <c r="B178" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -8734,7 +8734,7 @@
         <v>564</v>
       </c>
       <c r="B179" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -8742,7 +8742,7 @@
         <v>146</v>
       </c>
       <c r="B180" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -8750,7 +8750,7 @@
         <v>147</v>
       </c>
       <c r="B181" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -8758,7 +8758,7 @@
         <v>755</v>
       </c>
       <c r="B182" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -8766,7 +8766,7 @@
         <v>705</v>
       </c>
       <c r="B183" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -8774,7 +8774,7 @@
         <v>652</v>
       </c>
       <c r="B184" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -8782,7 +8782,7 @@
         <v>805</v>
       </c>
       <c r="B185" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -8790,7 +8790,7 @@
         <v>748</v>
       </c>
       <c r="B186" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -8798,7 +8798,7 @@
         <v>148</v>
       </c>
       <c r="B187" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -8806,7 +8806,7 @@
         <v>706</v>
       </c>
       <c r="B188" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -8814,7 +8814,7 @@
         <v>516</v>
       </c>
       <c r="B189" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -8822,7 +8822,7 @@
         <v>749</v>
       </c>
       <c r="B190" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -8830,7 +8830,7 @@
         <v>149</v>
       </c>
       <c r="B191" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -8838,7 +8838,7 @@
         <v>565</v>
       </c>
       <c r="B192" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -8846,7 +8846,7 @@
         <v>707</v>
       </c>
       <c r="B193" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -8854,7 +8854,7 @@
         <v>150</v>
       </c>
       <c r="B194" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -8862,7 +8862,7 @@
         <v>104</v>
       </c>
       <c r="B195" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -8870,7 +8870,7 @@
         <v>517</v>
       </c>
       <c r="B196" s="1">
-        <v>45750</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -8878,7 +8878,7 @@
         <v>151</v>
       </c>
       <c r="B197" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -8886,7 +8886,7 @@
         <v>481</v>
       </c>
       <c r="B198" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -8894,7 +8894,7 @@
         <v>708</v>
       </c>
       <c r="B199" s="1">
-        <v>103700</v>
+        <v>105400</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -8902,7 +8902,7 @@
         <v>64</v>
       </c>
       <c r="B200" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -8910,7 +8910,7 @@
         <v>152</v>
       </c>
       <c r="B201" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -8918,7 +8918,7 @@
         <v>65</v>
       </c>
       <c r="B202" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -8926,7 +8926,7 @@
         <v>545</v>
       </c>
       <c r="B203" s="1">
-        <v>85400</v>
+        <v>86800</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -8934,7 +8934,7 @@
         <v>547</v>
       </c>
       <c r="B204" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -8942,7 +8942,7 @@
         <v>66</v>
       </c>
       <c r="B205" s="1">
-        <v>79300</v>
+        <v>80600</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -8950,7 +8950,7 @@
         <v>67</v>
       </c>
       <c r="B206" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -8958,7 +8958,7 @@
         <v>68</v>
       </c>
       <c r="B207" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -8966,7 +8966,7 @@
         <v>69</v>
       </c>
       <c r="B208" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -8974,7 +8974,7 @@
         <v>70</v>
       </c>
       <c r="B209" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -8982,7 +8982,7 @@
         <v>71</v>
       </c>
       <c r="B210" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -8990,7 +8990,7 @@
         <v>72</v>
       </c>
       <c r="B211" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -8998,7 +8998,7 @@
         <v>473</v>
       </c>
       <c r="B212" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -9006,7 +9006,7 @@
         <v>160</v>
       </c>
       <c r="B213" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -9014,7 +9014,7 @@
         <v>161</v>
       </c>
       <c r="B214" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -9022,7 +9022,7 @@
         <v>75</v>
       </c>
       <c r="B215" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -9030,7 +9030,7 @@
         <v>159</v>
       </c>
       <c r="B216" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -9038,7 +9038,7 @@
         <v>107</v>
       </c>
       <c r="B217" s="1">
-        <v>152500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -9046,7 +9046,7 @@
         <v>108</v>
       </c>
       <c r="B218" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -9054,7 +9054,7 @@
         <v>110</v>
       </c>
       <c r="B219" s="1">
-        <v>122000</v>
+        <v>124000</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -9062,7 +9062,7 @@
         <v>105</v>
       </c>
       <c r="B220" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -9070,7 +9070,7 @@
         <v>106</v>
       </c>
       <c r="B221" s="1">
-        <v>91500</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -9078,7 +9078,7 @@
         <v>109</v>
       </c>
       <c r="B222" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -9086,7 +9086,7 @@
         <v>111</v>
       </c>
       <c r="B223" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -9094,7 +9094,7 @@
         <v>153</v>
       </c>
       <c r="B224" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -9102,7 +9102,7 @@
         <v>154</v>
       </c>
       <c r="B225" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -9110,7 +9110,7 @@
         <v>76</v>
       </c>
       <c r="B226" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -9118,7 +9118,7 @@
         <v>77</v>
       </c>
       <c r="B227" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -9126,7 +9126,7 @@
         <v>714</v>
       </c>
       <c r="B228" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -9134,7 +9134,7 @@
         <v>78</v>
       </c>
       <c r="B229" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -9142,7 +9142,7 @@
         <v>443</v>
       </c>
       <c r="B230" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -9150,7 +9150,7 @@
         <v>79</v>
       </c>
       <c r="B231" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -9158,7 +9158,7 @@
         <v>518</v>
       </c>
       <c r="B232" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -9166,7 +9166,7 @@
         <v>80</v>
       </c>
       <c r="B233" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -9174,7 +9174,7 @@
         <v>81</v>
       </c>
       <c r="B234" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -9182,7 +9182,7 @@
         <v>519</v>
       </c>
       <c r="B235" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -9190,7 +9190,7 @@
         <v>113</v>
       </c>
       <c r="B236" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -9198,7 +9198,7 @@
         <v>114</v>
       </c>
       <c r="B237" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -9206,7 +9206,7 @@
         <v>453</v>
       </c>
       <c r="B238" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -9214,7 +9214,7 @@
         <v>710</v>
       </c>
       <c r="B239" s="1">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -9222,7 +9222,7 @@
         <v>750</v>
       </c>
       <c r="B240" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -9230,7 +9230,7 @@
         <v>650</v>
       </c>
       <c r="B241" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -9238,7 +9238,7 @@
         <v>588</v>
       </c>
       <c r="B242" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -9246,7 +9246,7 @@
         <v>555</v>
       </c>
       <c r="B243" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -9254,7 +9254,7 @@
         <v>117</v>
       </c>
       <c r="B244" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -9262,7 +9262,7 @@
         <v>403</v>
       </c>
       <c r="B245" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -9270,7 +9270,7 @@
         <v>546</v>
       </c>
       <c r="B246" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -9278,7 +9278,7 @@
         <v>568</v>
       </c>
       <c r="B247" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -9286,7 +9286,7 @@
         <v>566</v>
       </c>
       <c r="B248" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -9294,7 +9294,7 @@
         <v>556</v>
       </c>
       <c r="B249" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -9302,7 +9302,7 @@
         <v>557</v>
       </c>
       <c r="B250" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -9310,7 +9310,7 @@
         <v>634</v>
       </c>
       <c r="B251" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -9318,7 +9318,7 @@
         <v>711</v>
       </c>
       <c r="B252" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -9326,7 +9326,7 @@
         <v>712</v>
       </c>
       <c r="B253" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -9334,7 +9334,7 @@
         <v>558</v>
       </c>
       <c r="B254" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -9342,7 +9342,7 @@
         <v>635</v>
       </c>
       <c r="B255" s="1">
-        <v>140300</v>
+        <v>142600</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -9350,7 +9350,7 @@
         <v>713</v>
       </c>
       <c r="B256" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -9358,7 +9358,7 @@
         <v>794</v>
       </c>
       <c r="B257" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -9366,7 +9366,7 @@
         <v>445</v>
       </c>
       <c r="B258" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -9374,7 +9374,7 @@
         <v>682</v>
       </c>
       <c r="B259" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -9382,7 +9382,7 @@
         <v>112</v>
       </c>
       <c r="B260" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -9390,7 +9390,7 @@
         <v>155</v>
       </c>
       <c r="B261" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -9398,7 +9398,7 @@
         <v>156</v>
       </c>
       <c r="B262" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
   </sheetData>
@@ -9428,7 +9428,7 @@
         <v>592</v>
       </c>
       <c r="B2" s="1">
-        <v>109800</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9436,7 +9436,7 @@
         <v>806</v>
       </c>
       <c r="B3" s="1">
-        <v>82350</v>
+        <v>83700</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9444,7 +9444,7 @@
         <v>807</v>
       </c>
       <c r="B4" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9452,7 +9452,7 @@
         <v>589</v>
       </c>
       <c r="B5" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9460,7 +9460,7 @@
         <v>808</v>
       </c>
       <c r="B6" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9468,7 +9468,7 @@
         <v>581</v>
       </c>
       <c r="B7" s="1">
-        <v>67100</v>
+        <v>68200</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9476,7 +9476,7 @@
         <v>648</v>
       </c>
       <c r="B8" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9484,7 +9484,7 @@
         <v>520</v>
       </c>
       <c r="B9" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -9492,7 +9492,7 @@
         <v>521</v>
       </c>
       <c r="B10" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9500,7 +9500,7 @@
         <v>522</v>
       </c>
       <c r="B11" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9508,7 +9508,7 @@
         <v>523</v>
       </c>
       <c r="B12" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -9516,7 +9516,7 @@
         <v>809</v>
       </c>
       <c r="B13" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -9524,7 +9524,7 @@
         <v>551</v>
       </c>
       <c r="B14" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -9532,7 +9532,7 @@
         <v>722</v>
       </c>
       <c r="B15" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -9540,7 +9540,7 @@
         <v>524</v>
       </c>
       <c r="B16" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -9548,7 +9548,7 @@
         <v>525</v>
       </c>
       <c r="B17" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -9556,7 +9556,7 @@
         <v>691</v>
       </c>
       <c r="B18" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -9564,7 +9564,7 @@
         <v>526</v>
       </c>
       <c r="B19" s="1">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -9572,7 +9572,7 @@
         <v>810</v>
       </c>
       <c r="B20" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -9580,7 +9580,7 @@
         <v>527</v>
       </c>
       <c r="B21" s="1">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -9588,7 +9588,7 @@
         <v>552</v>
       </c>
       <c r="B22" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -9596,7 +9596,7 @@
         <v>825</v>
       </c>
       <c r="B23" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -9604,7 +9604,7 @@
         <v>528</v>
       </c>
       <c r="B24" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -9612,7 +9612,7 @@
         <v>821</v>
       </c>
       <c r="B25" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -9620,7 +9620,7 @@
         <v>529</v>
       </c>
       <c r="B26" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -9628,7 +9628,7 @@
         <v>684</v>
       </c>
       <c r="B27" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -9636,7 +9636,7 @@
         <v>484</v>
       </c>
       <c r="B28">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -9644,7 +9644,7 @@
         <v>735</v>
       </c>
       <c r="B29">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -9652,7 +9652,7 @@
         <v>530</v>
       </c>
       <c r="B30">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -9660,7 +9660,7 @@
         <v>531</v>
       </c>
       <c r="B31">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -9668,7 +9668,7 @@
         <v>532</v>
       </c>
       <c r="B32">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -9676,7 +9676,7 @@
         <v>533</v>
       </c>
       <c r="B33">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -9684,7 +9684,7 @@
         <v>534</v>
       </c>
       <c r="B34">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -9692,7 +9692,7 @@
         <v>535</v>
       </c>
       <c r="B35">
-        <v>67100</v>
+        <v>68200</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -9700,7 +9700,7 @@
         <v>631</v>
       </c>
       <c r="B36">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -9708,7 +9708,7 @@
         <v>553</v>
       </c>
       <c r="B37">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -9716,7 +9716,7 @@
         <v>726</v>
       </c>
       <c r="B38">
-        <v>51850</v>
+        <v>52700</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -9724,7 +9724,7 @@
         <v>727</v>
       </c>
       <c r="B39">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -9732,7 +9732,7 @@
         <v>536</v>
       </c>
       <c r="B40">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -9740,7 +9740,7 @@
         <v>683</v>
       </c>
       <c r="B41">
-        <v>219600</v>
+        <v>223200</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -9748,7 +9748,7 @@
         <v>636</v>
       </c>
       <c r="B42">
-        <v>225700</v>
+        <v>229400</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -9756,7 +9756,7 @@
         <v>740</v>
       </c>
       <c r="B43">
-        <v>134200</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -9764,7 +9764,7 @@
         <v>537</v>
       </c>
       <c r="B44">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -9772,7 +9772,7 @@
         <v>538</v>
       </c>
       <c r="B45">
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -9780,7 +9780,7 @@
         <v>811</v>
       </c>
       <c r="B46">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -9788,7 +9788,7 @@
         <v>812</v>
       </c>
       <c r="B47">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -9796,7 +9796,7 @@
         <v>813</v>
       </c>
       <c r="B48">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -9804,7 +9804,7 @@
         <v>539</v>
       </c>
       <c r="B49">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -9812,7 +9812,7 @@
         <v>814</v>
       </c>
       <c r="B50">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -9820,7 +9820,7 @@
         <v>815</v>
       </c>
       <c r="B51">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -9828,7 +9828,7 @@
         <v>816</v>
       </c>
       <c r="B52">
-        <v>15250</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -9836,7 +9836,7 @@
         <v>588</v>
       </c>
       <c r="B53">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -9844,7 +9844,7 @@
         <v>817</v>
       </c>
       <c r="B54">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -9852,7 +9852,7 @@
         <v>818</v>
       </c>
       <c r="B55">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -9860,7 +9860,7 @@
         <v>819</v>
       </c>
       <c r="B56">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -9868,7 +9868,7 @@
         <v>548</v>
       </c>
       <c r="B57">
-        <v>42700</v>
+        <v>43400</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -9876,7 +9876,7 @@
         <v>549</v>
       </c>
       <c r="B58">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -9884,7 +9884,7 @@
         <v>403</v>
       </c>
       <c r="B59">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -9892,7 +9892,7 @@
         <v>546</v>
       </c>
       <c r="B60">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -9900,7 +9900,7 @@
         <v>556</v>
       </c>
       <c r="B61">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -9908,7 +9908,7 @@
         <v>557</v>
       </c>
       <c r="B62">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -9916,7 +9916,7 @@
         <v>540</v>
       </c>
       <c r="B63">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -9924,7 +9924,7 @@
         <v>541</v>
       </c>
       <c r="B64">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -9932,7 +9932,7 @@
         <v>637</v>
       </c>
       <c r="B65">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -9940,7 +9940,7 @@
         <v>542</v>
       </c>
       <c r="B66">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
   </sheetData>
@@ -9970,7 +9970,7 @@
         <v>383</v>
       </c>
       <c r="B2" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9978,7 +9978,7 @@
         <v>384</v>
       </c>
       <c r="B3" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9986,7 +9986,7 @@
         <v>385</v>
       </c>
       <c r="B4" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9994,7 +9994,7 @@
         <v>386</v>
       </c>
       <c r="B5" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -10002,7 +10002,7 @@
         <v>640</v>
       </c>
       <c r="B6" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -10010,7 +10010,7 @@
         <v>387</v>
       </c>
       <c r="B7" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -10018,7 +10018,7 @@
         <v>660</v>
       </c>
       <c r="B8" s="1">
-        <v>24400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -10026,7 +10026,7 @@
         <v>662</v>
       </c>
       <c r="B9" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -10034,7 +10034,7 @@
         <v>661</v>
       </c>
       <c r="B10" s="1">
-        <v>19520</v>
+        <v>19840</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -10042,7 +10042,7 @@
         <v>388</v>
       </c>
       <c r="B11" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -10050,7 +10050,7 @@
         <v>405</v>
       </c>
       <c r="B12" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -10058,7 +10058,7 @@
         <v>659</v>
       </c>
       <c r="B13" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -10066,7 +10066,7 @@
         <v>665</v>
       </c>
       <c r="B14" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -10074,7 +10074,7 @@
         <v>745</v>
       </c>
       <c r="B15" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -10082,7 +10082,7 @@
         <v>389</v>
       </c>
       <c r="B16" s="1">
-        <v>5490</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -10090,7 +10090,7 @@
         <v>589</v>
       </c>
       <c r="B17" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -10098,7 +10098,7 @@
         <v>823</v>
       </c>
       <c r="B18" s="1">
-        <v>51850</v>
+        <v>52700</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -10106,7 +10106,7 @@
         <v>663</v>
       </c>
       <c r="B19" s="1">
-        <v>106750</v>
+        <v>108500</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -10114,7 +10114,7 @@
         <v>655</v>
       </c>
       <c r="B20" s="1">
-        <v>118950</v>
+        <v>120900</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -10122,7 +10122,7 @@
         <v>656</v>
       </c>
       <c r="B21" s="1">
-        <v>134200</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -10130,7 +10130,7 @@
         <v>430</v>
       </c>
       <c r="B22" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -10138,7 +10138,7 @@
         <v>163</v>
       </c>
       <c r="B23" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -10146,7 +10146,7 @@
         <v>647</v>
       </c>
       <c r="B24" s="1">
-        <v>61000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -10154,7 +10154,7 @@
         <v>581</v>
       </c>
       <c r="B25" s="1">
-        <v>67100</v>
+        <v>68200</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -10162,7 +10162,7 @@
         <v>648</v>
       </c>
       <c r="B26" s="1">
-        <v>73200</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -10170,7 +10170,7 @@
         <v>657</v>
       </c>
       <c r="B27" s="1">
-        <v>82350</v>
+        <v>83700</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -10178,7 +10178,7 @@
         <v>658</v>
       </c>
       <c r="B28" s="1">
-        <v>97600</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -10186,7 +10186,7 @@
         <v>664</v>
       </c>
       <c r="B29" s="1">
-        <v>103700</v>
+        <v>105400</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -10194,7 +10194,7 @@
         <v>692</v>
       </c>
       <c r="B30" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -10202,7 +10202,7 @@
         <v>406</v>
       </c>
       <c r="B31" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -10210,7 +10210,7 @@
         <v>402</v>
       </c>
       <c r="B32" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -10218,7 +10218,7 @@
         <v>429</v>
       </c>
       <c r="B33" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -10226,7 +10226,7 @@
         <v>551</v>
       </c>
       <c r="B34" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -10234,7 +10234,7 @@
         <v>390</v>
       </c>
       <c r="B35" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -10242,7 +10242,7 @@
         <v>552</v>
       </c>
       <c r="B36" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -10250,7 +10250,7 @@
         <v>825</v>
       </c>
       <c r="B37" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -10258,7 +10258,7 @@
         <v>820</v>
       </c>
       <c r="B38" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -10266,7 +10266,7 @@
         <v>404</v>
       </c>
       <c r="B39" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -10274,7 +10274,7 @@
         <v>259</v>
       </c>
       <c r="B40" s="1">
-        <v>18300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -10282,7 +10282,7 @@
         <v>425</v>
       </c>
       <c r="B41" s="1">
-        <v>2440</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -10290,7 +10290,7 @@
         <v>484</v>
       </c>
       <c r="B42" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -10298,7 +10298,7 @@
         <v>735</v>
       </c>
       <c r="B43" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -10306,7 +10306,7 @@
         <v>391</v>
       </c>
       <c r="B44" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -10314,7 +10314,7 @@
         <v>392</v>
       </c>
       <c r="B45" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -10322,7 +10322,7 @@
         <v>393</v>
       </c>
       <c r="B46" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -10330,7 +10330,7 @@
         <v>638</v>
       </c>
       <c r="B47" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -10338,7 +10338,7 @@
         <v>394</v>
       </c>
       <c r="B48" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -10346,7 +10346,7 @@
         <v>395</v>
       </c>
       <c r="B49" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -10354,7 +10354,7 @@
         <v>396</v>
       </c>
       <c r="B50" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -10362,7 +10362,7 @@
         <v>728</v>
       </c>
       <c r="B51" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -10370,7 +10370,7 @@
         <v>553</v>
       </c>
       <c r="B52" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -10378,7 +10378,7 @@
         <v>718</v>
       </c>
       <c r="B53" s="1">
-        <v>33550</v>
+        <v>34100</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -10386,7 +10386,7 @@
         <v>719</v>
       </c>
       <c r="B54" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -10394,7 +10394,7 @@
         <v>752</v>
       </c>
       <c r="B55" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -10402,7 +10402,7 @@
         <v>723</v>
       </c>
       <c r="B56" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -10410,7 +10410,7 @@
         <v>720</v>
       </c>
       <c r="B57" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -10418,7 +10418,7 @@
         <v>724</v>
       </c>
       <c r="B58" s="1">
-        <v>45750</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -10426,7 +10426,7 @@
         <v>721</v>
       </c>
       <c r="B59" s="1">
-        <v>39650</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -10434,7 +10434,7 @@
         <v>725</v>
       </c>
       <c r="B60" s="1">
-        <v>48800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -10442,7 +10442,7 @@
         <v>726</v>
       </c>
       <c r="B61" s="1">
-        <v>51850</v>
+        <v>52700</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -10450,7 +10450,7 @@
         <v>727</v>
       </c>
       <c r="B62" s="1">
-        <v>54900</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -10458,7 +10458,7 @@
         <v>740</v>
       </c>
       <c r="B63" s="1">
-        <v>134200</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -10466,7 +10466,7 @@
         <v>827</v>
       </c>
       <c r="B64" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -10474,7 +10474,7 @@
         <v>639</v>
       </c>
       <c r="B65" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -10482,7 +10482,7 @@
         <v>543</v>
       </c>
       <c r="B66" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -10490,7 +10490,7 @@
         <v>397</v>
       </c>
       <c r="B67" s="1">
-        <v>10980</v>
+        <v>11160</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -10498,7 +10498,7 @@
         <v>653</v>
       </c>
       <c r="B68" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -10506,7 +10506,7 @@
         <v>398</v>
       </c>
       <c r="B69" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -10514,7 +10514,7 @@
         <v>399</v>
       </c>
       <c r="B70" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -10522,7 +10522,7 @@
         <v>400</v>
       </c>
       <c r="B71" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -10530,7 +10530,7 @@
         <v>582</v>
       </c>
       <c r="B72" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -10538,7 +10538,7 @@
         <v>401</v>
       </c>
       <c r="B73" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -10546,7 +10546,7 @@
         <v>588</v>
       </c>
       <c r="B74" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -10554,7 +10554,7 @@
         <v>554</v>
       </c>
       <c r="B75" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -10562,7 +10562,7 @@
         <v>555</v>
       </c>
       <c r="B76" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -10570,7 +10570,7 @@
         <v>644</v>
       </c>
       <c r="B77" s="1">
-        <v>4270</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -10578,7 +10578,7 @@
         <v>645</v>
       </c>
       <c r="B78" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -10586,7 +10586,7 @@
         <v>403</v>
       </c>
       <c r="B79" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -10594,7 +10594,7 @@
         <v>546</v>
       </c>
       <c r="B80" s="1">
-        <v>7320</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -10602,7 +10602,7 @@
         <v>556</v>
       </c>
       <c r="B81" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -10610,7 +10610,7 @@
         <v>557</v>
       </c>
       <c r="B82" s="1">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -10618,7 +10618,7 @@
         <v>558</v>
       </c>
       <c r="B83" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
   </sheetData>
